--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21550" windowHeight="10080" tabRatio="669"/>
+    <workbookView windowWidth="22400" windowHeight="10080" tabRatio="669"/>
   </bookViews>
   <sheets>
     <sheet name="模板1" sheetId="1" r:id="rId1"/>
@@ -35,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="138">
   <si>
     <t>团队</t>
   </si>
@@ -87,6 +65,9 @@
     <t>政企高套完成率</t>
   </si>
   <si>
+    <t>时间进度完成率</t>
+  </si>
+  <si>
     <t>揽装高套（红黄牌考核）</t>
   </si>
   <si>
@@ -102,9 +83,6 @@
     <t>积分任务值</t>
   </si>
   <si>
-    <t>时间进度完成率</t>
-  </si>
-  <si>
     <t>排名</t>
   </si>
   <si>
@@ -121,6 +99,268 @@
   </si>
   <si>
     <t>完成率</t>
+  </si>
+  <si>
+    <t>高套、积分可从02_326完美一单报表中取数（待上线）
+高套语句：新装：select * from zone_zq.ads_feng_skj_gt_new_list_d  where rn=1  and 
+  disc_divide_market_6_dl_name in('校园市场','行业客户');
+堡垒：select * from zone_zq.ads_pan_gc_338_blmb_new where mix_rn=1  and 
+  disc_divide_market_6_dl_name in('校园市场','行业客</t>
+  </si>
+  <si>
+    <t>党政军
+团队</t>
+  </si>
+  <si>
+    <t>钟俊杰</t>
+  </si>
+  <si>
+    <t>麦海芬</t>
+  </si>
+  <si>
+    <t>黄淡妮</t>
+  </si>
+  <si>
+    <t>邱海燕</t>
+  </si>
+  <si>
+    <t>李东</t>
+  </si>
+  <si>
+    <t>王锦添</t>
+  </si>
+  <si>
+    <t>黄观霞</t>
+  </si>
+  <si>
+    <t>团队合计</t>
+  </si>
+  <si>
+    <t>大企业
+团队</t>
+  </si>
+  <si>
+    <t>冯艺康</t>
+  </si>
+  <si>
+    <t>谢卓和</t>
+  </si>
+  <si>
+    <t>伍颖敏</t>
+  </si>
+  <si>
+    <t>潘观友</t>
+  </si>
+  <si>
+    <t>李玉强</t>
+  </si>
+  <si>
+    <t>张小敏</t>
+  </si>
+  <si>
+    <t>具进康</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>政企</t>
+  </si>
+  <si>
+    <t>端州</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>📊 累计商机统计表（所有数据）</t>
+  </si>
+  <si>
+    <t>户数</t>
+  </si>
+  <si>
+    <t>高套累计数</t>
+  </si>
+  <si>
+    <t>积分累计数</t>
+  </si>
+  <si>
+    <t>岗位角色</t>
+  </si>
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>高套目标</t>
+  </si>
+  <si>
+    <t>高套发展数</t>
+  </si>
+  <si>
+    <t>高端装维</t>
+  </si>
+  <si>
+    <t>3、商机挖掘时间通报</t>
+  </si>
+  <si>
+    <t>商机打卡指标（1日1商机）</t>
+  </si>
+  <si>
+    <t>有效商机指标（80%达标）</t>
+  </si>
+  <si>
+    <t>商机任务值</t>
+  </si>
+  <si>
+    <t>打卡商机数</t>
+  </si>
+  <si>
+    <t>商机完成率</t>
+  </si>
+  <si>
+    <t>当月有效商机</t>
+  </si>
+  <si>
+    <t>本月有效商机转化数</t>
+  </si>
+  <si>
+    <t>有效商机转化
+（达标值）</t>
+  </si>
+  <si>
+    <t>取数来源：标准化一套表中：4-《客户经理商机管控表》</t>
+  </si>
+  <si>
+    <t>一组</t>
+  </si>
+  <si>
+    <t>协同CP发展的主从网关数</t>
+  </si>
+  <si>
+    <t>智云工程师</t>
+  </si>
+  <si>
+    <t>零樑</t>
+  </si>
+  <si>
+    <t>何而恒</t>
+  </si>
+  <si>
+    <t>魏垚晖</t>
+  </si>
+  <si>
+    <t>吴文懿</t>
+  </si>
+  <si>
+    <t>陈梓铭</t>
+  </si>
+  <si>
+    <t>二组</t>
+  </si>
+  <si>
+    <t>程庆德</t>
+  </si>
+  <si>
+    <t>刘奇峻</t>
+  </si>
+  <si>
+    <t>龙家宝</t>
+  </si>
+  <si>
+    <t>罗紫杰</t>
+  </si>
+  <si>
+    <t>莫健铭</t>
+  </si>
+  <si>
+    <t>吴广仁</t>
+  </si>
+  <si>
+    <t>王洪明(挂整体指标)</t>
+  </si>
+  <si>
+    <t>点评:商机统计至20260224(17点），未达标的请关注。</t>
+  </si>
+  <si>
+    <t>4-1存量经营时间进度（20260301）</t>
+  </si>
+  <si>
+    <t>月度存量续约合同(号码级）</t>
+  </si>
+  <si>
+    <t>已续约数</t>
+  </si>
+  <si>
+    <t>累计完成率（90%达标）</t>
+  </si>
+  <si>
+    <t>已受理长期协议</t>
+  </si>
+  <si>
+    <t>长期协议续约率（50%达标）</t>
+  </si>
+  <si>
+    <t>未受理长期协议号码</t>
+  </si>
+  <si>
+    <t>续约情况</t>
+  </si>
+  <si>
+    <t>取数来源：每月月初市存量管理员统一下发当月到期清单</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>4-2存量经营时间进度（20260401）</t>
+  </si>
+  <si>
+    <t>点评:当月未达90%，长期续约未达50%的请关注。</t>
+  </si>
+  <si>
+    <t>4-3存量经营-协议到期未长期续约</t>
+  </si>
+  <si>
+    <t>用户名</t>
+  </si>
+  <si>
+    <t>存量续约号码数量</t>
+  </si>
+  <si>
+    <t>月租</t>
+  </si>
+  <si>
+    <t>协议到期时间
+（原协议时间）</t>
+  </si>
+  <si>
+    <t>协议到期时间
+（最新）</t>
+  </si>
+  <si>
+    <t>备注（代表号）</t>
+  </si>
+  <si>
+    <t>（统计时间由2025年4月开始）</t>
+  </si>
+  <si>
+    <t>1、完美一单积分完成通报（截至3月17日）
+全光组网</t>
+  </si>
+  <si>
+    <t>高套发展</t>
+  </si>
+  <si>
+    <t>高套完成率</t>
+  </si>
+  <si>
+    <t>发展户数</t>
+  </si>
+  <si>
+    <t>主网关数量</t>
+  </si>
+  <si>
+    <t>从网关数量</t>
   </si>
   <si>
     <t>高套、积分可从02_326完美一单报表中取数（待上线）
@@ -128,261 +368,6 @@
   disc_divide_market_6_dl_name in('校园市场','行业客户');
 堡垒：select * from zone_zq.ads_pan_gc_338_blmb_new where mix_rn=1  and 
   disc_divide_market_6_dl_name in('校园市场','行业客户');</t>
-  </si>
-  <si>
-    <t>党政军
-团队</t>
-  </si>
-  <si>
-    <t>钟俊杰</t>
-  </si>
-  <si>
-    <t>麦海芬</t>
-  </si>
-  <si>
-    <t>黄淡妮</t>
-  </si>
-  <si>
-    <t>邱海燕</t>
-  </si>
-  <si>
-    <t>李东</t>
-  </si>
-  <si>
-    <t>王锦添</t>
-  </si>
-  <si>
-    <t>黄观霞</t>
-  </si>
-  <si>
-    <t>团队合计</t>
-  </si>
-  <si>
-    <t>大企业
-团队</t>
-  </si>
-  <si>
-    <t>冯艺康</t>
-  </si>
-  <si>
-    <t>谢卓和</t>
-  </si>
-  <si>
-    <t>伍颖敏</t>
-  </si>
-  <si>
-    <t>潘观友</t>
-  </si>
-  <si>
-    <t>李玉强</t>
-  </si>
-  <si>
-    <t>张小敏</t>
-  </si>
-  <si>
-    <t>具进康</t>
-  </si>
-  <si>
-    <t>合计</t>
-  </si>
-  <si>
-    <t>政企</t>
-  </si>
-  <si>
-    <t>端州</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
-  <si>
-    <t>📊 累计商机统计表（所有数据）</t>
-  </si>
-  <si>
-    <t>户数</t>
-  </si>
-  <si>
-    <t>高套累计数</t>
-  </si>
-  <si>
-    <t>积分累计数</t>
-  </si>
-  <si>
-    <t>岗位角色</t>
-  </si>
-  <si>
-    <t>姓名</t>
-  </si>
-  <si>
-    <t>高套目标</t>
-  </si>
-  <si>
-    <t>高套发展数</t>
-  </si>
-  <si>
-    <t>高端装维</t>
-  </si>
-  <si>
-    <t>3、商机挖掘时间通报</t>
-  </si>
-  <si>
-    <t>商机打卡指标（1日1商机）</t>
-  </si>
-  <si>
-    <t>有效商机指标（80%达标）</t>
-  </si>
-  <si>
-    <t>商机任务值</t>
-  </si>
-  <si>
-    <t>打卡商机数</t>
-  </si>
-  <si>
-    <t>商机完成率</t>
-  </si>
-  <si>
-    <t>当月有效商机</t>
-  </si>
-  <si>
-    <t>本月有效商机转化数</t>
-  </si>
-  <si>
-    <t>有效商机转化
-（达标值）</t>
-  </si>
-  <si>
-    <t>取数来源：标准化一套表中：4-《客户经理商机管控表》</t>
-  </si>
-  <si>
-    <t>一组</t>
-  </si>
-  <si>
-    <t>协同CP发展的主从网关数</t>
-  </si>
-  <si>
-    <t>智云工程师</t>
-  </si>
-  <si>
-    <t>零樑</t>
-  </si>
-  <si>
-    <t>何而恒</t>
-  </si>
-  <si>
-    <t>魏垚晖</t>
-  </si>
-  <si>
-    <t>吴文懿</t>
-  </si>
-  <si>
-    <t>陈梓铭</t>
-  </si>
-  <si>
-    <t>二组</t>
-  </si>
-  <si>
-    <t>程庆德</t>
-  </si>
-  <si>
-    <t>刘奇峻</t>
-  </si>
-  <si>
-    <t>龙家宝</t>
-  </si>
-  <si>
-    <t>罗紫杰</t>
-  </si>
-  <si>
-    <t>莫健铭</t>
-  </si>
-  <si>
-    <t>吴广仁</t>
-  </si>
-  <si>
-    <t>王洪明(挂整体指标)</t>
-  </si>
-  <si>
-    <t>点评:商机统计至20260224(17点），未达标的请关注。</t>
-  </si>
-  <si>
-    <t>4-1存量经营时间进度（20260301）</t>
-  </si>
-  <si>
-    <t>月度存量续约合同(号码级）</t>
-  </si>
-  <si>
-    <t>已续约数</t>
-  </si>
-  <si>
-    <t>累计完成率（90%达标）</t>
-  </si>
-  <si>
-    <t>已受理长期协议</t>
-  </si>
-  <si>
-    <t>长期协议续约率（50%达标）</t>
-  </si>
-  <si>
-    <t>未受理长期协议号码</t>
-  </si>
-  <si>
-    <t>续约情况</t>
-  </si>
-  <si>
-    <t>取数来源：每月月初市存量管理员统一下发当月到期清单</t>
-  </si>
-  <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>4-2存量经营时间进度（20260401）</t>
-  </si>
-  <si>
-    <t>点评:当月未达90%，长期续约未达50%的请关注。</t>
-  </si>
-  <si>
-    <t>4-3存量经营-协议到期未长期续约</t>
-  </si>
-  <si>
-    <t>用户名</t>
-  </si>
-  <si>
-    <t>存量续约号码数量</t>
-  </si>
-  <si>
-    <t>月租</t>
-  </si>
-  <si>
-    <t>协议到期时间
-（原协议时间）</t>
-  </si>
-  <si>
-    <t>协议到期时间
-（最新）</t>
-  </si>
-  <si>
-    <t>备注（代表号）</t>
-  </si>
-  <si>
-    <t>（统计时间由2025年4月开始）</t>
-  </si>
-  <si>
-    <t>1、完美一单积分完成通报（截至3月17日）
-全光组网</t>
-  </si>
-  <si>
-    <t>高套发展</t>
-  </si>
-  <si>
-    <t>高套完成率</t>
-  </si>
-  <si>
-    <t>发展户数</t>
-  </si>
-  <si>
-    <t>主网关数量</t>
-  </si>
-  <si>
-    <t>从网关数量</t>
   </si>
   <si>
     <t>陈泳诗</t>
@@ -3469,9 +3454,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表5_11" displayName="表5_11" ref="O27:P41" totalsRowShown="0">
-  <sortState ref="O27:P41">
-    <sortCondition ref="P26:P40" descending="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表5_11" displayName="表5_11" ref="P27:Q41" totalsRowShown="0">
+  <sortState ref="P27:Q41">
+    <sortCondition ref="Q26:Q40" descending="1"/>
   </sortState>
   <tableColumns count="2">
     <tableColumn id="1" name="客户经理" dataDxfId="0">
@@ -3486,9 +3471,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表5_111617" displayName="表5_111617" ref="J27:M41" totalsRowShown="0">
-  <sortState ref="J27:M41">
-    <sortCondition ref="L26:L40" descending="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表5_111617" displayName="表5_111617" ref="K27:N41" totalsRowShown="0">
+  <sortState ref="K27:N41">
+    <sortCondition ref="M26:M40" descending="1"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" name="客户经理" dataDxfId="2">
@@ -3834,26 +3819,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA103"/>
+  <dimension ref="A1:AB103"/>
   <sheetFormatPr defaultColWidth="10.6363636363636" defaultRowHeight="14"/>
   <cols>
     <col min="4" max="4" width="9.25454545454545" style="3" customWidth="1"/>
     <col min="5" max="5" width="9.90909090909091" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.25454545454545" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.6272727272727" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.25454545454545" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.9" style="3" customWidth="1"/>
-    <col min="13" max="13" width="9.36363636363636" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.6363636363636" style="3" customWidth="1"/>
+    <col min="6" max="7" width="9.25454545454545" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.6272727272727" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.25454545454545" style="3" customWidth="1"/>
+    <col min="11" max="11" width="10.9" style="3" customWidth="1"/>
+    <col min="14" max="14" width="9.36363636363636" style="3" customWidth="1"/>
+    <col min="15" max="15" width="10.6363636363636" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:23">
+    <row r="1" ht="14.25" customHeight="1" spans="1:24">
       <c r="A1" s="97" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="17" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至4月27日）</v>
+        <v>完美一单积分完成通报（截至5月6日）</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -3869,9 +3854,10 @@
       <c r="N1" s="14"/>
       <c r="O1" s="14"/>
       <c r="P1" s="14"/>
-      <c r="Q1" s="15"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:23">
+      <c r="Q1" s="14"/>
+      <c r="R1" s="15"/>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:24">
       <c r="A2" s="98"/>
       <c r="B2" s="17" t="s">
         <v>1</v>
@@ -3881,25 +3867,26 @@
       <c r="E2" s="14"/>
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="17" t="s">
+      <c r="H2" s="14"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="14"/>
       <c r="K2" s="14"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="17" t="s">
+      <c r="N2" s="14"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="15"/>
-      <c r="S2" t="s">
+      <c r="Q2" s="14"/>
+      <c r="R2" s="15"/>
+      <c r="T2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" ht="70" customHeight="1" spans="1:23">
+    <row r="3" ht="70" customHeight="1" spans="1:24">
       <c r="A3" s="99"/>
       <c r="B3" s="17" t="s">
         <v>5</v>
@@ -3932,28 +3919,31 @@
         <v>14</v>
       </c>
       <c r="L3" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="N3" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="O3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="17" t="s">
+      <c r="P3" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="Q3" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="R3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="S3" s="19" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:23">
+    <row r="4" ht="14.25" customHeight="1" spans="1:24">
       <c r="A4" s="97" t="s">
         <v>22</v>
       </c>
@@ -3965,60 +3955,64 @@
       </c>
       <c r="D4" s="100">
         <f>_xlfn.XLOOKUP(B4,高套!A:A,高套!B:B,0)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E4" s="101">
         <f t="shared" ref="E4:E20" si="0">D4/C4</f>
-        <v>0.0568181818181818</v>
-      </c>
-      <c r="F4" s="20">
+        <v>0</v>
+      </c>
+      <c r="F4" s="21">
+        <f ca="1">D4/(C4/E23*B$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="20">
         <f>_xlfn.XLOOKUP(B4,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1</v>
-      </c>
-      <c r="G4" s="102" t="str">
-        <f t="shared" ref="G4:G10" si="1">IF(F4&gt;=3,"否","是")</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="102" t="str">
+        <f t="shared" ref="H4:H10" si="1">IF(G4&gt;=3,"否","是")</f>
         <v>是</v>
       </c>
-      <c r="H4" s="21">
-        <f t="shared" ref="H4:H20" si="2">D4/F4</f>
-        <v>0.5</v>
-      </c>
-      <c r="I4" s="22">
+      <c r="I4" s="21" t="e">
+        <f t="shared" ref="I4:I20" si="2">D4/G4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J4" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>201</v>
-      </c>
-      <c r="J4" s="20">
+        <v>0</v>
+      </c>
+      <c r="K4" s="20">
         <v>2500</v>
       </c>
-      <c r="K4" s="21">
-        <f ca="1" t="shared" ref="K4:K20" si="3">I4/(J4/31*B$23)</f>
-        <v>0.0923111111111111</v>
-      </c>
-      <c r="L4" s="22">
-        <f ca="1" t="shared" ref="L4:L10" si="4">VLOOKUP(B:B,U:W,3,0)</f>
-        <v>14</v>
+      <c r="L4" s="21">
+        <f ca="1">J4/(K4/E23*B$23)</f>
+        <v>0</v>
       </c>
       <c r="M4" s="22">
+        <f ca="1" t="shared" ref="M4:M10" si="3">VLOOKUP(B:B,V:X,3,0)</f>
+        <v>11</v>
+      </c>
+      <c r="N4" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>171</v>
-      </c>
-      <c r="N4" s="20" t="str">
-        <f ca="1" t="shared" ref="N4:N10" si="5">IF(AND(M4&lt;550,I4&lt;550),"否","")</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="20" t="str">
+        <f ca="1" t="shared" ref="O4:O10" si="4">IF(AND(N4&lt;550,J4&lt;550),"否","")</f>
         <v>否</v>
       </c>
-      <c r="O4" s="100">
-        <v>25</v>
-      </c>
-      <c r="P4" s="103">
+      <c r="P4" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="103">
         <f>_xlfn.XLOOKUP(B4,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="104">
-        <f t="shared" ref="Q4:Q19" si="6">P4/O4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:23">
+      <c r="R4" s="104">
+        <f t="shared" ref="R4:R19" si="5">Q4/P4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="1:24">
       <c r="A5" s="98"/>
       <c r="B5" s="20" t="s">
         <v>24</v>
@@ -4028,60 +4022,64 @@
       </c>
       <c r="D5" s="100">
         <f>_xlfn.XLOOKUP(B5,高套!A:A,高套!B:B,0)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="E5" s="101">
         <f t="shared" si="0"/>
-        <v>0.397727272727273</v>
-      </c>
-      <c r="F5" s="20">
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <f ca="1">D5/(C5/E23*B$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="20">
         <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>4</v>
-      </c>
-      <c r="G5" s="105" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="105" t="str">
         <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I5" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>81.93</v>
+      </c>
+      <c r="K5" s="20">
+        <v>2500</v>
+      </c>
+      <c r="L5" s="21">
+        <f ca="1">J5/(K5/E23*B$23)</f>
+        <v>0.169322</v>
+      </c>
+      <c r="M5" s="22">
+        <f ca="1" t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="N5" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="20" t="str">
+        <f ca="1" t="shared" si="4"/>
         <v>否</v>
       </c>
-      <c r="H5" s="21">
-        <f t="shared" si="2"/>
-        <v>0.875</v>
-      </c>
-      <c r="I5" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>798.66</v>
-      </c>
-      <c r="J5" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K5" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.366792</v>
-      </c>
-      <c r="L5" s="22">
-        <f ca="1" t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="M5" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>800.66</v>
-      </c>
-      <c r="N5" s="20" t="str">
-        <f ca="1" t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O5" s="100">
-        <v>25</v>
-      </c>
-      <c r="P5" s="103">
+      <c r="P5" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="103">
         <f>_xlfn.XLOOKUP(B5,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:23">
+      <c r="R5" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" spans="1:24">
       <c r="A6" s="98"/>
       <c r="B6" s="20" t="s">
         <v>25</v>
@@ -4097,65 +4095,69 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="21">
+        <f ca="1">D6/(C6/E23*B$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="20">
         <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>2</v>
-      </c>
-      <c r="G6" s="105" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="105" t="str">
         <f t="shared" si="1"/>
         <v>是</v>
       </c>
-      <c r="H6" s="21">
+      <c r="I6" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I6" s="22">
+      <c r="J6" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>332.4</v>
-      </c>
-      <c r="J6" s="20">
+        <v>98</v>
+      </c>
+      <c r="K6" s="20">
         <v>2500</v>
       </c>
-      <c r="K6" s="21">
+      <c r="L6" s="21">
+        <f ca="1">J6/(K6/E23*B$23)</f>
+        <v>0.202533333333333</v>
+      </c>
+      <c r="M6" s="22">
         <f ca="1" t="shared" si="3"/>
-        <v>0.152657777777778</v>
-      </c>
-      <c r="L6" s="22">
+        <v>6</v>
+      </c>
+      <c r="N6" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="20" t="str">
         <f ca="1" t="shared" si="4"/>
-        <v>13</v>
-      </c>
-      <c r="M6" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>397</v>
-      </c>
-      <c r="N6" s="20" t="str">
-        <f ca="1" t="shared" si="5"/>
         <v>否</v>
       </c>
-      <c r="O6" s="100">
-        <v>25</v>
-      </c>
-      <c r="P6" s="103">
+      <c r="P6" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="103">
         <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U6" s="25" t="s">
+      <c r="R6" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V6" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="V6">
-        <f ca="1" t="shared" ref="V6:V19" si="7">VLOOKUP(U:U,B:I,8,0)</f>
-        <v>201</v>
-      </c>
       <c r="W6">
-        <f ca="1" t="shared" ref="W6:W19" si="8">RANK(V6,V$6:V$21,0)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:23">
+        <f ca="1">VLOOKUP(V:V,B:J,9,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f ca="1" t="shared" ref="X6:X19" si="6">RANK(W6,W$6:W$21,0)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="1:24">
       <c r="A7" s="98"/>
       <c r="B7" s="20" t="s">
         <v>26</v>
@@ -4165,71 +4167,75 @@
       </c>
       <c r="D7" s="100">
         <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="E7" s="101">
         <f t="shared" si="0"/>
-        <v>0.397727272727273</v>
-      </c>
-      <c r="F7" s="20">
+        <v>0</v>
+      </c>
+      <c r="F7" s="21">
+        <f ca="1">D7/(C7/E23*B$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="20">
         <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="G7" s="105" t="str">
+        <v>0</v>
+      </c>
+      <c r="H7" s="105" t="str">
         <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I7" s="21" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J7" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>-1</v>
+      </c>
+      <c r="K7" s="20">
+        <v>2500</v>
+      </c>
+      <c r="L7" s="21">
+        <f ca="1">J7/(K7/E23*B$23)</f>
+        <v>-0.00206666666666667</v>
+      </c>
+      <c r="M7" s="22">
+        <f ca="1" t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="N7" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>-11</v>
+      </c>
+      <c r="O7" s="20" t="str">
+        <f ca="1" t="shared" si="4"/>
         <v>否</v>
       </c>
-      <c r="H7" s="21">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I7" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>630</v>
-      </c>
-      <c r="J7" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K7" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.289333333333333</v>
-      </c>
-      <c r="L7" s="22">
-        <f ca="1" t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="M7" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>817</v>
-      </c>
-      <c r="N7" s="20" t="str">
-        <f ca="1" t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O7" s="100">
-        <v>25</v>
-      </c>
-      <c r="P7" s="103">
+      <c r="P7" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="103">
         <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U7" s="25" t="s">
+      <c r="R7" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V7" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="V7">
-        <f ca="1" t="shared" si="7"/>
-        <v>798.66</v>
-      </c>
       <c r="W7">
-        <f ca="1" t="shared" si="8"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:23">
+        <f ca="1" t="shared" ref="W7:W19" si="7">VLOOKUP(V:V,B:J,9,0)</f>
+        <v>81.93</v>
+      </c>
+      <c r="X7">
+        <f ca="1" t="shared" si="6"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" spans="1:24">
       <c r="A8" s="98"/>
       <c r="B8" s="20" t="s">
         <v>27</v>
@@ -4239,71 +4245,75 @@
       </c>
       <c r="D8" s="100">
         <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
-        <v>13.5</v>
+        <v>1</v>
       </c>
       <c r="E8" s="101">
         <f t="shared" si="0"/>
-        <v>1.53409090909091</v>
-      </c>
-      <c r="F8" s="20">
+        <v>0.113636363636364</v>
+      </c>
+      <c r="F8" s="21">
+        <f ca="1">D8/(C8/E23*B$23)</f>
+        <v>0.587121212121212</v>
+      </c>
+      <c r="G8" s="20">
         <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>15.25</v>
-      </c>
-      <c r="G8" s="105" t="str">
+        <v>1</v>
+      </c>
+      <c r="H8" s="105" t="str">
         <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I8" s="21">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J8" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>80</v>
+      </c>
+      <c r="K8" s="20">
+        <v>2500</v>
+      </c>
+      <c r="L8" s="21">
+        <f ca="1">J8/(K8/E23*B$23)</f>
+        <v>0.165333333333333</v>
+      </c>
+      <c r="M8" s="22">
+        <f ca="1" t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="N8" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="20" t="str">
+        <f ca="1" t="shared" si="4"/>
         <v>否</v>
       </c>
-      <c r="H8" s="21">
-        <f t="shared" si="2"/>
-        <v>0.885245901639344</v>
-      </c>
-      <c r="I8" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1340.59</v>
-      </c>
-      <c r="J8" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K8" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.61567837037037</v>
-      </c>
-      <c r="L8" s="22">
-        <f ca="1" t="shared" si="4"/>
-        <v>5</v>
-      </c>
-      <c r="M8" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>448</v>
-      </c>
-      <c r="N8" s="20" t="str">
-        <f ca="1" t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O8" s="100">
+      <c r="P8" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="103">
+        <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V8" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="P8" s="103">
-        <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
+      <c r="W8">
+        <f ca="1" t="shared" si="7"/>
+        <v>98</v>
+      </c>
+      <c r="X8">
+        <f ca="1" t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="Q8" s="104">
-        <f t="shared" si="6"/>
-        <v>0.24</v>
-      </c>
-      <c r="U8" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="V8">
-        <f ca="1" t="shared" si="7"/>
-        <v>332.4</v>
-      </c>
-      <c r="W8">
-        <f ca="1" t="shared" si="8"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:23">
+    </row>
+    <row r="9" ht="16.5" customHeight="1" spans="1:24">
       <c r="A9" s="98"/>
       <c r="B9" s="20" t="s">
         <v>28</v>
@@ -4313,71 +4323,75 @@
       </c>
       <c r="D9" s="100">
         <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="101">
         <f t="shared" si="0"/>
-        <v>0.284090909090909</v>
-      </c>
-      <c r="F9" s="20">
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
+        <f ca="1">D9/(C9/E23*B$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="20">
         <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>6.5</v>
-      </c>
-      <c r="G9" s="105" t="str">
+        <v>0</v>
+      </c>
+      <c r="H9" s="105" t="str">
         <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I9" s="21" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J9" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>10</v>
+      </c>
+      <c r="K9" s="20">
+        <v>2500</v>
+      </c>
+      <c r="L9" s="21">
+        <f ca="1">J9/(K9/E23*B$23)</f>
+        <v>0.0206666666666667</v>
+      </c>
+      <c r="M9" s="22">
+        <f ca="1" t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="N9" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="20" t="str">
+        <f ca="1" t="shared" si="4"/>
         <v>否</v>
       </c>
-      <c r="H9" s="21">
-        <f t="shared" si="2"/>
-        <v>0.384615384615385</v>
-      </c>
-      <c r="I9" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1518</v>
-      </c>
-      <c r="J9" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K9" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.697155555555556</v>
-      </c>
-      <c r="L9" s="22">
-        <f ca="1" t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="M9" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>1143</v>
-      </c>
-      <c r="N9" s="20" t="str">
-        <f ca="1" t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O9" s="100">
-        <v>25</v>
-      </c>
-      <c r="P9" s="103">
+      <c r="P9" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="103">
         <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="Q9" s="104">
-        <f t="shared" si="6"/>
-        <v>0.12</v>
-      </c>
-      <c r="U9" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="R9" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V9" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <f ca="1" t="shared" si="7"/>
-        <v>630</v>
-      </c>
-      <c r="W9">
-        <f ca="1" t="shared" si="8"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:23">
+        <v>-1</v>
+      </c>
+      <c r="X9">
+        <f ca="1" t="shared" si="6"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" spans="1:24">
       <c r="A10" s="98"/>
       <c r="B10" s="20" t="s">
         <v>29</v>
@@ -4387,71 +4401,75 @@
       </c>
       <c r="D10" s="100">
         <f>_xlfn.XLOOKUP(B10,高套!A:A,高套!B:B,0)</f>
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="E10" s="101">
         <f t="shared" si="0"/>
-        <v>0.457954545454545</v>
-      </c>
-      <c r="F10" s="20">
+        <v>0</v>
+      </c>
+      <c r="F10" s="21">
+        <f ca="1">D10/(C10/E23*B$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="20">
         <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>4.03</v>
-      </c>
-      <c r="G10" s="105" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="105" t="str">
         <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I10" s="21">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>49</v>
+      </c>
+      <c r="K10" s="20">
+        <v>2500</v>
+      </c>
+      <c r="L10" s="21">
+        <f ca="1">J10/(K10/E23*B$23)</f>
+        <v>0.101266666666667</v>
+      </c>
+      <c r="M10" s="22">
+        <f ca="1" t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="N10" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>19</v>
+      </c>
+      <c r="O10" s="20" t="str">
+        <f ca="1" t="shared" si="4"/>
         <v>否</v>
       </c>
-      <c r="H10" s="21">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="I10" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1382.97</v>
-      </c>
-      <c r="J10" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K10" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.635141777777778</v>
-      </c>
-      <c r="L10" s="22">
-        <f ca="1" t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="M10" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>1390</v>
-      </c>
-      <c r="N10" s="20" t="str">
-        <f ca="1" t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="O10" s="100">
-        <v>25</v>
-      </c>
-      <c r="P10" s="103">
+      <c r="P10" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q10" s="103">
         <f>_xlfn.XLOOKUP(B10,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>6</v>
-      </c>
-      <c r="Q10" s="104">
-        <f t="shared" si="6"/>
-        <v>0.24</v>
-      </c>
-      <c r="U10" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="R10" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V10" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <f ca="1" t="shared" si="7"/>
-        <v>1340.59</v>
-      </c>
-      <c r="W10">
-        <f ca="1" t="shared" si="8"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:23">
+        <v>80</v>
+      </c>
+      <c r="X10">
+        <f ca="1" t="shared" si="6"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" spans="1:24">
       <c r="A11" s="99"/>
       <c r="B11" s="106" t="s">
         <v>30</v>
@@ -4462,64 +4480,68 @@
       </c>
       <c r="D11" s="106">
         <f>SUM(D4:D10)</f>
-        <v>27.53</v>
+        <v>1</v>
       </c>
       <c r="E11" s="107">
         <f t="shared" si="0"/>
-        <v>0.446915584415584</v>
-      </c>
-      <c r="F11" s="106">
-        <f>SUM(F4:F10)</f>
-        <v>36.28</v>
-      </c>
-      <c r="G11" s="107"/>
-      <c r="H11" s="107">
+        <v>0.0162337662337662</v>
+      </c>
+      <c r="F11" s="107">
+        <f ca="1">D11/(C11/E23*B$23)</f>
+        <v>0.0838744588744589</v>
+      </c>
+      <c r="G11" s="106">
+        <f>SUM(G4:G10)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="107"/>
+      <c r="I11" s="107">
         <f t="shared" si="2"/>
-        <v>0.758820286659316</v>
-      </c>
-      <c r="I11" s="108">
-        <f ca="1">SUM(I4:I10)</f>
-        <v>6203.62</v>
-      </c>
-      <c r="J11" s="106">
-        <f>SUM(J4:J10)</f>
+        <v>0.222222222222222</v>
+      </c>
+      <c r="J11" s="108">
+        <f ca="1">SUM(J4:J10)</f>
+        <v>317.93</v>
+      </c>
+      <c r="K11" s="106">
+        <f>SUM(K4:K10)</f>
         <v>17500</v>
       </c>
-      <c r="K11" s="107">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.407009989417989</v>
-      </c>
-      <c r="L11" s="106"/>
-      <c r="M11" s="108">
-        <f ca="1">SUM(M4:M10)</f>
-        <v>5166.66</v>
-      </c>
-      <c r="N11" s="106"/>
-      <c r="O11" s="106">
-        <f>SUM(O4:O10)</f>
-        <v>175</v>
-      </c>
+      <c r="L11" s="107">
+        <f ca="1">J11/(K11/E23*B$23)</f>
+        <v>0.0938650476190476</v>
+      </c>
+      <c r="M11" s="106"/>
+      <c r="N11" s="108">
+        <f ca="1">SUM(N4:N10)</f>
+        <v>8</v>
+      </c>
+      <c r="O11" s="106"/>
       <c r="P11" s="106">
         <f>SUM(P4:P10)</f>
-        <v>15</v>
-      </c>
-      <c r="Q11" s="109">
-        <f t="shared" si="6"/>
-        <v>0.0857142857142857</v>
-      </c>
-      <c r="U11" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q11" s="106">
+        <f>SUM(Q4:Q10)</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="109">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V11" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <f ca="1" t="shared" si="7"/>
-        <v>1518</v>
-      </c>
-      <c r="W11">
-        <f ca="1" t="shared" si="8"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:23">
+        <v>10</v>
+      </c>
+      <c r="X11">
+        <f ca="1" t="shared" si="6"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1" spans="1:24">
       <c r="A12" s="17" t="s">
         <v>31</v>
       </c>
@@ -4537,65 +4559,69 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="21">
+        <f ca="1">D12/(C12/E23*B$23)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="20">
         <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1.5</v>
-      </c>
-      <c r="G12" s="105" t="str">
-        <f t="shared" ref="G12:G18" si="9">IF(F12&gt;=3,"否","是")</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="105" t="str">
+        <f t="shared" ref="H12:H18" si="8">IF(G12&gt;=3,"否","是")</f>
         <v>是</v>
       </c>
-      <c r="H12" s="21">
+      <c r="I12" s="21" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="I12" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J12" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>360</v>
-      </c>
-      <c r="J12" s="20">
+        <v>0</v>
+      </c>
+      <c r="K12" s="20">
         <v>2500</v>
       </c>
-      <c r="K12" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.165333333333333</v>
-      </c>
-      <c r="L12" s="22">
-        <f ca="1" t="shared" ref="L12:L18" si="10">VLOOKUP(B:B,U:W,3,0)</f>
-        <v>12</v>
+      <c r="L12" s="21">
+        <f ca="1">J12/(K12/E23*B$23)</f>
+        <v>0</v>
       </c>
       <c r="M12" s="22">
+        <f ca="1" t="shared" ref="M12:M18" si="9">VLOOKUP(B:B,V:X,3,0)</f>
+        <v>11</v>
+      </c>
+      <c r="N12" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>350</v>
-      </c>
-      <c r="N12" s="20" t="str">
-        <f ca="1" t="shared" ref="N12:N18" si="11">IF(AND(M12&lt;550,I12&lt;550),"否","")</f>
+        <v>0</v>
+      </c>
+      <c r="O12" s="20" t="str">
+        <f ca="1" t="shared" ref="O12:O18" si="10">IF(AND(N12&lt;550,J12&lt;550),"否","")</f>
         <v>否</v>
       </c>
-      <c r="O12" s="100">
-        <v>25</v>
-      </c>
-      <c r="P12" s="103">
+      <c r="P12" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="103">
         <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="25" t="s">
+      <c r="R12" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V12" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <f ca="1" t="shared" si="7"/>
-        <v>1382.97</v>
-      </c>
-      <c r="W12">
-        <f ca="1" t="shared" si="8"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:23">
+        <v>49</v>
+      </c>
+      <c r="X12">
+        <f ca="1" t="shared" si="6"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:24">
       <c r="A13" s="110"/>
       <c r="B13" s="20" t="s">
         <v>33</v>
@@ -4605,71 +4631,75 @@
       </c>
       <c r="D13" s="100">
         <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
-        <v>9.75</v>
+        <v>4.73</v>
       </c>
       <c r="E13" s="101">
         <f t="shared" si="0"/>
-        <v>1.10795454545455</v>
-      </c>
-      <c r="F13" s="20">
+        <v>0.5375</v>
+      </c>
+      <c r="F13" s="21">
+        <f ca="1">D13/(C13/E23*B$23)</f>
+        <v>2.77708333333333</v>
+      </c>
+      <c r="G13" s="20">
         <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>9</v>
-      </c>
-      <c r="G13" s="105" t="str">
-        <f t="shared" si="9"/>
+        <v>4.73</v>
+      </c>
+      <c r="H13" s="105" t="str">
+        <f t="shared" si="8"/>
         <v>否</v>
       </c>
-      <c r="H13" s="21">
+      <c r="I13" s="21">
         <f t="shared" si="2"/>
-        <v>1.08333333333333</v>
-      </c>
-      <c r="I13" s="22">
+        <v>1</v>
+      </c>
+      <c r="J13" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1220.05</v>
-      </c>
-      <c r="J13" s="20">
+        <v>806.2</v>
+      </c>
+      <c r="K13" s="20">
         <v>2500</v>
       </c>
-      <c r="K13" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.560319259259259</v>
-      </c>
-      <c r="L13" s="22">
+      <c r="L13" s="21">
+        <f ca="1">J13/(K13/E23*B$23)</f>
+        <v>1.66614666666667</v>
+      </c>
+      <c r="M13" s="22">
+        <f ca="1" t="shared" si="9"/>
+        <v>2</v>
+      </c>
+      <c r="N13" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>746.2</v>
+      </c>
+      <c r="O13" s="20" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>6</v>
-      </c>
-      <c r="M13" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>892</v>
-      </c>
-      <c r="N13" s="20" t="str">
-        <f ca="1" t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O13" s="100">
-        <v>25</v>
-      </c>
-      <c r="P13" s="103">
+      <c r="P13" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q13" s="103">
         <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="W13">
+        <f ca="1" t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <f ca="1" t="shared" si="6"/>
         <v>11</v>
       </c>
-      <c r="Q13" s="104">
-        <f t="shared" si="6"/>
-        <v>0.44</v>
-      </c>
-      <c r="U13" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="V13">
-        <f ca="1" t="shared" si="7"/>
-        <v>360</v>
-      </c>
-      <c r="W13">
-        <f ca="1" t="shared" si="8"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:23">
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="1:24">
       <c r="A14" s="110"/>
       <c r="B14" s="20" t="s">
         <v>34</v>
@@ -4679,71 +4709,75 @@
       </c>
       <c r="D14" s="100">
         <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" s="101">
         <f t="shared" si="0"/>
-        <v>0.340909090909091</v>
-      </c>
-      <c r="F14" s="20">
+        <v>0.227272727272727</v>
+      </c>
+      <c r="F14" s="21">
+        <f ca="1">D14/(C14/E23*B$23)</f>
+        <v>1.17424242424242</v>
+      </c>
+      <c r="G14" s="20">
         <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>5</v>
-      </c>
-      <c r="G14" s="105" t="str">
-        <f t="shared" si="9"/>
+        <v>4.5</v>
+      </c>
+      <c r="H14" s="105" t="str">
+        <f t="shared" si="8"/>
         <v>否</v>
       </c>
-      <c r="H14" s="21">
+      <c r="I14" s="21">
         <f t="shared" si="2"/>
-        <v>0.6</v>
-      </c>
-      <c r="I14" s="22">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="J14" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1451</v>
-      </c>
-      <c r="J14" s="20">
+        <v>799</v>
+      </c>
+      <c r="K14" s="20">
         <v>2500</v>
       </c>
-      <c r="K14" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.666385185185185</v>
-      </c>
-      <c r="L14" s="22">
+      <c r="L14" s="21">
+        <f ca="1">J14/(K14/E23*B$23)</f>
+        <v>1.65126666666667</v>
+      </c>
+      <c r="M14" s="22">
+        <f ca="1" t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="N14" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>789</v>
+      </c>
+      <c r="O14" s="20" t="str">
         <f ca="1" t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="P14" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q14" s="103">
+        <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
         <v>3</v>
       </c>
-      <c r="M14" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>688</v>
-      </c>
-      <c r="N14" s="20" t="str">
-        <f ca="1" t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="O14" s="100">
-        <v>25</v>
-      </c>
-      <c r="P14" s="103">
-        <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="25" t="s">
+      <c r="R14" s="104">
+        <f t="shared" si="5"/>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="V14" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <f ca="1" t="shared" si="7"/>
-        <v>1220.05</v>
-      </c>
-      <c r="W14">
-        <f ca="1" t="shared" si="8"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:23">
+        <v>806.2</v>
+      </c>
+      <c r="X14">
+        <f ca="1" t="shared" si="6"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" spans="1:24">
       <c r="A15" s="110"/>
       <c r="B15" s="20" t="s">
         <v>35</v>
@@ -4759,65 +4793,69 @@
         <f t="shared" si="0"/>
         <v>0.568181818181818</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="21">
+        <f ca="1">D15/(C15/E23*B$23)</f>
+        <v>2.93560606060606</v>
+      </c>
+      <c r="G15" s="20">
         <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>2.75</v>
-      </c>
-      <c r="G15" s="105" t="str">
-        <f t="shared" si="9"/>
-        <v>是</v>
-      </c>
-      <c r="H15" s="21">
+        <v>9</v>
+      </c>
+      <c r="H15" s="105" t="str">
+        <f t="shared" si="8"/>
+        <v>否</v>
+      </c>
+      <c r="I15" s="21">
         <f t="shared" si="2"/>
-        <v>1.81818181818182</v>
-      </c>
-      <c r="I15" s="22">
+        <v>0.555555555555556</v>
+      </c>
+      <c r="J15" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1134</v>
-      </c>
-      <c r="J15" s="20">
+        <v>2583</v>
+      </c>
+      <c r="K15" s="20">
         <v>2500</v>
       </c>
-      <c r="K15" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.5208</v>
-      </c>
-      <c r="L15" s="22">
+      <c r="L15" s="21">
+        <f ca="1">J15/(K15/E23*B$23)</f>
+        <v>5.3382</v>
+      </c>
+      <c r="M15" s="22">
+        <f ca="1" t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="N15" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>2234</v>
+      </c>
+      <c r="O15" s="20" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>7</v>
-      </c>
-      <c r="M15" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>970</v>
-      </c>
-      <c r="N15" s="20" t="str">
-        <f ca="1" t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O15" s="100">
-        <v>25</v>
-      </c>
-      <c r="P15" s="103">
+      <c r="P15" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="103">
         <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q15" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U15" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="104">
+        <f t="shared" si="5"/>
+        <v>0.238095238095238</v>
+      </c>
+      <c r="V15" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <f ca="1" t="shared" si="7"/>
-        <v>1451</v>
-      </c>
-      <c r="W15">
-        <f ca="1" t="shared" si="8"/>
+        <v>799</v>
+      </c>
+      <c r="X15">
+        <f ca="1" t="shared" si="6"/>
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:23">
+    <row r="16" ht="16.5" customHeight="1" spans="1:24">
       <c r="A16" s="110"/>
       <c r="B16" s="20" t="s">
         <v>36</v>
@@ -4827,71 +4865,75 @@
       </c>
       <c r="D16" s="100">
         <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E16" s="101">
         <f t="shared" si="0"/>
-        <v>1.25</v>
-      </c>
-      <c r="F16" s="20">
+        <v>0.227272727272727</v>
+      </c>
+      <c r="F16" s="21">
+        <f ca="1">D16/(C16/E23*B$23)</f>
+        <v>1.17424242424242</v>
+      </c>
+      <c r="G16" s="20">
         <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>11</v>
-      </c>
-      <c r="G16" s="105" t="str">
-        <f t="shared" si="9"/>
-        <v>否</v>
-      </c>
-      <c r="H16" s="21">
+        <v>2</v>
+      </c>
+      <c r="H16" s="105" t="str">
+        <f t="shared" si="8"/>
+        <v>是</v>
+      </c>
+      <c r="I16" s="21">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I16" s="22">
+      <c r="J16" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>845.32</v>
-      </c>
-      <c r="J16" s="20">
+        <v>498</v>
+      </c>
+      <c r="K16" s="20">
         <v>2500</v>
       </c>
-      <c r="K16" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.388221037037037</v>
-      </c>
-      <c r="L16" s="22">
+      <c r="L16" s="21">
+        <f ca="1">J16/(K16/E23*B$23)</f>
+        <v>1.0292</v>
+      </c>
+      <c r="M16" s="22">
+        <f ca="1" t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="N16" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>399</v>
+      </c>
+      <c r="O16" s="20" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>8</v>
-      </c>
-      <c r="M16" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>848</v>
-      </c>
-      <c r="N16" s="20" t="str">
-        <f ca="1" t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="O16" s="100">
-        <v>25</v>
-      </c>
-      <c r="P16" s="103">
+        <v>否</v>
+      </c>
+      <c r="P16" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="103">
         <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>14</v>
-      </c>
-      <c r="Q16" s="104">
-        <f t="shared" si="6"/>
-        <v>0.56</v>
-      </c>
-      <c r="U16" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="R16" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V16" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <f ca="1" t="shared" si="7"/>
-        <v>1134</v>
-      </c>
-      <c r="W16">
-        <f ca="1" t="shared" si="8"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:23">
+        <v>2583</v>
+      </c>
+      <c r="X16">
+        <f ca="1" t="shared" si="6"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="1:24">
       <c r="A17" s="110"/>
       <c r="B17" s="20" t="s">
         <v>37</v>
@@ -4901,71 +4943,75 @@
       </c>
       <c r="D17" s="100">
         <f>_xlfn.XLOOKUP(B17,高套!A:A,高套!B:B,0)</f>
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="101">
         <f t="shared" si="0"/>
-        <v>0.397727272727273</v>
-      </c>
-      <c r="F17" s="20">
+        <v>0.340909090909091</v>
+      </c>
+      <c r="F17" s="21">
+        <f ca="1">D17/(C17/E23*B$23)</f>
+        <v>1.76136363636364</v>
+      </c>
+      <c r="G17" s="20">
         <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="G17" s="105" t="str">
-        <f t="shared" si="9"/>
+        <v>3</v>
+      </c>
+      <c r="H17" s="105" t="str">
+        <f t="shared" si="8"/>
         <v>否</v>
       </c>
-      <c r="H17" s="21">
+      <c r="I17" s="21">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I17" s="22">
+      <c r="J17" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>485</v>
-      </c>
-      <c r="J17" s="20">
+        <v>216</v>
+      </c>
+      <c r="K17" s="20">
         <v>2500</v>
       </c>
-      <c r="K17" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.222740740740741</v>
-      </c>
-      <c r="L17" s="22">
+      <c r="L17" s="21">
+        <f ca="1">J17/(K17/E23*B$23)</f>
+        <v>0.4464</v>
+      </c>
+      <c r="M17" s="22">
+        <f ca="1" t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="N17" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="20" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>11</v>
-      </c>
-      <c r="M17" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>325</v>
-      </c>
-      <c r="N17" s="20" t="str">
-        <f ca="1" t="shared" si="11"/>
         <v>否</v>
       </c>
-      <c r="O17" s="100">
-        <v>25</v>
-      </c>
-      <c r="P17" s="103">
+      <c r="P17" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q17" s="103">
         <f>_xlfn.XLOOKUP(B17,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q17" s="104">
-        <f t="shared" si="6"/>
-        <v>0.2</v>
-      </c>
-      <c r="U17" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="R17" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V17" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <f ca="1" t="shared" si="7"/>
-        <v>845.32</v>
-      </c>
-      <c r="W17">
-        <f ca="1" t="shared" si="8"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" spans="1:23">
+        <v>498</v>
+      </c>
+      <c r="X17">
+        <f ca="1" t="shared" si="6"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" spans="1:24">
       <c r="A18" s="110"/>
       <c r="B18" s="20" t="s">
         <v>38</v>
@@ -4975,71 +5021,75 @@
       </c>
       <c r="D18" s="100">
         <f>_xlfn.XLOOKUP(B18,高套!A:A,高套!B:B,0)</f>
-        <v>19.73</v>
+        <v>1.5</v>
       </c>
       <c r="E18" s="101">
         <f t="shared" si="0"/>
-        <v>2.24204545454545</v>
-      </c>
-      <c r="F18" s="20">
+        <v>0.170454545454545</v>
+      </c>
+      <c r="F18" s="21">
+        <f ca="1">D18/(C18/E23*B$23)</f>
+        <v>0.880681818181818</v>
+      </c>
+      <c r="G18" s="20">
         <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>19.73</v>
-      </c>
-      <c r="G18" s="105" t="str">
-        <f t="shared" si="9"/>
-        <v>否</v>
-      </c>
-      <c r="H18" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="105" t="str">
+        <f t="shared" si="8"/>
+        <v>是</v>
+      </c>
+      <c r="I18" s="21">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="I18" s="22">
+      <c r="J18" s="22">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>3867.94</v>
-      </c>
-      <c r="J18" s="20">
+        <v>-552.05</v>
+      </c>
+      <c r="K18" s="20">
         <v>2500</v>
       </c>
-      <c r="K18" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>1.77638725925926</v>
-      </c>
-      <c r="L18" s="22">
+      <c r="L18" s="21">
+        <f ca="1">J18/(K18/E23*B$23)</f>
+        <v>-1.14090333333333</v>
+      </c>
+      <c r="M18" s="22">
+        <f ca="1" t="shared" si="9"/>
+        <v>14</v>
+      </c>
+      <c r="N18" s="22">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
+        <v>45</v>
+      </c>
+      <c r="O18" s="20" t="str">
         <f ca="1" t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="M18" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:D,4,0)</f>
-        <v>3147.6</v>
-      </c>
-      <c r="N18" s="20" t="str">
-        <f ca="1" t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="O18" s="100">
-        <v>25</v>
-      </c>
-      <c r="P18" s="103">
+        <v>否</v>
+      </c>
+      <c r="P18" s="100">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="103">
         <f>_xlfn.XLOOKUP(B18,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>25</v>
-      </c>
-      <c r="Q18" s="104">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="U18" s="111" t="s">
+        <v>6</v>
+      </c>
+      <c r="R18" s="104">
+        <f t="shared" si="5"/>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="V18" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <f ca="1" t="shared" si="7"/>
-        <v>3867.94</v>
-      </c>
-      <c r="W18">
-        <f ca="1" t="shared" si="8"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:23">
+        <v>-552.05</v>
+      </c>
+      <c r="X18">
+        <f ca="1" t="shared" si="6"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" spans="1:24">
       <c r="A19" s="112"/>
       <c r="B19" s="26" t="s">
         <v>30</v>
@@ -5050,64 +5100,68 @@
       </c>
       <c r="D19" s="26">
         <f>SUM(D12:D18)</f>
-        <v>51.98</v>
+        <v>18.23</v>
       </c>
       <c r="E19" s="27">
         <f t="shared" si="0"/>
-        <v>0.843831168831169</v>
-      </c>
-      <c r="F19" s="26">
-        <f>SUM(F12:F18)</f>
-        <v>52.48</v>
-      </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27">
+        <v>0.295941558441558</v>
+      </c>
+      <c r="F19" s="107">
+        <f ca="1">D19/(C19/E23*B$23)</f>
+        <v>1.52903138528139</v>
+      </c>
+      <c r="G19" s="26">
+        <f>SUM(G12:G18)</f>
+        <v>24.73</v>
+      </c>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27">
         <f t="shared" si="2"/>
-        <v>0.99047256097561</v>
-      </c>
-      <c r="I19" s="113">
-        <f ca="1">SUM(I12:I18)</f>
-        <v>9363.31</v>
-      </c>
-      <c r="J19" s="26">
-        <f>SUM(J12:J18)</f>
+        <v>0.737161342498989</v>
+      </c>
+      <c r="J19" s="113">
+        <f ca="1">SUM(J12:J18)</f>
+        <v>4350.15</v>
+      </c>
+      <c r="K19" s="26">
+        <f>SUM(K12:K18)</f>
         <v>17500</v>
       </c>
-      <c r="K19" s="27">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.614312402116402</v>
-      </c>
-      <c r="L19" s="26"/>
-      <c r="M19" s="113">
-        <f ca="1">SUM(M12:M18)</f>
-        <v>7220.6</v>
-      </c>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26">
-        <f>SUM(O12:O18)</f>
-        <v>175</v>
-      </c>
+      <c r="L19" s="27">
+        <f ca="1">J19/(K19/E23*B$23)</f>
+        <v>1.28433</v>
+      </c>
+      <c r="M19" s="26"/>
+      <c r="N19" s="113">
+        <f ca="1">SUM(N12:N18)</f>
+        <v>4213.2</v>
+      </c>
+      <c r="O19" s="26"/>
       <c r="P19" s="26">
         <f>SUM(P12:P18)</f>
-        <v>55</v>
-      </c>
-      <c r="Q19" s="109">
-        <f t="shared" si="6"/>
-        <v>0.314285714285714</v>
-      </c>
-      <c r="U19" s="114" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q19" s="26">
+        <f>SUM(Q12:Q18)</f>
+        <v>14</v>
+      </c>
+      <c r="R19" s="109">
+        <f t="shared" si="5"/>
+        <v>0.0952380952380952</v>
+      </c>
+      <c r="V19" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <f ca="1" t="shared" si="7"/>
-        <v>485</v>
-      </c>
-      <c r="W19">
-        <f ca="1" t="shared" si="8"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="1:23">
+        <v>216</v>
+      </c>
+      <c r="X19">
+        <f ca="1" t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="1:24">
       <c r="A20" s="115" t="s">
         <v>39</v>
       </c>
@@ -5117,83 +5171,88 @@
       </c>
       <c r="D20" s="118">
         <f>D11+D19</f>
-        <v>79.51</v>
+        <v>19.23</v>
       </c>
       <c r="E20" s="119">
         <f t="shared" si="0"/>
-        <v>0.602348484848485</v>
-      </c>
-      <c r="F20" s="120">
-        <f>F11+F19</f>
-        <v>88.76</v>
-      </c>
-      <c r="G20" s="121"/>
-      <c r="H20" s="122">
+        <v>0.145681818181818</v>
+      </c>
+      <c r="F20" s="33">
+        <f ca="1">D20/(C20/E23*B$23)</f>
+        <v>0.752689393939394</v>
+      </c>
+      <c r="G20" s="120">
+        <f>G11+G19</f>
+        <v>29.23</v>
+      </c>
+      <c r="H20" s="121"/>
+      <c r="I20" s="122">
         <f t="shared" si="2"/>
-        <v>0.895786390265886</v>
-      </c>
-      <c r="I20" s="123">
-        <f ca="1">I11+I19</f>
-        <v>15566.93</v>
-      </c>
-      <c r="J20" s="117">
-        <f>J11+J19</f>
+        <v>0.657885733835101</v>
+      </c>
+      <c r="J20" s="123">
+        <f ca="1">J11+J19</f>
+        <v>4668.08</v>
+      </c>
+      <c r="K20" s="117">
+        <f>K11+K19</f>
         <v>35000</v>
       </c>
-      <c r="K20" s="124">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.510661195767196</v>
-      </c>
-      <c r="L20" s="125"/>
-      <c r="M20" s="126">
-        <f ca="1">M11+M19</f>
-        <v>12387.26</v>
-      </c>
-      <c r="N20" s="127" t="s">
+      <c r="L20" s="124">
+        <f ca="1">J20/(K20/E23*B$23)</f>
+        <v>0.689097523809524</v>
+      </c>
+      <c r="M20" s="125"/>
+      <c r="N20" s="126">
+        <f ca="1">N11+N19</f>
+        <v>4221.2</v>
+      </c>
+      <c r="O20" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="O20" s="128"/>
-      <c r="P20" s="129">
-        <f>P11+P19</f>
-        <v>70</v>
-      </c>
-      <c r="Q20" s="104">
-        <f>P20/O21</f>
-        <v>0.225806451612903</v>
-      </c>
-      <c r="U20" s="130"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:23">
+      <c r="P20" s="128"/>
+      <c r="Q20" s="129">
+        <f>Q11+Q19</f>
+        <v>14</v>
+      </c>
+      <c r="R20" s="104">
+        <f>Q20/P21</f>
+        <v>0.0451612903225806</v>
+      </c>
+      <c r="V20" s="130"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:24">
       <c r="A21" s="99"/>
       <c r="B21" s="131"/>
       <c r="C21" s="131"/>
       <c r="D21" s="131"/>
       <c r="E21" s="131"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="132"/>
-      <c r="H21" s="133"/>
-      <c r="I21" s="131"/>
+      <c r="F21" s="112"/>
+      <c r="G21" s="131"/>
+      <c r="H21" s="132"/>
+      <c r="I21" s="133"/>
       <c r="J21" s="131"/>
-      <c r="K21" s="112"/>
-      <c r="L21" s="134"/>
-      <c r="M21" s="133"/>
-      <c r="N21" s="135" t="s">
+      <c r="K21" s="131"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="134"/>
+      <c r="N21" s="133"/>
+      <c r="O21" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="O21" s="136">
+      <c r="P21" s="136">
         <v>310</v>
       </c>
-      <c r="P21" s="137">
-        <f>_xlfn.XLOOKUP(N21,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>214</v>
-      </c>
-      <c r="Q21" s="104">
-        <f>P21/O21</f>
-        <v>0.690322580645161</v>
-      </c>
-      <c r="U21" s="130"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1" spans="1:23">
+      <c r="Q21" s="137">
+        <f>_xlfn.XLOOKUP(O21,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>31</v>
+      </c>
+      <c r="R21" s="104">
+        <f>Q21/P21</f>
+        <v>0.1</v>
+      </c>
+      <c r="V21" s="130"/>
+    </row>
+    <row r="22" ht="13.5" customHeight="1" spans="1:24">
       <c r="A22" s="36"/>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -5202,121 +5261,129 @@
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
       <c r="H22" s="16"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="38"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="37"/>
       <c r="K22" s="38"/>
       <c r="L22" s="38"/>
       <c r="M22" s="38"/>
       <c r="N22" s="38"/>
       <c r="O22" s="38"/>
-    </row>
-    <row r="23" ht="16.5" customHeight="1" spans="1:23">
+      <c r="P22" s="38"/>
+    </row>
+    <row r="23" ht="16.5" customHeight="1" spans="1:24">
       <c r="A23" s="36" t="str">
         <f ca="1">MONTH(TODAY()-1)&amp;"月"</f>
-        <v>4月</v>
+        <v>5月</v>
       </c>
       <c r="B23" s="36">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="C23" s="36"/>
       <c r="D23" s="40"/>
-      <c r="E23" s="41"/>
+      <c r="E23">
+        <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
+        <v>31</v>
+      </c>
       <c r="F23" s="37"/>
       <c r="G23" s="37"/>
       <c r="H23" s="37"/>
       <c r="I23" s="37"/>
-      <c r="J23" s="38"/>
+      <c r="J23" s="37"/>
       <c r="K23" s="38"/>
       <c r="L23" s="38"/>
       <c r="M23" s="38"/>
       <c r="N23" s="38"/>
       <c r="O23" s="38"/>
-      <c r="P23" t="s">
+      <c r="P23" s="38"/>
+      <c r="Q23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:23">
+    <row r="24" ht="14.25" customHeight="1" spans="1:24">
       <c r="D24"/>
       <c r="E24"/>
       <c r="F24"/>
-      <c r="H24"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="38"/>
+      <c r="G24"/>
+      <c r="I24"/>
+      <c r="J24" s="37"/>
       <c r="K24" s="38"/>
       <c r="L24" s="38"/>
       <c r="M24" s="38"/>
       <c r="N24" s="38"/>
       <c r="O24" s="38"/>
-    </row>
-    <row r="25" ht="33" customHeight="1" spans="1:23">
+      <c r="P24" s="38"/>
+    </row>
+    <row r="25" ht="33" customHeight="1" spans="1:24">
       <c r="D25"/>
       <c r="E25"/>
       <c r="F25"/>
-      <c r="H25"/>
-      <c r="I25" s="49"/>
-      <c r="J25" s="138" t="str">
+      <c r="G25"/>
+      <c r="I25"/>
+      <c r="J25" s="49"/>
+      <c r="K25" s="138" t="str">
         <f ca="1">"📅 "&amp;MONTH(TODAY())&amp;"月份商机统计表（预计转化时间为"&amp;MONTH(TODAY())&amp;"月）"</f>
-        <v>📅 4月份商机统计表（预计转化时间为4月）</v>
-      </c>
-      <c r="K25" s="139"/>
+        <v>📅 5月份商机统计表（预计转化时间为5月）</v>
+      </c>
       <c r="L25" s="139"/>
-      <c r="M25" s="140"/>
-      <c r="O25" s="141" t="s">
+      <c r="M25" s="139"/>
+      <c r="N25" s="140"/>
+      <c r="P25" s="141" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1" spans="1:23">
+    <row r="26" ht="16.5" customHeight="1" spans="1:24">
       <c r="D26"/>
       <c r="E26"/>
       <c r="F26"/>
-      <c r="H26"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="142" t="str">
+      <c r="G26"/>
+      <c r="I26"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="142" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止4月27日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
-      </c>
-      <c r="K26" s="143"/>
+        <v>（数据截止5月6日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+      </c>
       <c r="L26" s="143"/>
-      <c r="M26" s="144"/>
-      <c r="O26" s="145" t="str">
+      <c r="M26" s="143"/>
+      <c r="N26" s="144"/>
+      <c r="P26" s="145" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止4月27日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:23">
+        <v>（数据截止5月6日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" spans="1:24">
       <c r="B27" s="146" t="str">
         <f ca="1">"🏆 高装高套目标完成情况（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>🏆 高装高套目标完成情况（截至4月27日）</v>
-      </c>
-      <c r="H27"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="9" t="s">
+        <v>🏆 高装高套目标完成情况（截至5月6日）</v>
+      </c>
+      <c r="I27"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="L27" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="M27" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="M27" s="11" t="s">
+      <c r="N27" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="O27" s="147" t="s">
+      <c r="P27" s="147" t="s">
         <v>5</v>
       </c>
-      <c r="P27" s="10" t="s">
+      <c r="Q27" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="Q27" s="148" t="s">
+      <c r="R27" s="148" t="s">
         <v>45</v>
       </c>
-      <c r="R27" s="149" t="s">
+      <c r="S27" s="149" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1" spans="1:23">
+    <row r="28" ht="16.5" customHeight="1" spans="1:24">
       <c r="B28" s="150" t="s">
         <v>47</v>
       </c>
@@ -5329,45 +5396,46 @@
       <c r="E28" s="150" t="s">
         <v>50</v>
       </c>
-      <c r="F28" s="150" t="s">
+      <c r="F28" s="150"/>
+      <c r="G28" s="150" t="s">
         <v>20</v>
       </c>
-      <c r="H28"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="151" t="str">
+      <c r="I28"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="151" t="str">
         <f>商机统计!A2</f>
         <v>谢卓和</v>
       </c>
-      <c r="K28" s="152">
+      <c r="L28" s="152">
         <f>商机统计!B2</f>
         <v>10</v>
       </c>
-      <c r="L28" s="152">
+      <c r="M28" s="152">
         <f>商机统计!C2</f>
         <v>35.5</v>
       </c>
-      <c r="M28" s="153">
+      <c r="N28" s="153">
         <f>商机统计!D2</f>
         <v>5607</v>
       </c>
-      <c r="O28" s="151" t="str">
+      <c r="P28" s="151" t="str">
         <f>商机统计!F2</f>
         <v>谢卓和</v>
       </c>
-      <c r="P28" s="152">
+      <c r="Q28" s="152">
         <f>商机统计!G2</f>
         <v>18</v>
       </c>
-      <c r="Q28" s="152">
+      <c r="R28" s="152">
         <f>商机统计!H2</f>
         <v>57.5</v>
       </c>
-      <c r="R28" s="153">
+      <c r="S28" s="153">
         <f>商机统计!I2</f>
         <v>8927</v>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1" spans="1:23">
+    <row r="29" ht="16.5" customHeight="1" spans="1:24">
       <c r="B29" s="154" t="s">
         <v>51</v>
       </c>
@@ -5383,46 +5451,47 @@
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="F29" s="156">
-        <f t="shared" ref="F29:F37" si="12">IFERROR(E29/D29,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="H29"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="157" t="str">
+      <c r="F29" s="156"/>
+      <c r="G29" s="156">
+        <f t="shared" ref="G29:G37" si="11">IFERROR(E29/D29,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="I29"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="157" t="str">
         <f>商机统计!A3</f>
         <v>黄观霞</v>
       </c>
-      <c r="K29" s="158">
+      <c r="L29" s="158">
         <f>商机统计!B3</f>
         <v>3</v>
       </c>
-      <c r="L29" s="158">
+      <c r="M29" s="158">
         <f>商机统计!C3</f>
         <v>21</v>
       </c>
-      <c r="M29" s="159">
+      <c r="N29" s="159">
         <f>商机统计!D3</f>
         <v>4047</v>
       </c>
-      <c r="O29" s="157" t="str">
+      <c r="P29" s="157" t="str">
         <f>商机统计!F3</f>
         <v>邱海燕</v>
       </c>
-      <c r="P29" s="158">
+      <c r="Q29" s="158">
         <f>商机统计!G3</f>
         <v>5</v>
       </c>
-      <c r="Q29" s="158">
+      <c r="R29" s="158">
         <f>商机统计!H3</f>
         <v>49.2</v>
       </c>
-      <c r="R29" s="159">
+      <c r="S29" s="159">
         <f>商机统计!I3</f>
         <v>6479</v>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1" spans="1:23">
+    <row r="30" ht="16.5" customHeight="1" spans="1:24">
       <c r="B30" s="160"/>
       <c r="C30" s="161" t="str">
         <f>高装高套!A3</f>
@@ -5436,46 +5505,47 @@
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="F30" s="162">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H30"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="163" t="str">
+      <c r="F30" s="162"/>
+      <c r="G30" s="162">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I30"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="163" t="str">
         <f>商机统计!A4</f>
         <v>王锦添</v>
       </c>
-      <c r="K30" s="164">
+      <c r="L30" s="164">
         <f>商机统计!B4</f>
         <v>6</v>
       </c>
-      <c r="L30" s="164">
+      <c r="M30" s="164">
         <f>商机统计!C4</f>
         <v>15.33</v>
       </c>
-      <c r="M30" s="165">
+      <c r="N30" s="165">
         <f>商机统计!D4</f>
         <v>3760</v>
       </c>
-      <c r="O30" s="163" t="str">
+      <c r="P30" s="163" t="str">
         <f>商机统计!F4</f>
         <v>黄淡妮</v>
       </c>
-      <c r="P30" s="164">
+      <c r="Q30" s="164">
         <f>商机统计!G4</f>
         <v>9</v>
       </c>
-      <c r="Q30" s="164">
+      <c r="R30" s="164">
         <f>商机统计!H4</f>
         <v>38.9</v>
       </c>
-      <c r="R30" s="165">
+      <c r="S30" s="165">
         <f>商机统计!I4</f>
         <v>7693</v>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1" spans="1:23">
+    <row r="31" ht="16.5" customHeight="1" spans="1:24">
       <c r="B31" s="160"/>
       <c r="C31" s="155" t="str">
         <f>高装高套!A4</f>
@@ -5489,46 +5559,47 @@
         <f>高装高套!B4</f>
         <v>0</v>
       </c>
-      <c r="F31" s="156">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H31"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="166" t="str">
+      <c r="F31" s="156"/>
+      <c r="G31" s="156">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I31"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="166" t="str">
         <f>商机统计!A5</f>
         <v>黄淡妮</v>
       </c>
-      <c r="K31" s="167">
+      <c r="L31" s="167">
         <f>商机统计!B5</f>
         <v>4</v>
       </c>
-      <c r="L31" s="167">
+      <c r="M31" s="167">
         <f>商机统计!C5</f>
         <v>12</v>
       </c>
-      <c r="M31" s="168">
+      <c r="N31" s="168">
         <f>商机统计!D5</f>
         <v>2515</v>
       </c>
-      <c r="O31" s="166" t="str">
+      <c r="P31" s="166" t="str">
         <f>商机统计!F5</f>
         <v>潘观友</v>
       </c>
-      <c r="P31" s="167">
+      <c r="Q31" s="167">
         <f>商机统计!G5</f>
         <v>10</v>
       </c>
-      <c r="Q31" s="167">
+      <c r="R31" s="167">
         <f>商机统计!H5</f>
         <v>35</v>
       </c>
-      <c r="R31" s="168">
+      <c r="S31" s="168">
         <f>商机统计!I5</f>
         <v>7814</v>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:23">
+    <row r="32" ht="16.5" customHeight="1" spans="1:24">
       <c r="B32" s="160"/>
       <c r="C32" s="161" t="str">
         <f>高装高套!A5</f>
@@ -5542,46 +5613,47 @@
         <f>高装高套!B5</f>
         <v>0</v>
       </c>
-      <c r="F32" s="162">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H32"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="169" t="str">
+      <c r="F32" s="162"/>
+      <c r="G32" s="162">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I32"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="169" t="str">
         <f>商机统计!A6</f>
         <v>潘观友</v>
       </c>
-      <c r="K32" s="170">
+      <c r="L32" s="170">
         <f>商机统计!B6</f>
         <v>3</v>
       </c>
-      <c r="L32" s="170">
+      <c r="M32" s="170">
         <f>商机统计!C6</f>
         <v>12</v>
       </c>
-      <c r="M32" s="171">
+      <c r="N32" s="171">
         <f>商机统计!D6</f>
         <v>2148</v>
       </c>
-      <c r="O32" s="169" t="str">
+      <c r="P32" s="169" t="str">
         <f>商机统计!F6</f>
         <v>具进康</v>
       </c>
-      <c r="P32" s="170">
+      <c r="Q32" s="170">
         <f>商机统计!G6</f>
         <v>9</v>
       </c>
-      <c r="Q32" s="170">
+      <c r="R32" s="170">
         <f>商机统计!H6</f>
         <v>28.5</v>
       </c>
-      <c r="R32" s="171">
+      <c r="S32" s="171">
         <f>商机统计!I6</f>
         <v>7383</v>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:18">
+    <row r="33" ht="16.5" customHeight="1" spans="1:19">
       <c r="B33" s="160"/>
       <c r="C33" s="155" t="str">
         <f>高装高套!A6</f>
@@ -5595,46 +5667,47 @@
         <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="F33" s="156">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H33"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="166" t="str">
+      <c r="F33" s="156"/>
+      <c r="G33" s="156">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I33"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="166" t="str">
         <f>商机统计!A7</f>
         <v>麦海芬</v>
       </c>
-      <c r="K33" s="167">
+      <c r="L33" s="167">
         <f>商机统计!B7</f>
         <v>4</v>
       </c>
-      <c r="L33" s="167">
+      <c r="M33" s="167">
         <f>商机统计!C7</f>
         <v>11.5</v>
       </c>
-      <c r="M33" s="168">
+      <c r="N33" s="168">
         <f>商机统计!D7</f>
         <v>2099</v>
       </c>
-      <c r="O33" s="166" t="str">
+      <c r="P33" s="166" t="str">
         <f>商机统计!F7</f>
         <v>伍颖敏</v>
       </c>
-      <c r="P33" s="167">
+      <c r="Q33" s="167">
         <f>商机统计!G7</f>
         <v>5</v>
       </c>
-      <c r="Q33" s="167">
+      <c r="R33" s="167">
         <f>商机统计!H7</f>
         <v>24.98</v>
       </c>
-      <c r="R33" s="168">
+      <c r="S33" s="168">
         <f>商机统计!I7</f>
         <v>4884</v>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" spans="1:18">
+    <row r="34" ht="16.5" customHeight="1" spans="1:19">
       <c r="B34" s="160"/>
       <c r="C34" s="161" t="str">
         <f>高装高套!A7</f>
@@ -5648,46 +5721,47 @@
         <f>高装高套!B7</f>
         <v>0</v>
       </c>
-      <c r="F34" s="162">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H34"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="169" t="str">
+      <c r="F34" s="162"/>
+      <c r="G34" s="162">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I34"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="169" t="str">
         <f>商机统计!A8</f>
         <v>李东</v>
       </c>
-      <c r="K34" s="170">
+      <c r="L34" s="170">
         <f>商机统计!B8</f>
         <v>5</v>
       </c>
-      <c r="L34" s="170">
+      <c r="M34" s="170">
         <f>商机统计!C8</f>
         <v>11</v>
       </c>
-      <c r="M34" s="171">
+      <c r="N34" s="171">
         <f>商机统计!D8</f>
         <v>1188</v>
       </c>
-      <c r="O34" s="169" t="str">
+      <c r="P34" s="169" t="str">
         <f>商机统计!F8</f>
         <v>黄观霞</v>
       </c>
-      <c r="P34" s="170">
+      <c r="Q34" s="170">
         <f>商机统计!G8</f>
         <v>3</v>
       </c>
-      <c r="Q34" s="170">
+      <c r="R34" s="170">
         <f>商机统计!H8</f>
         <v>21</v>
       </c>
-      <c r="R34" s="171">
+      <c r="S34" s="171">
         <f>商机统计!I8</f>
         <v>4047</v>
       </c>
     </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:18">
+    <row r="35" ht="16.5" customHeight="1" spans="1:19">
       <c r="B35" s="160"/>
       <c r="C35" s="155" t="str">
         <f>高装高套!A8</f>
@@ -5701,46 +5775,47 @@
         <f>高装高套!B8</f>
         <v>0</v>
       </c>
-      <c r="F35" s="156">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H35"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="166" t="str">
+      <c r="F35" s="156"/>
+      <c r="G35" s="156">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I35"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="166" t="str">
         <f>商机统计!A9</f>
         <v>邱海燕</v>
       </c>
-      <c r="K35" s="167">
+      <c r="L35" s="167">
         <f>商机统计!B9</f>
         <v>2</v>
       </c>
-      <c r="L35" s="167">
+      <c r="M35" s="167">
         <f>商机统计!C9</f>
         <v>10.8</v>
       </c>
-      <c r="M35" s="168">
+      <c r="N35" s="168">
         <f>商机统计!D9</f>
         <v>2129</v>
       </c>
-      <c r="O35" s="166" t="str">
+      <c r="P35" s="166" t="str">
         <f>商机统计!F9</f>
         <v>李玉强</v>
       </c>
-      <c r="P35" s="167">
+      <c r="Q35" s="167">
         <f>商机统计!G9</f>
         <v>7</v>
       </c>
-      <c r="Q35" s="167">
+      <c r="R35" s="167">
         <f>商机统计!H9</f>
         <v>17.5</v>
       </c>
-      <c r="R35" s="168">
+      <c r="S35" s="168">
         <f>商机统计!I9</f>
         <v>4460</v>
       </c>
     </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:18">
+    <row r="36" ht="16.5" customHeight="1" spans="1:19">
       <c r="B36" s="172"/>
       <c r="C36" s="161" t="str">
         <f>高装高套!A9</f>
@@ -5754,46 +5829,47 @@
         <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="F36" s="162">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H36"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="169" t="str">
+      <c r="F36" s="162"/>
+      <c r="G36" s="162">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I36"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="169" t="str">
         <f>商机统计!A10</f>
         <v>具进康</v>
       </c>
-      <c r="K36" s="170">
+      <c r="L36" s="170">
         <f>商机统计!B10</f>
         <v>6</v>
       </c>
-      <c r="L36" s="170">
+      <c r="M36" s="170">
         <f>商机统计!C10</f>
         <v>8.5</v>
       </c>
-      <c r="M36" s="171">
+      <c r="N36" s="171">
         <f>商机统计!D10</f>
         <v>2284</v>
       </c>
-      <c r="O36" s="169" t="str">
+      <c r="P36" s="169" t="str">
         <f>商机统计!F10</f>
         <v>张小敏</v>
       </c>
-      <c r="P36" s="170">
+      <c r="Q36" s="170">
         <f>商机统计!G10</f>
         <v>8</v>
       </c>
-      <c r="Q36" s="170">
+      <c r="R36" s="170">
         <f>商机统计!H10</f>
         <v>17</v>
       </c>
-      <c r="R36" s="171">
+      <c r="S36" s="171">
         <f>商机统计!I10</f>
         <v>4567</v>
       </c>
     </row>
-    <row r="37" ht="16.5" customHeight="1" spans="1:18">
+    <row r="37" ht="16.5" customHeight="1" spans="1:19">
       <c r="B37" s="173" t="s">
         <v>39</v>
       </c>
@@ -5806,250 +5882,257 @@
         <f>SUM(E29:E36)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="175">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="H37"/>
-      <c r="I37" s="59"/>
-      <c r="J37" s="166" t="str">
+      <c r="F37" s="175"/>
+      <c r="G37" s="175">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="I37"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="166" t="str">
         <f>商机统计!A11</f>
         <v>李玉强</v>
       </c>
-      <c r="K37" s="167">
+      <c r="L37" s="167">
         <f>商机统计!B11</f>
         <v>5</v>
       </c>
-      <c r="L37" s="167">
+      <c r="M37" s="167">
         <f>商机统计!C11</f>
         <v>7.5</v>
       </c>
-      <c r="M37" s="168">
+      <c r="N37" s="168">
         <f>商机统计!D11</f>
         <v>1324</v>
       </c>
-      <c r="O37" s="166" t="str">
+      <c r="P37" s="166" t="str">
         <f>商机统计!F11</f>
         <v>王锦添</v>
       </c>
-      <c r="P37" s="167">
+      <c r="Q37" s="167">
         <f>商机统计!G11</f>
         <v>6</v>
       </c>
-      <c r="Q37" s="167">
+      <c r="R37" s="167">
         <f>商机统计!H11</f>
         <v>15.33</v>
       </c>
-      <c r="R37" s="168">
+      <c r="S37" s="168">
         <f>商机统计!I11</f>
         <v>3760</v>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1" spans="1:18">
+    <row r="38" ht="16.5" customHeight="1" spans="1:19">
       <c r="D38"/>
       <c r="E38"/>
       <c r="F38"/>
-      <c r="H38"/>
-      <c r="I38" s="59"/>
-      <c r="J38" s="169" t="str">
+      <c r="G38"/>
+      <c r="I38"/>
+      <c r="J38" s="59"/>
+      <c r="K38" s="169" t="str">
         <f>商机统计!A12</f>
         <v>伍颖敏</v>
       </c>
-      <c r="K38" s="170">
+      <c r="L38" s="170">
         <f>商机统计!B12</f>
         <v>2</v>
       </c>
-      <c r="L38" s="170">
+      <c r="M38" s="170">
         <f>商机统计!C12</f>
         <v>4.5</v>
       </c>
-      <c r="M38" s="171">
+      <c r="N38" s="171">
         <f>商机统计!D12</f>
         <v>819</v>
       </c>
-      <c r="O38" s="169" t="str">
+      <c r="P38" s="169" t="str">
         <f>商机统计!F12</f>
         <v>李东</v>
       </c>
-      <c r="P38" s="170">
+      <c r="Q38" s="170">
         <f>商机统计!G12</f>
         <v>6</v>
       </c>
-      <c r="Q38" s="170">
+      <c r="R38" s="170">
         <f>商机统计!H12</f>
         <v>12</v>
       </c>
-      <c r="R38" s="171">
+      <c r="S38" s="171">
         <f>商机统计!I12</f>
         <v>1388</v>
       </c>
     </row>
-    <row r="39" ht="16.5" customHeight="1" spans="1:18">
+    <row r="39" ht="16.5" customHeight="1" spans="1:19">
       <c r="D39"/>
       <c r="E39"/>
       <c r="F39"/>
-      <c r="H39"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="166" t="str">
+      <c r="G39"/>
+      <c r="I39"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="166" t="str">
         <f>商机统计!A13</f>
         <v>张小敏</v>
       </c>
-      <c r="K39" s="167">
+      <c r="L39" s="167">
         <f>商机统计!B13</f>
         <v>1</v>
       </c>
-      <c r="L39" s="167">
+      <c r="M39" s="167">
         <f>商机统计!C13</f>
         <v>2.5</v>
       </c>
-      <c r="M39" s="168">
+      <c r="N39" s="168">
         <f>商机统计!D13</f>
         <v>399</v>
       </c>
-      <c r="O39" s="166" t="str">
+      <c r="P39" s="166" t="str">
         <f>商机统计!F13</f>
         <v>麦海芬</v>
       </c>
-      <c r="P39" s="167">
+      <c r="Q39" s="167">
         <f>商机统计!G13</f>
         <v>5</v>
       </c>
-      <c r="Q39" s="167">
+      <c r="R39" s="167">
         <f>商机统计!H13</f>
         <v>11.5</v>
       </c>
-      <c r="R39" s="168">
+      <c r="S39" s="168">
         <f>商机统计!I13</f>
         <v>2099</v>
       </c>
     </row>
-    <row r="40" ht="16.5" customHeight="1" spans="1:18">
+    <row r="40" ht="16.5" customHeight="1" spans="1:19">
       <c r="D40"/>
       <c r="E40"/>
       <c r="F40"/>
-      <c r="H40"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="169" t="str">
+      <c r="G40"/>
+      <c r="I40"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="169" t="str">
         <f>商机统计!A14</f>
         <v>钟俊杰</v>
       </c>
-      <c r="K40" s="170">
+      <c r="L40" s="170">
         <f>商机统计!B14</f>
         <v>0</v>
       </c>
-      <c r="L40" s="170">
+      <c r="M40" s="170">
         <f>商机统计!C14</f>
         <v>0</v>
       </c>
-      <c r="M40" s="171">
+      <c r="N40" s="171">
         <f>商机统计!D14</f>
         <v>0</v>
       </c>
-      <c r="O40" s="169" t="str">
+      <c r="P40" s="169" t="str">
         <f>商机统计!F14</f>
         <v>冯艺康</v>
       </c>
-      <c r="P40" s="170">
+      <c r="Q40" s="170">
         <f>商机统计!G14</f>
         <v>1</v>
       </c>
-      <c r="Q40" s="170">
+      <c r="R40" s="170">
         <f>商机统计!H14</f>
         <v>6</v>
       </c>
-      <c r="R40" s="171">
+      <c r="S40" s="171">
         <f>商机统计!I14</f>
         <v>1200</v>
       </c>
     </row>
-    <row r="41" ht="13.5" customHeight="1" spans="1:18">
+    <row r="41" ht="13.5" customHeight="1" spans="1:19">
       <c r="D41"/>
       <c r="E41"/>
       <c r="F41"/>
-      <c r="H41"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="176" t="str">
+      <c r="G41"/>
+      <c r="I41"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="176" t="str">
         <f>商机统计!A15</f>
         <v>冯艺康</v>
       </c>
-      <c r="K41" s="177">
+      <c r="L41" s="177">
         <f>商机统计!B15</f>
         <v>0</v>
       </c>
-      <c r="L41" s="177">
+      <c r="M41" s="177">
         <f>商机统计!C15</f>
         <v>0</v>
       </c>
-      <c r="M41" s="178">
+      <c r="N41" s="178">
         <f>商机统计!D15</f>
         <v>0</v>
       </c>
-      <c r="O41" s="176" t="str">
+      <c r="P41" s="176" t="str">
         <f>商机统计!F15</f>
         <v>钟俊杰</v>
       </c>
-      <c r="P41" s="177">
+      <c r="Q41" s="177">
         <f>商机统计!G15</f>
         <v>0</v>
       </c>
-      <c r="Q41" s="177">
+      <c r="R41" s="177">
         <f>商机统计!H15</f>
         <v>0</v>
       </c>
-      <c r="R41" s="178">
+      <c r="S41" s="178">
         <f>商机统计!I15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:19">
       <c r="D42"/>
       <c r="E42"/>
       <c r="F42"/>
-      <c r="H42"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="179" t="s">
+      <c r="G42"/>
+      <c r="I42"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="179" t="s">
         <v>39</v>
-      </c>
-      <c r="K42" s="179">
-        <f>SUM(K28:K41)</f>
-        <v>51</v>
       </c>
       <c r="L42" s="179">
         <f>SUM(L28:L41)</f>
-        <v>152.13</v>
+        <v>51</v>
       </c>
       <c r="M42" s="179">
         <f>SUM(M28:M41)</f>
+        <v>152.13</v>
+      </c>
+      <c r="N42" s="179">
+        <f>SUM(N28:N41)</f>
         <v>28319</v>
       </c>
-      <c r="O42" s="179" t="s">
+      <c r="P42" s="179" t="s">
         <v>39</v>
-      </c>
-      <c r="P42" s="179">
-        <f>SUM(P28:P41)</f>
-        <v>92</v>
       </c>
       <c r="Q42" s="179">
         <f>SUM(Q28:Q41)</f>
-        <v>334.41</v>
+        <v>92</v>
       </c>
       <c r="R42" s="179">
         <f>SUM(R28:R41)</f>
+        <v>334.41</v>
+      </c>
+      <c r="S42" s="179">
+        <f>SUM(S28:S41)</f>
         <v>64701</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:19">
       <c r="A43" s="63"/>
       <c r="B43" s="63"/>
       <c r="C43" s="66"/>
       <c r="D43" s="67"/>
       <c r="E43" s="68"/>
       <c r="F43" s="56"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="65"/>
       <c r="I43" s="56"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1" spans="1:18">
+      <c r="J43" s="56"/>
+    </row>
+    <row r="44" ht="13.5" customHeight="1" spans="1:19">
       <c r="A44" s="70" t="s">
         <v>52</v>
       </c>
@@ -6060,9 +6143,10 @@
       <c r="F44" s="43"/>
       <c r="G44" s="43"/>
       <c r="H44" s="43"/>
-      <c r="I44" s="44"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1" spans="1:18">
+      <c r="I44" s="43"/>
+      <c r="J44" s="44"/>
+    </row>
+    <row r="45" ht="13.5" customHeight="1" spans="1:19">
       <c r="A45" s="74" t="s">
         <v>0</v>
       </c>
@@ -6074,14 +6158,15 @@
       </c>
       <c r="D45" s="43"/>
       <c r="E45" s="44"/>
-      <c r="F45" s="70" t="s">
+      <c r="F45" s="69"/>
+      <c r="G45" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="G45" s="43"/>
       <c r="H45" s="43"/>
-      <c r="I45" s="44"/>
-    </row>
-    <row r="46" ht="39" customHeight="1" spans="1:18">
+      <c r="I45" s="43"/>
+      <c r="J45" s="44"/>
+    </row>
+    <row r="46" ht="39" customHeight="1" spans="1:19">
       <c r="A46" s="180"/>
       <c r="B46" s="180"/>
       <c r="C46" s="74" t="s">
@@ -6093,23 +6178,24 @@
       <c r="E46" s="74" t="s">
         <v>57</v>
       </c>
-      <c r="F46" s="74" t="s">
+      <c r="F46" s="74"/>
+      <c r="G46" s="74" t="s">
         <v>58</v>
       </c>
-      <c r="G46" s="75" t="s">
+      <c r="H46" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="H46" s="75" t="s">
+      <c r="I46" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="I46" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="J46" s="49" t="s">
+      <c r="J46" s="75" t="s">
+        <v>9</v>
+      </c>
+      <c r="K46" s="49" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="47" ht="13.5" customHeight="1" spans="1:18">
+    <row r="47" ht="13.5" customHeight="1" spans="1:19">
       <c r="A47" s="75" t="s">
         <v>62</v>
       </c>
@@ -6120,9 +6206,10 @@
       <c r="F47" s="79"/>
       <c r="G47" s="79"/>
       <c r="H47" s="79"/>
-      <c r="I47" s="80"/>
-    </row>
-    <row r="48" ht="23.25" customHeight="1" spans="1:18">
+      <c r="I47" s="79"/>
+      <c r="J47" s="80"/>
+    </row>
+    <row r="48" ht="23.25" customHeight="1" spans="1:19">
       <c r="A48" s="181"/>
       <c r="B48" s="77"/>
       <c r="C48" s="77"/>
@@ -6131,13 +6218,14 @@
       <c r="F48" s="79"/>
       <c r="G48" s="79"/>
       <c r="H48" s="79"/>
-      <c r="I48" s="80"/>
-      <c r="K48" s="182" t="str">
+      <c r="I48" s="79"/>
+      <c r="J48" s="80"/>
+      <c r="L48" s="182" t="str">
         <f ca="1">"📊 全光任务完成情况（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>📊 全光任务完成情况（截至4月27日）</v>
-      </c>
-    </row>
-    <row r="49" ht="42.75" customHeight="1" spans="1:15">
+        <v>📊 全光任务完成情况（截至5月6日）</v>
+      </c>
+    </row>
+    <row r="49" ht="42.75" customHeight="1" spans="1:16">
       <c r="A49" s="181"/>
       <c r="B49" s="77"/>
       <c r="C49" s="77"/>
@@ -6146,24 +6234,25 @@
       <c r="F49" s="79"/>
       <c r="G49" s="79"/>
       <c r="H49" s="79"/>
-      <c r="I49" s="80"/>
-      <c r="K49" s="183" t="s">
+      <c r="I49" s="79"/>
+      <c r="J49" s="80"/>
+      <c r="L49" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="L49" s="183" t="s">
+      <c r="M49" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="M49" s="183" t="s">
+      <c r="N49" s="183" t="s">
         <v>18</v>
       </c>
-      <c r="N49" s="184" t="s">
+      <c r="O49" s="184" t="s">
         <v>63</v>
       </c>
-      <c r="O49" s="183" t="s">
+      <c r="P49" s="183" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:16">
       <c r="A50" s="181"/>
       <c r="B50" s="77"/>
       <c r="C50" s="77"/>
@@ -6172,26 +6261,27 @@
       <c r="F50" s="79"/>
       <c r="G50" s="79"/>
       <c r="H50" s="79"/>
-      <c r="I50" s="80"/>
-      <c r="K50" s="185" t="s">
+      <c r="I50" s="79"/>
+      <c r="J50" s="80"/>
+      <c r="L50" s="185" t="s">
         <v>64</v>
       </c>
-      <c r="L50" s="186" t="s">
+      <c r="M50" s="186" t="s">
         <v>65</v>
       </c>
-      <c r="M50" s="186">
-        <v>100</v>
-      </c>
       <c r="N50" s="186">
+        <v>84</v>
+      </c>
+      <c r="O50" s="186">
         <f>交付高装!D2</f>
-        <v>6</v>
-      </c>
-      <c r="O50" s="187">
+        <v>3</v>
+      </c>
+      <c r="P50" s="187">
         <f>交付高装!E2</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
+        <v>0.0357142857142857</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" s="181"/>
       <c r="B51" s="77"/>
       <c r="C51" s="77"/>
@@ -6200,24 +6290,25 @@
       <c r="F51" s="79"/>
       <c r="G51" s="79"/>
       <c r="H51" s="79"/>
-      <c r="I51" s="80"/>
-      <c r="K51" s="188"/>
-      <c r="L51" s="186" t="s">
+      <c r="I51" s="79"/>
+      <c r="J51" s="80"/>
+      <c r="L51" s="188"/>
+      <c r="M51" s="186" t="s">
         <v>66</v>
       </c>
-      <c r="M51" s="186">
-        <v>100</v>
-      </c>
       <c r="N51" s="186">
+        <v>84</v>
+      </c>
+      <c r="O51" s="186">
         <f>交付高装!D3</f>
-        <v>9</v>
-      </c>
-      <c r="O51" s="187">
+        <v>5</v>
+      </c>
+      <c r="P51" s="187">
         <f>交付高装!E3</f>
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
+        <v>0.0595238095238095</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" s="181"/>
       <c r="B52" s="77"/>
       <c r="C52" s="77"/>
@@ -6226,24 +6317,25 @@
       <c r="F52" s="79"/>
       <c r="G52" s="79"/>
       <c r="H52" s="79"/>
-      <c r="I52" s="80"/>
-      <c r="K52" s="188"/>
-      <c r="L52" s="189" t="s">
+      <c r="I52" s="79"/>
+      <c r="J52" s="80"/>
+      <c r="L52" s="188"/>
+      <c r="M52" s="189" t="s">
         <v>67</v>
       </c>
-      <c r="M52" s="186">
-        <v>100</v>
-      </c>
       <c r="N52" s="186">
+        <v>84</v>
+      </c>
+      <c r="O52" s="186">
         <f>交付高装!D4</f>
-        <v>25</v>
-      </c>
-      <c r="O52" s="187">
+        <v>0</v>
+      </c>
+      <c r="P52" s="187">
         <f>交付高装!E4</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" s="181"/>
       <c r="B53" s="77"/>
       <c r="C53" s="77"/>
@@ -6252,24 +6344,25 @@
       <c r="F53" s="79"/>
       <c r="G53" s="79"/>
       <c r="H53" s="79"/>
-      <c r="I53" s="80"/>
-      <c r="K53" s="188"/>
-      <c r="L53" s="186" t="s">
+      <c r="I53" s="79"/>
+      <c r="J53" s="80"/>
+      <c r="L53" s="188"/>
+      <c r="M53" s="186" t="s">
         <v>68</v>
       </c>
-      <c r="M53" s="186">
-        <v>75</v>
-      </c>
       <c r="N53" s="186">
+        <v>63</v>
+      </c>
+      <c r="O53" s="186">
         <f>交付高装!D5</f>
-        <v>30</v>
-      </c>
-      <c r="O53" s="187">
+        <v>6</v>
+      </c>
+      <c r="P53" s="187">
         <f>交付高装!E5</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
+        <v>0.0983606557377049</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" s="180"/>
       <c r="B54" s="82" t="s">
         <v>30</v>
@@ -6280,26 +6373,27 @@
       <c r="F54" s="82"/>
       <c r="G54" s="82"/>
       <c r="H54" s="82"/>
-      <c r="I54" s="83"/>
-      <c r="K54" s="190" t="s">
+      <c r="I54" s="82"/>
+      <c r="J54" s="83"/>
+      <c r="L54" s="190" t="s">
         <v>51</v>
       </c>
-      <c r="L54" s="191" t="s">
+      <c r="M54" s="191" t="s">
         <v>69</v>
       </c>
-      <c r="M54" s="192">
-        <v>50</v>
-      </c>
       <c r="N54" s="192">
+        <v>42</v>
+      </c>
+      <c r="O54" s="192">
         <f>交付高装!D6</f>
-        <v>6</v>
-      </c>
-      <c r="O54" s="193">
+        <v>5</v>
+      </c>
+      <c r="P54" s="193">
         <f>交付高装!E6</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="55" ht="13.5" customHeight="1" spans="1:15">
+        <v>0.119047619047619</v>
+      </c>
+    </row>
+    <row r="55" ht="13.5" customHeight="1" spans="1:16">
       <c r="A55" s="94" t="s">
         <v>70</v>
       </c>
@@ -6310,24 +6404,25 @@
       <c r="F55" s="79"/>
       <c r="G55" s="79"/>
       <c r="H55" s="79"/>
-      <c r="I55" s="80"/>
-      <c r="K55" s="181"/>
-      <c r="L55" s="191" t="s">
+      <c r="I55" s="79"/>
+      <c r="J55" s="80"/>
+      <c r="L55" s="181"/>
+      <c r="M55" s="191" t="s">
         <v>71</v>
       </c>
-      <c r="M55" s="192">
-        <v>50</v>
-      </c>
       <c r="N55" s="192">
+        <v>42</v>
+      </c>
+      <c r="O55" s="192">
         <f>交付高装!D7</f>
-        <v>3</v>
-      </c>
-      <c r="O55" s="193">
+        <v>0</v>
+      </c>
+      <c r="P55" s="193">
         <f>交付高装!E7</f>
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" s="181"/>
       <c r="B56" s="77"/>
       <c r="C56" s="77"/>
@@ -6336,24 +6431,25 @@
       <c r="F56" s="79"/>
       <c r="G56" s="79"/>
       <c r="H56" s="79"/>
-      <c r="I56" s="80"/>
-      <c r="K56" s="181"/>
-      <c r="L56" s="191" t="s">
+      <c r="I56" s="79"/>
+      <c r="J56" s="80"/>
+      <c r="L56" s="181"/>
+      <c r="M56" s="191" t="s">
         <v>72</v>
       </c>
-      <c r="M56" s="192">
-        <v>50</v>
-      </c>
       <c r="N56" s="192">
+        <v>42</v>
+      </c>
+      <c r="O56" s="192">
         <f>交付高装!D8</f>
-        <v>0</v>
-      </c>
-      <c r="O56" s="193">
+        <v>3</v>
+      </c>
+      <c r="P56" s="193">
         <f>交付高装!E8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
       <c r="A57" s="181"/>
       <c r="B57" s="77"/>
       <c r="C57" s="77"/>
@@ -6362,24 +6458,25 @@
       <c r="F57" s="79"/>
       <c r="G57" s="79"/>
       <c r="H57" s="79"/>
-      <c r="I57" s="80"/>
-      <c r="K57" s="181"/>
-      <c r="L57" s="191" t="s">
+      <c r="I57" s="79"/>
+      <c r="J57" s="80"/>
+      <c r="L57" s="181"/>
+      <c r="M57" s="191" t="s">
         <v>73</v>
       </c>
-      <c r="M57" s="192">
-        <v>50</v>
-      </c>
       <c r="N57" s="192">
+        <v>42</v>
+      </c>
+      <c r="O57" s="192">
         <f>交付高装!D9</f>
-        <v>6</v>
-      </c>
-      <c r="O57" s="193">
+        <v>0</v>
+      </c>
+      <c r="P57" s="193">
         <f>交付高装!E9</f>
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" s="181"/>
       <c r="B58" s="77"/>
       <c r="C58" s="77"/>
@@ -6388,24 +6485,25 @@
       <c r="F58" s="79"/>
       <c r="G58" s="79"/>
       <c r="H58" s="79"/>
-      <c r="I58" s="80"/>
-      <c r="K58" s="181"/>
-      <c r="L58" s="191" t="s">
+      <c r="I58" s="79"/>
+      <c r="J58" s="80"/>
+      <c r="L58" s="181"/>
+      <c r="M58" s="191" t="s">
         <v>74</v>
       </c>
-      <c r="M58" s="192">
-        <v>50</v>
-      </c>
       <c r="N58" s="192">
+        <v>42</v>
+      </c>
+      <c r="O58" s="192">
         <f>交付高装!D10</f>
-        <v>11</v>
-      </c>
-      <c r="O58" s="193">
+        <v>0</v>
+      </c>
+      <c r="P58" s="193">
         <f>交付高装!E10</f>
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59" s="181"/>
       <c r="B59" s="77"/>
       <c r="C59" s="77"/>
@@ -6414,24 +6512,25 @@
       <c r="F59" s="79"/>
       <c r="G59" s="79"/>
       <c r="H59" s="79"/>
-      <c r="I59" s="80"/>
-      <c r="K59" s="181"/>
-      <c r="L59" s="191" t="s">
+      <c r="I59" s="79"/>
+      <c r="J59" s="80"/>
+      <c r="L59" s="181"/>
+      <c r="M59" s="191" t="s">
         <v>75</v>
       </c>
-      <c r="M59" s="192">
-        <v>50</v>
-      </c>
       <c r="N59" s="192">
+        <v>42</v>
+      </c>
+      <c r="O59" s="192">
         <f>交付高装!D11</f>
-        <v>14</v>
-      </c>
-      <c r="O59" s="193">
+        <v>0</v>
+      </c>
+      <c r="P59" s="193">
         <f>交付高装!E11</f>
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" s="181"/>
       <c r="B60" s="77"/>
       <c r="C60" s="77"/>
@@ -6440,24 +6539,25 @@
       <c r="F60" s="79"/>
       <c r="G60" s="79"/>
       <c r="H60" s="79"/>
-      <c r="I60" s="80"/>
-      <c r="K60" s="181"/>
-      <c r="L60" s="191" t="s">
+      <c r="I60" s="79"/>
+      <c r="J60" s="80"/>
+      <c r="L60" s="181"/>
+      <c r="M60" s="191" t="s">
         <v>76</v>
       </c>
-      <c r="M60" s="192">
-        <v>50</v>
-      </c>
       <c r="N60" s="192">
+        <v>42</v>
+      </c>
+      <c r="O60" s="192">
         <f>交付高装!D12</f>
-        <v>30</v>
-      </c>
-      <c r="O60" s="193">
+        <v>6</v>
+      </c>
+      <c r="P60" s="193">
         <f>交付高装!E12</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" s="181"/>
       <c r="B61" s="77"/>
       <c r="C61" s="77"/>
@@ -6466,24 +6566,25 @@
       <c r="F61" s="79"/>
       <c r="G61" s="79"/>
       <c r="H61" s="79"/>
-      <c r="I61" s="80"/>
-      <c r="K61" s="180"/>
-      <c r="L61" s="194" t="s">
+      <c r="I61" s="79"/>
+      <c r="J61" s="80"/>
+      <c r="L61" s="180"/>
+      <c r="M61" s="194" t="s">
         <v>77</v>
       </c>
-      <c r="M61" s="192">
+      <c r="N61" s="192">
         <v>310</v>
       </c>
-      <c r="N61" s="192">
-        <f>SUM(N50:N53)</f>
-        <v>70</v>
-      </c>
-      <c r="O61" s="193">
-        <f>N61/M61</f>
-        <v>0.225806451612903</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+      <c r="O61" s="192">
+        <f>SUM(O50:O53)</f>
+        <v>14</v>
+      </c>
+      <c r="P61" s="193">
+        <f>O61/N61</f>
+        <v>0.0451612903225806</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" s="181"/>
       <c r="B62" s="77"/>
       <c r="C62" s="77"/>
@@ -6492,9 +6593,10 @@
       <c r="F62" s="79"/>
       <c r="G62" s="79"/>
       <c r="H62" s="79"/>
-      <c r="I62" s="80"/>
-    </row>
-    <row r="63" spans="1:15">
+      <c r="I62" s="79"/>
+      <c r="J62" s="80"/>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" s="180"/>
       <c r="B63" s="82" t="s">
         <v>30</v>
@@ -6505,9 +6607,10 @@
       <c r="F63" s="82"/>
       <c r="G63" s="82"/>
       <c r="H63" s="82"/>
-      <c r="I63" s="83"/>
-    </row>
-    <row r="64" ht="13.5" customHeight="1" spans="1:15">
+      <c r="I63" s="82"/>
+      <c r="J63" s="83"/>
+    </row>
+    <row r="64" ht="13.5" customHeight="1" spans="1:16">
       <c r="A64" s="195" t="s">
         <v>39</v>
       </c>
@@ -6518,16 +6621,17 @@
       <c r="F64" s="82"/>
       <c r="G64" s="82"/>
       <c r="H64" s="82"/>
-      <c r="I64" s="83"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1" spans="1:10">
+      <c r="I64" s="82"/>
+      <c r="J64" s="83"/>
+    </row>
+    <row r="65" ht="13.5" customHeight="1" spans="1:11">
       <c r="A65" s="85" t="s">
         <v>78</v>
       </c>
-      <c r="H65" s="86"/>
       <c r="I65" s="86"/>
-    </row>
-    <row r="66" spans="1:10">
+      <c r="J65" s="86"/>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" s="65"/>
       <c r="B66" s="65"/>
       <c r="C66" s="65"/>
@@ -6537,8 +6641,9 @@
       <c r="G66" s="65"/>
       <c r="H66" s="65"/>
       <c r="I66" s="65"/>
-    </row>
-    <row r="67" ht="13.5" customHeight="1" spans="1:10">
+      <c r="J66" s="65"/>
+    </row>
+    <row r="67" ht="13.5" customHeight="1" spans="1:11">
       <c r="A67" s="75" t="s">
         <v>79</v>
       </c>
@@ -6549,9 +6654,10 @@
       <c r="F67" s="43"/>
       <c r="G67" s="43"/>
       <c r="H67" s="43"/>
-      <c r="I67" s="44"/>
-    </row>
-    <row r="68" ht="52" customHeight="1" spans="1:10">
+      <c r="I67" s="43"/>
+      <c r="J67" s="44"/>
+    </row>
+    <row r="68" ht="52" customHeight="1" spans="1:11">
       <c r="A68" s="74" t="s">
         <v>0</v>
       </c>
@@ -6567,23 +6673,24 @@
       <c r="E68" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="F68" s="75" t="s">
+      <c r="F68" s="75"/>
+      <c r="G68" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="G68" s="75" t="s">
+      <c r="H68" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="H68" s="75" t="s">
+      <c r="I68" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="I68" s="75" t="s">
+      <c r="J68" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="J68" t="s">
+      <c r="K68" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="69" ht="13.5" customHeight="1" spans="1:10">
+    <row r="69" ht="13.5" customHeight="1" spans="1:11">
       <c r="A69" s="196" t="s">
         <v>62</v>
       </c>
@@ -6592,44 +6699,48 @@
       <c r="D69" s="79"/>
       <c r="E69" s="80"/>
       <c r="F69" s="79"/>
-      <c r="G69" s="80"/>
-      <c r="H69" s="79"/>
+      <c r="G69" s="79"/>
+      <c r="H69" s="80"/>
       <c r="I69" s="79"/>
-    </row>
-    <row r="70" spans="1:10">
+      <c r="J69" s="79"/>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" s="181"/>
       <c r="B70" s="79"/>
       <c r="C70" s="79"/>
       <c r="D70" s="79"/>
       <c r="E70" s="80"/>
       <c r="F70" s="79"/>
-      <c r="G70" s="80"/>
-      <c r="H70" s="79"/>
+      <c r="G70" s="79"/>
+      <c r="H70" s="80"/>
       <c r="I70" s="79"/>
-    </row>
-    <row r="71" spans="1:10">
+      <c r="J70" s="79"/>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" s="181"/>
       <c r="B71" s="79"/>
       <c r="C71" s="79"/>
       <c r="D71" s="79"/>
       <c r="E71" s="80"/>
       <c r="F71" s="79"/>
-      <c r="G71" s="80"/>
-      <c r="H71" s="79"/>
+      <c r="G71" s="79"/>
+      <c r="H71" s="80"/>
       <c r="I71" s="79"/>
-    </row>
-    <row r="72" spans="1:10">
+      <c r="J71" s="79"/>
+    </row>
+    <row r="72" spans="1:11">
       <c r="A72" s="181"/>
       <c r="B72" s="79"/>
       <c r="C72" s="79"/>
       <c r="D72" s="79"/>
       <c r="E72" s="80"/>
       <c r="F72" s="79"/>
-      <c r="G72" s="80"/>
-      <c r="H72" s="79"/>
+      <c r="G72" s="79"/>
+      <c r="H72" s="80"/>
       <c r="I72" s="79"/>
-    </row>
-    <row r="73" spans="1:10">
+      <c r="J72" s="79"/>
+    </row>
+    <row r="73" spans="1:11">
       <c r="A73" s="181"/>
       <c r="B73" s="82" t="s">
         <v>30</v>
@@ -6638,11 +6749,12 @@
       <c r="D73" s="82"/>
       <c r="E73" s="83"/>
       <c r="F73" s="82"/>
-      <c r="G73" s="83"/>
-      <c r="H73" s="82"/>
+      <c r="G73" s="82"/>
+      <c r="H73" s="83"/>
       <c r="I73" s="82"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1" spans="1:10">
+      <c r="J73" s="82"/>
+    </row>
+    <row r="74" ht="13.5" customHeight="1" spans="1:11">
       <c r="A74" s="75" t="s">
         <v>70</v>
       </c>
@@ -6651,55 +6763,60 @@
       <c r="D74" s="79"/>
       <c r="E74" s="80"/>
       <c r="F74" s="79"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="79"/>
+      <c r="G74" s="79"/>
+      <c r="H74" s="80"/>
       <c r="I74" s="79"/>
-    </row>
-    <row r="75" spans="1:10">
+      <c r="J74" s="79"/>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" s="181"/>
       <c r="B75" s="79"/>
       <c r="C75" s="79"/>
       <c r="D75" s="79"/>
       <c r="E75" s="80"/>
       <c r="F75" s="79"/>
-      <c r="G75" s="80"/>
-      <c r="H75" s="79"/>
+      <c r="G75" s="79"/>
+      <c r="H75" s="80"/>
       <c r="I75" s="79"/>
-    </row>
-    <row r="76" spans="1:10">
+      <c r="J75" s="79"/>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" s="181"/>
       <c r="B76" s="79"/>
       <c r="C76" s="79"/>
       <c r="D76" s="79"/>
       <c r="E76" s="80"/>
       <c r="F76" s="79"/>
-      <c r="G76" s="80"/>
-      <c r="H76" s="79"/>
+      <c r="G76" s="79"/>
+      <c r="H76" s="80"/>
       <c r="I76" s="79"/>
-    </row>
-    <row r="77" spans="1:10">
+      <c r="J76" s="79"/>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" s="181"/>
       <c r="B77" s="79"/>
       <c r="C77" s="79"/>
       <c r="D77" s="79"/>
       <c r="E77" s="80"/>
       <c r="F77" s="79"/>
-      <c r="G77" s="80"/>
-      <c r="H77" s="79"/>
+      <c r="G77" s="79"/>
+      <c r="H77" s="80"/>
       <c r="I77" s="79"/>
-    </row>
-    <row r="78" spans="1:10">
+      <c r="J77" s="79"/>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" s="181"/>
       <c r="B78" s="79"/>
       <c r="C78" s="79"/>
       <c r="D78" s="79"/>
       <c r="E78" s="80"/>
       <c r="F78" s="79"/>
-      <c r="G78" s="80"/>
-      <c r="H78" s="79"/>
+      <c r="G78" s="79"/>
+      <c r="H78" s="80"/>
       <c r="I78" s="79"/>
-    </row>
-    <row r="79" spans="1:10">
+      <c r="J78" s="79"/>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" s="180"/>
       <c r="B79" s="82" t="s">
         <v>30</v>
@@ -6708,11 +6825,12 @@
       <c r="D79" s="82"/>
       <c r="E79" s="83"/>
       <c r="F79" s="82"/>
-      <c r="G79" s="83"/>
-      <c r="H79" s="82"/>
+      <c r="G79" s="82"/>
+      <c r="H79" s="83"/>
       <c r="I79" s="82"/>
-    </row>
-    <row r="80" ht="13.5" customHeight="1" spans="1:10">
+      <c r="J79" s="82"/>
+    </row>
+    <row r="80" ht="13.5" customHeight="1" spans="1:11">
       <c r="A80" s="82" t="s">
         <v>88</v>
       </c>
@@ -6721,11 +6839,12 @@
       <c r="D80" s="82"/>
       <c r="E80" s="83"/>
       <c r="F80" s="82"/>
-      <c r="G80" s="83"/>
-      <c r="H80" s="82"/>
+      <c r="G80" s="82"/>
+      <c r="H80" s="83"/>
       <c r="I80" s="82"/>
-    </row>
-    <row r="81" spans="1:9">
+      <c r="J80" s="82"/>
+    </row>
+    <row r="81" spans="1:10">
       <c r="A81" s="56"/>
       <c r="B81" s="56"/>
       <c r="C81" s="56"/>
@@ -6735,8 +6854,9 @@
       <c r="G81" s="56"/>
       <c r="H81" s="56"/>
       <c r="I81" s="56"/>
-    </row>
-    <row r="82" spans="1:9">
+      <c r="J81" s="56"/>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82" s="56"/>
       <c r="B82" s="56"/>
       <c r="C82" s="56"/>
@@ -6746,8 +6866,9 @@
       <c r="G82" s="56"/>
       <c r="H82" s="56"/>
       <c r="I82" s="56"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1" spans="1:9">
+      <c r="J82" s="56"/>
+    </row>
+    <row r="83" ht="13.5" customHeight="1" spans="1:10">
       <c r="A83" s="75" t="s">
         <v>89</v>
       </c>
@@ -6758,9 +6879,10 @@
       <c r="F83" s="43"/>
       <c r="G83" s="43"/>
       <c r="H83" s="43"/>
-      <c r="I83" s="44"/>
-    </row>
-    <row r="84" ht="52" customHeight="1" spans="1:9">
+      <c r="I83" s="43"/>
+      <c r="J83" s="44"/>
+    </row>
+    <row r="84" ht="52" customHeight="1" spans="1:10">
       <c r="A84" s="74" t="s">
         <v>0</v>
       </c>
@@ -6776,20 +6898,21 @@
       <c r="E84" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="F84" s="75" t="s">
+      <c r="F84" s="75"/>
+      <c r="G84" s="75" t="s">
         <v>83</v>
       </c>
-      <c r="G84" s="75" t="s">
+      <c r="H84" s="75" t="s">
         <v>84</v>
       </c>
-      <c r="H84" s="75" t="s">
+      <c r="I84" s="75" t="s">
         <v>85</v>
       </c>
-      <c r="I84" s="75" t="s">
+      <c r="J84" s="75" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="85" ht="13.5" customHeight="1" spans="1:9">
+    <row r="85" ht="13.5" customHeight="1" spans="1:10">
       <c r="A85" s="196" t="s">
         <v>62</v>
       </c>
@@ -6798,44 +6921,48 @@
       <c r="D85" s="79"/>
       <c r="E85" s="80"/>
       <c r="F85" s="79"/>
-      <c r="G85" s="80"/>
-      <c r="H85" s="79"/>
+      <c r="G85" s="79"/>
+      <c r="H85" s="80"/>
       <c r="I85" s="79"/>
-    </row>
-    <row r="86" spans="1:9">
+      <c r="J85" s="79"/>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86" s="181"/>
       <c r="B86" s="88"/>
       <c r="C86" s="77"/>
       <c r="D86" s="79"/>
       <c r="E86" s="80"/>
       <c r="F86" s="79"/>
-      <c r="G86" s="80"/>
-      <c r="H86" s="79"/>
+      <c r="G86" s="79"/>
+      <c r="H86" s="80"/>
       <c r="I86" s="79"/>
-    </row>
-    <row r="87" spans="1:9">
+      <c r="J86" s="79"/>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87" s="181"/>
       <c r="B87" s="88"/>
       <c r="C87" s="77"/>
       <c r="D87" s="79"/>
       <c r="E87" s="80"/>
       <c r="F87" s="79"/>
-      <c r="G87" s="80"/>
-      <c r="H87" s="79"/>
+      <c r="G87" s="79"/>
+      <c r="H87" s="80"/>
       <c r="I87" s="79"/>
-    </row>
-    <row r="88" spans="1:9">
+      <c r="J87" s="79"/>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88" s="181"/>
       <c r="B88" s="88"/>
       <c r="C88" s="77"/>
       <c r="D88" s="79"/>
       <c r="E88" s="80"/>
       <c r="F88" s="79"/>
-      <c r="G88" s="80"/>
-      <c r="H88" s="79"/>
+      <c r="G88" s="79"/>
+      <c r="H88" s="80"/>
       <c r="I88" s="79"/>
-    </row>
-    <row r="89" spans="1:9">
+      <c r="J88" s="79"/>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89" s="181"/>
       <c r="B89" s="195" t="s">
         <v>30</v>
@@ -6844,11 +6971,12 @@
       <c r="D89" s="82"/>
       <c r="E89" s="83"/>
       <c r="F89" s="82"/>
-      <c r="G89" s="83"/>
-      <c r="H89" s="82"/>
+      <c r="G89" s="82"/>
+      <c r="H89" s="83"/>
       <c r="I89" s="82"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1" spans="1:9">
+      <c r="J89" s="82"/>
+    </row>
+    <row r="90" ht="13.5" customHeight="1" spans="1:10">
       <c r="A90" s="75" t="s">
         <v>70</v>
       </c>
@@ -6857,22 +6985,24 @@
       <c r="D90" s="79"/>
       <c r="E90" s="80"/>
       <c r="F90" s="79"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="79"/>
+      <c r="G90" s="79"/>
+      <c r="H90" s="80"/>
       <c r="I90" s="79"/>
-    </row>
-    <row r="91" spans="1:9">
+      <c r="J90" s="79"/>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91" s="181"/>
       <c r="B91" s="88"/>
       <c r="C91" s="77"/>
       <c r="D91" s="79"/>
       <c r="E91" s="80"/>
       <c r="F91" s="79"/>
-      <c r="G91" s="80"/>
-      <c r="H91" s="79"/>
+      <c r="G91" s="79"/>
+      <c r="H91" s="80"/>
       <c r="I91" s="79"/>
-    </row>
-    <row r="92" spans="1:9">
+      <c r="J91" s="79"/>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92" s="180"/>
       <c r="B92" s="195" t="s">
         <v>30</v>
@@ -6881,11 +7011,12 @@
       <c r="D92" s="82"/>
       <c r="E92" s="83"/>
       <c r="F92" s="82"/>
-      <c r="G92" s="83"/>
-      <c r="H92" s="82"/>
+      <c r="G92" s="82"/>
+      <c r="H92" s="83"/>
       <c r="I92" s="82"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1" spans="1:9">
+      <c r="J92" s="82"/>
+    </row>
+    <row r="93" ht="13.5" customHeight="1" spans="1:10">
       <c r="A93" s="82" t="s">
         <v>88</v>
       </c>
@@ -6894,11 +7025,12 @@
       <c r="D93" s="82"/>
       <c r="E93" s="83"/>
       <c r="F93" s="82"/>
-      <c r="G93" s="83"/>
-      <c r="H93" s="82"/>
-      <c r="I93" s="89"/>
-    </row>
-    <row r="94" ht="13.5" customHeight="1" spans="1:9">
+      <c r="G93" s="82"/>
+      <c r="H93" s="83"/>
+      <c r="I93" s="82"/>
+      <c r="J93" s="89"/>
+    </row>
+    <row r="94" ht="13.5" customHeight="1" spans="1:10">
       <c r="A94" s="90" t="s">
         <v>90</v>
       </c>
@@ -6907,8 +7039,9 @@
       <c r="G94" s="56"/>
       <c r="H94" s="56"/>
       <c r="I94" s="56"/>
-    </row>
-    <row r="95" spans="1:9">
+      <c r="J94" s="56"/>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95" s="56"/>
       <c r="B95" s="56"/>
       <c r="C95" s="56"/>
@@ -6918,8 +7051,9 @@
       <c r="G95" s="56"/>
       <c r="H95" s="56"/>
       <c r="I95" s="56"/>
-    </row>
-    <row r="96" spans="1:9">
+      <c r="J95" s="56"/>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96" s="49"/>
       <c r="B96" s="49"/>
       <c r="C96" s="56"/>
@@ -6929,8 +7063,9 @@
       <c r="G96" s="56"/>
       <c r="H96" s="56"/>
       <c r="I96" s="56"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1" spans="1:9">
+      <c r="J96" s="56"/>
+    </row>
+    <row r="97" ht="13.5" customHeight="1" spans="1:10">
       <c r="A97" s="74" t="s">
         <v>91</v>
       </c>
@@ -6940,10 +7075,11 @@
       <c r="E97" s="43"/>
       <c r="F97" s="43"/>
       <c r="G97" s="43"/>
-      <c r="H97" s="44"/>
-      <c r="I97" s="56"/>
-    </row>
-    <row r="98" ht="52" customHeight="1" spans="1:9">
+      <c r="H97" s="43"/>
+      <c r="I97" s="44"/>
+      <c r="J97" s="56"/>
+    </row>
+    <row r="98" ht="52" customHeight="1" spans="1:10">
       <c r="A98" s="74" t="s">
         <v>0</v>
       </c>
@@ -6959,18 +7095,19 @@
       <c r="E98" s="93" t="s">
         <v>94</v>
       </c>
-      <c r="F98" s="94" t="s">
+      <c r="F98" s="94"/>
+      <c r="G98" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="G98" s="94" t="s">
+      <c r="H98" s="94" t="s">
         <v>96</v>
       </c>
-      <c r="H98" s="93" t="s">
+      <c r="I98" s="93" t="s">
         <v>97</v>
       </c>
-      <c r="I98" s="56"/>
-    </row>
-    <row r="99" ht="13.5" customHeight="1" spans="1:9">
+      <c r="J98" s="56"/>
+    </row>
+    <row r="99" ht="13.5" customHeight="1" spans="1:10">
       <c r="A99" s="196" t="s">
         <v>62</v>
       </c>
@@ -6981,9 +7118,10 @@
       <c r="F99" s="77"/>
       <c r="G99" s="77"/>
       <c r="H99" s="77"/>
-      <c r="I99" s="49"/>
-    </row>
-    <row r="100" spans="1:9">
+      <c r="I99" s="77"/>
+      <c r="J99" s="49"/>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100" s="181"/>
       <c r="B100" s="95"/>
       <c r="C100" s="77"/>
@@ -6992,9 +7130,10 @@
       <c r="F100" s="77"/>
       <c r="G100" s="77"/>
       <c r="H100" s="77"/>
-      <c r="I100" s="49"/>
-    </row>
-    <row r="101" spans="1:9">
+      <c r="I100" s="77"/>
+      <c r="J100" s="49"/>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101" s="75" t="s">
         <v>70</v>
       </c>
@@ -7005,9 +7144,10 @@
       <c r="F101" s="77"/>
       <c r="G101" s="77"/>
       <c r="H101" s="77"/>
-      <c r="I101" s="56"/>
-    </row>
-    <row r="102" spans="1:9">
+      <c r="I101" s="77"/>
+      <c r="J101" s="56"/>
+    </row>
+    <row r="102" spans="1:10">
       <c r="A102" s="56"/>
       <c r="B102" s="96" t="s">
         <v>98</v>
@@ -7016,11 +7156,12 @@
       <c r="D102" s="49"/>
       <c r="E102" s="49"/>
       <c r="F102" s="96"/>
-      <c r="G102" s="49"/>
+      <c r="G102" s="96"/>
       <c r="H102" s="49"/>
-      <c r="I102" s="56"/>
-    </row>
-    <row r="103" spans="1:9">
+      <c r="I102" s="49"/>
+      <c r="J102" s="56"/>
+    </row>
+    <row r="103" spans="1:10">
       <c r="A103" s="56"/>
       <c r="B103" s="56"/>
       <c r="C103" s="56"/>
@@ -7030,32 +7171,33 @@
       <c r="G103" s="56"/>
       <c r="H103" s="56"/>
       <c r="I103" s="56"/>
+      <c r="J103" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="B1:Q1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="R3:AA3"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="O25:R25"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="O26:R26"/>
-    <mergeCell ref="B27:F27"/>
+  <mergeCells count="51">
+    <mergeCell ref="B1:R1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="S3:AB3"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="P26:S26"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="A44:J44"/>
     <mergeCell ref="C45:E45"/>
-    <mergeCell ref="F45:I45"/>
-    <mergeCell ref="K48:O48"/>
+    <mergeCell ref="G45:J45"/>
+    <mergeCell ref="L48:P48"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="A67:I67"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A67:J67"/>
     <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A83:I83"/>
+    <mergeCell ref="A83:J83"/>
     <mergeCell ref="A93:B93"/>
     <mergeCell ref="A94:D94"/>
-    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A97:I97"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="A12:A19"/>
@@ -7078,14 +7220,20 @@
     <mergeCell ref="I20:I21"/>
     <mergeCell ref="J20:J21"/>
     <mergeCell ref="K20:K21"/>
-    <mergeCell ref="K50:K53"/>
-    <mergeCell ref="K54:K61"/>
     <mergeCell ref="L20:L21"/>
+    <mergeCell ref="L50:L53"/>
+    <mergeCell ref="L54:L61"/>
     <mergeCell ref="M20:M21"/>
+    <mergeCell ref="N20:N21"/>
     <mergeCell ref="A20:B21"/>
   </mergeCells>
-  <conditionalFormatting sqref="G1:G20 G22:G23 G43:G1048576">
+  <conditionalFormatting sqref="F20">
     <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"是"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H20 H22:H23 H43:H1048576">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7110,7 +7258,7 @@
         <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C1" t="s">
         <v>49</v>
@@ -7226,7 +7374,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -7338,13 +7486,13 @@
         <v>101</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>15</v>
@@ -7371,7 +7519,7 @@
         <v>20</v>
       </c>
       <c r="Q4" s="19" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1" spans="1:22">
@@ -7640,7 +7788,7 @@
     <row r="10" ht="16.5" customHeight="1" spans="1:22">
       <c r="A10" s="16"/>
       <c r="B10" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="20">
         <v>8.8</v>
@@ -8066,7 +8214,7 @@
         <v>348</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L17" s="20">
         <v>25</v>
@@ -8125,7 +8273,7 @@
         <v>185</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L18" s="20">
         <v>25</v>
@@ -8184,7 +8332,7 @@
         <v>67</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L19" s="20">
         <v>25</v>
@@ -8202,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="T19" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="U19">
         <f t="shared" si="0"/>
@@ -8216,7 +8364,7 @@
     <row r="20" ht="33" customHeight="1" spans="1:22">
       <c r="A20" s="16"/>
       <c r="B20" s="26" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C20" s="26">
         <v>61.6</v>
@@ -8271,7 +8419,7 @@
     <row r="21" ht="33" customHeight="1" spans="1:22">
       <c r="A21" s="16"/>
       <c r="B21" s="26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C21" s="26">
         <v>70.4</v>
@@ -8371,7 +8519,7 @@
     <row r="23" ht="15" customHeight="1" spans="1:22">
       <c r="A23" s="30"/>
       <c r="B23" s="36" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I23" s="37"/>
       <c r="J23" s="38"/>
@@ -8405,7 +8553,7 @@
     <row r="25" ht="16.5" customHeight="1" spans="1:22">
       <c r="A25" s="36"/>
       <c r="B25" s="42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C25" s="43"/>
       <c r="D25" s="43"/>
@@ -8428,22 +8576,22 @@
         <v>5</v>
       </c>
       <c r="C26" s="47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D26" s="47" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E26" s="47" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G26" s="47" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="49" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I26" s="49"/>
     </row>
@@ -8542,7 +8690,7 @@
     <row r="31" ht="16.5" customHeight="1" spans="1:22">
       <c r="A31" s="57"/>
       <c r="B31" s="51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" s="52">
         <v>66</v>
@@ -8895,7 +9043,7 @@
         <v>60</v>
       </c>
       <c r="I48" s="75" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J48" s="49" t="s">
         <v>61</v>
@@ -9684,7 +9832,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9692,7 +9840,7 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9700,7 +9848,7 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9716,7 +9864,7 @@
         <v>33</v>
       </c>
       <c r="B10">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9724,7 +9872,7 @@
         <v>34</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9732,7 +9880,7 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -9740,7 +9888,7 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9748,7 +9896,7 @@
         <v>37</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9756,7 +9904,7 @@
         <v>38</v>
       </c>
       <c r="B15">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -9764,7 +9912,7 @@
         <v>41</v>
       </c>
       <c r="B16">
-        <v>214</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -9784,7 +9932,7 @@
         <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -9792,7 +9940,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9800,7 +9948,7 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9816,7 +9964,7 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9824,7 +9972,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>13.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9832,7 +9980,7 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9840,7 +9988,7 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>4.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -9856,7 +10004,7 @@
         <v>33</v>
       </c>
       <c r="B10">
-        <v>9.75</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -9864,7 +10012,7 @@
         <v>34</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -9880,7 +10028,7 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -9888,7 +10036,7 @@
         <v>37</v>
       </c>
       <c r="B14">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -9896,7 +10044,7 @@
         <v>38</v>
       </c>
       <c r="B15">
-        <v>19.73</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -9916,18 +10064,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -9938,7 +10086,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -9949,7 +10097,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -9960,7 +10108,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -9971,7 +10119,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -9982,7 +10130,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -9993,7 +10141,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -10004,7 +10152,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -10033,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>16</v>
@@ -10044,13 +10192,13 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -10058,13 +10206,13 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="C3">
-        <v>798.66</v>
+        <v>81.93</v>
       </c>
       <c r="D3">
-        <v>800.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -10072,13 +10220,13 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C4">
-        <v>332.4</v>
+        <v>98</v>
       </c>
       <c r="D4">
-        <v>397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -10086,13 +10234,13 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>630</v>
+        <v>-1</v>
       </c>
       <c r="D5">
-        <v>817</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -10100,13 +10248,13 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>15.25</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>1340.59</v>
+        <v>80</v>
       </c>
       <c r="D6">
-        <v>448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -10114,13 +10262,13 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>1518</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>1143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -10128,13 +10276,13 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>4.03</v>
+        <v>0.5</v>
       </c>
       <c r="C8">
-        <v>1382.97</v>
+        <v>49</v>
       </c>
       <c r="D8">
-        <v>1390</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -10142,13 +10290,13 @@
         <v>32</v>
       </c>
       <c r="B9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -10156,13 +10304,13 @@
         <v>33</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>4.73</v>
       </c>
       <c r="C10">
-        <v>1220.05</v>
+        <v>806.2</v>
       </c>
       <c r="D10">
-        <v>892</v>
+        <v>746.2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -10170,13 +10318,13 @@
         <v>34</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="C11">
-        <v>1451</v>
+        <v>799</v>
       </c>
       <c r="D11">
-        <v>688</v>
+        <v>789</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -10184,13 +10332,13 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>2.75</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>1134</v>
+        <v>2583</v>
       </c>
       <c r="D12">
-        <v>970</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -10198,13 +10346,13 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>845.32</v>
+        <v>498</v>
       </c>
       <c r="D13">
-        <v>848</v>
+        <v>399</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -10212,13 +10360,13 @@
         <v>37</v>
       </c>
       <c r="B14">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>485</v>
+        <v>216</v>
       </c>
       <c r="D14">
-        <v>325</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -10226,13 +10374,13 @@
         <v>38</v>
       </c>
       <c r="B15">
-        <v>19.73</v>
+        <v>1.5</v>
       </c>
       <c r="C15">
-        <v>3867.94</v>
+        <v>-552.05</v>
       </c>
       <c r="D15">
-        <v>3147.6</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -10252,7 +10400,7 @@
         <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -10260,7 +10408,7 @@
         <v>23</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -10268,7 +10416,7 @@
         <v>24</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -10276,7 +10424,7 @@
         <v>25</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -10284,7 +10432,7 @@
         <v>26</v>
       </c>
       <c r="B5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10292,7 +10440,7 @@
         <v>27</v>
       </c>
       <c r="B6">
-        <v>15.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -10300,7 +10448,7 @@
         <v>28</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -10308,7 +10456,7 @@
         <v>29</v>
       </c>
       <c r="B8">
-        <v>4.03</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -10316,7 +10464,7 @@
         <v>32</v>
       </c>
       <c r="B9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -10324,7 +10472,7 @@
         <v>33</v>
       </c>
       <c r="B10">
-        <v>9</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -10332,7 +10480,7 @@
         <v>34</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -10340,7 +10488,7 @@
         <v>35</v>
       </c>
       <c r="B12">
-        <v>2.75</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -10348,7 +10496,7 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -10356,7 +10504,7 @@
         <v>37</v>
       </c>
       <c r="B14">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -10364,7 +10512,7 @@
         <v>38</v>
       </c>
       <c r="B15">
-        <v>19.73</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>
@@ -10806,16 +10954,16 @@
         <v>20</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" ht="14.75" customHeight="1" spans="1:13">
@@ -10826,15 +10974,15 @@
         <v>65</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D2">
         <f t="array" ref="D2">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B2))</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E13" si="0">D2/C2</f>
-        <v>0.06</v>
+        <v>0.0357142857142857</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>35</v>
@@ -10843,7 +10991,7 @@
         <v>69</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M2" s="8" t="s">
         <v>66</v>
@@ -10857,15 +11005,15 @@
         <v>66</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="D3">
         <f t="array" ref="D3">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B3))</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2">
         <f t="shared" si="0"/>
-        <v>0.09</v>
+        <v>0.0595238095238095</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>29</v>
@@ -10874,7 +11022,7 @@
         <v>69</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>66</v>
@@ -10888,15 +11036,15 @@
         <v>67</v>
       </c>
       <c r="C4">
-        <v>100</v>
-      </c>
-      <c r="D4" cm="1">
+        <v>84</v>
+      </c>
+      <c r="D4">
         <f t="array" ref="D4">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B4))</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4" s="2">
         <f t="shared" si="0"/>
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>28</v>
@@ -10905,7 +11053,7 @@
         <v>71</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M4" s="8" t="s">
         <v>66</v>
@@ -10919,15 +11067,15 @@
         <v>68</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D5">
         <f t="array" ref="D5">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B5))</f>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.0983606557377049</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>23</v>
@@ -10936,7 +11084,7 @@
         <v>71</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>66</v>
@@ -10950,15 +11098,15 @@
         <v>69</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D6">
         <f t="array" ref="D6">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*ISNUMBER(SEARCH(B6,$K$2:$K$16)))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.119047619047619</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>34</v>
@@ -10967,7 +11115,7 @@
         <v>72</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M6" s="8" t="s">
         <v>65</v>
@@ -10981,15 +11129,15 @@
         <v>71</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D7">
         <f t="array" ref="D7">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*ISNUMBER(SEARCH(B7,$K$2:$K$16)))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>26</v>
@@ -10998,7 +11146,7 @@
         <v>72</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>65</v>
@@ -11012,15 +11160,15 @@
         <v>72</v>
       </c>
       <c r="C8">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D8">
         <f t="array" ref="D8">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*ISNUMBER(SEARCH(B8,$K$2:$K$16)))</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>25</v>
@@ -11029,7 +11177,7 @@
         <v>73</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" s="8" t="s">
         <v>65</v>
@@ -11043,15 +11191,15 @@
         <v>73</v>
       </c>
       <c r="C9">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D9">
         <f t="array" ref="D9">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*ISNUMBER(SEARCH(B9,$K$2:$K$16)))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>27</v>
@@ -11060,7 +11208,7 @@
         <v>73</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>65</v>
@@ -11074,15 +11222,15 @@
         <v>74</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D10">
         <f t="array" ref="D10">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*ISNUMBER(SEARCH(B10,$K$2:$K$16)))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>32</v>
@@ -11091,7 +11239,7 @@
         <v>74</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M10" s="8" t="s">
         <v>67</v>
@@ -11105,15 +11253,15 @@
         <v>75</v>
       </c>
       <c r="C11">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <f t="array" ref="D11">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*ISNUMBER(SEARCH(B11,$K$2:$K$16)))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>0.28</v>
+        <v>0</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>33</v>
@@ -11122,7 +11270,7 @@
         <v>74</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M11" s="8" t="s">
         <v>67</v>
@@ -11136,15 +11284,15 @@
         <v>76</v>
       </c>
       <c r="C12">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D12">
         <f t="array" ref="D12">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*ISNUMBER(SEARCH(B12,$K$2:$K$16)))</f>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>36</v>
@@ -11153,7 +11301,7 @@
         <v>75</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M12" s="8" t="s">
         <v>67</v>
@@ -11164,7 +11312,7 @@
         <v>51</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -11184,7 +11332,7 @@
         <v>75</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M13" s="8" t="s">
         <v>67</v>
@@ -11198,7 +11346,7 @@
         <v>76</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M14" s="8" t="s">
         <v>68</v>
@@ -11212,7 +11360,7 @@
         <v>76</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>68</v>
@@ -11220,13 +11368,13 @@
     </row>
     <row r="16" ht="14.75" customHeight="1" spans="1:13">
       <c r="J16" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M16" s="8" t="s">
         <v>68</v>

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="90">
   <si>
     <t>团队</t>
   </si>
@@ -147,7 +147,7 @@
     <t>具进康</t>
   </si>
   <si>
-    <t>客户经理团队合计</t>
+    <t>合计</t>
   </si>
   <si>
     <t>政企</t>
@@ -198,15 +198,21 @@
     <t>高套目标</t>
   </si>
   <si>
-    <t>高套发展数</t>
-  </si>
-  <si>
-    <t>积分激励</t>
+    <t>高套发展</t>
   </si>
   <si>
     <t>协同CP发展的主从网关数</t>
   </si>
   <si>
+    <t>区县</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>完成</t>
+  </si>
+  <si>
     <t>智云工程师</t>
   </si>
   <si>
@@ -216,13 +222,40 @@
     <t>何而恒</t>
   </si>
   <si>
+    <t>高要</t>
+  </si>
+  <si>
     <t>魏垚晖</t>
   </si>
   <si>
+    <t>四会</t>
+  </si>
+  <si>
     <t>吴文懿</t>
   </si>
   <si>
-    <t>合计</t>
+    <t>怀集</t>
+  </si>
+  <si>
+    <t>德庆</t>
+  </si>
+  <si>
+    <t>广宁</t>
+  </si>
+  <si>
+    <t>封开</t>
+  </si>
+  <si>
+    <t>鼎湖</t>
+  </si>
+  <si>
+    <t>高新</t>
+  </si>
+  <si>
+    <t>合　计</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>王洪明(挂整体指标)</t>
@@ -280,14 +313,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
+    <numFmt numFmtId="177" formatCode="0.0%"/>
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="47">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -362,6 +397,13 @@
     </font>
     <font>
       <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
@@ -400,9 +442,28 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -590,7 +651,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="58">
+  <fills count="61">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,6 +702,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF3A7EC8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -672,6 +739,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDEEAF1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6E4F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF3FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -934,7 +1013,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="60">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -1279,6 +1358,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF1F3864"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FF2E75B6"/>
       </left>
@@ -1303,6 +1395,19 @@
       </top>
       <bottom style="thin">
         <color rgb="FF2E75B6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBDD7EE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBDD7EE"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBDD7EE"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1375,6 +1480,51 @@
       </top>
       <bottom style="thin">
         <color rgb="FFAABDD6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF4472C4"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4472C4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF4472C4"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F3864"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF4472C4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1717,137 +1867,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="52">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="53">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="53">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="57">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="54">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="55">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="29" borderId="56">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="58">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="55">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="58">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="30" borderId="57">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="59">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="58">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="59">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="60">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="61">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="60">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="62">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="63">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="64">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="43" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="44" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="40" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="41" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="42" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="43" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="44" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="42" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="45" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="43" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="46" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="44" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="47" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="45" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="48" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="46" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="49" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="47" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="50" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="48" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="51" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="49" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="52" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="50" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="53" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="51" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="54" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="52" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="55" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="53" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="56" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="54" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="57" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="55" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="45" fillId="56" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="57" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="58" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="59" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="60" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1962,7 +2112,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2018,146 +2168,185 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="17" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="18" fillId="18" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="21" fillId="9" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2212,7 +2401,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="33">
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -2237,6 +2426,12 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFC00000"/>
+      </font>
     </dxf>
     <dxf>
       <alignment vertical="center"/>
@@ -2455,25 +2650,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="21"/>
-      <tableStyleElement type="headerRow" dxfId="20"/>
-      <tableStyleElement type="totalRow" dxfId="19"/>
-      <tableStyleElement type="firstColumn" dxfId="18"/>
-      <tableStyleElement type="lastColumn" dxfId="17"/>
-      <tableStyleElement type="firstRowStripe" dxfId="16"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="15"/>
+      <tableStyleElement type="wholeTable" dxfId="22"/>
+      <tableStyleElement type="headerRow" dxfId="21"/>
+      <tableStyleElement type="totalRow" dxfId="20"/>
+      <tableStyleElement type="firstColumn" dxfId="19"/>
+      <tableStyleElement type="lastColumn" dxfId="18"/>
+      <tableStyleElement type="firstRowStripe" dxfId="17"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="31"/>
-      <tableStyleElement type="totalRow" dxfId="30"/>
-      <tableStyleElement type="firstRowStripe" dxfId="29"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="28"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="27"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="26"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="25"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="24"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="23"/>
-      <tableStyleElement type="pageFieldValues" dxfId="22"/>
+      <tableStyleElement type="headerRow" dxfId="32"/>
+      <tableStyleElement type="totalRow" dxfId="31"/>
+      <tableStyleElement type="firstRowStripe" dxfId="30"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="29"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="28"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="27"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="26"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="25"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="24"/>
+      <tableStyleElement type="pageFieldValues" dxfId="23"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2530,10 +2725,10 @@
     <sortCondition ref="H1:H2" descending="1"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" name="客户经理" dataDxfId="7"/>
-    <tableColumn id="2" name="户数" dataDxfId="8"/>
-    <tableColumn id="3" name="高套累计数" dataDxfId="9"/>
-    <tableColumn id="4" name="积分累计数" dataDxfId="10"/>
+    <tableColumn id="1" name="客户经理" dataDxfId="8"/>
+    <tableColumn id="2" name="户数" dataDxfId="9"/>
+    <tableColumn id="3" name="高套累计数" dataDxfId="10"/>
+    <tableColumn id="4" name="积分累计数" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2545,10 +2740,10 @@
     <sortCondition ref="C1:C15" descending="1"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" name="客户经理" dataDxfId="11"/>
-    <tableColumn id="2" name="户数" dataDxfId="12"/>
-    <tableColumn id="3" name="高套累计数" dataDxfId="13"/>
-    <tableColumn id="4" name="积分累计数" dataDxfId="14"/>
+    <tableColumn id="1" name="客户经理" dataDxfId="12"/>
+    <tableColumn id="2" name="户数" dataDxfId="13"/>
+    <tableColumn id="3" name="高套累计数" dataDxfId="14"/>
+    <tableColumn id="4" name="积分累计数" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2821,7 +3016,7 @@
       </c>
       <c r="B1" s="13" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至5月7日）</v>
+        <v>完美一单积分完成通报（截至5月18日）</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -2923,7 +3118,7 @@
         <v>20</v>
       </c>
       <c r="C4" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="20">
         <f>_xlfn.XLOOKUP(B4,高套!A:A,高套!B:B,0)</f>
@@ -2950,23 +3145,23 @@
       </c>
       <c r="J4" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K4" s="22">
         <f ca="1" t="shared" ref="K4:K20" si="2">J4/I4</f>
-        <v>0</v>
+        <v>0.0116</v>
       </c>
       <c r="L4" s="22">
         <f ca="1">J4/(I4/W5*T$5)</f>
-        <v>0</v>
+        <v>0.0199777777777778</v>
       </c>
       <c r="M4" s="24">
         <f ca="1" t="shared" ref="M4:M10" si="3">VLOOKUP(B:B,U:W,3,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N4" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>43.5</v>
       </c>
       <c r="O4" s="20">
         <v>21</v>
@@ -2986,7 +3181,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="20">
         <f>_xlfn.XLOOKUP(B5,高套!A:A,高套!B:B,0)</f>
@@ -3002,7 +3197,7 @@
       </c>
       <c r="G5" s="19">
         <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H5" s="27" t="str">
         <f t="shared" si="1"/>
@@ -3013,15 +3208,15 @@
       </c>
       <c r="J5" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>81.93</v>
+        <v>532.59</v>
       </c>
       <c r="K5" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.032772</v>
+        <v>0.213036</v>
       </c>
       <c r="L5" s="22">
         <f ca="1">J5/(I5/W5*T$5)</f>
-        <v>0.145133142857143</v>
+        <v>0.366895333333333</v>
       </c>
       <c r="M5" s="24">
         <f ca="1" t="shared" si="3"/>
@@ -3029,7 +3224,7 @@
       </c>
       <c r="N5" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>122.895</v>
+        <v>98.895</v>
       </c>
       <c r="O5" s="20">
         <v>21</v>
@@ -3048,7 +3243,7 @@
       </c>
       <c r="T5" s="28">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="U5" s="28"/>
       <c r="V5" s="29"/>
@@ -3063,7 +3258,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="20">
         <f>_xlfn.XLOOKUP(B6,高套!A:A,高套!B:B,0)</f>
@@ -3079,7 +3274,7 @@
       </c>
       <c r="G6" s="19">
         <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H6" s="27" t="str">
         <f t="shared" si="1"/>
@@ -3090,23 +3285,23 @@
       </c>
       <c r="J6" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>282</v>
+        <v>251.98</v>
       </c>
       <c r="K6" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.1128</v>
+        <v>0.100792</v>
       </c>
       <c r="L6" s="22">
         <f ca="1">J6/(I6/W5*T$5)</f>
-        <v>0.499542857142857</v>
+        <v>0.173586222222222</v>
       </c>
       <c r="M6" s="24">
         <f ca="1" t="shared" si="3"/>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N6" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>366</v>
+        <v>507</v>
       </c>
       <c r="O6" s="20">
         <v>21</v>
@@ -3126,23 +3321,23 @@
         <v>23</v>
       </c>
       <c r="C7" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="20">
         <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F7" s="22">
         <f ca="1">D7/(C7/W5*T$5)</f>
-        <v>0</v>
+        <v>0.172222222222222</v>
       </c>
       <c r="G7" s="19">
         <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="H7" s="27" t="str">
         <f t="shared" si="1"/>
@@ -3153,23 +3348,23 @@
       </c>
       <c r="J7" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>-1</v>
+        <v>598.6</v>
       </c>
       <c r="K7" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>-0.0004</v>
+        <v>0.23944</v>
       </c>
       <c r="L7" s="22">
         <f ca="1">J7/(I7/W5*T$5)</f>
-        <v>-0.00177142857142857</v>
+        <v>0.412368888888889</v>
       </c>
       <c r="M7" s="24">
         <f ca="1" t="shared" si="3"/>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="N7" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>-1.5</v>
+        <v>1317.9</v>
       </c>
       <c r="O7" s="20">
         <v>21</v>
@@ -3189,61 +3384,61 @@
         <v>24</v>
       </c>
       <c r="C8" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="20">
         <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E8" s="21">
         <f t="shared" si="0"/>
-        <v>0.113636363636364</v>
+        <v>0.8</v>
       </c>
       <c r="F8" s="22">
         <f ca="1">D8/(C8/W5*T$5)</f>
-        <v>0.503246753246753</v>
+        <v>1.37777777777778</v>
       </c>
       <c r="G8" s="19">
         <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H8" s="27" t="str">
         <f t="shared" si="1"/>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="I8" s="19">
         <v>2500</v>
       </c>
       <c r="J8" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>479</v>
+        <v>889</v>
       </c>
       <c r="K8" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.1916</v>
+        <v>0.3556</v>
       </c>
       <c r="L8" s="22">
         <f ca="1">J8/(I8/W5*T$5)</f>
-        <v>0.848514285714286</v>
+        <v>0.612422222222222</v>
       </c>
       <c r="M8" s="24">
         <f ca="1" t="shared" si="3"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N8" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>698.5</v>
+        <v>2530.5</v>
       </c>
       <c r="O8" s="20">
         <v>21</v>
       </c>
       <c r="P8" s="25">
         <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q8" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.619047619047619</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:23">
@@ -3252,7 +3447,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D9" s="20">
         <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
@@ -3268,7 +3463,7 @@
       </c>
       <c r="G9" s="19">
         <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="H9" s="27" t="str">
         <f t="shared" si="1"/>
@@ -3279,23 +3474,23 @@
       </c>
       <c r="J9" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1010</v>
+        <v>1472.81</v>
       </c>
       <c r="K9" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.404</v>
+        <v>0.589124</v>
       </c>
       <c r="L9" s="22">
         <f ca="1">J9/(I9/W5*T$5)</f>
-        <v>1.78914285714286</v>
+        <v>1.01460244444444</v>
       </c>
       <c r="M9" s="24">
         <f ca="1" t="shared" si="3"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N9" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>3015</v>
+        <v>4078.5</v>
       </c>
       <c r="O9" s="20">
         <v>21</v>
@@ -3313,11 +3508,11 @@
       </c>
       <c r="V9">
         <f ca="1" t="shared" ref="V9:V22" si="5">VLOOKUP(U:U,B:J,9,0)</f>
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="W9">
         <f ca="1" t="shared" ref="W9:W22" si="6">RANK(V9,V$9:V$22,0)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:23">
@@ -3326,7 +3521,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="20">
         <f>_xlfn.XLOOKUP(B10,高套!A:A,高套!B:B,0)</f>
@@ -3342,34 +3537,34 @@
       </c>
       <c r="G10" s="19">
         <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="H10" s="27" t="str">
         <f t="shared" si="1"/>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="I10" s="19">
         <v>2500</v>
       </c>
       <c r="J10" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>49</v>
+        <v>668</v>
       </c>
       <c r="K10" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.0196</v>
+        <v>0.2672</v>
       </c>
       <c r="L10" s="22">
         <f ca="1">J10/(I10/W5*T$5)</f>
-        <v>0.0868</v>
+        <v>0.460177777777778</v>
       </c>
       <c r="M10" s="24">
         <f ca="1" t="shared" si="3"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N10" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>173.5</v>
+        <v>1800.5</v>
       </c>
       <c r="O10" s="20">
         <v>21</v>
@@ -3387,7 +3582,7 @@
       </c>
       <c r="V10">
         <f ca="1" t="shared" si="5"/>
-        <v>81.93</v>
+        <v>532.59</v>
       </c>
       <c r="W10">
         <f ca="1" t="shared" si="6"/>
@@ -3401,23 +3596,23 @@
       </c>
       <c r="C11" s="31">
         <f>SUM(C4:C10)</f>
-        <v>61.6</v>
+        <v>70</v>
       </c>
       <c r="D11" s="31">
         <f>SUM(D4:D10)</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E11" s="32">
         <f t="shared" si="0"/>
-        <v>0.0162337662337662</v>
+        <v>0.128571428571429</v>
       </c>
       <c r="F11" s="32">
         <f ca="1">D11/(C11/W5*T$5)</f>
-        <v>0.0718923933209648</v>
+        <v>0.221428571428571</v>
       </c>
       <c r="G11" s="31">
         <f>SUM(G4:G10)</f>
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="33">
@@ -3426,15 +3621,15 @@
       </c>
       <c r="J11" s="31">
         <f ca="1">SUM(J4:J10)</f>
-        <v>1900.93</v>
+        <v>4441.98</v>
       </c>
       <c r="K11" s="32">
         <f ca="1" t="shared" si="2"/>
-        <v>0.108624571428571</v>
+        <v>0.253827428571429</v>
       </c>
       <c r="L11" s="32">
         <f ca="1">J11/(I11/W5*T$5)</f>
-        <v>0.481051673469388</v>
+        <v>0.437147238095238</v>
       </c>
       <c r="M11" s="31"/>
       <c r="N11" s="33"/>
@@ -3444,22 +3639,22 @@
       </c>
       <c r="P11" s="31">
         <f>SUM(P4:P10)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q11" s="34">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.0884353741496599</v>
       </c>
       <c r="U11" s="30" t="s">
         <v>22</v>
       </c>
       <c r="V11">
         <f ca="1" t="shared" si="5"/>
-        <v>282</v>
+        <v>251.98</v>
       </c>
       <c r="W11">
         <f ca="1" t="shared" si="6"/>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:23">
@@ -3470,7 +3665,7 @@
         <v>29</v>
       </c>
       <c r="C12" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D12" s="20">
         <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
@@ -3509,10 +3704,10 @@
       </c>
       <c r="M12" s="24">
         <f ca="1" t="shared" ref="M12:M18" si="8">VLOOKUP(B:B,U:W,3,0)</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N12" s="24">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="O12" s="20">
@@ -3531,11 +3726,11 @@
       </c>
       <c r="V12">
         <f ca="1" t="shared" si="5"/>
-        <v>-1</v>
+        <v>598.6</v>
       </c>
       <c r="W12">
         <f ca="1" t="shared" si="6"/>
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:23">
@@ -3544,23 +3739,23 @@
         <v>30</v>
       </c>
       <c r="C13" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D13" s="20">
         <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
-        <v>4.73</v>
+        <v>16.98</v>
       </c>
       <c r="E13" s="21">
         <f t="shared" si="0"/>
-        <v>0.5375</v>
+        <v>1.698</v>
       </c>
       <c r="F13" s="22">
         <f ca="1">D13/(C13/W5*T$5)</f>
-        <v>2.38035714285714</v>
+        <v>2.92433333333333</v>
       </c>
       <c r="G13" s="19">
         <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>4.73</v>
+        <v>18.98</v>
       </c>
       <c r="H13" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3571,45 +3766,45 @@
       </c>
       <c r="J13" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>806.2</v>
+        <v>2618.2</v>
       </c>
       <c r="K13" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.32248</v>
+        <v>1.04728</v>
       </c>
       <c r="L13" s="22">
         <f ca="1">J13/(I13/W5*T$5)</f>
-        <v>1.42812571428571</v>
+        <v>1.80364888888889</v>
       </c>
       <c r="M13" s="24">
         <f ca="1" t="shared" si="8"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" s="24">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
-        <v>1189.3</v>
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>4867.3</v>
       </c>
       <c r="O13" s="20">
         <v>21</v>
       </c>
       <c r="P13" s="25">
         <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Q13" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.857142857142857</v>
       </c>
       <c r="U13" s="30" t="s">
         <v>24</v>
       </c>
       <c r="V13">
         <f ca="1" t="shared" si="5"/>
-        <v>479</v>
+        <v>889</v>
       </c>
       <c r="W13">
         <f ca="1" t="shared" si="6"/>
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:23">
@@ -3618,19 +3813,19 @@
         <v>31</v>
       </c>
       <c r="C14" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="20">
         <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="E14" s="21">
         <f t="shared" si="0"/>
-        <v>0.227272727272727</v>
+        <v>0.45</v>
       </c>
       <c r="F14" s="22">
         <f ca="1">D14/(C14/W5*T$5)</f>
-        <v>1.00649350649351</v>
+        <v>0.775</v>
       </c>
       <c r="G14" s="19">
         <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3645,23 +3840,23 @@
       </c>
       <c r="J14" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>799</v>
+        <v>828</v>
       </c>
       <c r="K14" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.3196</v>
+        <v>0.3312</v>
       </c>
       <c r="L14" s="22">
         <f ca="1">J14/(I14/W5*T$5)</f>
-        <v>1.41537142857143</v>
+        <v>0.5704</v>
       </c>
       <c r="M14" s="24">
         <f ca="1" t="shared" si="8"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N14" s="24">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
-        <v>2375.5</v>
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>2439</v>
       </c>
       <c r="O14" s="20">
         <v>21</v>
@@ -3679,11 +3874,11 @@
       </c>
       <c r="V14">
         <f ca="1" t="shared" si="5"/>
-        <v>1010</v>
+        <v>1472.81</v>
       </c>
       <c r="W14">
         <f ca="1" t="shared" si="6"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:23">
@@ -3692,23 +3887,23 @@
         <v>32</v>
       </c>
       <c r="C15" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D15" s="20">
         <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="E15" s="21">
         <f t="shared" si="0"/>
-        <v>0.568181818181818</v>
+        <v>1.25</v>
       </c>
       <c r="F15" s="22">
         <f ca="1">D15/(C15/W5*T$5)</f>
-        <v>2.51623376623377</v>
+        <v>2.15277777777778</v>
       </c>
       <c r="G15" s="19">
         <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H15" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3719,45 +3914,45 @@
       </c>
       <c r="J15" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2583</v>
+        <v>3760</v>
       </c>
       <c r="K15" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>1.0332</v>
+        <v>1.504</v>
       </c>
       <c r="L15" s="22">
         <f ca="1">J15/(I15/W5*T$5)</f>
-        <v>4.5756</v>
+        <v>2.59022222222222</v>
       </c>
       <c r="M15" s="24">
         <f ca="1" t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="N15" s="24">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
-        <v>6071.5</v>
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>8612</v>
       </c>
       <c r="O15" s="20">
         <v>21</v>
       </c>
       <c r="P15" s="25">
         <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="26">
         <f t="shared" si="4"/>
-        <v>0.238095238095238</v>
+        <v>0.380952380952381</v>
       </c>
       <c r="U15" s="30" t="s">
         <v>26</v>
       </c>
       <c r="V15">
         <f ca="1" t="shared" si="5"/>
-        <v>49</v>
+        <v>668</v>
       </c>
       <c r="W15">
         <f ca="1" t="shared" si="6"/>
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:23">
@@ -3766,23 +3961,23 @@
         <v>33</v>
       </c>
       <c r="C16" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="20">
         <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="E16" s="21">
         <f t="shared" si="0"/>
-        <v>0.852272727272727</v>
+        <v>1.4</v>
       </c>
       <c r="F16" s="22">
         <f ca="1">D16/(C16/W5*T$5)</f>
-        <v>3.77435064935065</v>
+        <v>2.41111111111111</v>
       </c>
       <c r="G16" s="19">
         <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="H16" s="27" t="str">
         <f t="shared" si="7"/>
@@ -3793,34 +3988,34 @@
       </c>
       <c r="J16" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>741.16</v>
+        <v>2137.65</v>
       </c>
       <c r="K16" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.296464</v>
+        <v>0.85506</v>
       </c>
       <c r="L16" s="22">
         <f ca="1">J16/(I16/W5*T$5)</f>
-        <v>1.312912</v>
+        <v>1.47260333333333</v>
       </c>
       <c r="M16" s="24">
         <f ca="1" t="shared" si="8"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N16" s="24">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
-        <v>2993.74</v>
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>6818.105</v>
       </c>
       <c r="O16" s="20">
         <v>21</v>
       </c>
       <c r="P16" s="25">
         <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q16" s="26">
         <f t="shared" si="4"/>
-        <v>0.285714285714286</v>
+        <v>0.761904761904762</v>
       </c>
       <c r="U16" s="30" t="s">
         <v>29</v>
@@ -3831,7 +4026,7 @@
       </c>
       <c r="W16">
         <f ca="1" t="shared" si="6"/>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:23">
@@ -3840,7 +4035,7 @@
         <v>34</v>
       </c>
       <c r="C17" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D17" s="20">
         <f>_xlfn.XLOOKUP(B17,高套!A:A,高套!B:B,0)</f>
@@ -3848,11 +4043,11 @@
       </c>
       <c r="E17" s="21">
         <f t="shared" si="0"/>
-        <v>0.340909090909091</v>
+        <v>0.3</v>
       </c>
       <c r="F17" s="22">
         <f ca="1">D17/(C17/W5*T$5)</f>
-        <v>1.50974025974026</v>
+        <v>0.516666666666667</v>
       </c>
       <c r="G17" s="19">
         <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3867,45 +4062,45 @@
       </c>
       <c r="J17" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="K17" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>0.0864</v>
+        <v>0.1184</v>
       </c>
       <c r="L17" s="22">
         <f ca="1">J17/(I17/W5*T$5)</f>
-        <v>0.382628571428571</v>
+        <v>0.203911111111111</v>
       </c>
       <c r="M17" s="24">
         <f ca="1" t="shared" si="8"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N17" s="24">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
-        <v>304</v>
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>1524</v>
       </c>
       <c r="O17" s="20">
         <v>21</v>
       </c>
       <c r="P17" s="25">
         <f>_xlfn.XLOOKUP(B17,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q17" s="26">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="U17" s="30" t="s">
         <v>30</v>
       </c>
       <c r="V17">
         <f ca="1" t="shared" si="5"/>
-        <v>806.2</v>
+        <v>2618.2</v>
       </c>
       <c r="W17">
         <f ca="1" t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:23">
@@ -3914,50 +4109,50 @@
         <v>35</v>
       </c>
       <c r="C18" s="19">
-        <v>8.8</v>
+        <v>10</v>
       </c>
       <c r="D18" s="20">
         <f>_xlfn.XLOOKUP(B18,高套!A:A,高套!B:B,0)</f>
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="E18" s="21">
         <f t="shared" si="0"/>
-        <v>0.170454545454545</v>
+        <v>0.35</v>
       </c>
       <c r="F18" s="22">
         <f ca="1">D18/(C18/W5*T$5)</f>
-        <v>0.75487012987013</v>
+        <v>0.602777777777778</v>
       </c>
       <c r="G18" s="19">
         <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="H18" s="27" t="str">
         <f t="shared" si="7"/>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="I18" s="19">
         <v>2500</v>
       </c>
       <c r="J18" s="19">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>-552.05</v>
+        <v>-226.05</v>
       </c>
       <c r="K18" s="22">
         <f ca="1" t="shared" si="2"/>
-        <v>-0.22082</v>
+        <v>-0.09042</v>
       </c>
       <c r="L18" s="22">
         <f ca="1">J18/(I18/W5*T$5)</f>
-        <v>-0.977917142857143</v>
+        <v>-0.155723333333333</v>
       </c>
       <c r="M18" s="24">
         <f ca="1" t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="N18" s="24">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
-        <v>-848.075</v>
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>-339.075</v>
       </c>
       <c r="O18" s="20">
         <v>21</v>
@@ -3975,11 +4170,11 @@
       </c>
       <c r="V18">
         <f ca="1" t="shared" si="5"/>
-        <v>799</v>
+        <v>828</v>
       </c>
       <c r="W18">
         <f ca="1" t="shared" si="6"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:23">
@@ -3989,23 +4184,23 @@
       </c>
       <c r="C19" s="37">
         <f>SUM(C12:C18)</f>
-        <v>61.6</v>
+        <v>70</v>
       </c>
       <c r="D19" s="37">
         <f>SUM(D12:D18)</f>
-        <v>23.73</v>
+        <v>54.48</v>
       </c>
       <c r="E19" s="38">
         <f t="shared" si="0"/>
-        <v>0.385227272727273</v>
+        <v>0.778285714285714</v>
       </c>
       <c r="F19" s="32">
         <f ca="1">D19/(C19/W5*T$5)</f>
-        <v>1.70600649350649</v>
+        <v>1.34038095238095</v>
       </c>
       <c r="G19" s="37">
         <f>SUM(G12:G18)</f>
-        <v>30.23</v>
+        <v>58.98</v>
       </c>
       <c r="H19" s="38"/>
       <c r="I19" s="39">
@@ -4014,15 +4209,15 @@
       </c>
       <c r="J19" s="37">
         <f ca="1">SUM(J12:J18)</f>
-        <v>4593.31</v>
+        <v>9413.8</v>
       </c>
       <c r="K19" s="38">
         <f ca="1" t="shared" si="2"/>
-        <v>0.262474857142857</v>
+        <v>0.537931428571429</v>
       </c>
       <c r="L19" s="38">
         <f ca="1">J19/(I19/W5*T$5)</f>
-        <v>1.16238865306122</v>
+        <v>0.926437460317461</v>
       </c>
       <c r="M19" s="37"/>
       <c r="N19" s="39"/>
@@ -4032,18 +4227,18 @@
       </c>
       <c r="P19" s="37">
         <f>SUM(P12:P18)</f>
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="Q19" s="34">
         <f t="shared" si="4"/>
-        <v>0.136054421768707</v>
+        <v>0.36734693877551</v>
       </c>
       <c r="U19" s="30" t="s">
         <v>32</v>
       </c>
       <c r="V19">
         <f ca="1" t="shared" si="5"/>
-        <v>2583</v>
+        <v>3760</v>
       </c>
       <c r="W19">
         <f ca="1" t="shared" si="6"/>
@@ -4059,20 +4254,20 @@
         <v>132</v>
       </c>
       <c r="D20" s="43">
-        <f>D11+D19</f>
-        <v>24.73</v>
+        <f>_xlfn.XLOOKUP("端州",高套!A:A,高套!B:B,0)</f>
+        <v>64.98</v>
       </c>
       <c r="E20" s="44">
         <f t="shared" si="0"/>
-        <v>0.187348484848485</v>
+        <v>0.492272727272727</v>
       </c>
       <c r="F20" s="45">
         <f ca="1">D20/(C20/W5*T$5)</f>
-        <v>0.829686147186147</v>
+        <v>0.84780303030303</v>
       </c>
       <c r="G20" s="46">
         <f>G11+G19</f>
-        <v>40.23</v>
+        <v>80.98</v>
       </c>
       <c r="H20" s="45"/>
       <c r="I20" s="47">
@@ -4081,15 +4276,15 @@
       </c>
       <c r="J20" s="42">
         <f ca="1">J11+J19</f>
-        <v>6494.24</v>
+        <v>13855.78</v>
       </c>
       <c r="K20" s="48">
         <f ca="1" t="shared" si="2"/>
-        <v>0.185549714285714</v>
+        <v>0.395879428571429</v>
       </c>
       <c r="L20" s="49">
         <f ca="1">J20/(I20/W5*T$5)</f>
-        <v>0.821720163265306</v>
+        <v>0.681792349206349</v>
       </c>
       <c r="M20" s="50"/>
       <c r="N20" s="51" t="s">
@@ -4098,22 +4293,22 @@
       <c r="O20" s="52"/>
       <c r="P20" s="53">
         <f>P11+P19</f>
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="Q20" s="26">
         <f>P20/O21</f>
-        <v>0.0645161290322581</v>
+        <v>0.216129032258065</v>
       </c>
       <c r="U20" s="30" t="s">
         <v>33</v>
       </c>
       <c r="V20">
         <f ca="1" t="shared" si="5"/>
-        <v>741.16</v>
+        <v>2137.65</v>
       </c>
       <c r="W20">
         <f ca="1" t="shared" si="6"/>
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:23">
@@ -4138,18 +4333,18 @@
       </c>
       <c r="P21" s="58">
         <f>_xlfn.XLOOKUP(N21,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>40</v>
+        <v>144</v>
       </c>
       <c r="Q21" s="26">
         <f>P21/O21</f>
-        <v>0.129032258064516</v>
+        <v>0.464516129032258</v>
       </c>
       <c r="U21" s="59" t="s">
         <v>35</v>
       </c>
       <c r="V21">
         <f ca="1" t="shared" si="5"/>
-        <v>-552.05</v>
+        <v>-226.05</v>
       </c>
       <c r="W21">
         <f ca="1" t="shared" si="6"/>
@@ -4186,7 +4381,7 @@
         <v>41</v>
       </c>
       <c r="J22" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
       <c r="K22" s="22" t="s">
@@ -4216,11 +4411,11 @@
       </c>
       <c r="V22">
         <f ca="1" t="shared" si="5"/>
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="W22">
         <f ca="1" t="shared" si="6"/>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:23">
@@ -4251,7 +4446,7 @@
         <v>41</v>
       </c>
       <c r="J23" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
       <c r="K23" s="22" t="s">
@@ -4305,7 +4500,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
       <c r="K24" s="22" t="s">
@@ -4350,7 +4545,7 @@
       </c>
       <c r="G25" s="19">
         <f>高装高套!B5</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" s="22" t="s">
         <v>41</v>
@@ -4359,8 +4554,8 @@
         <v>41</v>
       </c>
       <c r="J25" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
-        <v>0</v>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>138.6</v>
       </c>
       <c r="K25" s="22" t="s">
         <v>41</v>
@@ -4373,7 +4568,7 @@
       </c>
       <c r="N25" s="24">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>762.3</v>
       </c>
       <c r="O25" s="20" t="s">
         <v>41</v>
@@ -4413,7 +4608,7 @@
         <v>41</v>
       </c>
       <c r="J26" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
       <c r="K26" s="22" t="s">
@@ -4467,7 +4662,7 @@
         <v>41</v>
       </c>
       <c r="J27" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>239</v>
       </c>
       <c r="K27" s="22" t="s">
@@ -4521,7 +4716,7 @@
         <v>41</v>
       </c>
       <c r="J28" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
       <c r="K28" s="22" t="s">
@@ -4575,7 +4770,7 @@
         <v>41</v>
       </c>
       <c r="J29" s="19">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),完美一单!A:C,3,0)</f>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
       <c r="K29" s="22" t="s">
@@ -4620,7 +4815,7 @@
       </c>
       <c r="G30" s="19">
         <f>SUM(G22:G29)</f>
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="H30" s="22" t="s">
         <v>41</v>
@@ -4630,7 +4825,7 @@
       </c>
       <c r="J30" s="19">
         <f ca="1">SUM(J22:J29)</f>
-        <v>239</v>
+        <v>377.6</v>
       </c>
       <c r="K30" s="22" t="s">
         <v>41</v>
@@ -4661,479 +4856,672 @@
       <c r="J32"/>
       <c r="N32"/>
     </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:14">
+    <row r="33" ht="16.5" customHeight="1" spans="1:19">
       <c r="A33" s="62" t="str">
-        <f ca="1">"高装高套目标完成情况（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>高装高套目标完成情况（截至5月7日）</v>
-      </c>
-      <c r="B33" s="62"/>
-      <c r="C33" s="62"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="62"/>
-      <c r="F33" s="62"/>
+        <f>"高装高套目标完成情况"</f>
+        <v>高装高套目标完成情况</v>
+      </c>
       <c r="G33"/>
       <c r="I33" s="63" t="str">
-        <f ca="1">"全光任务完成情况（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>全光任务完成情况（截至5月7日）</v>
-      </c>
-      <c r="K33" s="11"/>
+        <f>"全光任务完成情况"</f>
+        <v>全光任务完成情况</v>
+      </c>
       <c r="N33"/>
-    </row>
-    <row r="34" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A34" s="64" t="s">
+      <c r="O33" s="64" t="str">
+        <f>"区县目标完成情况"</f>
+        <v>区县目标完成情况</v>
+      </c>
+    </row>
+    <row r="34" ht="33" customHeight="1" spans="1:19">
+      <c r="A34" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="64" t="s">
+      <c r="C34" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="64" t="s">
+      <c r="D34" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="64" t="s">
+      <c r="E34" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="F34" s="64" t="s">
+      <c r="F34" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="G34"/>
+      <c r="I34" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="J34" s="66" t="s">
+        <v>51</v>
+      </c>
+      <c r="K34" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="L34" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="G34"/>
-      <c r="I34" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="J34" s="65" t="s">
-        <v>51</v>
-      </c>
-      <c r="K34" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="L34" s="66" t="s">
+      <c r="M34" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="N34"/>
+      <c r="O34" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="M34" s="65" t="s">
+      <c r="P34" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q34" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="R34" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="N34"/>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A35" s="67" t="s">
+      <c r="S34" s="68" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A35" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="68" t="str">
+      <c r="B35" s="70" t="str">
         <f>高装高套!A2</f>
         <v>陈梓铭</v>
       </c>
-      <c r="C35" s="68">
+      <c r="C35" s="70">
         <v>1</v>
       </c>
-      <c r="D35" s="68">
+      <c r="D35" s="70">
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="E35" s="69">
+      <c r="E35" s="71">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="69">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+      <c r="F35" s="71">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G35"/>
-      <c r="I35" s="70" t="s">
-        <v>56</v>
-      </c>
-      <c r="J35" s="71" t="s">
-        <v>57</v>
-      </c>
-      <c r="K35" s="71">
+      <c r="I35" s="72" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35" s="73" t="s">
+        <v>59</v>
+      </c>
+      <c r="K35" s="73">
         <v>84</v>
       </c>
-      <c r="L35" s="71">
+      <c r="L35" s="73">
         <f>交付高装!D2</f>
-        <v>3</v>
-      </c>
-      <c r="M35" s="72">
+        <v>16</v>
+      </c>
+      <c r="M35" s="74">
         <f>交付高装!E2</f>
-        <v>0.0357142857142857</v>
+        <v>0.19047619047619</v>
       </c>
       <c r="N35"/>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A36" s="73"/>
-      <c r="B36" s="74" t="str">
+      <c r="O35" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" s="76">
+        <v>4.25</v>
+      </c>
+      <c r="Q35" s="76">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O35,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>3.61</v>
+      </c>
+      <c r="R35" s="77">
+        <f ca="1" t="shared" ref="R35:R44" si="9">Q35/P35</f>
+        <v>0.849411764705882</v>
+      </c>
+      <c r="S35" s="78">
+        <f ca="1">RANK(R35,R35:R43)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A36" s="79"/>
+      <c r="B36" s="80" t="str">
         <f>高装高套!A3</f>
         <v>程庆德</v>
       </c>
-      <c r="C36" s="74">
+      <c r="C36" s="80">
         <v>1</v>
       </c>
-      <c r="D36" s="74">
+      <c r="D36" s="80">
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="E36" s="75">
+      <c r="E36" s="81">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="75">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+      <c r="F36" s="81">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G36"/>
-      <c r="I36" s="76"/>
-      <c r="J36" s="71" t="s">
-        <v>58</v>
-      </c>
-      <c r="K36" s="71">
+      <c r="I36" s="82"/>
+      <c r="J36" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="K36" s="73">
         <v>84</v>
       </c>
-      <c r="L36" s="71">
+      <c r="L36" s="73">
         <f>交付高装!D3</f>
-        <v>5</v>
-      </c>
-      <c r="M36" s="72">
+        <v>8</v>
+      </c>
+      <c r="M36" s="74">
         <f>交付高装!E3</f>
-        <v>0.0595238095238095</v>
+        <v>0.0952380952380952</v>
       </c>
       <c r="N36"/>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A37" s="73"/>
-      <c r="B37" s="68" t="str">
+      <c r="O36" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="P36" s="83">
+        <v>5.75</v>
+      </c>
+      <c r="Q36" s="83">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O36,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>4.66</v>
+      </c>
+      <c r="R36" s="77">
+        <f ca="1" t="shared" si="9"/>
+        <v>0.810434782608696</v>
+      </c>
+      <c r="S36" s="84">
+        <f ca="1">RANK(R36,R35:R43)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A37" s="79"/>
+      <c r="B37" s="70" t="str">
         <f>高装高套!A4</f>
         <v>刘奇峻</v>
       </c>
-      <c r="C37" s="68">
+      <c r="C37" s="70">
         <v>1</v>
       </c>
-      <c r="D37" s="68">
+      <c r="D37" s="70">
         <f>高装高套!B4</f>
         <v>0</v>
       </c>
-      <c r="E37" s="69">
+      <c r="E37" s="71">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="69">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+      <c r="F37" s="71">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G37"/>
-      <c r="I37" s="76"/>
-      <c r="J37" s="77" t="s">
-        <v>59</v>
-      </c>
-      <c r="K37" s="71">
+      <c r="I37" s="82"/>
+      <c r="J37" s="85" t="s">
+        <v>62</v>
+      </c>
+      <c r="K37" s="73">
         <v>84</v>
       </c>
-      <c r="L37" s="71">
+      <c r="L37" s="73">
         <f>交付高装!D4</f>
-        <v>6</v>
-      </c>
-      <c r="M37" s="72">
+        <v>34</v>
+      </c>
+      <c r="M37" s="74">
         <f>交付高装!E4</f>
-        <v>0.0714285714285714</v>
+        <v>0.404761904761905</v>
       </c>
       <c r="N37"/>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A38" s="73"/>
-      <c r="B38" s="74" t="str">
+      <c r="O37" s="75" t="s">
+        <v>63</v>
+      </c>
+      <c r="P37" s="76">
+        <v>3.52</v>
+      </c>
+      <c r="Q37" s="76">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O37,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>3.78</v>
+      </c>
+      <c r="R37" s="77">
+        <f ca="1" t="shared" si="9"/>
+        <v>1.07386363636364</v>
+      </c>
+      <c r="S37" s="78">
+        <f ca="1">RANK(R37,R35:R43)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A38" s="79"/>
+      <c r="B38" s="80" t="str">
         <f>高装高套!A5</f>
         <v>龙家宝</v>
       </c>
-      <c r="C38" s="74">
+      <c r="C38" s="80">
         <v>1</v>
       </c>
-      <c r="D38" s="74">
+      <c r="D38" s="80">
         <f>高装高套!B5</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="75">
+        <v>2</v>
+      </c>
+      <c r="E38" s="81">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="75">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>138.6</v>
+      </c>
+      <c r="F38" s="81">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>762.3</v>
       </c>
       <c r="G38"/>
-      <c r="I38" s="76"/>
-      <c r="J38" s="71" t="s">
-        <v>60</v>
-      </c>
-      <c r="K38" s="71">
+      <c r="I38" s="82"/>
+      <c r="J38" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="K38" s="73">
         <v>63</v>
       </c>
-      <c r="L38" s="71">
+      <c r="L38" s="73">
         <f>交付高装!D5</f>
-        <v>6</v>
-      </c>
-      <c r="M38" s="72">
+        <v>9</v>
+      </c>
+      <c r="M38" s="74">
         <f>交付高装!E5</f>
-        <v>0.0983606557377049</v>
+        <v>0.147540983606557</v>
       </c>
       <c r="N38"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A39" s="73"/>
-      <c r="B39" s="68" t="str">
+      <c r="O38" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="P38" s="83">
+        <v>3.97</v>
+      </c>
+      <c r="Q38" s="83">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O38,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>4.54</v>
+      </c>
+      <c r="R38" s="77">
+        <f ca="1" t="shared" si="9"/>
+        <v>1.14357682619647</v>
+      </c>
+      <c r="S38" s="84">
+        <f ca="1">RANK(R38,R35:R43)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A39" s="79"/>
+      <c r="B39" s="70" t="str">
         <f>高装高套!A6</f>
         <v>罗紫杰</v>
       </c>
-      <c r="C39" s="68">
+      <c r="C39" s="70">
         <v>1</v>
       </c>
-      <c r="D39" s="68">
+      <c r="D39" s="70">
         <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="E39" s="69">
+      <c r="E39" s="71">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="69">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+      <c r="F39" s="71">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G39"/>
-      <c r="I39" s="78" t="s">
+      <c r="I39" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="J39" s="79" t="s">
+      <c r="J39" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="K39" s="80">
+      <c r="K39" s="88">
         <v>42</v>
       </c>
-      <c r="L39" s="80">
+      <c r="L39" s="88">
         <f>交付高装!D6</f>
-        <v>0</v>
-      </c>
-      <c r="M39" s="81">
+        <v>8</v>
+      </c>
+      <c r="M39" s="89">
         <f>交付高装!E6</f>
-        <v>0</v>
+        <v>0.19047619047619</v>
       </c>
       <c r="N39"/>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A40" s="73"/>
-      <c r="B40" s="74" t="str">
+      <c r="O39" s="75" t="s">
+        <v>66</v>
+      </c>
+      <c r="P39" s="76">
+        <v>2.38</v>
+      </c>
+      <c r="Q39" s="76">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O39,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>3.94</v>
+      </c>
+      <c r="R39" s="77">
+        <f ca="1" t="shared" si="9"/>
+        <v>1.65546218487395</v>
+      </c>
+      <c r="S39" s="78">
+        <f ca="1">RANK(R39,R35:R43)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A40" s="79"/>
+      <c r="B40" s="80" t="str">
         <f>高装高套!A7</f>
         <v>莫健铭</v>
       </c>
-      <c r="C40" s="74">
+      <c r="C40" s="80">
         <v>1</v>
       </c>
-      <c r="D40" s="74">
+      <c r="D40" s="80">
         <f>高装高套!B7</f>
         <v>1.5</v>
       </c>
-      <c r="E40" s="75">
+      <c r="E40" s="81">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>239</v>
       </c>
-      <c r="F40" s="75">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+      <c r="F40" s="81">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>1075.5</v>
       </c>
       <c r="G40"/>
-      <c r="I40" s="82"/>
-      <c r="J40" s="79" t="s">
+      <c r="I40" s="90"/>
+      <c r="J40" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="K40" s="80">
+      <c r="K40" s="88">
         <v>42</v>
       </c>
-      <c r="L40" s="80">
+      <c r="L40" s="88">
         <f>交付高装!D7</f>
         <v>0</v>
       </c>
-      <c r="M40" s="81">
+      <c r="M40" s="89">
         <f>交付高装!E7</f>
         <v>0</v>
       </c>
       <c r="N40"/>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A41" s="73"/>
-      <c r="B41" s="68" t="str">
+      <c r="O40" s="75" t="s">
+        <v>67</v>
+      </c>
+      <c r="P40" s="91">
+        <v>2.6</v>
+      </c>
+      <c r="Q40" s="91">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O40,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>2.58</v>
+      </c>
+      <c r="R40" s="77">
+        <f ca="1" t="shared" si="9"/>
+        <v>0.992307692307692</v>
+      </c>
+      <c r="S40" s="84">
+        <f ca="1">RANK(R40,R35:R43)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A41" s="79"/>
+      <c r="B41" s="70" t="str">
         <f>高装高套!A8</f>
         <v>吴广仁</v>
       </c>
-      <c r="C41" s="68">
+      <c r="C41" s="70">
         <v>1</v>
       </c>
-      <c r="D41" s="68">
+      <c r="D41" s="70">
         <f>高装高套!B8</f>
         <v>0</v>
       </c>
-      <c r="E41" s="69">
+      <c r="E41" s="71">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="69">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+      <c r="F41" s="71">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G41"/>
-      <c r="I41" s="82"/>
-      <c r="J41" s="79" t="s">
+      <c r="I41" s="90"/>
+      <c r="J41" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="K41" s="80">
+      <c r="K41" s="88">
         <v>42</v>
       </c>
-      <c r="L41" s="80">
+      <c r="L41" s="88">
         <f>交付高装!D8</f>
-        <v>0</v>
-      </c>
-      <c r="M41" s="81">
+        <v>3</v>
+      </c>
+      <c r="M41" s="89">
         <f>交付高装!E8</f>
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="N41"/>
-    </row>
-    <row r="42" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A42" s="83"/>
-      <c r="B42" s="74" t="str">
+      <c r="O41" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="P41" s="76">
+        <v>2.41</v>
+      </c>
+      <c r="Q41" s="76">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O41,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>1.66</v>
+      </c>
+      <c r="R41" s="77">
+        <f ca="1" t="shared" si="9"/>
+        <v>0.688796680497925</v>
+      </c>
+      <c r="S41" s="78">
+        <f ca="1">RANK(R41,R35:R43)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" ht="13.5" customHeight="1" spans="1:19">
+      <c r="A42" s="92"/>
+      <c r="B42" s="80" t="str">
         <f>高装高套!A9</f>
         <v>王洪明</v>
       </c>
-      <c r="C42" s="74">
+      <c r="C42" s="80">
         <v>1</v>
       </c>
-      <c r="D42" s="74">
+      <c r="D42" s="80">
         <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="E42" s="75">
+      <c r="E42" s="81">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="75">
-        <f ca="1">VLOOKUP(_xlfn.SINGLE(B:B),激励!A:B,2,0)</f>
+      <c r="F42" s="81">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G42"/>
-      <c r="I42" s="82"/>
-      <c r="J42" s="79" t="s">
+      <c r="I42" s="90"/>
+      <c r="J42" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="K42" s="80">
+      <c r="K42" s="88">
         <v>42</v>
       </c>
-      <c r="L42" s="80">
+      <c r="L42" s="88">
         <f>交付高装!D9</f>
-        <v>0</v>
-      </c>
-      <c r="M42" s="81">
+        <v>13</v>
+      </c>
+      <c r="M42" s="89">
         <f>交付高装!E9</f>
-        <v>0</v>
+        <v>0.30952380952381</v>
       </c>
       <c r="N42"/>
-    </row>
-    <row r="43" ht="16.5" customHeight="1" spans="1:14">
-      <c r="A43" s="84" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43" s="85"/>
-      <c r="C43" s="84">
-        <f t="shared" ref="C43:F43" si="9">SUM(C35:C42)</f>
+      <c r="O42" s="75" t="s">
+        <v>69</v>
+      </c>
+      <c r="P42" s="83">
+        <v>3.22</v>
+      </c>
+      <c r="Q42" s="83">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O42,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>2.45</v>
+      </c>
+      <c r="R42" s="77">
+        <f ca="1" t="shared" si="9"/>
+        <v>0.760869565217391</v>
+      </c>
+      <c r="S42" s="84">
+        <f ca="1">RANK(R42,R35:R43)</f>
         <v>8</v>
       </c>
-      <c r="D43" s="84">
-        <f t="shared" si="9"/>
-        <v>1.5</v>
-      </c>
-      <c r="E43" s="84">
+    </row>
+    <row r="43" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A43" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="94"/>
+      <c r="C43" s="93">
+        <f>SUM(C35:C42)</f>
+        <v>8</v>
+      </c>
+      <c r="D43" s="93">
+        <f>SUM(D35:D42)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E43" s="93">
+        <f ca="1">SUM(E35:E42)</f>
+        <v>377.6</v>
+      </c>
+      <c r="F43" s="93" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43"/>
+      <c r="I43" s="90"/>
+      <c r="J43" s="87" t="s">
+        <v>45</v>
+      </c>
+      <c r="K43" s="88">
+        <v>42</v>
+      </c>
+      <c r="L43" s="88">
+        <f>交付高装!D10</f>
+        <v>18</v>
+      </c>
+      <c r="M43" s="89">
+        <f>交付高装!E10</f>
+        <v>0.428571428571429</v>
+      </c>
+      <c r="N43"/>
+      <c r="O43" s="75" t="s">
+        <v>70</v>
+      </c>
+      <c r="P43" s="76">
+        <v>3.36</v>
+      </c>
+      <c r="Q43" s="76">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(O43,高套!A:A,高套!B:B,0)/T5,2)</f>
+        <v>2.74</v>
+      </c>
+      <c r="R43" s="77">
         <f ca="1" t="shared" si="9"/>
-        <v>239</v>
-      </c>
-      <c r="F43" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43"/>
-      <c r="I43" s="82"/>
-      <c r="J43" s="79" t="s">
-        <v>45</v>
-      </c>
-      <c r="K43" s="80">
-        <v>42</v>
-      </c>
-      <c r="L43" s="80">
-        <f>交付高装!D10</f>
-        <v>0</v>
-      </c>
-      <c r="M43" s="81">
-        <f>交付高装!E10</f>
-        <v>0</v>
-      </c>
-      <c r="N43"/>
-    </row>
-    <row r="44" spans="1:14">
+        <v>0.815476190476191</v>
+      </c>
+      <c r="S43" s="78">
+        <f ca="1">RANK(R43,R35:R43)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" ht="14.75" customHeight="1" spans="1:19">
       <c r="F44"/>
       <c r="G44"/>
-      <c r="I44" s="82"/>
-      <c r="J44" s="79" t="s">
+      <c r="I44" s="90"/>
+      <c r="J44" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="K44" s="80">
+      <c r="K44" s="88">
         <v>42</v>
       </c>
-      <c r="L44" s="80">
+      <c r="L44" s="88">
         <f>交付高装!D11</f>
-        <v>0</v>
-      </c>
-      <c r="M44" s="81">
+        <v>16</v>
+      </c>
+      <c r="M44" s="89">
         <f>交付高装!E11</f>
-        <v>0</v>
+        <v>0.380952380952381</v>
       </c>
       <c r="N44"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1" spans="1:14">
+      <c r="O44" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="P44" s="96">
+        <f>SUM(P35:P43)</f>
+        <v>31.46</v>
+      </c>
+      <c r="Q44" s="96">
+        <f ca="1">SUM(Q35:Q43)</f>
+        <v>29.96</v>
+      </c>
+      <c r="R44" s="97">
+        <f ca="1" t="shared" si="9"/>
+        <v>0.952320406865862</v>
+      </c>
+      <c r="S44" s="98" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" ht="13.5" customHeight="1" spans="1:19">
       <c r="F45"/>
       <c r="G45"/>
-      <c r="I45" s="82"/>
-      <c r="J45" s="79" t="s">
+      <c r="I45" s="90"/>
+      <c r="J45" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="K45" s="80">
+      <c r="K45" s="88">
         <v>42</v>
       </c>
-      <c r="L45" s="80">
+      <c r="L45" s="88">
         <f>交付高装!D12</f>
-        <v>0</v>
-      </c>
-      <c r="M45" s="81">
+        <v>9</v>
+      </c>
+      <c r="M45" s="89">
         <f>交付高装!E12</f>
-        <v>0</v>
+        <v>0.214285714285714</v>
       </c>
       <c r="N45"/>
     </row>
-    <row r="46" ht="13.5" customHeight="1" spans="1:14">
+    <row r="46" ht="13.5" customHeight="1" spans="1:19">
       <c r="F46"/>
       <c r="G46"/>
-      <c r="I46" s="86"/>
-      <c r="J46" s="87" t="s">
-        <v>62</v>
-      </c>
-      <c r="K46" s="80">
+      <c r="I46" s="99"/>
+      <c r="J46" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="K46" s="88">
         <v>310</v>
       </c>
-      <c r="L46" s="80">
+      <c r="L46" s="88">
         <f>SUM(L35:L38)</f>
-        <v>20</v>
-      </c>
-      <c r="M46" s="81">
+        <v>67</v>
+      </c>
+      <c r="M46" s="89">
         <f>L46/K46</f>
-        <v>0.0645161290322581</v>
+        <v>0.216129032258065</v>
       </c>
       <c r="N46"/>
     </row>
     <row r="47" ht="13.5" customHeight="1"/>
-    <row r="48" ht="13.5" customHeight="1" spans="1:14">
+    <row r="48" ht="13.5" customHeight="1" spans="1:19">
       <c r="F48"/>
       <c r="G48"/>
       <c r="I48"/>
@@ -5141,30 +5529,30 @@
       <c r="N48"/>
     </row>
     <row r="49" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A49" s="88" t="str">
+      <c r="A49" s="101" t="str">
         <f ca="1">""&amp;MONTH(TODAY())&amp;"月份商机统计表（预计转化时间为"&amp;MONTH(TODAY())&amp;"月）"</f>
         <v>5月份商机统计表（预计转化时间为5月）</v>
       </c>
-      <c r="B49" s="89"/>
-      <c r="C49" s="89"/>
-      <c r="D49" s="90"/>
+      <c r="B49" s="102"/>
+      <c r="C49" s="102"/>
+      <c r="D49" s="103"/>
       <c r="F49"/>
-      <c r="G49" s="91" t="s">
-        <v>63</v>
+      <c r="G49" s="104" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="50" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A50" s="92" t="str">
+      <c r="A50" s="105" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止5月7日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
-      </c>
-      <c r="B50" s="93"/>
-      <c r="C50" s="93"/>
-      <c r="D50" s="94"/>
+        <v>（数据截止5月18日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+      </c>
+      <c r="B50" s="106"/>
+      <c r="C50" s="106"/>
+      <c r="D50" s="107"/>
       <c r="F50"/>
-      <c r="G50" s="95" t="str">
+      <c r="G50" s="108" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止5月7日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+        <v>（数据截止5月18日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
       </c>
     </row>
     <row r="51" ht="14.75" customHeight="1" spans="1:14">
@@ -5172,556 +5560,556 @@
         <v>4</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F51"/>
-      <c r="G51" s="96" t="s">
+      <c r="G51" s="109" t="s">
         <v>4</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="I51" s="97" t="s">
-        <v>65</v>
-      </c>
-      <c r="J51" s="98" t="s">
-        <v>66</v>
+        <v>75</v>
+      </c>
+      <c r="I51" s="110" t="s">
+        <v>76</v>
+      </c>
+      <c r="J51" s="111" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="99" t="str">
+      <c r="A52" s="112" t="str">
         <f>商机统计!A2</f>
         <v>谢卓和</v>
       </c>
-      <c r="B52" s="100">
+      <c r="B52" s="113">
         <f>商机统计!B2</f>
         <v>14</v>
       </c>
-      <c r="C52" s="100">
+      <c r="C52" s="113">
         <f>商机统计!C2</f>
         <v>47.5</v>
       </c>
-      <c r="D52" s="101">
+      <c r="D52" s="114">
         <f>商机统计!D2</f>
         <v>5190</v>
       </c>
       <c r="F52"/>
-      <c r="G52" s="99" t="str">
+      <c r="G52" s="112" t="str">
         <f>商机统计!F2</f>
         <v>谢卓和</v>
       </c>
-      <c r="H52" s="100">
+      <c r="H52" s="113">
         <f>商机统计!G2</f>
         <v>17</v>
       </c>
-      <c r="I52" s="100">
+      <c r="I52" s="113">
         <f>商机统计!H2</f>
         <v>60.5</v>
       </c>
-      <c r="J52" s="101">
+      <c r="J52" s="114">
         <f>商机统计!I2</f>
         <v>6798</v>
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="102" t="str">
+      <c r="A53" s="115" t="str">
         <f>商机统计!A3</f>
         <v>黄淡妮</v>
       </c>
-      <c r="B53" s="103">
+      <c r="B53" s="116">
         <f>商机统计!B3</f>
         <v>10</v>
       </c>
-      <c r="C53" s="103">
+      <c r="C53" s="116">
         <f>商机统计!C3</f>
         <v>40.9</v>
       </c>
-      <c r="D53" s="104">
+      <c r="D53" s="117">
         <f>商机统计!D3</f>
         <v>6793</v>
       </c>
-      <c r="G53" s="102" t="str">
+      <c r="G53" s="115" t="str">
         <f>商机统计!F3</f>
         <v>邱海燕</v>
       </c>
-      <c r="H53" s="103">
+      <c r="H53" s="116">
         <f>商机统计!G3</f>
         <v>5</v>
       </c>
-      <c r="I53" s="103">
+      <c r="I53" s="116">
         <f>商机统计!H3</f>
         <v>49.2</v>
       </c>
-      <c r="J53" s="104">
+      <c r="J53" s="117">
         <f>商机统计!I3</f>
         <v>6479</v>
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="105" t="str">
+      <c r="A54" s="118" t="str">
         <f>商机统计!A4</f>
         <v>具进康</v>
       </c>
-      <c r="B54" s="106">
+      <c r="B54" s="119">
         <f>商机统计!B4</f>
         <v>8</v>
       </c>
-      <c r="C54" s="106">
+      <c r="C54" s="119">
         <f>商机统计!C4</f>
         <v>20.5</v>
       </c>
-      <c r="D54" s="107">
+      <c r="D54" s="120">
         <f>商机统计!D4</f>
         <v>4882</v>
       </c>
-      <c r="G54" s="105" t="str">
+      <c r="G54" s="118" t="str">
         <f>商机统计!F4</f>
         <v>黄淡妮</v>
       </c>
-      <c r="H54" s="106">
+      <c r="H54" s="119">
         <f>商机统计!G4</f>
         <v>11</v>
       </c>
-      <c r="I54" s="106">
+      <c r="I54" s="119">
         <f>商机统计!H4</f>
         <v>43.9</v>
       </c>
-      <c r="J54" s="107">
+      <c r="J54" s="120">
         <f>商机统计!I4</f>
         <v>7393</v>
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="108" t="str">
+      <c r="A55" s="121" t="str">
         <f>商机统计!A5</f>
         <v>张小敏</v>
       </c>
-      <c r="B55" s="109">
+      <c r="B55" s="122">
         <f>商机统计!B5</f>
         <v>10</v>
       </c>
-      <c r="C55" s="109">
+      <c r="C55" s="122">
         <f>商机统计!C5</f>
         <v>20</v>
       </c>
-      <c r="D55" s="110">
+      <c r="D55" s="123">
         <f>商机统计!D5</f>
         <v>4375</v>
       </c>
-      <c r="G55" s="108" t="str">
+      <c r="G55" s="121" t="str">
         <f>商机统计!F5</f>
         <v>潘观友</v>
       </c>
-      <c r="H55" s="109">
+      <c r="H55" s="122">
         <f>商机统计!G5</f>
         <v>10</v>
       </c>
-      <c r="I55" s="109">
+      <c r="I55" s="122">
         <f>商机统计!H5</f>
         <v>36.8</v>
       </c>
-      <c r="J55" s="110">
+      <c r="J55" s="123">
         <f>商机统计!I5</f>
         <v>6317</v>
       </c>
     </row>
     <row r="56" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A56" s="111" t="str">
+      <c r="A56" s="124" t="str">
         <f>商机统计!A6</f>
         <v>潘观友</v>
       </c>
-      <c r="B56" s="112">
+      <c r="B56" s="125">
         <f>商机统计!B6</f>
         <v>6</v>
       </c>
-      <c r="C56" s="112">
+      <c r="C56" s="125">
         <f>商机统计!C6</f>
         <v>19.8</v>
       </c>
-      <c r="D56" s="113">
+      <c r="D56" s="126">
         <f>商机统计!D6</f>
         <v>1400</v>
       </c>
-      <c r="G56" s="111" t="str">
+      <c r="G56" s="124" t="str">
         <f>商机统计!F6</f>
         <v>张小敏</v>
       </c>
-      <c r="H56" s="112">
+      <c r="H56" s="125">
         <f>商机统计!G6</f>
         <v>11</v>
       </c>
-      <c r="I56" s="112">
+      <c r="I56" s="125">
         <f>商机统计!H6</f>
         <v>23</v>
       </c>
-      <c r="J56" s="113">
+      <c r="J56" s="126">
         <f>商机统计!I6</f>
         <v>5575</v>
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="108" t="str">
+      <c r="A57" s="121" t="str">
         <f>商机统计!A7</f>
         <v>李东</v>
       </c>
-      <c r="B57" s="109">
+      <c r="B57" s="122">
         <f>商机统计!B7</f>
         <v>3</v>
       </c>
-      <c r="C57" s="109">
+      <c r="C57" s="122">
         <f>商机统计!C7</f>
         <v>14</v>
       </c>
-      <c r="D57" s="110">
+      <c r="D57" s="123">
         <f>商机统计!D7</f>
         <v>1329</v>
       </c>
-      <c r="G57" s="108" t="str">
+      <c r="G57" s="121" t="str">
         <f>商机统计!F7</f>
         <v>具进康</v>
       </c>
-      <c r="H57" s="109">
+      <c r="H57" s="122">
         <f>商机统计!G7</f>
         <v>10</v>
       </c>
-      <c r="I57" s="109">
+      <c r="I57" s="122">
         <f>商机统计!H7</f>
         <v>22.5</v>
       </c>
-      <c r="J57" s="110">
+      <c r="J57" s="123">
         <f>商机统计!I7</f>
         <v>5181</v>
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="111" t="str">
+      <c r="A58" s="124" t="str">
         <f>商机统计!A8</f>
         <v>王锦添</v>
       </c>
-      <c r="B58" s="112">
+      <c r="B58" s="125">
         <f>商机统计!B8</f>
         <v>4</v>
       </c>
-      <c r="C58" s="112">
+      <c r="C58" s="125">
         <f>商机统计!C8</f>
         <v>12</v>
       </c>
-      <c r="D58" s="113">
+      <c r="D58" s="126">
         <f>商机统计!D8</f>
         <v>2280</v>
       </c>
-      <c r="G58" s="111" t="str">
+      <c r="G58" s="124" t="str">
         <f>商机统计!F8</f>
         <v>黄观霞</v>
       </c>
-      <c r="H58" s="112">
+      <c r="H58" s="125">
         <f>商机统计!G8</f>
         <v>4</v>
       </c>
-      <c r="I58" s="112">
+      <c r="I58" s="125">
         <f>商机统计!H8</f>
         <v>22</v>
       </c>
-      <c r="J58" s="113">
+      <c r="J58" s="126">
         <f>商机统计!I8</f>
         <v>4216</v>
       </c>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="108" t="str">
+      <c r="A59" s="121" t="str">
         <f>商机统计!A9</f>
         <v>李玉强</v>
       </c>
-      <c r="B59" s="109">
+      <c r="B59" s="122">
         <f>商机统计!B9</f>
         <v>6</v>
       </c>
-      <c r="C59" s="109">
+      <c r="C59" s="122">
         <f>商机统计!C9</f>
         <v>9.5</v>
       </c>
-      <c r="D59" s="110">
+      <c r="D59" s="123">
         <f>商机统计!D9</f>
         <v>1184</v>
       </c>
       <c r="E59"/>
       <c r="F59"/>
-      <c r="G59" s="108" t="str">
+      <c r="G59" s="121" t="str">
         <f>商机统计!F9</f>
         <v>李玉强</v>
       </c>
-      <c r="H59" s="109">
+      <c r="H59" s="122">
         <f>商机统计!G9</f>
         <v>8</v>
       </c>
-      <c r="I59" s="109">
+      <c r="I59" s="122">
         <f>商机统计!H9</f>
         <v>19.5</v>
       </c>
-      <c r="J59" s="110">
+      <c r="J59" s="123">
         <f>商机统计!I9</f>
         <v>3820</v>
       </c>
       <c r="N59"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="111" t="str">
+      <c r="A60" s="124" t="str">
         <f>商机统计!A10</f>
         <v>麦海芬</v>
       </c>
-      <c r="B60" s="112">
+      <c r="B60" s="125">
         <f>商机统计!B10</f>
         <v>5</v>
       </c>
-      <c r="C60" s="112">
+      <c r="C60" s="125">
         <f>商机统计!C10</f>
         <v>8.5</v>
       </c>
-      <c r="D60" s="113">
+      <c r="D60" s="126">
         <f>商机统计!D10</f>
         <v>1498</v>
       </c>
       <c r="E60"/>
       <c r="F60"/>
-      <c r="G60" s="111" t="str">
+      <c r="G60" s="124" t="str">
         <f>商机统计!F10</f>
         <v>伍颖敏</v>
       </c>
-      <c r="H60" s="112">
+      <c r="H60" s="125">
         <f>商机统计!G10</f>
         <v>4</v>
       </c>
-      <c r="I60" s="112">
+      <c r="I60" s="125">
         <f>商机统计!H10</f>
         <v>18.48</v>
       </c>
-      <c r="J60" s="113">
+      <c r="J60" s="126">
         <f>商机统计!I10</f>
         <v>3675</v>
       </c>
       <c r="N60"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="108" t="str">
+      <c r="A61" s="121" t="str">
         <f>商机统计!A11</f>
         <v>钟俊杰</v>
       </c>
-      <c r="B61" s="109">
+      <c r="B61" s="122">
         <f>商机统计!B11</f>
         <v>1</v>
       </c>
-      <c r="C61" s="109">
+      <c r="C61" s="122">
         <f>商机统计!C11</f>
         <v>1.5</v>
       </c>
-      <c r="D61" s="110">
+      <c r="D61" s="123">
         <f>商机统计!D11</f>
         <v>199</v>
       </c>
       <c r="E61"/>
       <c r="F61"/>
-      <c r="G61" s="108" t="str">
+      <c r="G61" s="121" t="str">
         <f>商机统计!F11</f>
         <v>王锦添</v>
       </c>
-      <c r="H61" s="109">
+      <c r="H61" s="122">
         <f>商机统计!G11</f>
         <v>5</v>
       </c>
-      <c r="I61" s="109">
+      <c r="I61" s="122">
         <f>商机统计!H11</f>
         <v>16</v>
       </c>
-      <c r="J61" s="110">
+      <c r="J61" s="123">
         <f>商机统计!I11</f>
         <v>3080</v>
       </c>
       <c r="N61"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="111" t="str">
+      <c r="A62" s="124" t="str">
         <f>商机统计!A12</f>
         <v>伍颖敏</v>
       </c>
-      <c r="B62" s="112">
+      <c r="B62" s="125">
         <f>商机统计!B12</f>
         <v>1</v>
       </c>
-      <c r="C62" s="112">
+      <c r="C62" s="125">
         <f>商机统计!C12</f>
         <v>1.5</v>
       </c>
-      <c r="D62" s="113">
+      <c r="D62" s="126">
         <f>商机统计!D12</f>
         <v>280</v>
       </c>
       <c r="E62"/>
       <c r="F62"/>
-      <c r="G62" s="111" t="str">
+      <c r="G62" s="124" t="str">
         <f>商机统计!F12</f>
         <v>李东</v>
       </c>
-      <c r="H62" s="112">
+      <c r="H62" s="125">
         <f>商机统计!G12</f>
         <v>4</v>
       </c>
-      <c r="I62" s="112">
+      <c r="I62" s="125">
         <f>商机统计!H12</f>
         <v>15</v>
       </c>
-      <c r="J62" s="113">
+      <c r="J62" s="126">
         <f>商机统计!I12</f>
         <v>1529</v>
       </c>
       <c r="N62"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="108" t="str">
+      <c r="A63" s="121" t="str">
         <f>商机统计!A13</f>
         <v>邱海燕</v>
       </c>
-      <c r="B63" s="109">
+      <c r="B63" s="122">
         <f>商机统计!B13</f>
         <v>1</v>
       </c>
-      <c r="C63" s="109">
+      <c r="C63" s="122">
         <f>商机统计!C13</f>
         <v>1</v>
       </c>
-      <c r="D63" s="110">
+      <c r="D63" s="123">
         <f>商机统计!D13</f>
         <v>169</v>
       </c>
       <c r="E63"/>
       <c r="F63"/>
-      <c r="G63" s="108" t="str">
+      <c r="G63" s="121" t="str">
         <f>商机统计!F13</f>
         <v>麦海芬</v>
       </c>
-      <c r="H63" s="109">
+      <c r="H63" s="122">
         <f>商机统计!G13</f>
         <v>5</v>
       </c>
-      <c r="I63" s="109">
+      <c r="I63" s="122">
         <f>商机统计!H13</f>
         <v>8.5</v>
       </c>
-      <c r="J63" s="110">
+      <c r="J63" s="123">
         <f>商机统计!I13</f>
         <v>1498</v>
       </c>
       <c r="N63"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="111" t="str">
+      <c r="A64" s="124" t="str">
         <f>商机统计!A14</f>
         <v>黄观霞</v>
       </c>
-      <c r="B64" s="112">
+      <c r="B64" s="125">
         <f>商机统计!B14</f>
         <v>1</v>
       </c>
-      <c r="C64" s="112">
+      <c r="C64" s="125">
         <f>商机统计!C14</f>
         <v>1</v>
       </c>
-      <c r="D64" s="113">
+      <c r="D64" s="126">
         <f>商机统计!D14</f>
         <v>169</v>
       </c>
       <c r="E64"/>
       <c r="F64"/>
-      <c r="G64" s="111" t="str">
+      <c r="G64" s="124" t="str">
         <f>商机统计!F14</f>
         <v>冯艺康</v>
       </c>
-      <c r="H64" s="112">
+      <c r="H64" s="125">
         <f>商机统计!G14</f>
         <v>1</v>
       </c>
-      <c r="I64" s="112">
+      <c r="I64" s="125">
         <f>商机统计!H14</f>
         <v>6</v>
       </c>
-      <c r="J64" s="113">
+      <c r="J64" s="126">
         <f>商机统计!I14</f>
         <v>1200</v>
       </c>
       <c r="N64"/>
     </row>
     <row r="65" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A65" s="114" t="str">
+      <c r="A65" s="127" t="str">
         <f>商机统计!A15</f>
         <v>冯艺康</v>
       </c>
-      <c r="B65" s="115">
+      <c r="B65" s="128">
         <f>商机统计!B15</f>
         <v>0</v>
       </c>
-      <c r="C65" s="115">
+      <c r="C65" s="128">
         <f>商机统计!C15</f>
         <v>0</v>
       </c>
-      <c r="D65" s="116">
+      <c r="D65" s="129">
         <f>商机统计!D15</f>
         <v>0</v>
       </c>
       <c r="E65"/>
       <c r="F65"/>
-      <c r="G65" s="114" t="str">
+      <c r="G65" s="127" t="str">
         <f>商机统计!F15</f>
         <v>钟俊杰</v>
       </c>
-      <c r="H65" s="115">
+      <c r="H65" s="128">
         <f>商机统计!G15</f>
         <v>1</v>
       </c>
-      <c r="I65" s="115">
+      <c r="I65" s="128">
         <f>商机统计!H15</f>
         <v>1.5</v>
       </c>
-      <c r="J65" s="116">
+      <c r="J65" s="129">
         <f>商机统计!I15</f>
         <v>199</v>
       </c>
       <c r="N65"/>
     </row>
     <row r="66" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A66" s="117" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="117">
+      <c r="A66" s="130" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" s="130">
         <f>SUM(B52:B65)</f>
         <v>70</v>
       </c>
-      <c r="C66" s="117">
+      <c r="C66" s="130">
         <f>SUM(C52:C65)</f>
         <v>197.7</v>
       </c>
-      <c r="D66" s="117">
+      <c r="D66" s="130">
         <f>SUM(D52:D65)</f>
         <v>29748</v>
       </c>
       <c r="E66"/>
       <c r="F66"/>
-      <c r="G66" s="117" t="s">
-        <v>61</v>
-      </c>
-      <c r="H66" s="117">
+      <c r="G66" s="130" t="s">
+        <v>36</v>
+      </c>
+      <c r="H66" s="130">
         <f>SUM(H52:H65)</f>
         <v>96</v>
       </c>
-      <c r="I66" s="117">
+      <c r="I66" s="130">
         <f>SUM(I52:I65)</f>
         <v>342.88</v>
       </c>
-      <c r="J66" s="117">
+      <c r="J66" s="130">
         <f>SUM(J52:J65)</f>
         <v>56960</v>
       </c>
@@ -6066,7 +6454,7 @@
       <c r="N104"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="B1:Q1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:N2"/>
@@ -6074,6 +6462,7 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="I33:M33"/>
+    <mergeCell ref="O33:S33"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="G49:J49"/>
@@ -6100,18 +6489,35 @@
     <mergeCell ref="A20:B21"/>
   </mergeCells>
   <conditionalFormatting sqref="F20">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H20">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H105:H1048576">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
       <formula>"是"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R35:R43">
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>AND(R35&lt;1,R35&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FF2E75B6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8170aa37-59b5-4f8a-b348-6868bebd218e}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6121,13 +6527,33 @@
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
   </tableParts>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8170aa37-59b5-4f8a-b348-6868bebd218e}">
+            <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:axisColor indexed="65"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>R35:R43</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6135,7 +6561,7 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6167,7 +6593,7 @@
         <v>23</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6175,7 +6601,7 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6207,7 +6633,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>4.73</v>
+        <v>16.98</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6215,7 +6641,7 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6223,7 +6649,7 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6231,7 +6657,7 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>7.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6247,7 +6673,79 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>1.5</v>
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16">
+        <v>64.98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17">
+        <v>83.92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19">
+        <v>44.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20">
+        <v>49.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B21">
+        <v>81.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>67</v>
+      </c>
+      <c r="B22">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23">
+        <v>70.92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24">
+        <v>29.79</v>
       </c>
     </row>
   </sheetData>
@@ -6307,7 +6805,7 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6339,7 +6837,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6355,7 +6853,7 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6363,7 +6861,7 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6371,7 +6869,7 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6387,7 +6885,7 @@
         <v>38</v>
       </c>
       <c r="B16">
-        <v>40</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -6413,7 +6911,7 @@
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -6424,10 +6922,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -6435,13 +6933,13 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>81.93</v>
+        <v>532.59</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>466.66</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6449,10 +6947,10 @@
         <v>22</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C4">
-        <v>282</v>
+        <v>251.98</v>
       </c>
       <c r="D4">
         <v>116</v>
@@ -6463,13 +6961,13 @@
         <v>23</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>598.6</v>
       </c>
       <c r="D5">
-        <v>-11</v>
+        <v>148.6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6477,13 +6975,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>479</v>
+        <v>889</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>809</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6491,13 +6989,13 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="C7">
-        <v>1010</v>
+        <v>1472.81</v>
       </c>
       <c r="D7">
-        <v>1000</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6505,13 +7003,13 @@
         <v>26</v>
       </c>
       <c r="B8">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="C8">
-        <v>49</v>
+        <v>668</v>
       </c>
       <c r="D8">
-        <v>19</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6533,13 +7031,13 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>4.73</v>
+        <v>18.98</v>
       </c>
       <c r="C10">
-        <v>806.2</v>
+        <v>2618.2</v>
       </c>
       <c r="D10">
-        <v>746.2</v>
+        <v>1874.2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6550,10 +7048,10 @@
         <v>4.5</v>
       </c>
       <c r="C11">
-        <v>799</v>
+        <v>828</v>
       </c>
       <c r="D11">
-        <v>789</v>
+        <v>818</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6561,13 +7059,13 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>2583</v>
+        <v>3760</v>
       </c>
       <c r="D12">
-        <v>2234</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6575,13 +7073,13 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>7.5</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>741.16</v>
+        <v>2137.65</v>
       </c>
       <c r="D13">
-        <v>399</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6592,10 +7090,10 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6603,13 +7101,13 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="C15">
-        <v>-552.05</v>
+        <v>-226.05</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>371</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -6659,10 +7157,10 @@
         <v>44</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>138.6</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -6741,7 +7239,7 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
         <v>52</v>
@@ -6785,7 +7283,7 @@
         <v>44</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6852,7 +7350,7 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6868,7 +7366,7 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6876,7 +7374,7 @@
         <v>22</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6884,7 +7382,7 @@
         <v>23</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6892,7 +7390,7 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6900,7 +7398,7 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6908,7 +7406,7 @@
         <v>26</v>
       </c>
       <c r="B8">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6924,7 +7422,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>4.73</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6940,7 +7438,7 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6948,7 +7446,7 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>7.5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6964,7 +7462,7 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
@@ -6984,25 +7482,25 @@
         <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -7402,35 +7900,35 @@
         <v>18</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" ht="14.75" customHeight="1" spans="1:13">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>84</v>
       </c>
       <c r="D2">
         <f t="array" ref="D2">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B2))</f>
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E2" s="6">
         <f t="shared" ref="E2:E13" si="0">D2/C2</f>
-        <v>0.0357142857142857</v>
+        <v>0.19047619047619</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>32</v>
@@ -7439,29 +7937,29 @@
         <v>40</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" ht="14.75" customHeight="1" spans="1:13">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3">
         <v>84</v>
       </c>
       <c r="D3">
         <f t="array" ref="D3">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B3))</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E3" s="6">
         <f t="shared" si="0"/>
-        <v>0.0595238095238095</v>
+        <v>0.0952380952380952</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>26</v>
@@ -7470,29 +7968,29 @@
         <v>40</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="14.75" customHeight="1" spans="1:13">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>84</v>
       </c>
       <c r="D4">
         <f t="array" ref="D4">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B4))</f>
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>0.0714285714285714</v>
+        <v>0.404761904761905</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>25</v>
@@ -7501,29 +7999,29 @@
         <v>42</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="14.75" customHeight="1" spans="1:13">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>61</v>
       </c>
       <c r="D5">
         <f t="array" ref="D5">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B5))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" s="6">
         <f t="shared" si="0"/>
-        <v>0.0983606557377049</v>
+        <v>0.147540983606557</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>20</v>
@@ -7532,10 +8030,10 @@
         <v>42</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" ht="14.75" customHeight="1" spans="1:13">
@@ -7549,12 +8047,12 @@
         <v>42</v>
       </c>
       <c r="D6">
-        <f t="array" ref="D6">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B6))</f>
-        <v>0</v>
+        <f t="array" ref="D6">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B6))</f>
+        <v>8</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.19047619047619</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>31</v>
@@ -7563,10 +8061,10 @@
         <v>43</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" ht="14.75" customHeight="1" spans="1:13">
@@ -7580,7 +8078,7 @@
         <v>42</v>
       </c>
       <c r="D7">
-        <f t="array" ref="D7">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B7))</f>
+        <f t="array" ref="D7">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B7))</f>
         <v>0</v>
       </c>
       <c r="E7" s="6">
@@ -7594,10 +8092,10 @@
         <v>43</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" ht="14.75" customHeight="1" spans="1:13">
@@ -7611,12 +8109,12 @@
         <v>42</v>
       </c>
       <c r="D8">
-        <f t="array" ref="D8">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B8))</f>
-        <v>0</v>
+        <f t="array" ref="D8">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B8))</f>
+        <v>3</v>
       </c>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>22</v>
@@ -7625,10 +8123,10 @@
         <v>44</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" ht="14.75" customHeight="1" spans="1:13">
@@ -7642,12 +8140,12 @@
         <v>42</v>
       </c>
       <c r="D9">
-        <f t="array" ref="D9">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B9))</f>
-        <v>0</v>
+        <f t="array" ref="D9">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B9))</f>
+        <v>13</v>
       </c>
       <c r="E9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30952380952381</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>24</v>
@@ -7656,10 +8154,10 @@
         <v>44</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" ht="14.75" customHeight="1" spans="1:13">
@@ -7673,12 +8171,12 @@
         <v>42</v>
       </c>
       <c r="D10">
-        <f t="array" ref="D10">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B10))</f>
-        <v>0</v>
+        <f t="array" ref="D10">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B10))</f>
+        <v>18</v>
       </c>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.428571428571429</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>29</v>
@@ -7687,10 +8185,10 @@
         <v>45</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="14.75" customHeight="1" spans="1:13">
@@ -7704,12 +8202,12 @@
         <v>42</v>
       </c>
       <c r="D11">
-        <f t="array" ref="D11">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B11))</f>
-        <v>0</v>
+        <f t="array" ref="D11">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B11))</f>
+        <v>16</v>
       </c>
       <c r="E11" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.380952380952381</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>30</v>
@@ -7718,10 +8216,10 @@
         <v>45</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" ht="14.75" customHeight="1" spans="1:13">
@@ -7735,12 +8233,12 @@
         <v>42</v>
       </c>
       <c r="D12">
-        <f t="array" ref="D12">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B12))</f>
-        <v>0</v>
+        <f t="array" ref="D12">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B12))</f>
+        <v>9</v>
       </c>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.214285714285714</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>33</v>
@@ -7749,10 +8247,10 @@
         <v>46</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" ht="14.75" customHeight="1" spans="1:13">
@@ -7766,7 +8264,7 @@
         <v>25</v>
       </c>
       <c r="D13">
-        <f t="array" ref="D13">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B13))</f>
+        <f t="array" ref="D13">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B13))</f>
         <v>0</v>
       </c>
       <c r="E13" s="6">
@@ -7780,10 +8278,10 @@
         <v>46</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" ht="14.75" customHeight="1" spans="1:13">
@@ -7794,10 +8292,10 @@
         <v>47</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" ht="14.75" customHeight="1" spans="1:13">
@@ -7808,24 +8306,24 @@
         <v>47</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" ht="14.75" customHeight="1" spans="1:13">
       <c r="J16" s="7" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -7845,7 +8343,7 @@
         <v>51</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7853,7 +8351,7 @@
         <v>20</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7861,7 +8359,7 @@
         <v>21</v>
       </c>
       <c r="B3">
-        <v>122.895</v>
+        <v>98.895</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7869,7 +8367,7 @@
         <v>22</v>
       </c>
       <c r="B4">
-        <v>366</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7877,7 +8375,7 @@
         <v>23</v>
       </c>
       <c r="B5">
-        <v>-1.5</v>
+        <v>1317.9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7885,7 +8383,7 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>698.5</v>
+        <v>2530.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7893,7 +8391,7 @@
         <v>25</v>
       </c>
       <c r="B7">
-        <v>3015</v>
+        <v>4078.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7901,7 +8399,7 @@
         <v>26</v>
       </c>
       <c r="B8">
-        <v>173.5</v>
+        <v>1800.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7917,7 +8415,7 @@
         <v>30</v>
       </c>
       <c r="B10">
-        <v>1189.3</v>
+        <v>4867.3</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7925,7 +8423,7 @@
         <v>31</v>
       </c>
       <c r="B11">
-        <v>2375.5</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7933,7 +8431,7 @@
         <v>32</v>
       </c>
       <c r="B12">
-        <v>6071.5</v>
+        <v>8612</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7941,7 +8439,7 @@
         <v>33</v>
       </c>
       <c r="B13">
-        <v>2993.74</v>
+        <v>6818.105</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7949,7 +8447,7 @@
         <v>34</v>
       </c>
       <c r="B14">
-        <v>304</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7957,7 +8455,7 @@
         <v>35</v>
       </c>
       <c r="B15">
-        <v>-848.075</v>
+        <v>-339.075</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7989,7 +8487,7 @@
         <v>44</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>762.3</v>
       </c>
     </row>
     <row r="20" spans="1:2">

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="91">
   <si>
     <t>团队</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>黄牌预警（低于3户）</t>
+  </si>
+  <si>
+    <t>客户经理牌级</t>
   </si>
   <si>
     <t>积分任务值</t>
@@ -651,7 +654,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="61">
+  <fills count="60">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,12 +676,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1873,7 +1870,7 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="30" borderId="57">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="57">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
@@ -1897,16 +1894,16 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="31" borderId="60">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="60">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="61">
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="61">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="32" borderId="60">
+    <xf numFmtId="0" fontId="38" fillId="31" borderId="60">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="33" borderId="62">
+    <xf numFmtId="0" fontId="39" fillId="32" borderId="62">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="63">
@@ -1915,89 +1912,89 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="64">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="41" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="42" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="43" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="43" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="44" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="45" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="45" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="46" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="47" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="47" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="48" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="49" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="49" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="50" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="51" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="51" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="52" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="53" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="53" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="54" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="55" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="55" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="56" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="57" borderId="0">
+    <xf numFmtId="0" fontId="46" fillId="57" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="58" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="59" borderId="0">
+    <xf numFmtId="0" fontId="45" fillId="59" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="60" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2041,6 +2038,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2057,7 +2057,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2069,9 +2069,6 @@
     <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2081,27 +2078,27 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2122,6 +2119,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2162,125 +2162,125 @@
     <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="15" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="18" fillId="16" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="19" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="20" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="18" fillId="18" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="21" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="21" fillId="9" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2292,25 +2292,43 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="28" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2319,34 +2337,16 @@
     <xf numFmtId="0" fontId="26" fillId="28" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2999,24 +2999,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W104"/>
+  <dimension ref="A1:X104"/>
   <sheetFormatPr defaultColWidth="10.6363636363636" defaultRowHeight="14"/>
   <cols>
     <col min="4" max="4" width="9.25454545454545" style="11" customWidth="1"/>
     <col min="5" max="5" width="9.90909090909091" style="11" customWidth="1"/>
     <col min="6" max="7" width="9.25454545454545" style="11" customWidth="1"/>
-    <col min="9" max="9" width="9.25454545454545" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.9" style="11" customWidth="1"/>
-    <col min="14" max="14" width="9.90909090909091" style="11" customWidth="1"/>
+    <col min="9" max="10" width="9.25454545454545" style="11" customWidth="1"/>
+    <col min="11" max="11" width="10.9" style="11" customWidth="1"/>
+    <col min="15" max="15" width="9.90909090909091" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:23">
+    <row r="1" ht="14.25" customHeight="1" spans="1:24">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至5月18日）</v>
+        <v>完美一单积分完成通报（截至6月3日）</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -3032,9 +3032,10 @@
       <c r="N1" s="14"/>
       <c r="O1" s="14"/>
       <c r="P1" s="14"/>
-      <c r="Q1" s="15"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:23">
+      <c r="Q1" s="14"/>
+      <c r="R1" s="15"/>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:24">
       <c r="A2" s="16"/>
       <c r="B2" s="13" t="s">
         <v>1</v>
@@ -3045,22 +3046,23 @@
       <c r="F2" s="14"/>
       <c r="G2" s="14"/>
       <c r="H2" s="15"/>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="17"/>
+      <c r="J2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="J2" s="14"/>
       <c r="K2" s="14"/>
       <c r="L2" s="14"/>
       <c r="M2" s="14"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="13" t="s">
+      <c r="N2" s="14"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="P2" s="14"/>
-      <c r="Q2" s="15"/>
-    </row>
-    <row r="3" ht="70" customHeight="1" spans="1:23">
-      <c r="A3" s="17"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="15"/>
+    </row>
+    <row r="3" ht="70" customHeight="1" spans="1:24">
+      <c r="A3" s="18"/>
       <c r="B3" s="13" t="s">
         <v>4</v>
       </c>
@@ -3092,10 +3094,10 @@
         <v>13</v>
       </c>
       <c r="L3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>14</v>
       </c>
       <c r="N3" s="13" t="s">
         <v>15</v>
@@ -3106,493 +3108,524 @@
       <c r="P3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="18" t="s">
+      <c r="Q3" s="13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1" spans="1:23">
+      <c r="R3" s="19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1" spans="1:24">
       <c r="A4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="19">
+      <c r="B4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="20">
         <v>10</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <f>_xlfn.XLOOKUP(B4,高套!A:A,高套!B:B,0)</f>
+        <v>5</v>
+      </c>
+      <c r="E4" s="22">
+        <f t="shared" ref="E4:E20" si="0">D4/C4</f>
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="23">
+        <f ca="1">D4/(C4/X5*U$5)</f>
+        <v>5</v>
+      </c>
+      <c r="G4" s="20">
+        <f>_xlfn.XLOOKUP(B4,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>6.5</v>
+      </c>
+      <c r="H4" s="24" t="str">
+        <f t="shared" ref="H4:H10" si="1">IF(G4&gt;=3,"否","是")</f>
+        <v>否</v>
+      </c>
+      <c r="I4" s="20" t="str">
+        <f t="shared" ref="I4:I10" si="2">IF(G4&gt;=15,"金牌",IF(G4&gt;=12,"银牌",""))</f>
+        <v/>
+      </c>
+      <c r="J4" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K4" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>936</v>
+      </c>
+      <c r="L4" s="23">
+        <f ca="1" t="shared" ref="L4:L20" si="3">K4/J4</f>
+        <v>0.3744</v>
+      </c>
+      <c r="M4" s="23">
+        <f ca="1">K4/(J4/X5*U$5)</f>
+        <v>3.744</v>
+      </c>
+      <c r="N4" s="25">
+        <f ca="1" t="shared" ref="N4:N10" si="4">VLOOKUP(B:B,V:X,3,0)</f>
+        <v>12</v>
+      </c>
+      <c r="O4" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>3241.5</v>
+      </c>
+      <c r="P4" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q4" s="26">
+        <f>_xlfn.XLOOKUP(B4,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>4</v>
+      </c>
+      <c r="R4" s="27">
+        <f t="shared" ref="R4:R19" si="5">Q4/P4</f>
+        <v>0.19047619047619</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A5" s="16"/>
+      <c r="B5" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="20">
+        <v>10</v>
+      </c>
+      <c r="D5" s="21">
+        <f>_xlfn.XLOOKUP(B5,高套!A:A,高套!B:B,0)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E5" s="22">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="F5" s="23">
+        <f ca="1">D5/(C5/X5*U$5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="20">
+        <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H5" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I5" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J5" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K5" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>1059.34</v>
+      </c>
+      <c r="L5" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.423736</v>
+      </c>
+      <c r="M5" s="23">
+        <f ca="1">K5/(J5/X5*U$5)</f>
+        <v>4.23736</v>
+      </c>
+      <c r="N5" s="25">
+        <f ca="1" t="shared" si="4"/>
+        <v>10</v>
+      </c>
+      <c r="O5" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>1774.27</v>
+      </c>
+      <c r="P5" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q5" s="26">
+        <f>_xlfn.XLOOKUP(B5,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="21">
-        <f t="shared" ref="E4:E20" si="0">D4/C4</f>
+      <c r="R5" s="27">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="F4" s="22">
-        <f ca="1">D4/(C4/W5*T$5)</f>
+      <c r="T5" s="28" t="str">
+        <f ca="1">MONTH(TODAY()-1)&amp;"月"</f>
+        <v>6月</v>
+      </c>
+      <c r="U5" s="28">
+        <f ca="1">DAY(TODAY()-1)</f>
+        <v>3</v>
+      </c>
+      <c r="V5" s="28"/>
+      <c r="W5" s="29"/>
+      <c r="X5">
+        <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A6" s="16"/>
+      <c r="B6" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="20">
+        <v>10</v>
+      </c>
+      <c r="D6" s="21">
+        <f>_xlfn.XLOOKUP(B6,高套!A:A,高套!B:B,0)</f>
+        <v>8</v>
+      </c>
+      <c r="E6" s="22">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="F6" s="23">
+        <f ca="1">D6/(C6/X5*U$5)</f>
+        <v>8</v>
+      </c>
+      <c r="G6" s="20">
+        <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>9.5</v>
+      </c>
+      <c r="H6" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I6" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J6" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K6" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>1445.54</v>
+      </c>
+      <c r="L6" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.578216</v>
+      </c>
+      <c r="M6" s="23">
+        <f ca="1">K6/(J6/X5*U$5)</f>
+        <v>5.78216</v>
+      </c>
+      <c r="N6" s="25">
+        <f ca="1" t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="O6" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>4097.34</v>
+      </c>
+      <c r="P6" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q6" s="26">
+        <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="19">
-        <f>_xlfn.XLOOKUP(B4,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+      <c r="R6" s="27">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H4" s="23" t="str">
-        <f t="shared" ref="H4:H10" si="1">IF(G4&gt;=3,"否","是")</f>
-        <v>是</v>
-      </c>
-      <c r="I4" s="19">
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A7" s="16"/>
+      <c r="B7" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="20">
+        <v>10</v>
+      </c>
+      <c r="D7" s="21">
+        <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
+        <v>4</v>
+      </c>
+      <c r="E7" s="22">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="23">
+        <f ca="1">D7/(C7/X5*U$5)</f>
+        <v>4</v>
+      </c>
+      <c r="G7" s="20">
+        <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>5.5</v>
+      </c>
+      <c r="H7" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I7" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J7" s="20">
         <v>2500</v>
       </c>
-      <c r="J4" s="19">
+      <c r="K7" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)+2500</f>
+        <v>3536.17</v>
+      </c>
+      <c r="L7" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>1.414468</v>
+      </c>
+      <c r="M7" s="23">
+        <f ca="1">K7/(J7/X5*U$5)</f>
+        <v>14.14468</v>
+      </c>
+      <c r="N7" s="25">
+        <f ca="1" t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="O7" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>2635.98</v>
+      </c>
+      <c r="P7" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q7" s="26">
+        <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>3</v>
+      </c>
+      <c r="R7" s="27">
+        <f t="shared" si="5"/>
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A8" s="16"/>
+      <c r="B8" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="20">
+        <v>10</v>
+      </c>
+      <c r="D8" s="21">
+        <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
+        <v>9</v>
+      </c>
+      <c r="E8" s="22">
+        <f t="shared" si="0"/>
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="23">
+        <f ca="1">D8/(C8/X5*U$5)</f>
+        <v>9</v>
+      </c>
+      <c r="G8" s="20">
+        <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>9</v>
+      </c>
+      <c r="H8" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I8" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J8" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K8" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>29</v>
-      </c>
-      <c r="K4" s="22">
-        <f ca="1" t="shared" ref="K4:K20" si="2">J4/I4</f>
-        <v>0.0116</v>
-      </c>
-      <c r="L4" s="22">
-        <f ca="1">J4/(I4/W5*T$5)</f>
-        <v>0.0199777777777778</v>
-      </c>
-      <c r="M4" s="24">
-        <f ca="1" t="shared" ref="M4:M10" si="3">VLOOKUP(B:B,U:W,3,0)</f>
+        <v>1231.67</v>
+      </c>
+      <c r="L8" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.492668</v>
+      </c>
+      <c r="M8" s="23">
+        <f ca="1">K8/(J8/X5*U$5)</f>
+        <v>4.92668</v>
+      </c>
+      <c r="N8" s="25">
+        <f ca="1" t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="O8" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>2732</v>
+      </c>
+      <c r="P8" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q8" s="26">
+        <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>13</v>
+      </c>
+      <c r="R8" s="27">
+        <f t="shared" si="5"/>
+        <v>0.619047619047619</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A9" s="16"/>
+      <c r="B9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="20">
+        <v>10</v>
+      </c>
+      <c r="D9" s="21">
+        <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
+        <v>8</v>
+      </c>
+      <c r="E9" s="22">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="F9" s="23">
+        <f ca="1">D9/(C9/X5*U$5)</f>
+        <v>8</v>
+      </c>
+      <c r="G9" s="20">
+        <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>14.5</v>
+      </c>
+      <c r="H9" s="24" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I9" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v>银牌</v>
+      </c>
+      <c r="J9" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K9" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>2619.81</v>
+      </c>
+      <c r="L9" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>1.047924</v>
+      </c>
+      <c r="M9" s="23">
+        <f ca="1">K9/(J9/X5*U$5)</f>
+        <v>10.47924</v>
+      </c>
+      <c r="N9" s="25">
+        <f ca="1" t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="O9" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>5748</v>
+      </c>
+      <c r="P9" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="26">
+        <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>2</v>
+      </c>
+      <c r="R9" s="27">
+        <f t="shared" si="5"/>
+        <v>0.0952380952380952</v>
+      </c>
+      <c r="V9" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="W9">
+        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
+        <v>936</v>
+      </c>
+      <c r="X9">
+        <f ca="1" t="shared" ref="X9:X22" si="6">RANK(W9,W$9:W$22,0)</f>
         <v>12</v>
       </c>
-      <c r="N4" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>43.5</v>
-      </c>
-      <c r="O4" s="20">
-        <v>21</v>
-      </c>
-      <c r="P4" s="25">
-        <f>_xlfn.XLOOKUP(B4,全光组网!A:A,全光组网!B:B,0)</f>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A10" s="16"/>
+      <c r="B10" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="20">
+        <v>10</v>
+      </c>
+      <c r="D10" s="21">
+        <f>_xlfn.XLOOKUP(B10,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="26">
-        <f t="shared" ref="Q4:Q19" si="4">P4/O4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A5" s="16"/>
-      <c r="B5" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="19">
-        <v>10</v>
-      </c>
-      <c r="D5" s="20">
-        <f>_xlfn.XLOOKUP(B5,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="21">
+      <c r="E10" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="22">
-        <f ca="1">D5/(C5/W5*T$5)</f>
+      <c r="F10" s="23">
+        <f ca="1">D10/(C10/X5*U$5)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="19">
-        <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>是</v>
-      </c>
-      <c r="I5" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J5" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>532.59</v>
-      </c>
-      <c r="K5" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.213036</v>
-      </c>
-      <c r="L5" s="22">
-        <f ca="1">J5/(I5/W5*T$5)</f>
-        <v>0.366895333333333</v>
-      </c>
-      <c r="M5" s="24">
-        <f ca="1" t="shared" si="3"/>
-        <v>9</v>
-      </c>
-      <c r="N5" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>98.895</v>
-      </c>
-      <c r="O5" s="20">
-        <v>21</v>
-      </c>
-      <c r="P5" s="25">
-        <f>_xlfn.XLOOKUP(B5,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S5" s="28" t="str">
-        <f ca="1">MONTH(TODAY()-1)&amp;"月"</f>
-        <v>5月</v>
-      </c>
-      <c r="T5" s="28">
-        <f ca="1">DAY(TODAY()-1)</f>
-        <v>18</v>
-      </c>
-      <c r="U5" s="28"/>
-      <c r="V5" s="29"/>
-      <c r="W5">
-        <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A6" s="16"/>
-      <c r="B6" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="19">
-        <v>10</v>
-      </c>
-      <c r="D6" s="20">
-        <f>_xlfn.XLOOKUP(B6,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6" s="22">
-        <f ca="1">D6/(C6/W5*T$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="19">
-        <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1.5</v>
-      </c>
-      <c r="H6" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>是</v>
-      </c>
-      <c r="I6" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J6" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>251.98</v>
-      </c>
-      <c r="K6" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.100792</v>
-      </c>
-      <c r="L6" s="22">
-        <f ca="1">J6/(I6/W5*T$5)</f>
-        <v>0.173586222222222</v>
-      </c>
-      <c r="M6" s="24">
-        <f ca="1" t="shared" si="3"/>
-        <v>11</v>
-      </c>
-      <c r="N6" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>507</v>
-      </c>
-      <c r="O6" s="20">
-        <v>21</v>
-      </c>
-      <c r="P6" s="25">
-        <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q6" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A7" s="16"/>
-      <c r="B7" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="19">
-        <v>10</v>
-      </c>
-      <c r="D7" s="20">
-        <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E7" s="21">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-      <c r="F7" s="22">
-        <f ca="1">D7/(C7/W5*T$5)</f>
-        <v>0.172222222222222</v>
-      </c>
-      <c r="G7" s="19">
-        <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>2.5</v>
-      </c>
-      <c r="H7" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>是</v>
-      </c>
-      <c r="I7" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J7" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>598.6</v>
-      </c>
-      <c r="K7" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.23944</v>
-      </c>
-      <c r="L7" s="22">
-        <f ca="1">J7/(I7/W5*T$5)</f>
-        <v>0.412368888888889</v>
-      </c>
-      <c r="M7" s="24">
-        <f ca="1" t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="N7" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1317.9</v>
-      </c>
-      <c r="O7" s="20">
-        <v>21</v>
-      </c>
-      <c r="P7" s="25">
-        <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A8" s="16"/>
-      <c r="B8" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="19">
-        <v>10</v>
-      </c>
-      <c r="D8" s="20">
-        <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
-        <v>8</v>
-      </c>
-      <c r="E8" s="21">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="F8" s="22">
-        <f ca="1">D8/(C8/W5*T$5)</f>
-        <v>1.37777777777778</v>
-      </c>
-      <c r="G8" s="19">
-        <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>8</v>
-      </c>
-      <c r="H8" s="27" t="str">
+      <c r="G10" s="20">
+        <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H10" s="24" t="str">
         <f t="shared" si="1"/>
         <v>否</v>
       </c>
-      <c r="I8" s="19">
+      <c r="I10" s="20" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J10" s="20">
         <v>2500</v>
       </c>
-      <c r="J8" s="19">
+      <c r="K10" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>889</v>
-      </c>
-      <c r="K8" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.3556</v>
-      </c>
-      <c r="L8" s="22">
-        <f ca="1">J8/(I8/W5*T$5)</f>
-        <v>0.612422222222222</v>
-      </c>
-      <c r="M8" s="24">
+        <v>2978</v>
+      </c>
+      <c r="L10" s="23">
         <f ca="1" t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="N8" s="24">
+        <v>1.1912</v>
+      </c>
+      <c r="M10" s="23">
+        <f ca="1">K10/(J10/X5*U$5)</f>
+        <v>11.912</v>
+      </c>
+      <c r="N10" s="25">
+        <f ca="1" t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="O10" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>2530.5</v>
-      </c>
-      <c r="O8" s="20">
+        <v>3704</v>
+      </c>
+      <c r="P10" s="21">
         <v>21</v>
       </c>
-      <c r="P8" s="25">
-        <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>13</v>
-      </c>
-      <c r="Q8" s="26">
-        <f t="shared" si="4"/>
-        <v>0.619047619047619</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A9" s="16"/>
-      <c r="B9" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="19">
-        <v>10</v>
-      </c>
-      <c r="D9" s="20">
-        <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F9" s="22">
-        <f ca="1">D9/(C9/W5*T$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="19">
-        <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>6.5</v>
-      </c>
-      <c r="H9" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I9" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J9" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1472.81</v>
-      </c>
-      <c r="K9" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.589124</v>
-      </c>
-      <c r="L9" s="22">
-        <f ca="1">J9/(I9/W5*T$5)</f>
-        <v>1.01460244444444</v>
-      </c>
-      <c r="M9" s="24">
-        <f ca="1" t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="N9" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>4078.5</v>
-      </c>
-      <c r="O9" s="20">
-        <v>21</v>
-      </c>
-      <c r="P9" s="25">
-        <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q9" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U9" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="V9">
-        <f ca="1" t="shared" ref="V9:V22" si="5">VLOOKUP(U:U,B:J,9,0)</f>
-        <v>29</v>
-      </c>
-      <c r="W9">
-        <f ca="1" t="shared" ref="W9:W22" si="6">RANK(V9,V$9:V$22,0)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A10" s="16"/>
-      <c r="B10" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="19">
-        <v>10</v>
-      </c>
-      <c r="D10" s="20">
-        <f>_xlfn.XLOOKUP(B10,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="22">
-        <f ca="1">D10/(C10/W5*T$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="19">
-        <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="H10" s="27" t="str">
-        <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I10" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J10" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>668</v>
-      </c>
-      <c r="K10" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.2672</v>
-      </c>
-      <c r="L10" s="22">
-        <f ca="1">J10/(I10/W5*T$5)</f>
-        <v>0.460177777777778</v>
-      </c>
-      <c r="M10" s="24">
-        <f ca="1" t="shared" si="3"/>
-        <v>7</v>
-      </c>
-      <c r="N10" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1800.5</v>
-      </c>
-      <c r="O10" s="20">
-        <v>21</v>
-      </c>
-      <c r="P10" s="25">
+      <c r="Q10" s="26">
         <f>_xlfn.XLOOKUP(B10,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="26">
-        <f t="shared" si="4"/>
+      <c r="R10" s="27">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U10" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="V10">
-        <f ca="1" t="shared" si="5"/>
-        <v>532.59</v>
+      <c r="V10" s="30" t="s">
+        <v>22</v>
       </c>
       <c r="W10">
+        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
+        <v>1059.34</v>
+      </c>
+      <c r="X10">
         <f ca="1" t="shared" si="6"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A11" s="17"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A11" s="18"/>
       <c r="B11" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" s="31">
         <f>SUM(C4:C10)</f>
@@ -3600,587 +3633,616 @@
       </c>
       <c r="D11" s="31">
         <f>SUM(D4:D10)</f>
-        <v>9</v>
+        <v>35.5</v>
       </c>
       <c r="E11" s="32">
         <f t="shared" si="0"/>
-        <v>0.128571428571429</v>
+        <v>0.507142857142857</v>
       </c>
       <c r="F11" s="32">
-        <f ca="1">D11/(C11/W5*T$5)</f>
-        <v>0.221428571428571</v>
+        <f ca="1">D11/(C11/X5*U$5)</f>
+        <v>5.07142857142857</v>
       </c>
       <c r="G11" s="31">
         <f>SUM(G4:G10)</f>
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="H11" s="32"/>
-      <c r="I11" s="33">
-        <f>SUM(I4:I10)</f>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33">
+        <f>SUM(J4:J10)</f>
         <v>17500</v>
       </c>
-      <c r="J11" s="31">
-        <f ca="1">SUM(J4:J10)</f>
-        <v>4441.98</v>
-      </c>
-      <c r="K11" s="32">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.253827428571429</v>
+      <c r="K11" s="31">
+        <f ca="1">SUM(K4:K10)</f>
+        <v>13806.53</v>
       </c>
       <c r="L11" s="32">
-        <f ca="1">J11/(I11/W5*T$5)</f>
-        <v>0.437147238095238</v>
-      </c>
-      <c r="M11" s="31"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="31">
-        <f>SUM(O4:O10)</f>
-        <v>147</v>
-      </c>
+        <f ca="1" t="shared" si="3"/>
+        <v>0.788944571428571</v>
+      </c>
+      <c r="M11" s="32">
+        <f ca="1">K11/(J11/X5*U$5)</f>
+        <v>7.88944571428571</v>
+      </c>
+      <c r="N11" s="31"/>
+      <c r="O11" s="33"/>
       <c r="P11" s="31">
         <f>SUM(P4:P10)</f>
-        <v>13</v>
-      </c>
-      <c r="Q11" s="34">
-        <f t="shared" si="4"/>
-        <v>0.0884353741496599</v>
-      </c>
-      <c r="U11" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q11" s="31">
+        <f>SUM(Q4:Q10)</f>
         <v>22</v>
       </c>
-      <c r="V11">
-        <f ca="1" t="shared" si="5"/>
-        <v>251.98</v>
+      <c r="R11" s="34">
+        <f t="shared" si="5"/>
+        <v>0.149659863945578</v>
+      </c>
+      <c r="V11" s="30" t="s">
+        <v>23</v>
       </c>
       <c r="W11">
-        <f ca="1" t="shared" si="6"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:23">
-      <c r="A12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="19">
-        <v>10</v>
-      </c>
-      <c r="D12" s="20">
-        <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F12" s="22">
-        <f ca="1">D12/(C12/W5*T$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="19">
-        <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="27" t="str">
-        <f t="shared" ref="H12:H18" si="7">IF(G12&gt;=3,"否","是")</f>
-        <v>是</v>
-      </c>
-      <c r="I12" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J12" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="22">
-        <f ca="1">J12/(I12/W5*T$5)</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="24">
-        <f ca="1" t="shared" ref="M12:M18" si="8">VLOOKUP(B:B,U:W,3,0)</f>
-        <v>13</v>
-      </c>
-      <c r="N12" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O12" s="20">
-        <v>21</v>
-      </c>
-      <c r="P12" s="25">
-        <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="26">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U12" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="V12">
-        <f ca="1" t="shared" si="5"/>
-        <v>598.6</v>
-      </c>
-      <c r="W12">
+        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
+        <v>1445.54</v>
+      </c>
+      <c r="X11">
         <f ca="1" t="shared" si="6"/>
         <v>8</v>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:23">
+    <row r="12" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A12" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="20">
+        <v>10</v>
+      </c>
+      <c r="D12" s="21">
+        <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
+        <v>14</v>
+      </c>
+      <c r="E12" s="22">
+        <f t="shared" si="0"/>
+        <v>1.4</v>
+      </c>
+      <c r="F12" s="23">
+        <f ca="1">D12/(C12/X5*U$5)</f>
+        <v>14</v>
+      </c>
+      <c r="G12" s="20">
+        <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>18</v>
+      </c>
+      <c r="H12" s="24" t="str">
+        <f t="shared" ref="H12:H18" si="7">IF(G12&gt;=3,"否","是")</f>
+        <v>否</v>
+      </c>
+      <c r="I12" s="20" t="str">
+        <f t="shared" ref="I12:I18" si="8">IF(G12&gt;=15,"金牌",IF(G12&gt;=12,"银牌",""))</f>
+        <v>金牌</v>
+      </c>
+      <c r="J12" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K12" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>3446</v>
+      </c>
+      <c r="L12" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>1.3784</v>
+      </c>
+      <c r="M12" s="23">
+        <f ca="1">K12/(J12/X5*U$5)</f>
+        <v>13.784</v>
+      </c>
+      <c r="N12" s="25">
+        <f ca="1" t="shared" ref="N12:N18" si="9">VLOOKUP(B:B,V:X,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="O12" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>13055</v>
+      </c>
+      <c r="P12" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q12" s="26">
+        <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>17</v>
+      </c>
+      <c r="R12" s="27">
+        <f t="shared" si="5"/>
+        <v>0.80952380952381</v>
+      </c>
+      <c r="V12" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="W12">
+        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
+        <v>3536.17</v>
+      </c>
+      <c r="X12">
+        <f ca="1" t="shared" si="6"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:24">
       <c r="A13" s="35"/>
-      <c r="B13" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="19">
+      <c r="B13" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="20">
         <v>10</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="21">
         <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
-        <v>16.98</v>
-      </c>
-      <c r="E13" s="21">
+        <v>18.98</v>
+      </c>
+      <c r="E13" s="22">
         <f t="shared" si="0"/>
-        <v>1.698</v>
-      </c>
-      <c r="F13" s="22">
-        <f ca="1">D13/(C13/W5*T$5)</f>
-        <v>2.92433333333333</v>
-      </c>
-      <c r="G13" s="19">
+        <v>1.898</v>
+      </c>
+      <c r="F13" s="23">
+        <f ca="1">D13/(C13/X5*U$5)</f>
+        <v>18.98</v>
+      </c>
+      <c r="G13" s="20">
         <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>18.98</v>
-      </c>
-      <c r="H13" s="27" t="str">
+        <v>22.98</v>
+      </c>
+      <c r="H13" s="24" t="str">
         <f t="shared" si="7"/>
         <v>否</v>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="20" t="str">
+        <f t="shared" si="8"/>
+        <v>金牌</v>
+      </c>
+      <c r="J13" s="20">
         <v>2500</v>
       </c>
-      <c r="J13" s="19">
+      <c r="K13" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2618.2</v>
-      </c>
-      <c r="K13" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>1.04728</v>
-      </c>
-      <c r="L13" s="22">
-        <f ca="1">J13/(I13/W5*T$5)</f>
-        <v>1.80364888888889</v>
-      </c>
-      <c r="M13" s="24">
-        <f ca="1" t="shared" si="8"/>
-        <v>2</v>
-      </c>
-      <c r="N13" s="24">
+        <v>2703.2</v>
+      </c>
+      <c r="L13" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>1.08128</v>
+      </c>
+      <c r="M13" s="23">
+        <f ca="1">K13/(J13/X5*U$5)</f>
+        <v>10.8128</v>
+      </c>
+      <c r="N13" s="25">
+        <f ca="1" t="shared" si="9"/>
+        <v>5</v>
+      </c>
+      <c r="O13" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>4867.3</v>
-      </c>
-      <c r="O13" s="20">
+        <v>6851.8</v>
+      </c>
+      <c r="P13" s="21">
         <v>21</v>
       </c>
-      <c r="P13" s="25">
+      <c r="Q13" s="26">
         <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>18</v>
-      </c>
-      <c r="Q13" s="26">
-        <f t="shared" si="4"/>
-        <v>0.857142857142857</v>
-      </c>
-      <c r="U13" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="V13">
-        <f ca="1" t="shared" si="5"/>
-        <v>889</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="27">
+        <f t="shared" si="5"/>
+        <v>1.23809523809524</v>
+      </c>
+      <c r="V13" s="30" t="s">
+        <v>25</v>
       </c>
       <c r="W13">
+        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
+        <v>1231.67</v>
+      </c>
+      <c r="X13">
         <f ca="1" t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="1:24">
       <c r="A14" s="35"/>
-      <c r="B14" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="19">
+      <c r="B14" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="20">
         <v>10</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="21">
         <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
         <v>4.5</v>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="22">
         <f t="shared" si="0"/>
         <v>0.45</v>
       </c>
-      <c r="F14" s="22">
-        <f ca="1">D14/(C14/W5*T$5)</f>
-        <v>0.775</v>
-      </c>
-      <c r="G14" s="19">
+      <c r="F14" s="23">
+        <f ca="1">D14/(C14/X5*U$5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G14" s="20">
         <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
         <v>4.5</v>
       </c>
-      <c r="H14" s="27" t="str">
+      <c r="H14" s="24" t="str">
         <f t="shared" si="7"/>
         <v>否</v>
       </c>
-      <c r="I14" s="19">
+      <c r="I14" s="20" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="J14" s="20">
         <v>2500</v>
       </c>
-      <c r="J14" s="19">
+      <c r="K14" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>828</v>
       </c>
-      <c r="K14" s="22">
-        <f ca="1" t="shared" si="2"/>
+      <c r="L14" s="23">
+        <f ca="1" t="shared" si="3"/>
         <v>0.3312</v>
       </c>
-      <c r="L14" s="22">
-        <f ca="1">J14/(I14/W5*T$5)</f>
-        <v>0.5704</v>
-      </c>
-      <c r="M14" s="24">
-        <f ca="1" t="shared" si="8"/>
-        <v>6</v>
-      </c>
-      <c r="N14" s="24">
+      <c r="M14" s="23">
+        <f ca="1">K14/(J14/X5*U$5)</f>
+        <v>3.312</v>
+      </c>
+      <c r="N14" s="25">
+        <f ca="1" t="shared" si="9"/>
+        <v>13</v>
+      </c>
+      <c r="O14" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>2439</v>
       </c>
-      <c r="O14" s="20">
+      <c r="P14" s="21">
         <v>21</v>
       </c>
-      <c r="P14" s="25">
+      <c r="Q14" s="26">
         <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
         <v>3</v>
       </c>
-      <c r="Q14" s="26">
-        <f t="shared" si="4"/>
+      <c r="R14" s="27">
+        <f t="shared" si="5"/>
         <v>0.142857142857143</v>
       </c>
-      <c r="U14" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="V14">
-        <f ca="1" t="shared" si="5"/>
-        <v>1472.81</v>
+      <c r="V14" s="30" t="s">
+        <v>26</v>
       </c>
       <c r="W14">
+        <f ca="1" t="shared" ref="W14:W22" si="10">VLOOKUP(V:V,B:K,10,0)</f>
+        <v>2619.81</v>
+      </c>
+      <c r="X14">
+        <f ca="1" t="shared" si="6"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A15" s="35"/>
+      <c r="B15" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="20">
+        <v>10</v>
+      </c>
+      <c r="D15" s="21">
+        <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
+        <v>12.5</v>
+      </c>
+      <c r="E15" s="22">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="F15" s="23">
+        <f ca="1">D15/(C15/X5*U$5)</f>
+        <v>12.5</v>
+      </c>
+      <c r="G15" s="20">
+        <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>15</v>
+      </c>
+      <c r="H15" s="24" t="str">
+        <f t="shared" si="7"/>
+        <v>否</v>
+      </c>
+      <c r="I15" s="20" t="str">
+        <f t="shared" si="8"/>
+        <v>金牌</v>
+      </c>
+      <c r="J15" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K15" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>3907</v>
+      </c>
+      <c r="L15" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>1.5628</v>
+      </c>
+      <c r="M15" s="23">
+        <f ca="1">K15/(J15/X5*U$5)</f>
+        <v>15.628</v>
+      </c>
+      <c r="N15" s="25">
+        <f ca="1" t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O15" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>11230</v>
+      </c>
+      <c r="P15" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q15" s="26">
+        <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>11</v>
+      </c>
+      <c r="R15" s="27">
+        <f t="shared" si="5"/>
+        <v>0.523809523809524</v>
+      </c>
+      <c r="V15" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="W15">
+        <f ca="1" t="shared" si="10"/>
+        <v>2978</v>
+      </c>
+      <c r="X15">
         <f ca="1" t="shared" si="6"/>
         <v>4</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A15" s="35"/>
-      <c r="B15" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="19">
+    <row r="16" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A16" s="35"/>
+      <c r="B16" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="20">
         <v>10</v>
       </c>
-      <c r="D15" s="20">
-        <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
-        <v>12.5</v>
-      </c>
-      <c r="E15" s="21">
+      <c r="D16" s="21">
+        <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
+        <v>14</v>
+      </c>
+      <c r="E16" s="22">
         <f t="shared" si="0"/>
-        <v>1.25</v>
-      </c>
-      <c r="F15" s="22">
-        <f ca="1">D15/(C15/W5*T$5)</f>
-        <v>2.15277777777778</v>
-      </c>
-      <c r="G15" s="19">
-        <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>15</v>
-      </c>
-      <c r="H15" s="27" t="str">
+        <v>1.4</v>
+      </c>
+      <c r="F16" s="23">
+        <f ca="1">D16/(C16/X5*U$5)</f>
+        <v>14</v>
+      </c>
+      <c r="G16" s="20">
+        <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>14</v>
+      </c>
+      <c r="H16" s="24" t="str">
         <f t="shared" si="7"/>
         <v>否</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I16" s="20" t="str">
+        <f t="shared" si="8"/>
+        <v>银牌</v>
+      </c>
+      <c r="J16" s="20">
         <v>2500</v>
       </c>
-      <c r="J15" s="19">
+      <c r="K16" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>3760</v>
-      </c>
-      <c r="K15" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>1.504</v>
-      </c>
-      <c r="L15" s="22">
-        <f ca="1">J15/(I15/W5*T$5)</f>
-        <v>2.59022222222222</v>
-      </c>
-      <c r="M15" s="24">
-        <f ca="1" t="shared" si="8"/>
+        <v>2137.65</v>
+      </c>
+      <c r="L16" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.85506</v>
+      </c>
+      <c r="M16" s="23">
+        <f ca="1">K16/(J16/X5*U$5)</f>
+        <v>8.5506</v>
+      </c>
+      <c r="N16" s="25">
+        <f ca="1" t="shared" si="9"/>
+        <v>7</v>
+      </c>
+      <c r="O16" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>6539.605</v>
+      </c>
+      <c r="P16" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q16" s="26">
+        <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>16</v>
+      </c>
+      <c r="R16" s="27">
+        <f t="shared" si="5"/>
+        <v>0.761904761904762</v>
+      </c>
+      <c r="V16" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="W16">
+        <f ca="1" t="shared" si="10"/>
+        <v>3446</v>
+      </c>
+      <c r="X16">
+        <f ca="1" t="shared" si="6"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A17" s="35"/>
+      <c r="B17" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="20">
+        <v>10</v>
+      </c>
+      <c r="D17" s="21">
+        <f>_xlfn.XLOOKUP(B17,高套!A:A,高套!B:B,0)</f>
+        <v>10</v>
+      </c>
+      <c r="E17" s="22">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="N15" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>8612</v>
-      </c>
-      <c r="O15" s="20">
-        <v>21</v>
-      </c>
-      <c r="P15" s="25">
-        <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>8</v>
-      </c>
-      <c r="Q15" s="26">
-        <f t="shared" si="4"/>
-        <v>0.380952380952381</v>
-      </c>
-      <c r="U15" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="V15">
-        <f ca="1" t="shared" si="5"/>
-        <v>668</v>
-      </c>
-      <c r="W15">
-        <f ca="1" t="shared" si="6"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A16" s="35"/>
-      <c r="B16" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="19">
+      <c r="F17" s="23">
+        <f ca="1">D17/(C17/X5*U$5)</f>
         <v>10</v>
       </c>
-      <c r="D16" s="20">
-        <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
-        <v>14</v>
-      </c>
-      <c r="E16" s="21">
-        <f t="shared" si="0"/>
-        <v>1.4</v>
-      </c>
-      <c r="F16" s="22">
-        <f ca="1">D16/(C16/W5*T$5)</f>
-        <v>2.41111111111111</v>
-      </c>
-      <c r="G16" s="19">
-        <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>14</v>
-      </c>
-      <c r="H16" s="27" t="str">
+      <c r="G17" s="20">
+        <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>10</v>
+      </c>
+      <c r="H17" s="24" t="str">
         <f t="shared" si="7"/>
         <v>否</v>
       </c>
-      <c r="I16" s="19">
+      <c r="I17" s="20" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="J17" s="20">
         <v>2500</v>
       </c>
-      <c r="J16" s="19">
+      <c r="K17" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2137.65</v>
-      </c>
-      <c r="K16" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.85506</v>
-      </c>
-      <c r="L16" s="22">
-        <f ca="1">J16/(I16/W5*T$5)</f>
-        <v>1.47260333333333</v>
-      </c>
-      <c r="M16" s="24">
-        <f ca="1" t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="N16" s="24">
+        <v>1019</v>
+      </c>
+      <c r="L17" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.4076</v>
+      </c>
+      <c r="M17" s="23">
+        <f ca="1">K17/(J17/X5*U$5)</f>
+        <v>4.076</v>
+      </c>
+      <c r="N17" s="25">
+        <f ca="1" t="shared" si="9"/>
+        <v>11</v>
+      </c>
+      <c r="O17" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>6818.105</v>
-      </c>
-      <c r="O16" s="20">
+        <v>4800.64</v>
+      </c>
+      <c r="P17" s="21">
         <v>21</v>
       </c>
-      <c r="P16" s="25">
-        <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>16</v>
-      </c>
-      <c r="Q16" s="26">
-        <f t="shared" si="4"/>
-        <v>0.761904761904762</v>
-      </c>
-      <c r="U16" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="V16">
-        <f ca="1" t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="W16">
+      <c r="Q17" s="26">
+        <f>_xlfn.XLOOKUP(B17,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>9</v>
+      </c>
+      <c r="R17" s="27">
+        <f t="shared" si="5"/>
+        <v>0.428571428571429</v>
+      </c>
+      <c r="V17" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17">
+        <f ca="1" t="shared" si="10"/>
+        <v>2703.2</v>
+      </c>
+      <c r="X17">
+        <f ca="1" t="shared" si="6"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A18" s="35"/>
+      <c r="B18" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="20">
+        <v>10</v>
+      </c>
+      <c r="D18" s="21">
+        <f>_xlfn.XLOOKUP(B18,高套!A:A,高套!B:B,0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="E18" s="22">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="F18" s="23">
+        <f ca="1">D18/(C18/X5*U$5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="G18" s="20">
+        <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="H18" s="24" t="str">
+        <f t="shared" si="7"/>
+        <v>否</v>
+      </c>
+      <c r="I18" s="20" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="J18" s="20">
+        <v>2500</v>
+      </c>
+      <c r="K18" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>-127.05</v>
+      </c>
+      <c r="L18" s="23">
+        <f ca="1" t="shared" si="3"/>
+        <v>-0.05082</v>
+      </c>
+      <c r="M18" s="23">
+        <f ca="1">K18/(J18/X5*U$5)</f>
+        <v>-0.5082</v>
+      </c>
+      <c r="N18" s="25">
+        <f ca="1" t="shared" si="9"/>
+        <v>14</v>
+      </c>
+      <c r="O18" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>-210.575</v>
+      </c>
+      <c r="P18" s="21">
+        <v>21</v>
+      </c>
+      <c r="Q18" s="26">
+        <f>_xlfn.XLOOKUP(B18,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>6</v>
+      </c>
+      <c r="R18" s="27">
+        <f t="shared" si="5"/>
+        <v>0.285714285714286</v>
+      </c>
+      <c r="V18" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="W18">
+        <f ca="1" t="shared" si="10"/>
+        <v>828</v>
+      </c>
+      <c r="X18">
         <f ca="1" t="shared" si="6"/>
         <v>13</v>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A17" s="35"/>
-      <c r="B17" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="19">
-        <v>10</v>
-      </c>
-      <c r="D17" s="20">
-        <f>_xlfn.XLOOKUP(B17,高套!A:A,高套!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="E17" s="21">
-        <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="F17" s="22">
-        <f ca="1">D17/(C17/W5*T$5)</f>
-        <v>0.516666666666667</v>
-      </c>
-      <c r="G17" s="19">
-        <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="H17" s="27" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I17" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J17" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>296</v>
-      </c>
-      <c r="K17" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.1184</v>
-      </c>
-      <c r="L17" s="22">
-        <f ca="1">J17/(I17/W5*T$5)</f>
-        <v>0.203911111111111</v>
-      </c>
-      <c r="M17" s="24">
-        <f ca="1" t="shared" si="8"/>
-        <v>10</v>
-      </c>
-      <c r="N17" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1524</v>
-      </c>
-      <c r="O17" s="20">
-        <v>21</v>
-      </c>
-      <c r="P17" s="25">
-        <f>_xlfn.XLOOKUP(B17,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="Q17" s="26">
-        <f t="shared" si="4"/>
-        <v>0.142857142857143</v>
-      </c>
-      <c r="U17" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="V17">
-        <f ca="1" t="shared" si="5"/>
-        <v>2618.2</v>
-      </c>
-      <c r="W17">
-        <f ca="1" t="shared" si="6"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A18" s="35"/>
-      <c r="B18" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="19">
-        <v>10</v>
-      </c>
-      <c r="D18" s="20">
-        <f>_xlfn.XLOOKUP(B18,高套!A:A,高套!B:B,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="E18" s="21">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-      <c r="F18" s="22">
-        <f ca="1">D18/(C18/W5*T$5)</f>
-        <v>0.602777777777778</v>
-      </c>
-      <c r="G18" s="19">
-        <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="H18" s="27" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I18" s="19">
-        <v>2500</v>
-      </c>
-      <c r="J18" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>-226.05</v>
-      </c>
-      <c r="K18" s="22">
-        <f ca="1" t="shared" si="2"/>
-        <v>-0.09042</v>
-      </c>
-      <c r="L18" s="22">
-        <f ca="1">J18/(I18/W5*T$5)</f>
-        <v>-0.155723333333333</v>
-      </c>
-      <c r="M18" s="24">
-        <f ca="1" t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="N18" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>-339.075</v>
-      </c>
-      <c r="O18" s="20">
-        <v>21</v>
-      </c>
-      <c r="P18" s="25">
-        <f>_xlfn.XLOOKUP(B18,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>6</v>
-      </c>
-      <c r="Q18" s="26">
-        <f t="shared" si="4"/>
-        <v>0.285714285714286</v>
-      </c>
-      <c r="U18" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="V18">
-        <f ca="1" t="shared" si="5"/>
-        <v>828</v>
-      </c>
-      <c r="W18">
-        <f ca="1" t="shared" si="6"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:23">
+    <row r="19" ht="16.5" customHeight="1" spans="1:24">
       <c r="A19" s="36"/>
       <c r="B19" s="37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="37">
         <f>SUM(C12:C18)</f>
@@ -4188,66 +4250,67 @@
       </c>
       <c r="D19" s="37">
         <f>SUM(D12:D18)</f>
-        <v>54.48</v>
+        <v>77.48</v>
       </c>
       <c r="E19" s="38">
         <f t="shared" si="0"/>
-        <v>0.778285714285714</v>
+        <v>1.10685714285714</v>
       </c>
       <c r="F19" s="32">
-        <f ca="1">D19/(C19/W5*T$5)</f>
-        <v>1.34038095238095</v>
+        <f ca="1">D19/(C19/X5*U$5)</f>
+        <v>11.0685714285714</v>
       </c>
       <c r="G19" s="37">
         <f>SUM(G12:G18)</f>
-        <v>58.98</v>
+        <v>87.98</v>
       </c>
       <c r="H19" s="38"/>
-      <c r="I19" s="39">
-        <f>SUM(I12:I18)</f>
+      <c r="I19" s="39"/>
+      <c r="J19" s="39">
+        <f>SUM(J12:J18)</f>
         <v>17500</v>
       </c>
-      <c r="J19" s="37">
-        <f ca="1">SUM(J12:J18)</f>
-        <v>9413.8</v>
-      </c>
-      <c r="K19" s="38">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.537931428571429</v>
+      <c r="K19" s="37">
+        <f ca="1">SUM(K12:K18)</f>
+        <v>13913.8</v>
       </c>
       <c r="L19" s="38">
-        <f ca="1">J19/(I19/W5*T$5)</f>
-        <v>0.926437460317461</v>
-      </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="37">
-        <f>SUM(O12:O18)</f>
-        <v>147</v>
-      </c>
+        <f ca="1" t="shared" si="3"/>
+        <v>0.795074285714286</v>
+      </c>
+      <c r="M19" s="38">
+        <f ca="1">K19/(J19/X5*U$5)</f>
+        <v>7.95074285714286</v>
+      </c>
+      <c r="N19" s="37"/>
+      <c r="O19" s="39"/>
       <c r="P19" s="37">
         <f>SUM(P12:P18)</f>
-        <v>54</v>
-      </c>
-      <c r="Q19" s="34">
-        <f t="shared" si="4"/>
-        <v>0.36734693877551</v>
-      </c>
-      <c r="U19" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="V19">
-        <f ca="1" t="shared" si="5"/>
-        <v>3760</v>
+        <v>147</v>
+      </c>
+      <c r="Q19" s="37">
+        <f>SUM(Q12:Q18)</f>
+        <v>88</v>
+      </c>
+      <c r="R19" s="34">
+        <f t="shared" si="5"/>
+        <v>0.598639455782313</v>
+      </c>
+      <c r="V19" s="30" t="s">
+        <v>33</v>
       </c>
       <c r="W19">
+        <f ca="1" t="shared" si="10"/>
+        <v>3907</v>
+      </c>
+      <c r="X19">
         <f ca="1" t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" spans="1:23">
+    <row r="20" ht="15" customHeight="1" spans="1:24">
       <c r="A20" s="40" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B20" s="41"/>
       <c r="C20" s="42">
@@ -4255,2219 +4318,2292 @@
       </c>
       <c r="D20" s="43">
         <f>_xlfn.XLOOKUP("端州",高套!A:A,高套!B:B,0)</f>
-        <v>64.98</v>
+        <v>114.48</v>
       </c>
       <c r="E20" s="44">
         <f t="shared" si="0"/>
-        <v>0.492272727272727</v>
+        <v>0.867272727272727</v>
       </c>
       <c r="F20" s="45">
-        <f ca="1">D20/(C20/W5*T$5)</f>
-        <v>0.84780303030303</v>
+        <f ca="1">D20/(C20/X5*U$5)</f>
+        <v>8.67272727272727</v>
       </c>
       <c r="G20" s="46">
         <f>G11+G19</f>
-        <v>80.98</v>
+        <v>141.98</v>
       </c>
       <c r="H20" s="45"/>
-      <c r="I20" s="47">
-        <f>I11+I19</f>
+      <c r="I20" s="47"/>
+      <c r="J20" s="48">
+        <f>J11+J19</f>
         <v>35000</v>
       </c>
-      <c r="J20" s="42">
-        <f ca="1">J11+J19</f>
-        <v>13855.78</v>
-      </c>
-      <c r="K20" s="48">
-        <f ca="1" t="shared" si="2"/>
-        <v>0.395879428571429</v>
+      <c r="K20" s="42">
+        <f ca="1">K11+K19</f>
+        <v>27720.33</v>
       </c>
       <c r="L20" s="49">
-        <f ca="1">J20/(I20/W5*T$5)</f>
-        <v>0.681792349206349</v>
-      </c>
-      <c r="M20" s="50"/>
-      <c r="N20" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="O20" s="52"/>
-      <c r="P20" s="53">
-        <f>P11+P19</f>
-        <v>67</v>
-      </c>
-      <c r="Q20" s="26">
-        <f>P20/O21</f>
-        <v>0.216129032258065</v>
-      </c>
-      <c r="U20" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="V20">
-        <f ca="1" t="shared" si="5"/>
+        <f ca="1" t="shared" si="3"/>
+        <v>0.792009428571429</v>
+      </c>
+      <c r="M20" s="50">
+        <f ca="1">K20/(J20/X5*U$5)</f>
+        <v>7.92009428571429</v>
+      </c>
+      <c r="N20" s="51"/>
+      <c r="O20" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="P20" s="53"/>
+      <c r="Q20" s="54">
+        <f>Q11+Q19</f>
+        <v>110</v>
+      </c>
+      <c r="R20" s="27">
+        <f>Q20/P21</f>
+        <v>0.354838709677419</v>
+      </c>
+      <c r="V20" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="W20">
+        <f ca="1" t="shared" si="10"/>
         <v>2137.65</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <f ca="1" t="shared" si="6"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="1:23">
-      <c r="A21" s="17"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="54"/>
-      <c r="E21" s="54"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:24">
+      <c r="A21" s="18"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="55"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
       <c r="F21" s="36"/>
-      <c r="G21" s="54"/>
+      <c r="G21" s="55"/>
       <c r="H21" s="36"/>
-      <c r="I21" s="54"/>
-      <c r="J21" s="54"/>
+      <c r="I21" s="56"/>
+      <c r="J21" s="55"/>
       <c r="K21" s="55"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="O21" s="57">
+      <c r="L21" s="56"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="57"/>
+      <c r="O21" s="52" t="s">
+        <v>39</v>
+      </c>
+      <c r="P21" s="58">
         <v>310</v>
       </c>
-      <c r="P21" s="58">
-        <f>_xlfn.XLOOKUP(N21,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>144</v>
-      </c>
-      <c r="Q21" s="26">
-        <f>P21/O21</f>
-        <v>0.464516129032258</v>
-      </c>
-      <c r="U21" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="V21">
-        <f ca="1" t="shared" si="5"/>
-        <v>-226.05</v>
+      <c r="Q21" s="59">
+        <f>_xlfn.XLOOKUP(O21,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>274</v>
+      </c>
+      <c r="R21" s="27">
+        <f>Q21/P21</f>
+        <v>0.883870967741936</v>
+      </c>
+      <c r="V21" s="60" t="s">
+        <v>36</v>
       </c>
       <c r="W21">
+        <f ca="1" t="shared" si="10"/>
+        <v>-127.05</v>
+      </c>
+      <c r="X21">
         <f ca="1" t="shared" si="6"/>
         <v>14</v>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1" spans="1:23">
+    <row r="22" ht="16.5" customHeight="1" spans="1:24">
       <c r="A22" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="B22" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="19">
+      <c r="C22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="20">
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="H22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" s="19">
+      <c r="H22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="K22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M22" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N22" s="24">
+      <c r="L22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N22" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O22" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="O22" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P22" s="25" t="s">
-        <v>41</v>
+      <c r="P22" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="Q22" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="U22" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="V22">
-        <f ca="1" t="shared" si="5"/>
-        <v>296</v>
+        <v>42</v>
+      </c>
+      <c r="R22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="V22" s="61" t="s">
+        <v>35</v>
       </c>
       <c r="W22">
+        <f ca="1" t="shared" si="10"/>
+        <v>1019</v>
+      </c>
+      <c r="X22">
         <f ca="1" t="shared" si="6"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1" spans="1:23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1" spans="1:24">
       <c r="A23" s="35"/>
-      <c r="B23" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="B23" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="20">
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="H23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" s="19">
+      <c r="H23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K23" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="K23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L23" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N23" s="24">
+      <c r="L23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M23" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N23" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O23" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>313.5</v>
+      </c>
+      <c r="P23" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R23" s="27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A24" s="35"/>
+      <c r="B24" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="20">
+        <f>高装高套!B4</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K24" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M24" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N24" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O24" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="O23" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P23" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q23" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:23">
-      <c r="A24" s="35"/>
-      <c r="B24" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G24" s="19">
-        <f>高装高套!B4</f>
+      <c r="P24" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q24" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R24" s="27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A25" s="35"/>
+      <c r="B25" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="20">
+        <f>高装高套!B5</f>
+        <v>2</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="20">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>138.6</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N25" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O25" s="25">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>762.3</v>
+      </c>
+      <c r="P25" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q25" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R25" s="27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A26" s="35"/>
+      <c r="B26" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="20">
+        <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="H24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J24" s="19">
+      <c r="H26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="K24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L24" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M24" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N24" s="24">
+      <c r="L26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N26" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O26" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="O24" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P24" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q24" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1" spans="1:23">
-      <c r="A25" s="35"/>
-      <c r="B25" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G25" s="19">
-        <f>高装高套!B5</f>
-        <v>2</v>
-      </c>
-      <c r="H25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J25" s="19">
+      <c r="P26" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q26" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R26" s="27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A27" s="35"/>
+      <c r="B27" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="20">
+        <f>高装高套!B7</f>
+        <v>1.5</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>138.6</v>
-      </c>
-      <c r="K25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L25" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M25" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N25" s="24">
+        <v>239</v>
+      </c>
+      <c r="L27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N27" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O27" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>762.3</v>
-      </c>
-      <c r="O25" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P25" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q25" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1" spans="1:23">
-      <c r="A26" s="35"/>
-      <c r="B26" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G26" s="19">
-        <f>高装高套!B6</f>
+        <v>1075.5</v>
+      </c>
+      <c r="P27" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R27" s="27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A28" s="35"/>
+      <c r="B28" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="20">
+        <f>高装高套!B8</f>
         <v>0</v>
       </c>
-      <c r="H26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J26" s="19">
+      <c r="H28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M26" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N26" s="24">
+      <c r="L28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M28" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O28" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="O26" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P26" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q26" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A27" s="35"/>
-      <c r="B27" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="19">
-        <f>高装高套!B7</f>
-        <v>1.5</v>
-      </c>
-      <c r="H27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J27" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>239</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M27" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N27" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1075.5</v>
-      </c>
-      <c r="O27" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P27" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q27" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A28" s="35"/>
-      <c r="B28" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" s="19">
-        <f>高装高套!B8</f>
+      <c r="P28" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q28" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R28" s="27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A29" s="36"/>
+      <c r="B29" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="20">
+        <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="H28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J28" s="19">
+      <c r="H29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" s="20">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M28" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N28" s="24">
+      <c r="L29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M29" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N29" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="O29" s="25">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O28" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P28" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q28" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A29" s="36"/>
-      <c r="B29" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G29" s="19">
-        <f>高装高套!B9</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J29" s="19">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M29" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="N29" s="24">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O29" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="P29" s="25" t="s">
-        <v>41</v>
+        <v>1345.5</v>
+      </c>
+      <c r="P29" s="21" t="s">
+        <v>42</v>
       </c>
       <c r="Q29" s="26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="30" ht="16.5" customHeight="1" spans="1:23">
-      <c r="A30" s="61" t="s">
-        <v>49</v>
+        <v>42</v>
+      </c>
+      <c r="R29" s="27" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A30" s="62" t="s">
+        <v>50</v>
       </c>
       <c r="B30" s="15"/>
-      <c r="C30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G30" s="19">
+      <c r="C30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="20">
         <f>SUM(G22:G29)</f>
         <v>3.5</v>
       </c>
-      <c r="H30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="I30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="J30" s="19">
-        <f ca="1">SUM(J22:J29)</f>
+      <c r="H30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="20">
+        <f ca="1">SUM(K22:K29)</f>
         <v>377.6</v>
       </c>
-      <c r="K30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="L30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="M30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="N30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="O30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="P30" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q30" s="22" t="s">
-        <v>41</v>
+      <c r="L30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="M30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="N30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="O30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="P30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q30" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="R30" s="23" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1"/>
-    <row r="32" ht="16.5" customHeight="1" spans="1:23">
+    <row r="32" ht="16.5" customHeight="1" spans="1:24">
       <c r="G32"/>
       <c r="I32"/>
       <c r="J32"/>
-      <c r="N32"/>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A33" s="62" t="str">
+      <c r="K32"/>
+      <c r="O32"/>
+    </row>
+    <row r="33" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A33" s="63" t="str">
         <f>"高装高套目标完成情况"</f>
         <v>高装高套目标完成情况</v>
       </c>
       <c r="G33"/>
-      <c r="I33" s="63" t="str">
+      <c r="I33"/>
+      <c r="J33" s="64" t="str">
         <f>"全光任务完成情况"</f>
         <v>全光任务完成情况</v>
       </c>
-      <c r="N33"/>
-      <c r="O33" s="64" t="str">
+      <c r="O33"/>
+      <c r="P33" s="65" t="str">
         <f>"区县目标完成情况"</f>
         <v>区县目标完成情况</v>
       </c>
     </row>
-    <row r="34" ht="33" customHeight="1" spans="1:19">
-      <c r="A34" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" s="65" t="s">
+    <row r="34" ht="33" customHeight="1" spans="1:20">
+      <c r="A34" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="65" t="s">
+      <c r="B34" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D34" s="65" t="s">
+      <c r="C34" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="65" t="s">
+      <c r="D34" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="E34" s="66" t="s">
+        <v>13</v>
+      </c>
+      <c r="F34" s="66" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34"/>
+      <c r="I34"/>
+      <c r="J34" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="K34" s="67" t="s">
+        <v>52</v>
+      </c>
+      <c r="L34" s="67" t="s">
+        <v>17</v>
+      </c>
+      <c r="M34" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="O34"/>
+      <c r="P34" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q34" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="R34" s="69" t="s">
+        <v>58</v>
+      </c>
+      <c r="S34" s="69" t="s">
+        <v>19</v>
+      </c>
+      <c r="T34" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="G34"/>
-      <c r="I34" s="66" t="s">
-        <v>50</v>
-      </c>
-      <c r="J34" s="66" t="s">
-        <v>51</v>
-      </c>
-      <c r="K34" s="66" t="s">
-        <v>16</v>
-      </c>
-      <c r="L34" s="67" t="s">
-        <v>54</v>
-      </c>
-      <c r="M34" s="66" t="s">
-        <v>18</v>
-      </c>
-      <c r="N34"/>
-      <c r="O34" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="P34" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q34" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="R34" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="S34" s="68" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A35" s="69" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="70" t="str">
+    </row>
+    <row r="35" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A35" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="71" t="str">
         <f>高装高套!A2</f>
         <v>陈梓铭</v>
       </c>
-      <c r="C35" s="70">
+      <c r="C35" s="71">
         <v>1</v>
       </c>
-      <c r="D35" s="70">
+      <c r="D35" s="71">
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="E35" s="71">
+      <c r="E35" s="72">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="71">
+      <c r="F35" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G35"/>
-      <c r="I35" s="72" t="s">
-        <v>58</v>
-      </c>
+      <c r="I35"/>
       <c r="J35" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="K35" s="73">
+      <c r="K35" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="L35" s="74">
         <v>84</v>
       </c>
-      <c r="L35" s="73">
+      <c r="M35" s="74">
         <f>交付高装!D2</f>
-        <v>16</v>
-      </c>
-      <c r="M35" s="74">
+        <v>19</v>
+      </c>
+      <c r="N35" s="75">
         <f>交付高装!E2</f>
-        <v>0.19047619047619</v>
-      </c>
-      <c r="N35"/>
-      <c r="O35" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="P35" s="76">
+        <v>0.226190476190476</v>
+      </c>
+      <c r="O35"/>
+      <c r="P35" s="76" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q35" s="77">
         <v>4.25</v>
       </c>
-      <c r="Q35" s="76">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O35,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>3.61</v>
-      </c>
       <c r="R35" s="77">
-        <f ca="1" t="shared" ref="R35:R44" si="9">Q35/P35</f>
-        <v>0.849411764705882</v>
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P35,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>38.16</v>
       </c>
       <c r="S35" s="78">
-        <f ca="1">RANK(R35,R35:R43)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A36" s="79"/>
-      <c r="B36" s="80" t="str">
+        <f ca="1" t="shared" ref="S35:S44" si="11">R35/Q35</f>
+        <v>8.97882352941176</v>
+      </c>
+      <c r="T35" s="79">
+        <f ca="1">RANK(S35,S35:S43)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A36" s="80"/>
+      <c r="B36" s="81" t="str">
         <f>高装高套!A3</f>
         <v>程庆德</v>
       </c>
-      <c r="C36" s="80">
+      <c r="C36" s="81">
         <v>1</v>
       </c>
-      <c r="D36" s="80">
+      <c r="D36" s="81">
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="E36" s="81">
+      <c r="E36" s="82">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="81">
+      <c r="F36" s="82">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>313.5</v>
+      </c>
+      <c r="G36"/>
+      <c r="I36"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="L36" s="74">
+        <v>84</v>
+      </c>
+      <c r="M36" s="74">
+        <f>交付高装!D3</f>
+        <v>17</v>
+      </c>
+      <c r="N36" s="75">
+        <f>交付高装!E3</f>
+        <v>0.202380952380952</v>
+      </c>
+      <c r="O36"/>
+      <c r="P36" s="76" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q36" s="84">
+        <v>5.75</v>
+      </c>
+      <c r="R36" s="84">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P36,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>82.15</v>
+      </c>
+      <c r="S36" s="78">
+        <f ca="1" t="shared" si="11"/>
+        <v>14.2869565217391</v>
+      </c>
+      <c r="T36" s="85">
+        <f ca="1">RANK(S36,S35:S43)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A37" s="80"/>
+      <c r="B37" s="71" t="str">
+        <f>高装高套!A4</f>
+        <v>刘奇峻</v>
+      </c>
+      <c r="C37" s="71">
+        <v>1</v>
+      </c>
+      <c r="D37" s="71">
+        <f>高装高套!B4</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="72">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="G36"/>
-      <c r="I36" s="82"/>
-      <c r="J36" s="73" t="s">
-        <v>60</v>
-      </c>
-      <c r="K36" s="73">
+      <c r="G37"/>
+      <c r="I37"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="L37" s="74">
         <v>84</v>
       </c>
-      <c r="L36" s="73">
-        <f>交付高装!D3</f>
+      <c r="M37" s="74">
+        <f>交付高装!D4</f>
+        <v>59</v>
+      </c>
+      <c r="N37" s="75">
+        <f>交付高装!E4</f>
+        <v>0.702380952380952</v>
+      </c>
+      <c r="O37"/>
+      <c r="P37" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q37" s="77">
+        <v>3.52</v>
+      </c>
+      <c r="R37" s="77">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P37,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>116.6</v>
+      </c>
+      <c r="S37" s="78">
+        <f ca="1" t="shared" si="11"/>
+        <v>33.125</v>
+      </c>
+      <c r="T37" s="79">
+        <f ca="1">RANK(S37,S35:S43)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A38" s="80"/>
+      <c r="B38" s="81" t="str">
+        <f>高装高套!A5</f>
+        <v>龙家宝</v>
+      </c>
+      <c r="C38" s="81">
+        <v>1</v>
+      </c>
+      <c r="D38" s="81">
+        <f>高装高套!B5</f>
+        <v>2</v>
+      </c>
+      <c r="E38" s="82">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>138.6</v>
+      </c>
+      <c r="F38" s="82">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>762.3</v>
+      </c>
+      <c r="G38"/>
+      <c r="I38"/>
+      <c r="J38" s="83"/>
+      <c r="K38" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="L38" s="74">
+        <v>63</v>
+      </c>
+      <c r="M38" s="74">
+        <f>交付高装!D5</f>
+        <v>15</v>
+      </c>
+      <c r="N38" s="75">
+        <f>交付高装!E5</f>
+        <v>0.245901639344262</v>
+      </c>
+      <c r="O38"/>
+      <c r="P38" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q38" s="84">
+        <v>3.97</v>
+      </c>
+      <c r="R38" s="84">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P38,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>37.42</v>
+      </c>
+      <c r="S38" s="78">
+        <f ca="1" t="shared" si="11"/>
+        <v>9.42569269521411</v>
+      </c>
+      <c r="T38" s="85">
+        <f ca="1">RANK(S38,S35:S43)</f>
         <v>8</v>
       </c>
-      <c r="M36" s="74">
-        <f>交付高装!E3</f>
-        <v>0.0952380952380952</v>
-      </c>
-      <c r="N36"/>
-      <c r="O36" s="75" t="s">
-        <v>61</v>
-      </c>
-      <c r="P36" s="83">
-        <v>5.75</v>
-      </c>
-      <c r="Q36" s="83">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O36,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>4.66</v>
-      </c>
-      <c r="R36" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>0.810434782608696</v>
-      </c>
-      <c r="S36" s="84">
-        <f ca="1">RANK(R36,R35:R43)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A37" s="79"/>
-      <c r="B37" s="70" t="str">
-        <f>高装高套!A4</f>
-        <v>刘奇峻</v>
-      </c>
-      <c r="C37" s="70">
+    </row>
+    <row r="39" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A39" s="80"/>
+      <c r="B39" s="71" t="str">
+        <f>高装高套!A6</f>
+        <v>罗紫杰</v>
+      </c>
+      <c r="C39" s="71">
         <v>1</v>
       </c>
-      <c r="D37" s="70">
-        <f>高装高套!B4</f>
+      <c r="D39" s="71">
+        <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="E37" s="71">
+      <c r="E39" s="72">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="71">
+      <c r="F39" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="G37"/>
-      <c r="I37" s="82"/>
-      <c r="J37" s="85" t="s">
-        <v>62</v>
-      </c>
-      <c r="K37" s="73">
-        <v>84</v>
-      </c>
-      <c r="L37" s="73">
-        <f>交付高装!D4</f>
-        <v>34</v>
-      </c>
-      <c r="M37" s="74">
-        <f>交付高装!E4</f>
-        <v>0.404761904761905</v>
-      </c>
-      <c r="N37"/>
-      <c r="O37" s="75" t="s">
-        <v>63</v>
-      </c>
-      <c r="P37" s="76">
-        <v>3.52</v>
-      </c>
-      <c r="Q37" s="76">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O37,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>3.78</v>
-      </c>
-      <c r="R37" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>1.07386363636364</v>
-      </c>
-      <c r="S37" s="78">
-        <f ca="1">RANK(R37,R35:R43)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A38" s="79"/>
-      <c r="B38" s="80" t="str">
-        <f>高装高套!A5</f>
-        <v>龙家宝</v>
-      </c>
-      <c r="C38" s="80">
+      <c r="G39"/>
+      <c r="I39"/>
+      <c r="J39" s="87" t="s">
+        <v>40</v>
+      </c>
+      <c r="K39" s="88" t="s">
+        <v>41</v>
+      </c>
+      <c r="L39" s="89">
+        <v>42</v>
+      </c>
+      <c r="M39" s="89">
+        <f>交付高装!D6</f>
+        <v>11</v>
+      </c>
+      <c r="N39" s="90">
+        <f>交付高装!E6</f>
+        <v>0.261904761904762</v>
+      </c>
+      <c r="O39"/>
+      <c r="P39" s="76" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q39" s="77">
+        <v>2.38</v>
+      </c>
+      <c r="R39" s="77">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P39,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>35.47</v>
+      </c>
+      <c r="S39" s="78">
+        <f ca="1" t="shared" si="11"/>
+        <v>14.9033613445378</v>
+      </c>
+      <c r="T39" s="79">
+        <f ca="1">RANK(S39,S35:S43)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A40" s="80"/>
+      <c r="B40" s="81" t="str">
+        <f>高装高套!A7</f>
+        <v>莫健铭</v>
+      </c>
+      <c r="C40" s="81">
         <v>1</v>
       </c>
-      <c r="D38" s="80">
-        <f>高装高套!B5</f>
-        <v>2</v>
-      </c>
-      <c r="E38" s="81">
+      <c r="D40" s="81">
+        <f>高装高套!B7</f>
+        <v>1.5</v>
+      </c>
+      <c r="E40" s="82">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>138.6</v>
-      </c>
-      <c r="F38" s="81">
+        <v>239</v>
+      </c>
+      <c r="F40" s="82">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>762.3</v>
-      </c>
-      <c r="G38"/>
-      <c r="I38" s="82"/>
-      <c r="J38" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="K38" s="73">
-        <v>63</v>
-      </c>
-      <c r="L38" s="73">
-        <f>交付高装!D5</f>
-        <v>9</v>
-      </c>
-      <c r="M38" s="74">
-        <f>交付高装!E5</f>
-        <v>0.147540983606557</v>
-      </c>
-      <c r="N38"/>
-      <c r="O38" s="75" t="s">
-        <v>65</v>
-      </c>
-      <c r="P38" s="83">
-        <v>3.97</v>
-      </c>
-      <c r="Q38" s="83">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O38,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>4.54</v>
-      </c>
-      <c r="R38" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>1.14357682619647</v>
-      </c>
-      <c r="S38" s="84">
-        <f ca="1">RANK(R38,R35:R43)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A39" s="79"/>
-      <c r="B39" s="70" t="str">
-        <f>高装高套!A6</f>
-        <v>罗紫杰</v>
-      </c>
-      <c r="C39" s="70">
+        <v>1075.5</v>
+      </c>
+      <c r="G40"/>
+      <c r="I40"/>
+      <c r="J40" s="91"/>
+      <c r="K40" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="L40" s="89">
+        <v>42</v>
+      </c>
+      <c r="M40" s="89">
+        <f>交付高装!D7</f>
+        <v>6</v>
+      </c>
+      <c r="N40" s="90">
+        <f>交付高装!E7</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="O40"/>
+      <c r="P40" s="76" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q40" s="92">
+        <v>2.6</v>
+      </c>
+      <c r="R40" s="92">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P40,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>31.55</v>
+      </c>
+      <c r="S40" s="78">
+        <f ca="1" t="shared" si="11"/>
+        <v>12.1346153846154</v>
+      </c>
+      <c r="T40" s="85">
+        <f ca="1">RANK(S40,S35:S43)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A41" s="80"/>
+      <c r="B41" s="71" t="str">
+        <f>高装高套!A8</f>
+        <v>吴广仁</v>
+      </c>
+      <c r="C41" s="71">
         <v>1</v>
       </c>
-      <c r="D39" s="70">
-        <f>高装高套!B6</f>
+      <c r="D41" s="71">
+        <f>高装高套!B8</f>
         <v>0</v>
       </c>
-      <c r="E39" s="71">
+      <c r="E41" s="72">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="71">
+      <c r="F41" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="G39"/>
-      <c r="I39" s="86" t="s">
-        <v>39</v>
-      </c>
-      <c r="J39" s="87" t="s">
-        <v>40</v>
-      </c>
-      <c r="K39" s="88">
-        <v>42</v>
-      </c>
-      <c r="L39" s="88">
-        <f>交付高装!D6</f>
-        <v>8</v>
-      </c>
-      <c r="M39" s="89">
-        <f>交付高装!E6</f>
-        <v>0.19047619047619</v>
-      </c>
-      <c r="N39"/>
-      <c r="O39" s="75" t="s">
-        <v>66</v>
-      </c>
-      <c r="P39" s="76">
-        <v>2.38</v>
-      </c>
-      <c r="Q39" s="76">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O39,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>3.94</v>
-      </c>
-      <c r="R39" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>1.65546218487395</v>
-      </c>
-      <c r="S39" s="78">
-        <f ca="1">RANK(R39,R35:R43)</f>
+      <c r="G41"/>
+      <c r="J41" s="91"/>
+      <c r="K41" s="88" t="s">
+        <v>44</v>
+      </c>
+      <c r="L41" s="89">
+        <v>42</v>
+      </c>
+      <c r="M41" s="89">
+        <f>交付高装!D8</f>
+        <v>6</v>
+      </c>
+      <c r="N41" s="90">
+        <f>交付高装!E8</f>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="O41"/>
+      <c r="P41" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q41" s="77">
+        <v>2.41</v>
+      </c>
+      <c r="R41" s="77">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P41,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>27.6</v>
+      </c>
+      <c r="S41" s="78">
+        <f ca="1" t="shared" si="11"/>
+        <v>11.4522821576763</v>
+      </c>
+      <c r="T41" s="79">
+        <f ca="1">RANK(S41,S35:S43)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" ht="13.5" customHeight="1" spans="1:20">
+      <c r="A42" s="93"/>
+      <c r="B42" s="81" t="str">
+        <f>高装高套!A9</f>
+        <v>王洪明</v>
+      </c>
+      <c r="C42" s="81">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A40" s="79"/>
-      <c r="B40" s="80" t="str">
-        <f>高装高套!A7</f>
-        <v>莫健铭</v>
-      </c>
-      <c r="C40" s="80">
-        <v>1</v>
-      </c>
-      <c r="D40" s="80">
-        <f>高装高套!B7</f>
-        <v>1.5</v>
-      </c>
-      <c r="E40" s="81">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>239</v>
-      </c>
-      <c r="F40" s="81">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1075.5</v>
-      </c>
-      <c r="G40"/>
-      <c r="I40" s="90"/>
-      <c r="J40" s="87" t="s">
-        <v>42</v>
-      </c>
-      <c r="K40" s="88">
-        <v>42</v>
-      </c>
-      <c r="L40" s="88">
-        <f>交付高装!D7</f>
+      <c r="D42" s="81">
+        <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="M40" s="89">
-        <f>交付高装!E7</f>
-        <v>0</v>
-      </c>
-      <c r="N40"/>
-      <c r="O40" s="75" t="s">
-        <v>67</v>
-      </c>
-      <c r="P40" s="91">
-        <v>2.6</v>
-      </c>
-      <c r="Q40" s="91">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O40,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>2.58</v>
-      </c>
-      <c r="R40" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>0.992307692307692</v>
-      </c>
-      <c r="S40" s="84">
-        <f ca="1">RANK(R40,R35:R43)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A41" s="79"/>
-      <c r="B41" s="70" t="str">
-        <f>高装高套!A8</f>
-        <v>吴广仁</v>
-      </c>
-      <c r="C41" s="70">
-        <v>1</v>
-      </c>
-      <c r="D41" s="70">
-        <f>高装高套!B8</f>
-        <v>0</v>
-      </c>
-      <c r="E41" s="71">
+      <c r="E42" s="82">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="71">
+      <c r="F42" s="82">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="G41"/>
-      <c r="I41" s="90"/>
-      <c r="J41" s="87" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41" s="88">
-        <v>42</v>
-      </c>
-      <c r="L41" s="88">
-        <f>交付高装!D8</f>
-        <v>3</v>
-      </c>
-      <c r="M41" s="89">
-        <f>交付高装!E8</f>
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="N41"/>
-      <c r="O41" s="75" t="s">
-        <v>68</v>
-      </c>
-      <c r="P41" s="76">
-        <v>2.41</v>
-      </c>
-      <c r="Q41" s="76">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O41,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>1.66</v>
-      </c>
-      <c r="R41" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>0.688796680497925</v>
-      </c>
-      <c r="S41" s="78">
-        <f ca="1">RANK(R41,R35:R43)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42" ht="13.5" customHeight="1" spans="1:19">
-      <c r="A42" s="92"/>
-      <c r="B42" s="80" t="str">
-        <f>高装高套!A9</f>
-        <v>王洪明</v>
-      </c>
-      <c r="C42" s="80">
-        <v>1</v>
-      </c>
-      <c r="D42" s="80">
-        <f>高装高套!B9</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="81">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="81">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>1345.5</v>
       </c>
       <c r="G42"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="87" t="s">
-        <v>44</v>
-      </c>
-      <c r="K42" s="88">
-        <v>42</v>
-      </c>
-      <c r="L42" s="88">
+      <c r="J42" s="91"/>
+      <c r="K42" s="88" t="s">
+        <v>45</v>
+      </c>
+      <c r="L42" s="89">
+        <v>42</v>
+      </c>
+      <c r="M42" s="89">
         <f>交付高装!D9</f>
         <v>13</v>
       </c>
-      <c r="M42" s="89">
+      <c r="N42" s="90">
         <f>交付高装!E9</f>
         <v>0.30952380952381</v>
       </c>
-      <c r="N42"/>
-      <c r="O42" s="75" t="s">
-        <v>69</v>
-      </c>
-      <c r="P42" s="83">
+      <c r="O42"/>
+      <c r="P42" s="76" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q42" s="84">
         <v>3.22</v>
       </c>
-      <c r="Q42" s="83">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O42,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>2.45</v>
-      </c>
-      <c r="R42" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>0.760869565217391</v>
-      </c>
-      <c r="S42" s="84">
-        <f ca="1">RANK(R42,R35:R43)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A43" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="B43" s="94"/>
-      <c r="C43" s="93">
+      <c r="R42" s="84">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P42,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>38.38</v>
+      </c>
+      <c r="S42" s="78">
+        <f ca="1" t="shared" si="11"/>
+        <v>11.9192546583851</v>
+      </c>
+      <c r="T42" s="85">
+        <f ca="1">RANK(S42,S35:S43)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" customHeight="1" spans="1:20">
+      <c r="A43" s="94" t="s">
+        <v>37</v>
+      </c>
+      <c r="B43" s="95"/>
+      <c r="C43" s="94">
         <f>SUM(C35:C42)</f>
         <v>8</v>
       </c>
-      <c r="D43" s="93">
+      <c r="D43" s="94">
         <f>SUM(D35:D42)</f>
         <v>3.5</v>
       </c>
-      <c r="E43" s="93">
+      <c r="E43" s="94">
         <f ca="1">SUM(E35:E42)</f>
         <v>377.6</v>
       </c>
-      <c r="F43" s="93" t="s">
-        <v>41</v>
+      <c r="F43" s="94" t="s">
+        <v>42</v>
       </c>
       <c r="G43"/>
-      <c r="I43" s="90"/>
-      <c r="J43" s="87" t="s">
-        <v>45</v>
-      </c>
-      <c r="K43" s="88">
-        <v>42</v>
-      </c>
-      <c r="L43" s="88">
+      <c r="J43" s="91"/>
+      <c r="K43" s="88" t="s">
+        <v>46</v>
+      </c>
+      <c r="L43" s="89">
+        <v>42</v>
+      </c>
+      <c r="M43" s="89">
         <f>交付高装!D10</f>
-        <v>18</v>
-      </c>
-      <c r="M43" s="89">
+        <v>43</v>
+      </c>
+      <c r="N43" s="90">
         <f>交付高装!E10</f>
-        <v>0.428571428571429</v>
-      </c>
-      <c r="N43"/>
-      <c r="O43" s="75" t="s">
-        <v>70</v>
-      </c>
-      <c r="P43" s="76">
+        <v>1.02380952380952</v>
+      </c>
+      <c r="O43"/>
+      <c r="P43" s="76" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q43" s="77">
         <v>3.36</v>
       </c>
-      <c r="Q43" s="76">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(O43,高套!A:A,高套!B:B,0)/T5,2)</f>
-        <v>2.74</v>
-      </c>
       <c r="R43" s="77">
-        <f ca="1" t="shared" si="9"/>
-        <v>0.815476190476191</v>
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P43,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>39.39</v>
       </c>
       <c r="S43" s="78">
-        <f ca="1">RANK(R43,R35:R43)</f>
+        <f ca="1" t="shared" si="11"/>
+        <v>11.7232142857143</v>
+      </c>
+      <c r="T43" s="79">
+        <f ca="1">RANK(S43,S35:S43)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="44" ht="14.75" customHeight="1" spans="1:19">
+    <row r="44" ht="14.75" customHeight="1" spans="1:20">
       <c r="F44"/>
       <c r="G44"/>
-      <c r="I44" s="90"/>
-      <c r="J44" s="87" t="s">
-        <v>46</v>
-      </c>
-      <c r="K44" s="88">
-        <v>42</v>
-      </c>
-      <c r="L44" s="88">
+      <c r="J44" s="91"/>
+      <c r="K44" s="88" t="s">
+        <v>47</v>
+      </c>
+      <c r="L44" s="89">
+        <v>42</v>
+      </c>
+      <c r="M44" s="89">
         <f>交付高装!D11</f>
         <v>16</v>
       </c>
-      <c r="M44" s="89">
+      <c r="N44" s="90">
         <f>交付高装!E11</f>
         <v>0.380952380952381</v>
       </c>
-      <c r="N44"/>
-      <c r="O44" s="95" t="s">
-        <v>71</v>
-      </c>
-      <c r="P44" s="96">
-        <f>SUM(P35:P43)</f>
+      <c r="O44"/>
+      <c r="P44" s="96" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q44" s="97">
+        <f>SUM(Q35:Q43)</f>
         <v>31.46</v>
       </c>
-      <c r="Q44" s="96">
-        <f ca="1">SUM(Q35:Q43)</f>
-        <v>29.96</v>
-      </c>
       <c r="R44" s="97">
-        <f ca="1" t="shared" si="9"/>
-        <v>0.952320406865862</v>
-      </c>
-      <c r="S44" s="98" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="45" ht="13.5" customHeight="1" spans="1:19">
+        <f ca="1">SUM(R35:R43)</f>
+        <v>446.72</v>
+      </c>
+      <c r="S44" s="98">
+        <f ca="1" t="shared" si="11"/>
+        <v>14.1996185632549</v>
+      </c>
+      <c r="T44" s="99" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" ht="13.5" customHeight="1" spans="1:20">
       <c r="F45"/>
       <c r="G45"/>
-      <c r="I45" s="90"/>
-      <c r="J45" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="K45" s="88">
-        <v>42</v>
-      </c>
-      <c r="L45" s="88">
+      <c r="J45" s="91"/>
+      <c r="K45" s="88" t="s">
+        <v>48</v>
+      </c>
+      <c r="L45" s="89">
+        <v>42</v>
+      </c>
+      <c r="M45" s="89">
         <f>交付高装!D12</f>
-        <v>9</v>
-      </c>
-      <c r="M45" s="89">
+        <v>15</v>
+      </c>
+      <c r="N45" s="90">
         <f>交付高装!E12</f>
-        <v>0.214285714285714</v>
-      </c>
-      <c r="N45"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1" spans="1:19">
+        <v>0.357142857142857</v>
+      </c>
+      <c r="O45"/>
+    </row>
+    <row r="46" ht="13.5" customHeight="1" spans="1:20">
       <c r="F46"/>
       <c r="G46"/>
-      <c r="I46" s="99"/>
-      <c r="J46" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="K46" s="88">
+      <c r="J46" s="100"/>
+      <c r="K46" s="101" t="s">
+        <v>74</v>
+      </c>
+      <c r="L46" s="89">
         <v>310</v>
       </c>
-      <c r="L46" s="88">
-        <f>SUM(L35:L38)</f>
-        <v>67</v>
-      </c>
       <c r="M46" s="89">
-        <f>L46/K46</f>
-        <v>0.216129032258065</v>
-      </c>
-      <c r="N46"/>
+        <f>SUM(M35:M38)</f>
+        <v>110</v>
+      </c>
+      <c r="N46" s="90">
+        <f>M46/L46</f>
+        <v>0.354838709677419</v>
+      </c>
+      <c r="O46"/>
     </row>
     <row r="47" ht="13.5" customHeight="1"/>
-    <row r="48" ht="13.5" customHeight="1" spans="1:19">
+    <row r="48" ht="13.5" customHeight="1" spans="1:20">
       <c r="F48"/>
       <c r="G48"/>
       <c r="I48"/>
       <c r="J48"/>
-      <c r="N48"/>
-    </row>
-    <row r="49" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A49" s="101" t="str">
+      <c r="K48"/>
+      <c r="O48"/>
+    </row>
+    <row r="49" ht="13.5" customHeight="1" spans="1:15">
+      <c r="A49" s="102" t="str">
         <f ca="1">""&amp;MONTH(TODAY())&amp;"月份商机统计表（预计转化时间为"&amp;MONTH(TODAY())&amp;"月）"</f>
-        <v>5月份商机统计表（预计转化时间为5月）</v>
-      </c>
-      <c r="B49" s="102"/>
-      <c r="C49" s="102"/>
-      <c r="D49" s="103"/>
+        <v>6月份商机统计表（预计转化时间为6月）</v>
+      </c>
+      <c r="B49" s="103"/>
+      <c r="C49" s="103"/>
+      <c r="D49" s="104"/>
       <c r="F49"/>
-      <c r="G49" s="104" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A50" s="105" t="str">
+      <c r="G49" s="105" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="50" ht="13.5" customHeight="1" spans="1:15">
+      <c r="A50" s="106" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止5月18日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
-      </c>
-      <c r="B50" s="106"/>
-      <c r="C50" s="106"/>
-      <c r="D50" s="107"/>
+        <v>（数据截止6月3日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+      </c>
+      <c r="B50" s="107"/>
+      <c r="C50" s="107"/>
+      <c r="D50" s="108"/>
       <c r="F50"/>
-      <c r="G50" s="108" t="str">
+      <c r="G50" s="109" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止5月18日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
-      </c>
-    </row>
-    <row r="51" ht="14.75" customHeight="1" spans="1:14">
+        <v>（数据截止6月3日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+      </c>
+    </row>
+    <row r="51" ht="14.75" customHeight="1" spans="1:15">
       <c r="A51" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C51" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F51"/>
+      <c r="G51" s="110" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D51" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="F51"/>
-      <c r="G51" s="109" t="s">
-        <v>4</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I51" s="110" t="s">
-        <v>76</v>
-      </c>
+      <c r="I51" s="111"/>
       <c r="J51" s="111" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="112" t="str">
+      <c r="K51" s="112" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="113" t="str">
         <f>商机统计!A2</f>
         <v>谢卓和</v>
       </c>
-      <c r="B52" s="113">
+      <c r="B52" s="114">
         <f>商机统计!B2</f>
         <v>14</v>
       </c>
-      <c r="C52" s="113">
+      <c r="C52" s="114">
         <f>商机统计!C2</f>
         <v>47.5</v>
       </c>
-      <c r="D52" s="114">
+      <c r="D52" s="115">
         <f>商机统计!D2</f>
         <v>5190</v>
       </c>
       <c r="F52"/>
-      <c r="G52" s="112" t="str">
+      <c r="G52" s="113" t="str">
         <f>商机统计!F2</f>
         <v>谢卓和</v>
       </c>
-      <c r="H52" s="113">
+      <c r="H52" s="114">
         <f>商机统计!G2</f>
         <v>17</v>
       </c>
-      <c r="I52" s="113">
+      <c r="I52" s="114"/>
+      <c r="J52" s="114">
         <f>商机统计!H2</f>
         <v>60.5</v>
       </c>
-      <c r="J52" s="114">
+      <c r="K52" s="115">
         <f>商机统计!I2</f>
         <v>6798</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="115" t="str">
+    <row r="53" spans="1:15">
+      <c r="A53" s="116" t="str">
         <f>商机统计!A3</f>
         <v>黄淡妮</v>
       </c>
-      <c r="B53" s="116">
+      <c r="B53" s="117">
         <f>商机统计!B3</f>
         <v>10</v>
       </c>
-      <c r="C53" s="116">
+      <c r="C53" s="117">
         <f>商机统计!C3</f>
         <v>40.9</v>
       </c>
-      <c r="D53" s="117">
+      <c r="D53" s="118">
         <f>商机统计!D3</f>
         <v>6793</v>
       </c>
-      <c r="G53" s="115" t="str">
+      <c r="G53" s="116" t="str">
         <f>商机统计!F3</f>
         <v>邱海燕</v>
       </c>
-      <c r="H53" s="116">
+      <c r="H53" s="117">
         <f>商机统计!G3</f>
         <v>5</v>
       </c>
-      <c r="I53" s="116">
+      <c r="I53" s="117"/>
+      <c r="J53" s="117">
         <f>商机统计!H3</f>
         <v>49.2</v>
       </c>
-      <c r="J53" s="117">
+      <c r="K53" s="118">
         <f>商机统计!I3</f>
         <v>6479</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="118" t="str">
+    <row r="54" spans="1:15">
+      <c r="A54" s="119" t="str">
         <f>商机统计!A4</f>
         <v>具进康</v>
       </c>
-      <c r="B54" s="119">
+      <c r="B54" s="120">
         <f>商机统计!B4</f>
         <v>8</v>
       </c>
-      <c r="C54" s="119">
+      <c r="C54" s="120">
         <f>商机统计!C4</f>
         <v>20.5</v>
       </c>
-      <c r="D54" s="120">
+      <c r="D54" s="121">
         <f>商机统计!D4</f>
         <v>4882</v>
       </c>
-      <c r="G54" s="118" t="str">
+      <c r="G54" s="119" t="str">
         <f>商机统计!F4</f>
         <v>黄淡妮</v>
       </c>
-      <c r="H54" s="119">
+      <c r="H54" s="120">
         <f>商机统计!G4</f>
         <v>11</v>
       </c>
-      <c r="I54" s="119">
+      <c r="I54" s="120"/>
+      <c r="J54" s="120">
         <f>商机统计!H4</f>
         <v>43.9</v>
       </c>
-      <c r="J54" s="120">
+      <c r="K54" s="121">
         <f>商机统计!I4</f>
         <v>7393</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="121" t="str">
+    <row r="55" spans="1:15">
+      <c r="A55" s="122" t="str">
         <f>商机统计!A5</f>
         <v>张小敏</v>
       </c>
-      <c r="B55" s="122">
+      <c r="B55" s="123">
         <f>商机统计!B5</f>
         <v>10</v>
       </c>
-      <c r="C55" s="122">
+      <c r="C55" s="123">
         <f>商机统计!C5</f>
         <v>20</v>
       </c>
-      <c r="D55" s="123">
+      <c r="D55" s="124">
         <f>商机统计!D5</f>
         <v>4375</v>
       </c>
-      <c r="G55" s="121" t="str">
+      <c r="G55" s="122" t="str">
         <f>商机统计!F5</f>
         <v>潘观友</v>
       </c>
-      <c r="H55" s="122">
+      <c r="H55" s="123">
         <f>商机统计!G5</f>
         <v>10</v>
       </c>
-      <c r="I55" s="122">
+      <c r="I55" s="123"/>
+      <c r="J55" s="123">
         <f>商机统计!H5</f>
         <v>36.8</v>
       </c>
-      <c r="J55" s="123">
+      <c r="K55" s="124">
         <f>商机统计!I5</f>
         <v>6317</v>
       </c>
     </row>
-    <row r="56" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A56" s="124" t="str">
+    <row r="56" ht="13.5" customHeight="1" spans="1:15">
+      <c r="A56" s="125" t="str">
         <f>商机统计!A6</f>
         <v>潘观友</v>
       </c>
-      <c r="B56" s="125">
+      <c r="B56" s="126">
         <f>商机统计!B6</f>
         <v>6</v>
       </c>
-      <c r="C56" s="125">
+      <c r="C56" s="126">
         <f>商机统计!C6</f>
         <v>19.8</v>
       </c>
-      <c r="D56" s="126">
+      <c r="D56" s="127">
         <f>商机统计!D6</f>
         <v>1400</v>
       </c>
-      <c r="G56" s="124" t="str">
+      <c r="G56" s="125" t="str">
         <f>商机统计!F6</f>
         <v>张小敏</v>
       </c>
-      <c r="H56" s="125">
+      <c r="H56" s="126">
         <f>商机统计!G6</f>
         <v>11</v>
       </c>
-      <c r="I56" s="125">
+      <c r="I56" s="126"/>
+      <c r="J56" s="126">
         <f>商机统计!H6</f>
         <v>23</v>
       </c>
-      <c r="J56" s="126">
+      <c r="K56" s="127">
         <f>商机统计!I6</f>
         <v>5575</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="121" t="str">
+    <row r="57" spans="1:15">
+      <c r="A57" s="122" t="str">
         <f>商机统计!A7</f>
         <v>李东</v>
       </c>
-      <c r="B57" s="122">
+      <c r="B57" s="123">
         <f>商机统计!B7</f>
         <v>3</v>
       </c>
-      <c r="C57" s="122">
+      <c r="C57" s="123">
         <f>商机统计!C7</f>
         <v>14</v>
       </c>
-      <c r="D57" s="123">
+      <c r="D57" s="124">
         <f>商机统计!D7</f>
         <v>1329</v>
       </c>
-      <c r="G57" s="121" t="str">
+      <c r="G57" s="122" t="str">
         <f>商机统计!F7</f>
         <v>具进康</v>
       </c>
-      <c r="H57" s="122">
+      <c r="H57" s="123">
         <f>商机统计!G7</f>
         <v>10</v>
       </c>
-      <c r="I57" s="122">
+      <c r="I57" s="123"/>
+      <c r="J57" s="123">
         <f>商机统计!H7</f>
         <v>22.5</v>
       </c>
-      <c r="J57" s="123">
+      <c r="K57" s="124">
         <f>商机统计!I7</f>
         <v>5181</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="124" t="str">
+    <row r="58" spans="1:15">
+      <c r="A58" s="125" t="str">
         <f>商机统计!A8</f>
         <v>王锦添</v>
       </c>
-      <c r="B58" s="125">
+      <c r="B58" s="126">
         <f>商机统计!B8</f>
         <v>4</v>
       </c>
-      <c r="C58" s="125">
+      <c r="C58" s="126">
         <f>商机统计!C8</f>
         <v>12</v>
       </c>
-      <c r="D58" s="126">
+      <c r="D58" s="127">
         <f>商机统计!D8</f>
         <v>2280</v>
       </c>
-      <c r="G58" s="124" t="str">
+      <c r="G58" s="125" t="str">
         <f>商机统计!F8</f>
         <v>黄观霞</v>
       </c>
-      <c r="H58" s="125">
+      <c r="H58" s="126">
         <f>商机统计!G8</f>
         <v>4</v>
       </c>
-      <c r="I58" s="125">
+      <c r="I58" s="126"/>
+      <c r="J58" s="126">
         <f>商机统计!H8</f>
         <v>22</v>
       </c>
-      <c r="J58" s="126">
+      <c r="K58" s="127">
         <f>商机统计!I8</f>
         <v>4216</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="121" t="str">
+    <row r="59" spans="1:15">
+      <c r="A59" s="122" t="str">
         <f>商机统计!A9</f>
         <v>李玉强</v>
       </c>
-      <c r="B59" s="122">
+      <c r="B59" s="123">
         <f>商机统计!B9</f>
         <v>6</v>
       </c>
-      <c r="C59" s="122">
+      <c r="C59" s="123">
         <f>商机统计!C9</f>
         <v>9.5</v>
       </c>
-      <c r="D59" s="123">
+      <c r="D59" s="124">
         <f>商机统计!D9</f>
         <v>1184</v>
       </c>
       <c r="E59"/>
       <c r="F59"/>
-      <c r="G59" s="121" t="str">
+      <c r="G59" s="122" t="str">
         <f>商机统计!F9</f>
         <v>李玉强</v>
       </c>
-      <c r="H59" s="122">
+      <c r="H59" s="123">
         <f>商机统计!G9</f>
         <v>8</v>
       </c>
-      <c r="I59" s="122">
+      <c r="I59" s="123"/>
+      <c r="J59" s="123">
         <f>商机统计!H9</f>
         <v>19.5</v>
       </c>
-      <c r="J59" s="123">
+      <c r="K59" s="124">
         <f>商机统计!I9</f>
         <v>3820</v>
       </c>
-      <c r="N59"/>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="124" t="str">
+      <c r="O59"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="125" t="str">
         <f>商机统计!A10</f>
         <v>麦海芬</v>
       </c>
-      <c r="B60" s="125">
+      <c r="B60" s="126">
         <f>商机统计!B10</f>
         <v>5</v>
       </c>
-      <c r="C60" s="125">
+      <c r="C60" s="126">
         <f>商机统计!C10</f>
         <v>8.5</v>
       </c>
-      <c r="D60" s="126">
+      <c r="D60" s="127">
         <f>商机统计!D10</f>
         <v>1498</v>
       </c>
       <c r="E60"/>
       <c r="F60"/>
-      <c r="G60" s="124" t="str">
+      <c r="G60" s="125" t="str">
         <f>商机统计!F10</f>
         <v>伍颖敏</v>
       </c>
-      <c r="H60" s="125">
+      <c r="H60" s="126">
         <f>商机统计!G10</f>
         <v>4</v>
       </c>
-      <c r="I60" s="125">
+      <c r="I60" s="126"/>
+      <c r="J60" s="126">
         <f>商机统计!H10</f>
         <v>18.48</v>
       </c>
-      <c r="J60" s="126">
+      <c r="K60" s="127">
         <f>商机统计!I10</f>
         <v>3675</v>
       </c>
-      <c r="N60"/>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="121" t="str">
+      <c r="O60"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="122" t="str">
         <f>商机统计!A11</f>
         <v>钟俊杰</v>
       </c>
-      <c r="B61" s="122">
+      <c r="B61" s="123">
         <f>商机统计!B11</f>
         <v>1</v>
       </c>
-      <c r="C61" s="122">
+      <c r="C61" s="123">
         <f>商机统计!C11</f>
         <v>1.5</v>
       </c>
-      <c r="D61" s="123">
+      <c r="D61" s="124">
         <f>商机统计!D11</f>
         <v>199</v>
       </c>
       <c r="E61"/>
       <c r="F61"/>
-      <c r="G61" s="121" t="str">
+      <c r="G61" s="122" t="str">
         <f>商机统计!F11</f>
         <v>王锦添</v>
       </c>
-      <c r="H61" s="122">
+      <c r="H61" s="123">
         <f>商机统计!G11</f>
         <v>5</v>
       </c>
-      <c r="I61" s="122">
+      <c r="I61" s="123"/>
+      <c r="J61" s="123">
         <f>商机统计!H11</f>
         <v>16</v>
       </c>
-      <c r="J61" s="123">
+      <c r="K61" s="124">
         <f>商机统计!I11</f>
         <v>3080</v>
       </c>
-      <c r="N61"/>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="124" t="str">
+      <c r="O61"/>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="125" t="str">
         <f>商机统计!A12</f>
         <v>伍颖敏</v>
       </c>
-      <c r="B62" s="125">
+      <c r="B62" s="126">
         <f>商机统计!B12</f>
         <v>1</v>
       </c>
-      <c r="C62" s="125">
+      <c r="C62" s="126">
         <f>商机统计!C12</f>
         <v>1.5</v>
       </c>
-      <c r="D62" s="126">
+      <c r="D62" s="127">
         <f>商机统计!D12</f>
         <v>280</v>
       </c>
       <c r="E62"/>
       <c r="F62"/>
-      <c r="G62" s="124" t="str">
+      <c r="G62" s="125" t="str">
         <f>商机统计!F12</f>
         <v>李东</v>
       </c>
-      <c r="H62" s="125">
+      <c r="H62" s="126">
         <f>商机统计!G12</f>
         <v>4</v>
       </c>
-      <c r="I62" s="125">
+      <c r="I62" s="126"/>
+      <c r="J62" s="126">
         <f>商机统计!H12</f>
         <v>15</v>
       </c>
-      <c r="J62" s="126">
+      <c r="K62" s="127">
         <f>商机统计!I12</f>
         <v>1529</v>
       </c>
-      <c r="N62"/>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="121" t="str">
+      <c r="O62"/>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="122" t="str">
         <f>商机统计!A13</f>
         <v>邱海燕</v>
       </c>
-      <c r="B63" s="122">
+      <c r="B63" s="123">
         <f>商机统计!B13</f>
         <v>1</v>
       </c>
-      <c r="C63" s="122">
+      <c r="C63" s="123">
         <f>商机统计!C13</f>
         <v>1</v>
       </c>
-      <c r="D63" s="123">
+      <c r="D63" s="124">
         <f>商机统计!D13</f>
         <v>169</v>
       </c>
       <c r="E63"/>
       <c r="F63"/>
-      <c r="G63" s="121" t="str">
+      <c r="G63" s="122" t="str">
         <f>商机统计!F13</f>
         <v>麦海芬</v>
       </c>
-      <c r="H63" s="122">
+      <c r="H63" s="123">
         <f>商机统计!G13</f>
         <v>5</v>
       </c>
-      <c r="I63" s="122">
+      <c r="I63" s="123"/>
+      <c r="J63" s="123">
         <f>商机统计!H13</f>
         <v>8.5</v>
       </c>
-      <c r="J63" s="123">
+      <c r="K63" s="124">
         <f>商机统计!I13</f>
         <v>1498</v>
       </c>
-      <c r="N63"/>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="124" t="str">
+      <c r="O63"/>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="125" t="str">
         <f>商机统计!A14</f>
         <v>黄观霞</v>
       </c>
-      <c r="B64" s="125">
+      <c r="B64" s="126">
         <f>商机统计!B14</f>
         <v>1</v>
       </c>
-      <c r="C64" s="125">
+      <c r="C64" s="126">
         <f>商机统计!C14</f>
         <v>1</v>
       </c>
-      <c r="D64" s="126">
+      <c r="D64" s="127">
         <f>商机统计!D14</f>
         <v>169</v>
       </c>
       <c r="E64"/>
       <c r="F64"/>
-      <c r="G64" s="124" t="str">
+      <c r="G64" s="125" t="str">
         <f>商机统计!F14</f>
         <v>冯艺康</v>
       </c>
-      <c r="H64" s="125">
+      <c r="H64" s="126">
         <f>商机统计!G14</f>
         <v>1</v>
       </c>
-      <c r="I64" s="125">
+      <c r="I64" s="126"/>
+      <c r="J64" s="126">
         <f>商机统计!H14</f>
         <v>6</v>
       </c>
-      <c r="J64" s="126">
+      <c r="K64" s="127">
         <f>商机统计!I14</f>
         <v>1200</v>
       </c>
-      <c r="N64"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A65" s="127" t="str">
+      <c r="O64"/>
+    </row>
+    <row r="65" ht="13.5" customHeight="1" spans="1:15">
+      <c r="A65" s="128" t="str">
         <f>商机统计!A15</f>
         <v>冯艺康</v>
       </c>
-      <c r="B65" s="128">
+      <c r="B65" s="129">
         <f>商机统计!B15</f>
         <v>0</v>
       </c>
-      <c r="C65" s="128">
+      <c r="C65" s="129">
         <f>商机统计!C15</f>
         <v>0</v>
       </c>
-      <c r="D65" s="129">
+      <c r="D65" s="130">
         <f>商机统计!D15</f>
         <v>0</v>
       </c>
       <c r="E65"/>
       <c r="F65"/>
-      <c r="G65" s="127" t="str">
+      <c r="G65" s="128" t="str">
         <f>商机统计!F15</f>
         <v>钟俊杰</v>
       </c>
-      <c r="H65" s="128">
+      <c r="H65" s="129">
         <f>商机统计!G15</f>
         <v>1</v>
       </c>
-      <c r="I65" s="128">
+      <c r="I65" s="129"/>
+      <c r="J65" s="129">
         <f>商机统计!H15</f>
         <v>1.5</v>
       </c>
-      <c r="J65" s="129">
+      <c r="K65" s="130">
         <f>商机统计!I15</f>
         <v>199</v>
       </c>
-      <c r="N65"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1" spans="1:14">
-      <c r="A66" s="130" t="s">
-        <v>36</v>
-      </c>
-      <c r="B66" s="130">
+      <c r="O65"/>
+    </row>
+    <row r="66" ht="13.5" customHeight="1" spans="1:15">
+      <c r="A66" s="131" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="131">
         <f>SUM(B52:B65)</f>
         <v>70</v>
       </c>
-      <c r="C66" s="130">
+      <c r="C66" s="131">
         <f>SUM(C52:C65)</f>
         <v>197.7</v>
       </c>
-      <c r="D66" s="130">
+      <c r="D66" s="131">
         <f>SUM(D52:D65)</f>
         <v>29748</v>
       </c>
       <c r="E66"/>
       <c r="F66"/>
-      <c r="G66" s="130" t="s">
-        <v>36</v>
-      </c>
-      <c r="H66" s="130">
+      <c r="G66" s="131" t="s">
+        <v>37</v>
+      </c>
+      <c r="H66" s="131">
         <f>SUM(H52:H65)</f>
         <v>96</v>
       </c>
-      <c r="I66" s="130">
-        <f>SUM(I52:I65)</f>
+      <c r="I66" s="131"/>
+      <c r="J66" s="131">
+        <f>SUM(J52:J65)</f>
         <v>342.88</v>
       </c>
-      <c r="J66" s="130">
-        <f>SUM(J52:J65)</f>
+      <c r="K66" s="131">
+        <f>SUM(K52:K65)</f>
         <v>56960</v>
       </c>
-      <c r="N66"/>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66"/>
+    </row>
+    <row r="67" spans="1:15">
       <c r="D67"/>
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67"/>
-      <c r="N67"/>
-    </row>
-    <row r="68" ht="13.5" customHeight="1" spans="1:14">
+      <c r="O67"/>
+    </row>
+    <row r="68" ht="13.5" customHeight="1" spans="1:15">
       <c r="D68"/>
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68"/>
-      <c r="N68"/>
-    </row>
-    <row r="69" ht="52" customHeight="1" spans="1:14">
+      <c r="O68"/>
+    </row>
+    <row r="69" ht="52" customHeight="1" spans="1:15">
       <c r="D69"/>
       <c r="E69"/>
       <c r="F69"/>
       <c r="G69"/>
       <c r="I69"/>
       <c r="J69"/>
-      <c r="N69"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1" spans="1:14">
+      <c r="K69"/>
+      <c r="O69"/>
+    </row>
+    <row r="70" ht="13.5" customHeight="1" spans="1:15">
       <c r="D70"/>
       <c r="E70"/>
       <c r="F70"/>
       <c r="G70"/>
       <c r="I70"/>
       <c r="J70"/>
-      <c r="N70"/>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="K70"/>
+      <c r="O70"/>
+    </row>
+    <row r="71" spans="1:15">
       <c r="D71"/>
       <c r="E71"/>
       <c r="F71"/>
       <c r="G71"/>
       <c r="I71"/>
       <c r="J71"/>
-      <c r="N71"/>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="K71"/>
+      <c r="O71"/>
+    </row>
+    <row r="72" spans="1:15">
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72"/>
       <c r="G72"/>
       <c r="I72"/>
       <c r="J72"/>
-      <c r="N72"/>
-    </row>
-    <row r="73" spans="1:14">
+      <c r="K72"/>
+      <c r="O72"/>
+    </row>
+    <row r="73" spans="1:15">
       <c r="D73"/>
       <c r="E73"/>
       <c r="F73"/>
       <c r="G73"/>
       <c r="I73"/>
       <c r="J73"/>
-      <c r="N73"/>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="K73"/>
+      <c r="O73"/>
+    </row>
+    <row r="74" spans="1:15">
       <c r="D74"/>
       <c r="E74"/>
       <c r="F74"/>
       <c r="G74"/>
       <c r="I74"/>
       <c r="J74"/>
-      <c r="N74"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1" spans="1:14">
+      <c r="K74"/>
+      <c r="O74"/>
+    </row>
+    <row r="75" ht="13.5" customHeight="1" spans="1:15">
       <c r="D75"/>
       <c r="E75"/>
       <c r="F75"/>
       <c r="G75"/>
       <c r="I75"/>
       <c r="J75"/>
-      <c r="N75"/>
-    </row>
-    <row r="76" spans="1:14">
+      <c r="K75"/>
+      <c r="O75"/>
+    </row>
+    <row r="76" spans="1:15">
       <c r="D76"/>
       <c r="E76"/>
       <c r="F76"/>
       <c r="G76"/>
       <c r="I76"/>
       <c r="J76"/>
-      <c r="N76"/>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="K76"/>
+      <c r="O76"/>
+    </row>
+    <row r="77" spans="1:15">
       <c r="D77"/>
       <c r="E77"/>
       <c r="F77"/>
       <c r="G77"/>
       <c r="I77"/>
       <c r="J77"/>
-      <c r="N77"/>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="K77"/>
+      <c r="O77"/>
+    </row>
+    <row r="78" spans="1:15">
       <c r="D78"/>
       <c r="E78"/>
       <c r="F78"/>
       <c r="G78"/>
       <c r="I78"/>
       <c r="J78"/>
-      <c r="N78"/>
-    </row>
-    <row r="79" spans="1:14">
+      <c r="K78"/>
+      <c r="O78"/>
+    </row>
+    <row r="79" spans="1:15">
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79"/>
       <c r="G79"/>
       <c r="I79"/>
       <c r="J79"/>
-      <c r="N79"/>
-    </row>
-    <row r="80" spans="1:14">
+      <c r="K79"/>
+      <c r="O79"/>
+    </row>
+    <row r="80" spans="1:15">
       <c r="D80"/>
       <c r="E80"/>
       <c r="F80"/>
       <c r="G80"/>
       <c r="I80"/>
       <c r="J80"/>
-      <c r="N80"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K80"/>
+      <c r="O80"/>
+    </row>
+    <row r="81" ht="13.5" customHeight="1" spans="4:15">
       <c r="D81"/>
       <c r="E81"/>
       <c r="F81"/>
       <c r="G81"/>
       <c r="I81"/>
       <c r="J81"/>
-      <c r="N81"/>
-    </row>
-    <row r="82" spans="4:14">
+      <c r="K81"/>
+      <c r="O81"/>
+    </row>
+    <row r="82" spans="4:15">
       <c r="D82"/>
       <c r="E82"/>
       <c r="F82"/>
       <c r="G82"/>
       <c r="I82"/>
       <c r="J82"/>
-      <c r="N82"/>
-    </row>
-    <row r="83" spans="4:14">
+      <c r="K82"/>
+      <c r="O82"/>
+    </row>
+    <row r="83" spans="4:15">
       <c r="D83"/>
       <c r="E83"/>
       <c r="F83"/>
       <c r="G83"/>
       <c r="I83"/>
       <c r="J83"/>
-      <c r="N83"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K83"/>
+      <c r="O83"/>
+    </row>
+    <row r="84" ht="13.5" customHeight="1" spans="4:15">
       <c r="D84"/>
       <c r="E84"/>
       <c r="F84"/>
       <c r="G84"/>
       <c r="I84"/>
       <c r="J84"/>
-      <c r="N84"/>
-    </row>
-    <row r="85" ht="52" customHeight="1" spans="4:14">
+      <c r="K84"/>
+      <c r="O84"/>
+    </row>
+    <row r="85" ht="52" customHeight="1" spans="4:15">
       <c r="D85"/>
       <c r="E85"/>
       <c r="F85"/>
       <c r="G85"/>
       <c r="I85"/>
       <c r="J85"/>
-      <c r="N85"/>
-    </row>
-    <row r="86" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K85"/>
+      <c r="O85"/>
+    </row>
+    <row r="86" ht="13.5" customHeight="1" spans="4:15">
       <c r="D86"/>
       <c r="E86"/>
       <c r="F86"/>
       <c r="G86"/>
       <c r="I86"/>
       <c r="J86"/>
-      <c r="N86"/>
-    </row>
-    <row r="87" spans="4:14">
+      <c r="K86"/>
+      <c r="O86"/>
+    </row>
+    <row r="87" spans="4:15">
       <c r="D87"/>
       <c r="E87"/>
       <c r="F87"/>
       <c r="G87"/>
       <c r="I87"/>
       <c r="J87"/>
-      <c r="N87"/>
-    </row>
-    <row r="88" spans="4:14">
+      <c r="K87"/>
+      <c r="O87"/>
+    </row>
+    <row r="88" spans="4:15">
       <c r="D88"/>
       <c r="E88"/>
       <c r="F88"/>
       <c r="G88"/>
       <c r="I88"/>
       <c r="J88"/>
-      <c r="N88"/>
-    </row>
-    <row r="89" spans="4:14">
+      <c r="K88"/>
+      <c r="O88"/>
+    </row>
+    <row r="89" spans="4:15">
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89"/>
       <c r="G89"/>
       <c r="I89"/>
       <c r="J89"/>
-      <c r="N89"/>
-    </row>
-    <row r="90" spans="4:14">
+      <c r="K89"/>
+      <c r="O89"/>
+    </row>
+    <row r="90" spans="4:15">
       <c r="D90"/>
       <c r="E90"/>
       <c r="F90"/>
       <c r="G90"/>
       <c r="I90"/>
       <c r="J90"/>
-      <c r="N90"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K90"/>
+      <c r="O90"/>
+    </row>
+    <row r="91" ht="13.5" customHeight="1" spans="4:15">
       <c r="D91"/>
       <c r="E91"/>
       <c r="F91"/>
       <c r="G91"/>
       <c r="I91"/>
       <c r="J91"/>
-      <c r="N91"/>
-    </row>
-    <row r="92" spans="4:14">
+      <c r="K91"/>
+      <c r="O91"/>
+    </row>
+    <row r="92" spans="4:15">
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92"/>
       <c r="I92"/>
       <c r="J92"/>
-      <c r="N92"/>
-    </row>
-    <row r="93" spans="4:14">
+      <c r="K92"/>
+      <c r="O92"/>
+    </row>
+    <row r="93" spans="4:15">
       <c r="D93"/>
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93"/>
       <c r="I93"/>
       <c r="J93"/>
-      <c r="N93"/>
-    </row>
-    <row r="94" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K93"/>
+      <c r="O93"/>
+    </row>
+    <row r="94" ht="13.5" customHeight="1" spans="4:15">
       <c r="D94"/>
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94"/>
       <c r="I94"/>
       <c r="J94"/>
-      <c r="N94"/>
-    </row>
-    <row r="95" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K94"/>
+      <c r="O94"/>
+    </row>
+    <row r="95" ht="13.5" customHeight="1" spans="4:15">
       <c r="D95"/>
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95"/>
       <c r="I95"/>
       <c r="J95"/>
-      <c r="N95"/>
-    </row>
-    <row r="96" spans="4:14">
+      <c r="K95"/>
+      <c r="O95"/>
+    </row>
+    <row r="96" spans="4:15">
       <c r="D96"/>
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96"/>
       <c r="I96"/>
       <c r="J96"/>
-      <c r="N96"/>
-    </row>
-    <row r="97" spans="4:14">
+      <c r="K96"/>
+      <c r="O96"/>
+    </row>
+    <row r="97" spans="4:15">
       <c r="D97"/>
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97"/>
       <c r="I97"/>
       <c r="J97"/>
-      <c r="N97"/>
-    </row>
-    <row r="98" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K97"/>
+      <c r="O97"/>
+    </row>
+    <row r="98" ht="13.5" customHeight="1" spans="4:15">
       <c r="D98"/>
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98"/>
       <c r="I98"/>
       <c r="J98"/>
-      <c r="N98"/>
-    </row>
-    <row r="99" ht="52" customHeight="1" spans="4:14">
+      <c r="K98"/>
+      <c r="O98"/>
+    </row>
+    <row r="99" ht="52" customHeight="1" spans="4:15">
       <c r="D99"/>
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99"/>
       <c r="I99"/>
       <c r="J99"/>
-      <c r="N99"/>
-    </row>
-    <row r="100" ht="13.5" customHeight="1" spans="4:14">
+      <c r="K99"/>
+      <c r="O99"/>
+    </row>
+    <row r="100" ht="13.5" customHeight="1" spans="4:15">
       <c r="D100"/>
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100"/>
       <c r="I100"/>
       <c r="J100"/>
-      <c r="N100"/>
-    </row>
-    <row r="101" spans="4:14">
+      <c r="K100"/>
+      <c r="O100"/>
+    </row>
+    <row r="101" spans="4:15">
       <c r="D101"/>
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101"/>
       <c r="I101"/>
       <c r="J101"/>
-      <c r="N101"/>
-    </row>
-    <row r="102" spans="4:14">
+      <c r="K101"/>
+      <c r="O101"/>
+    </row>
+    <row r="102" spans="4:15">
       <c r="D102"/>
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102"/>
       <c r="I102"/>
       <c r="J102"/>
-      <c r="N102"/>
-    </row>
-    <row r="103" spans="4:14">
+      <c r="K102"/>
+      <c r="O102"/>
+    </row>
+    <row r="103" spans="4:15">
       <c r="D103"/>
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103"/>
       <c r="I103"/>
       <c r="J103"/>
-      <c r="N103"/>
-    </row>
-    <row r="104" spans="4:14">
+      <c r="K103"/>
+      <c r="O103"/>
+    </row>
+    <row r="104" spans="4:15">
       <c r="D104"/>
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104"/>
       <c r="I104"/>
       <c r="J104"/>
-      <c r="N104"/>
+      <c r="K104"/>
+      <c r="O104"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="B1:Q1"/>
+  <mergeCells count="33">
+    <mergeCell ref="B1:R1"/>
     <mergeCell ref="B2:H2"/>
-    <mergeCell ref="I2:N2"/>
-    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="J2:O2"/>
+    <mergeCell ref="P2:R2"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="I33:M33"/>
-    <mergeCell ref="O33:S33"/>
+    <mergeCell ref="J33:N33"/>
+    <mergeCell ref="P33:T33"/>
     <mergeCell ref="A43:B43"/>
     <mergeCell ref="A49:D49"/>
-    <mergeCell ref="G49:J49"/>
+    <mergeCell ref="G49:K49"/>
     <mergeCell ref="A50:D50"/>
-    <mergeCell ref="G50:J50"/>
+    <mergeCell ref="G50:K50"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="A12:A19"/>
@@ -6480,12 +6616,13 @@
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="H20:H21"/>
     <mergeCell ref="I20:I21"/>
-    <mergeCell ref="I35:I38"/>
-    <mergeCell ref="I39:I46"/>
     <mergeCell ref="J20:J21"/>
+    <mergeCell ref="J35:J38"/>
+    <mergeCell ref="J39:J46"/>
     <mergeCell ref="K20:K21"/>
     <mergeCell ref="L20:L21"/>
     <mergeCell ref="M20:M21"/>
+    <mergeCell ref="N20:N21"/>
     <mergeCell ref="A20:B21"/>
   </mergeCells>
   <conditionalFormatting sqref="F20">
@@ -6493,20 +6630,12 @@
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H20">
+  <conditionalFormatting sqref="H4:H18">
     <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H105:H1048576">
-    <cfRule type="cellIs" dxfId="6" priority="15" operator="equal">
-      <formula>"是"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R35:R43">
-    <cfRule type="expression" dxfId="7" priority="2">
-      <formula>AND(R35&lt;1,R35&lt;&gt;"")</formula>
-    </cfRule>
+  <conditionalFormatting sqref="S35:S43">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6515,9 +6644,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8170aa37-59b5-4f8a-b348-6868bebd218e}</x14:id>
+          <x14:id>{aab5e57b-8037-4bf4-a5e3-2297d3afadbc}</x14:id>
         </ext>
       </extLst>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="2">
+      <formula>AND(S35&lt;1,S35&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6531,7 +6663,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8170aa37-59b5-4f8a-b348-6868bebd218e}">
+          <x14:cfRule type="dataBar" id="{aab5e57b-8037-4bf4-a5e3-2297d3afadbc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -6542,7 +6674,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>R35:R43</xm:sqref>
+          <xm:sqref>S35:S43</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -6558,63 +6690,63 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6622,23 +6754,23 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>16.98</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>4.5</v>
@@ -6646,7 +6778,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>12.5</v>
@@ -6654,7 +6786,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>14</v>
@@ -6662,15 +6794,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -6678,74 +6810,74 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <v>64.98</v>
+        <v>114.48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B17">
-        <v>83.92</v>
+        <v>246.45</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B18">
-        <v>68</v>
+        <v>349.81</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19">
-        <v>44.08</v>
+        <v>115.13</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20">
-        <v>49.25</v>
+        <v>118.17</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B21">
-        <v>81.7</v>
+        <v>112.25</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B22">
-        <v>46.4</v>
+        <v>94.65</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23">
-        <v>70.92</v>
+        <v>106.42</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24">
-        <v>29.79</v>
+        <v>82.79</v>
       </c>
     </row>
   </sheetData>
@@ -6762,23 +6894,23 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6786,7 +6918,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6794,15 +6926,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>13</v>
@@ -6810,15 +6942,15 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -6826,23 +6958,23 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -6850,15 +6982,15 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>16</v>
@@ -6866,15 +6998,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -6882,10 +7014,10 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16">
-        <v>144</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -6902,147 +7034,147 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>936</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>648</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>532.59</v>
+        <v>1059.34</v>
       </c>
       <c r="D3">
-        <v>466.66</v>
+        <v>756.66</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="C4">
-        <v>251.98</v>
+        <v>1445.54</v>
       </c>
       <c r="D4">
-        <v>116</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="C5">
-        <v>598.6</v>
+        <v>1036.17</v>
       </c>
       <c r="D5">
-        <v>148.6</v>
+        <v>752.61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6">
-        <v>889</v>
+        <v>1231.67</v>
       </c>
       <c r="D6">
-        <v>809</v>
+        <v>1150.67</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
       <c r="C7">
-        <v>1472.81</v>
+        <v>2619.81</v>
       </c>
       <c r="D7">
-        <v>1387</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>668</v>
+        <v>2978</v>
       </c>
       <c r="D8">
-        <v>475</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3446</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>18.98</v>
+        <v>22.98</v>
       </c>
       <c r="C10">
-        <v>2618.2</v>
+        <v>2703.2</v>
       </c>
       <c r="D10">
-        <v>1874.2</v>
+        <v>2103.2</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>4.5</v>
@@ -7056,21 +7188,21 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>15</v>
       </c>
       <c r="C12">
-        <v>3760</v>
+        <v>3907</v>
       </c>
       <c r="D12">
-        <v>2831</v>
+        <v>2868</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>14</v>
@@ -7084,35 +7216,35 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>296</v>
+        <v>1019</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>3.5</v>
       </c>
       <c r="C15">
-        <v>-226.05</v>
+        <v>-127.05</v>
       </c>
       <c r="D15">
-        <v>371</v>
+        <v>470</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -7126,7 +7258,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -7140,7 +7272,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -7154,7 +7286,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -7168,7 +7300,7 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -7182,7 +7314,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21">
         <v>1.5</v>
@@ -7196,7 +7328,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -7210,7 +7342,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -7236,18 +7368,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -7258,7 +7390,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -7269,7 +7401,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -7280,7 +7412,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -7291,7 +7423,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -7302,7 +7434,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7">
         <v>1.5</v>
@@ -7313,7 +7445,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -7324,7 +7456,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -7347,87 +7479,87 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>6.5</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>18.98</v>
+        <v>22.98</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>4.5</v>
@@ -7435,7 +7567,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
         <v>15</v>
@@ -7443,7 +7575,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
         <v>14</v>
@@ -7451,15 +7583,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
         <v>3.5</v>
@@ -7482,30 +7614,30 @@
         <v>4</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -7517,7 +7649,7 @@
         <v>5190</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G2">
         <v>17</v>
@@ -7531,7 +7663,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -7543,7 +7675,7 @@
         <v>6793</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7557,7 +7689,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -7569,7 +7701,7 @@
         <v>4882</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>11</v>
@@ -7583,7 +7715,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -7595,7 +7727,7 @@
         <v>4375</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -7609,7 +7741,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -7621,7 +7753,7 @@
         <v>1400</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6">
         <v>11</v>
@@ -7635,7 +7767,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -7647,7 +7779,7 @@
         <v>1329</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -7661,7 +7793,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -7673,7 +7805,7 @@
         <v>2280</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>4</v>
@@ -7687,7 +7819,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -7699,7 +7831,7 @@
         <v>1184</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9">
         <v>8</v>
@@ -7713,7 +7845,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>5</v>
@@ -7725,7 +7857,7 @@
         <v>1498</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10">
         <v>4</v>
@@ -7739,7 +7871,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -7751,7 +7883,7 @@
         <v>199</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7765,7 +7897,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -7777,7 +7909,7 @@
         <v>280</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12">
         <v>4</v>
@@ -7791,7 +7923,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -7803,7 +7935,7 @@
         <v>169</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7817,7 +7949,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -7829,7 +7961,7 @@
         <v>169</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -7843,7 +7975,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -7855,7 +7987,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -7885,256 +8017,256 @@
   <sheetData>
     <row r="1" ht="14.75" customHeight="1" spans="1:13">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" ht="14.75" customHeight="1" spans="1:13">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>84</v>
       </c>
       <c r="D2">
         <f t="array" ref="D2">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B2))</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" s="6">
         <f t="shared" ref="E2:E13" si="0">D2/C2</f>
-        <v>0.19047619047619</v>
+        <v>0.226190476190476</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="14.75" customHeight="1" spans="1:13">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>84</v>
       </c>
       <c r="D3">
         <f t="array" ref="D3">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B3))</f>
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E3" s="6">
         <f t="shared" si="0"/>
-        <v>0.0952380952380952</v>
+        <v>0.202380952380952</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="14.75" customHeight="1" spans="1:13">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>84</v>
       </c>
       <c r="D4">
         <f t="array" ref="D4">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B4))</f>
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>0.404761904761905</v>
+        <v>0.702380952380952</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" ht="14.75" customHeight="1" spans="1:13">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>61</v>
       </c>
       <c r="D5">
         <f t="array" ref="D5">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B5))</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E5" s="6">
         <f t="shared" si="0"/>
-        <v>0.147540983606557</v>
+        <v>0.245901639344262</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="14.75" customHeight="1" spans="1:13">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>42</v>
       </c>
       <c r="D6">
         <f t="array" ref="D6">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B6))</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
-        <v>0.19047619047619</v>
+        <v>0.261904761904762</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="14.75" customHeight="1" spans="1:13">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>42</v>
       </c>
       <c r="D7">
         <f t="array" ref="D7">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B7))</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E7" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="14.75" customHeight="1" spans="1:13">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8">
         <v>42</v>
       </c>
       <c r="D8">
         <f t="array" ref="D8">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B8))</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" ht="14.75" customHeight="1" spans="1:13">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <v>42</v>
@@ -8148,55 +8280,55 @@
         <v>0.30952380952381</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="14.75" customHeight="1" spans="1:13">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>42</v>
       </c>
       <c r="D10">
         <f t="array" ref="D10">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B10))</f>
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
-        <v>0.428571428571429</v>
+        <v>1.02380952380952</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="14.75" customHeight="1" spans="1:13">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11">
         <v>42</v>
@@ -8210,55 +8342,55 @@
         <v>0.380952380952381</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" ht="14.75" customHeight="1" spans="1:13">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>42</v>
       </c>
       <c r="D12">
         <f t="array" ref="D12">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B12))</f>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
-        <v>0.214285714285714</v>
+        <v>0.357142857142857</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" ht="14.75" customHeight="1" spans="1:13">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -8272,58 +8404,58 @@
         <v>0</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" ht="14.75" customHeight="1" spans="1:13">
       <c r="J14" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="14.75" customHeight="1" spans="1:13">
       <c r="J15" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="14.75" customHeight="1" spans="1:13">
       <c r="J16" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -8340,87 +8472,87 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>43.5</v>
+        <v>3241.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>98.895</v>
+        <v>1774.27</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>507</v>
+        <v>4097.34</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>1317.9</v>
+        <v>2635.98</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>2530.5</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>4078.5</v>
+        <v>5748</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>1800.5</v>
+        <v>3704</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>13055</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>4867.3</v>
+        <v>6851.8</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11">
         <v>2439</v>
@@ -8428,39 +8560,39 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>8612</v>
+        <v>11230</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>6818.105</v>
+        <v>6539.605</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>1524</v>
+        <v>4800.64</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15">
-        <v>-339.075</v>
+        <v>-210.575</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -8468,15 +8600,15 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>313.5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -8484,7 +8616,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19">
         <v>762.3</v>
@@ -8492,7 +8624,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -8500,7 +8632,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B21">
         <v>1075.5</v>
@@ -8508,7 +8640,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8516,10 +8648,10 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1345.5</v>
       </c>
     </row>
   </sheetData>

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -32,6 +32,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3016,7 +3038,7 @@
       </c>
       <c r="B1" s="13" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至6月3日）</v>
+        <v>完美一单积分完成通报（截至6月24日）</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -3135,7 +3157,7 @@
       </c>
       <c r="F4" s="23">
         <f ca="1">D4/(C4/X5*U$5)</f>
-        <v>5</v>
+        <v>0.625</v>
       </c>
       <c r="G4" s="20">
         <f>_xlfn.XLOOKUP(B4,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3162,7 +3184,7 @@
       </c>
       <c r="M4" s="23">
         <f ca="1">K4/(J4/X5*U$5)</f>
-        <v>3.744</v>
+        <v>0.468</v>
       </c>
       <c r="N4" s="25">
         <f ca="1" t="shared" ref="N4:N10" si="4">VLOOKUP(B:B,V:X,3,0)</f>
@@ -3173,15 +3195,15 @@
         <v>3241.5</v>
       </c>
       <c r="P4" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q4" s="26">
         <f>_xlfn.XLOOKUP(B4,全光组网!A:A,全光组网!B:B,0)</f>
         <v>4</v>
       </c>
       <c r="R4" s="27">
-        <f t="shared" ref="R4:R19" si="5">Q4/P4</f>
-        <v>0.19047619047619</v>
+        <f t="shared" ref="R4:R20" si="5">Q4/P4</f>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:24">
@@ -3202,7 +3224,7 @@
       </c>
       <c r="F5" s="23">
         <f ca="1">D5/(C5/X5*U$5)</f>
-        <v>1.5</v>
+        <v>0.1875</v>
       </c>
       <c r="G5" s="20">
         <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3229,7 +3251,7 @@
       </c>
       <c r="M5" s="23">
         <f ca="1">K5/(J5/X5*U$5)</f>
-        <v>4.23736</v>
+        <v>0.52967</v>
       </c>
       <c r="N5" s="25">
         <f ca="1" t="shared" si="4"/>
@@ -3240,7 +3262,7 @@
         <v>1774.27</v>
       </c>
       <c r="P5" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="26">
         <f>_xlfn.XLOOKUP(B5,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3256,7 +3278,7 @@
       </c>
       <c r="U5" s="28">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="V5" s="28"/>
       <c r="W5" s="29"/>
@@ -3283,7 +3305,7 @@
       </c>
       <c r="F6" s="23">
         <f ca="1">D6/(C6/X5*U$5)</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G6" s="20">
         <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3310,7 +3332,7 @@
       </c>
       <c r="M6" s="23">
         <f ca="1">K6/(J6/X5*U$5)</f>
-        <v>5.78216</v>
+        <v>0.72277</v>
       </c>
       <c r="N6" s="25">
         <f ca="1" t="shared" si="4"/>
@@ -3321,7 +3343,7 @@
         <v>4097.34</v>
       </c>
       <c r="P6" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="26">
         <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3350,7 +3372,7 @@
       </c>
       <c r="F7" s="23">
         <f ca="1">D7/(C7/X5*U$5)</f>
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="G7" s="20">
         <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3377,7 +3399,7 @@
       </c>
       <c r="M7" s="23">
         <f ca="1">K7/(J7/X5*U$5)</f>
-        <v>14.14468</v>
+        <v>1.768085</v>
       </c>
       <c r="N7" s="25">
         <f ca="1" t="shared" si="4"/>
@@ -3388,7 +3410,7 @@
         <v>2635.98</v>
       </c>
       <c r="P7" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="26">
         <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3396,7 +3418,7 @@
       </c>
       <c r="R7" s="27">
         <f t="shared" si="5"/>
-        <v>0.142857142857143</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:24">
@@ -3417,7 +3439,7 @@
       </c>
       <c r="F8" s="23">
         <f ca="1">D8/(C8/X5*U$5)</f>
-        <v>9</v>
+        <v>1.125</v>
       </c>
       <c r="G8" s="20">
         <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3444,7 +3466,7 @@
       </c>
       <c r="M8" s="23">
         <f ca="1">K8/(J8/X5*U$5)</f>
-        <v>4.92668</v>
+        <v>0.615835</v>
       </c>
       <c r="N8" s="25">
         <f ca="1" t="shared" si="4"/>
@@ -3455,7 +3477,7 @@
         <v>2732</v>
       </c>
       <c r="P8" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q8" s="26">
         <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3463,7 +3485,7 @@
       </c>
       <c r="R8" s="27">
         <f t="shared" si="5"/>
-        <v>0.619047619047619</v>
+        <v>0.866666666666667</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:24">
@@ -3484,7 +3506,7 @@
       </c>
       <c r="F9" s="23">
         <f ca="1">D9/(C9/X5*U$5)</f>
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G9" s="20">
         <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3511,7 +3533,7 @@
       </c>
       <c r="M9" s="23">
         <f ca="1">K9/(J9/X5*U$5)</f>
-        <v>10.47924</v>
+        <v>1.309905</v>
       </c>
       <c r="N9" s="25">
         <f ca="1" t="shared" si="4"/>
@@ -3522,7 +3544,7 @@
         <v>5748</v>
       </c>
       <c r="P9" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="26">
         <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3530,7 +3552,7 @@
       </c>
       <c r="R9" s="27">
         <f t="shared" si="5"/>
-        <v>0.0952380952380952</v>
+        <v>0.133333333333333</v>
       </c>
       <c r="V9" s="30" t="s">
         <v>21</v>
@@ -3589,7 +3611,7 @@
       </c>
       <c r="M10" s="23">
         <f ca="1">K10/(J10/X5*U$5)</f>
-        <v>11.912</v>
+        <v>1.489</v>
       </c>
       <c r="N10" s="25">
         <f ca="1" t="shared" si="4"/>
@@ -3600,7 +3622,7 @@
         <v>3704</v>
       </c>
       <c r="P10" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="26">
         <f>_xlfn.XLOOKUP(B10,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3641,7 +3663,7 @@
       </c>
       <c r="F11" s="32">
         <f ca="1">D11/(C11/X5*U$5)</f>
-        <v>5.07142857142857</v>
+        <v>0.633928571428571</v>
       </c>
       <c r="G11" s="31">
         <f>SUM(G4:G10)</f>
@@ -3663,13 +3685,13 @@
       </c>
       <c r="M11" s="32">
         <f ca="1">K11/(J11/X5*U$5)</f>
-        <v>7.88944571428571</v>
+        <v>0.986180714285714</v>
       </c>
       <c r="N11" s="31"/>
       <c r="O11" s="33"/>
       <c r="P11" s="31">
         <f>SUM(P4:P10)</f>
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="Q11" s="31">
         <f>SUM(Q4:Q10)</f>
@@ -3677,7 +3699,7 @@
       </c>
       <c r="R11" s="34">
         <f t="shared" si="5"/>
-        <v>0.149659863945578</v>
+        <v>0.20952380952381</v>
       </c>
       <c r="V11" s="30" t="s">
         <v>23</v>
@@ -3711,7 +3733,7 @@
       </c>
       <c r="F12" s="23">
         <f ca="1">D12/(C12/X5*U$5)</f>
-        <v>14</v>
+        <v>1.75</v>
       </c>
       <c r="G12" s="20">
         <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3738,7 +3760,7 @@
       </c>
       <c r="M12" s="23">
         <f ca="1">K12/(J12/X5*U$5)</f>
-        <v>13.784</v>
+        <v>1.723</v>
       </c>
       <c r="N12" s="25">
         <f ca="1" t="shared" ref="N12:N18" si="9">VLOOKUP(B:B,V:X,3,0)</f>
@@ -3749,7 +3771,7 @@
         <v>13055</v>
       </c>
       <c r="P12" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q12" s="26">
         <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3757,7 +3779,7 @@
       </c>
       <c r="R12" s="27">
         <f t="shared" si="5"/>
-        <v>0.80952380952381</v>
+        <v>1.13333333333333</v>
       </c>
       <c r="V12" s="30" t="s">
         <v>24</v>
@@ -3789,7 +3811,7 @@
       </c>
       <c r="F13" s="23">
         <f ca="1">D13/(C13/X5*U$5)</f>
-        <v>18.98</v>
+        <v>2.3725</v>
       </c>
       <c r="G13" s="20">
         <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3816,7 +3838,7 @@
       </c>
       <c r="M13" s="23">
         <f ca="1">K13/(J13/X5*U$5)</f>
-        <v>10.8128</v>
+        <v>1.3516</v>
       </c>
       <c r="N13" s="25">
         <f ca="1" t="shared" si="9"/>
@@ -3827,7 +3849,7 @@
         <v>6851.8</v>
       </c>
       <c r="P13" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q13" s="26">
         <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3835,7 +3857,7 @@
       </c>
       <c r="R13" s="27">
         <f t="shared" si="5"/>
-        <v>1.23809523809524</v>
+        <v>1.73333333333333</v>
       </c>
       <c r="V13" s="30" t="s">
         <v>25</v>
@@ -3867,7 +3889,7 @@
       </c>
       <c r="F14" s="23">
         <f ca="1">D14/(C14/X5*U$5)</f>
-        <v>4.5</v>
+        <v>0.5625</v>
       </c>
       <c r="G14" s="20">
         <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3894,7 +3916,7 @@
       </c>
       <c r="M14" s="23">
         <f ca="1">K14/(J14/X5*U$5)</f>
-        <v>3.312</v>
+        <v>0.414</v>
       </c>
       <c r="N14" s="25">
         <f ca="1" t="shared" si="9"/>
@@ -3905,7 +3927,7 @@
         <v>2439</v>
       </c>
       <c r="P14" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q14" s="26">
         <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3913,7 +3935,7 @@
       </c>
       <c r="R14" s="27">
         <f t="shared" si="5"/>
-        <v>0.142857142857143</v>
+        <v>0.2</v>
       </c>
       <c r="V14" s="30" t="s">
         <v>26</v>
@@ -3945,7 +3967,7 @@
       </c>
       <c r="F15" s="23">
         <f ca="1">D15/(C15/X5*U$5)</f>
-        <v>12.5</v>
+        <v>1.5625</v>
       </c>
       <c r="G15" s="20">
         <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3972,7 +3994,7 @@
       </c>
       <c r="M15" s="23">
         <f ca="1">K15/(J15/X5*U$5)</f>
-        <v>15.628</v>
+        <v>1.9535</v>
       </c>
       <c r="N15" s="25">
         <f ca="1" t="shared" si="9"/>
@@ -3983,7 +4005,7 @@
         <v>11230</v>
       </c>
       <c r="P15" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q15" s="26">
         <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
@@ -3991,7 +4013,7 @@
       </c>
       <c r="R15" s="27">
         <f t="shared" si="5"/>
-        <v>0.523809523809524</v>
+        <v>0.733333333333333</v>
       </c>
       <c r="V15" s="30" t="s">
         <v>27</v>
@@ -4023,7 +4045,7 @@
       </c>
       <c r="F16" s="23">
         <f ca="1">D16/(C16/X5*U$5)</f>
-        <v>14</v>
+        <v>1.75</v>
       </c>
       <c r="G16" s="20">
         <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -4050,7 +4072,7 @@
       </c>
       <c r="M16" s="23">
         <f ca="1">K16/(J16/X5*U$5)</f>
-        <v>8.5506</v>
+        <v>1.068825</v>
       </c>
       <c r="N16" s="25">
         <f ca="1" t="shared" si="9"/>
@@ -4061,7 +4083,7 @@
         <v>6539.605</v>
       </c>
       <c r="P16" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q16" s="26">
         <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
@@ -4069,7 +4091,7 @@
       </c>
       <c r="R16" s="27">
         <f t="shared" si="5"/>
-        <v>0.761904761904762</v>
+        <v>1.06666666666667</v>
       </c>
       <c r="V16" s="30" t="s">
         <v>30</v>
@@ -4101,7 +4123,7 @@
       </c>
       <c r="F17" s="23">
         <f ca="1">D17/(C17/X5*U$5)</f>
-        <v>10</v>
+        <v>1.25</v>
       </c>
       <c r="G17" s="20">
         <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -4128,7 +4150,7 @@
       </c>
       <c r="M17" s="23">
         <f ca="1">K17/(J17/X5*U$5)</f>
-        <v>4.076</v>
+        <v>0.5095</v>
       </c>
       <c r="N17" s="25">
         <f ca="1" t="shared" si="9"/>
@@ -4139,7 +4161,7 @@
         <v>4800.64</v>
       </c>
       <c r="P17" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q17" s="26">
         <f>_xlfn.XLOOKUP(B17,全光组网!A:A,全光组网!B:B,0)</f>
@@ -4147,7 +4169,7 @@
       </c>
       <c r="R17" s="27">
         <f t="shared" si="5"/>
-        <v>0.428571428571429</v>
+        <v>0.6</v>
       </c>
       <c r="V17" s="30" t="s">
         <v>31</v>
@@ -4179,7 +4201,7 @@
       </c>
       <c r="F18" s="23">
         <f ca="1">D18/(C18/X5*U$5)</f>
-        <v>3.5</v>
+        <v>0.4375</v>
       </c>
       <c r="G18" s="20">
         <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -4206,7 +4228,7 @@
       </c>
       <c r="M18" s="23">
         <f ca="1">K18/(J18/X5*U$5)</f>
-        <v>-0.5082</v>
+        <v>-0.063525</v>
       </c>
       <c r="N18" s="25">
         <f ca="1" t="shared" si="9"/>
@@ -4217,7 +4239,7 @@
         <v>-210.575</v>
       </c>
       <c r="P18" s="21">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Q18" s="26">
         <f>_xlfn.XLOOKUP(B18,全光组网!A:A,全光组网!B:B,0)</f>
@@ -4225,7 +4247,7 @@
       </c>
       <c r="R18" s="27">
         <f t="shared" si="5"/>
-        <v>0.285714285714286</v>
+        <v>0.4</v>
       </c>
       <c r="V18" s="30" t="s">
         <v>32</v>
@@ -4258,7 +4280,7 @@
       </c>
       <c r="F19" s="32">
         <f ca="1">D19/(C19/X5*U$5)</f>
-        <v>11.0685714285714</v>
+        <v>1.38357142857143</v>
       </c>
       <c r="G19" s="37">
         <f>SUM(G12:G18)</f>
@@ -4280,13 +4302,13 @@
       </c>
       <c r="M19" s="38">
         <f ca="1">K19/(J19/X5*U$5)</f>
-        <v>7.95074285714286</v>
+        <v>0.993842857142857</v>
       </c>
       <c r="N19" s="37"/>
       <c r="O19" s="39"/>
       <c r="P19" s="37">
         <f>SUM(P12:P18)</f>
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="Q19" s="37">
         <f>SUM(Q12:Q18)</f>
@@ -4294,7 +4316,7 @@
       </c>
       <c r="R19" s="34">
         <f t="shared" si="5"/>
-        <v>0.598639455782313</v>
+        <v>0.838095238095238</v>
       </c>
       <c r="V19" s="30" t="s">
         <v>33</v>
@@ -4326,7 +4348,7 @@
       </c>
       <c r="F20" s="45">
         <f ca="1">D20/(C20/X5*U$5)</f>
-        <v>8.67272727272727</v>
+        <v>1.08409090909091</v>
       </c>
       <c r="G20" s="46">
         <f>G11+G19</f>
@@ -4348,20 +4370,22 @@
       </c>
       <c r="M20" s="50">
         <f ca="1">K20/(J20/X5*U$5)</f>
-        <v>7.92009428571429</v>
+        <v>0.990011785714286</v>
       </c>
       <c r="N20" s="51"/>
       <c r="O20" s="52" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="53"/>
+      <c r="P20" s="53">
+        <v>210</v>
+      </c>
       <c r="Q20" s="54">
         <f>Q11+Q19</f>
         <v>110</v>
       </c>
       <c r="R20" s="27">
-        <f>Q20/P21</f>
-        <v>0.354838709677419</v>
+        <f t="shared" si="5"/>
+        <v>0.523809523809524</v>
       </c>
       <c r="V20" s="30" t="s">
         <v>34</v>
@@ -5033,7 +5057,7 @@
         <v>60</v>
       </c>
       <c r="L35" s="74">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="M35" s="74">
         <f>交付高装!D2</f>
@@ -5041,7 +5065,7 @@
       </c>
       <c r="N35" s="75">
         <f>交付高装!E2</f>
-        <v>0.226190476190476</v>
+        <v>0.316666666666667</v>
       </c>
       <c r="O35"/>
       <c r="P35" s="76" t="s">
@@ -5052,11 +5076,11 @@
       </c>
       <c r="R35" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P35,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>38.16</v>
+        <v>4.77</v>
       </c>
       <c r="S35" s="78">
         <f ca="1" t="shared" ref="S35:S44" si="11">R35/Q35</f>
-        <v>8.97882352941176</v>
+        <v>1.12235294117647</v>
       </c>
       <c r="T35" s="79">
         <f ca="1">RANK(S35,S35:S43)</f>
@@ -5091,7 +5115,7 @@
         <v>61</v>
       </c>
       <c r="L36" s="74">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="M36" s="74">
         <f>交付高装!D3</f>
@@ -5099,7 +5123,7 @@
       </c>
       <c r="N36" s="75">
         <f>交付高装!E3</f>
-        <v>0.202380952380952</v>
+        <v>0.283333333333333</v>
       </c>
       <c r="O36"/>
       <c r="P36" s="76" t="s">
@@ -5110,11 +5134,11 @@
       </c>
       <c r="R36" s="84">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P36,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>82.15</v>
+        <v>10.27</v>
       </c>
       <c r="S36" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>14.2869565217391</v>
+        <v>1.78608695652174</v>
       </c>
       <c r="T36" s="85">
         <f ca="1">RANK(S36,S35:S43)</f>
@@ -5149,7 +5173,7 @@
         <v>63</v>
       </c>
       <c r="L37" s="74">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="M37" s="74">
         <f>交付高装!D4</f>
@@ -5157,7 +5181,7 @@
       </c>
       <c r="N37" s="75">
         <f>交付高装!E4</f>
-        <v>0.702380952380952</v>
+        <v>0.983333333333333</v>
       </c>
       <c r="O37"/>
       <c r="P37" s="76" t="s">
@@ -5168,11 +5192,11 @@
       </c>
       <c r="R37" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P37,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>116.6</v>
+        <v>14.58</v>
       </c>
       <c r="S37" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>33.125</v>
+        <v>4.14204545454545</v>
       </c>
       <c r="T37" s="79">
         <f ca="1">RANK(S37,S35:S43)</f>
@@ -5207,7 +5231,7 @@
         <v>65</v>
       </c>
       <c r="L38" s="74">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="M38" s="74">
         <f>交付高装!D5</f>
@@ -5215,7 +5239,7 @@
       </c>
       <c r="N38" s="75">
         <f>交付高装!E5</f>
-        <v>0.245901639344262</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="O38"/>
       <c r="P38" s="76" t="s">
@@ -5226,11 +5250,11 @@
       </c>
       <c r="R38" s="84">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P38,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>37.42</v>
+        <v>4.68</v>
       </c>
       <c r="S38" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>9.42569269521411</v>
+        <v>1.17884130982368</v>
       </c>
       <c r="T38" s="85">
         <f ca="1">RANK(S38,S35:S43)</f>
@@ -5267,7 +5291,7 @@
         <v>41</v>
       </c>
       <c r="L39" s="89">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M39" s="89">
         <f>交付高装!D6</f>
@@ -5275,7 +5299,7 @@
       </c>
       <c r="N39" s="90">
         <f>交付高装!E6</f>
-        <v>0.261904761904762</v>
+        <v>0.366666666666667</v>
       </c>
       <c r="O39"/>
       <c r="P39" s="76" t="s">
@@ -5286,11 +5310,11 @@
       </c>
       <c r="R39" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P39,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>35.47</v>
+        <v>4.43</v>
       </c>
       <c r="S39" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>14.9033613445378</v>
+        <v>1.86134453781513</v>
       </c>
       <c r="T39" s="79">
         <f ca="1">RANK(S39,S35:S43)</f>
@@ -5325,7 +5349,7 @@
         <v>43</v>
       </c>
       <c r="L40" s="89">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M40" s="89">
         <f>交付高装!D7</f>
@@ -5333,7 +5357,7 @@
       </c>
       <c r="N40" s="90">
         <f>交付高装!E7</f>
-        <v>0.142857142857143</v>
+        <v>0.2</v>
       </c>
       <c r="O40"/>
       <c r="P40" s="76" t="s">
@@ -5344,11 +5368,11 @@
       </c>
       <c r="R40" s="92">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P40,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>31.55</v>
+        <v>3.94</v>
       </c>
       <c r="S40" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>12.1346153846154</v>
+        <v>1.51538461538462</v>
       </c>
       <c r="T40" s="85">
         <f ca="1">RANK(S40,S35:S43)</f>
@@ -5382,7 +5406,7 @@
         <v>44</v>
       </c>
       <c r="L41" s="89">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M41" s="89">
         <f>交付高装!D8</f>
@@ -5390,7 +5414,7 @@
       </c>
       <c r="N41" s="90">
         <f>交付高装!E8</f>
-        <v>0.142857142857143</v>
+        <v>0.2</v>
       </c>
       <c r="O41"/>
       <c r="P41" s="76" t="s">
@@ -5401,11 +5425,11 @@
       </c>
       <c r="R41" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P41,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>27.6</v>
+        <v>3.45</v>
       </c>
       <c r="S41" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>11.4522821576763</v>
+        <v>1.43153526970954</v>
       </c>
       <c r="T41" s="79">
         <f ca="1">RANK(S41,S35:S43)</f>
@@ -5439,7 +5463,7 @@
         <v>45</v>
       </c>
       <c r="L42" s="89">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M42" s="89">
         <f>交付高装!D9</f>
@@ -5447,7 +5471,7 @@
       </c>
       <c r="N42" s="90">
         <f>交付高装!E9</f>
-        <v>0.30952380952381</v>
+        <v>0.433333333333333</v>
       </c>
       <c r="O42"/>
       <c r="P42" s="76" t="s">
@@ -5458,11 +5482,11 @@
       </c>
       <c r="R42" s="84">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P42,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>38.38</v>
+        <v>4.8</v>
       </c>
       <c r="S42" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>11.9192546583851</v>
+        <v>1.49068322981366</v>
       </c>
       <c r="T42" s="85">
         <f ca="1">RANK(S42,S35:S43)</f>
@@ -5495,7 +5519,7 @@
         <v>46</v>
       </c>
       <c r="L43" s="89">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M43" s="89">
         <f>交付高装!D10</f>
@@ -5503,7 +5527,7 @@
       </c>
       <c r="N43" s="90">
         <f>交付高装!E10</f>
-        <v>1.02380952380952</v>
+        <v>1.43333333333333</v>
       </c>
       <c r="O43"/>
       <c r="P43" s="76" t="s">
@@ -5514,11 +5538,11 @@
       </c>
       <c r="R43" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P43,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>39.39</v>
+        <v>4.92</v>
       </c>
       <c r="S43" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>11.7232142857143</v>
+        <v>1.46428571428571</v>
       </c>
       <c r="T43" s="79">
         <f ca="1">RANK(S43,S35:S43)</f>
@@ -5533,7 +5557,7 @@
         <v>47</v>
       </c>
       <c r="L44" s="89">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M44" s="89">
         <f>交付高装!D11</f>
@@ -5541,7 +5565,7 @@
       </c>
       <c r="N44" s="90">
         <f>交付高装!E11</f>
-        <v>0.380952380952381</v>
+        <v>0.533333333333333</v>
       </c>
       <c r="O44"/>
       <c r="P44" s="96" t="s">
@@ -5553,11 +5577,11 @@
       </c>
       <c r="R44" s="97">
         <f ca="1">SUM(R35:R43)</f>
-        <v>446.72</v>
+        <v>55.84</v>
       </c>
       <c r="S44" s="98">
         <f ca="1" t="shared" si="11"/>
-        <v>14.1996185632549</v>
+        <v>1.77495232040687</v>
       </c>
       <c r="T44" s="99" t="s">
         <v>73</v>
@@ -5571,7 +5595,7 @@
         <v>48</v>
       </c>
       <c r="L45" s="89">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="M45" s="89">
         <f>交付高装!D12</f>
@@ -5579,7 +5603,7 @@
       </c>
       <c r="N45" s="90">
         <f>交付高装!E12</f>
-        <v>0.357142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="O45"/>
     </row>
@@ -5591,7 +5615,7 @@
         <v>74</v>
       </c>
       <c r="L46" s="89">
-        <v>310</v>
+        <v>210</v>
       </c>
       <c r="M46" s="89">
         <f>SUM(M35:M38)</f>
@@ -5599,7 +5623,7 @@
       </c>
       <c r="N46" s="90">
         <f>M46/L46</f>
-        <v>0.354838709677419</v>
+        <v>0.523809523809524</v>
       </c>
       <c r="O46"/>
     </row>
@@ -5628,7 +5652,7 @@
     <row r="50" ht="13.5" customHeight="1" spans="1:15">
       <c r="A50" s="106" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止6月3日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+        <v>（数据截止6月24日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
       </c>
       <c r="B50" s="107"/>
       <c r="C50" s="107"/>
@@ -5636,7 +5660,7 @@
       <c r="F50"/>
       <c r="G50" s="109" t="str">
         <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止6月3日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
+        <v>（数据截止6月24日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
       </c>
     </row>
     <row r="51" ht="14.75" customHeight="1" spans="1:15">
@@ -6644,7 +6668,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aab5e57b-8037-4bf4-a5e3-2297d3afadbc}</x14:id>
+          <x14:id>{7e9633ac-b9a7-477d-b85d-894e9dfcaebc}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -6663,7 +6687,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aab5e57b-8037-4bf4-a5e3-2297d3afadbc}">
+          <x14:cfRule type="dataBar" id="{7e9633ac-b9a7-477d-b85d-894e9dfcaebc}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -8052,7 +8076,7 @@
         <v>60</v>
       </c>
       <c r="C2">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D2">
         <f t="array" ref="D2">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B2))</f>
@@ -8060,7 +8084,7 @@
       </c>
       <c r="E2" s="6">
         <f t="shared" ref="E2:E13" si="0">D2/C2</f>
-        <v>0.226190476190476</v>
+        <v>0.316666666666667</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>33</v>
@@ -8083,7 +8107,7 @@
         <v>61</v>
       </c>
       <c r="C3">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D3">
         <f t="array" ref="D3">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B3))</f>
@@ -8091,7 +8115,7 @@
       </c>
       <c r="E3" s="6">
         <f t="shared" si="0"/>
-        <v>0.202380952380952</v>
+        <v>0.283333333333333</v>
       </c>
       <c r="J3" s="7" t="s">
         <v>27</v>
@@ -8114,7 +8138,7 @@
         <v>63</v>
       </c>
       <c r="C4">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D4">
         <f t="array" ref="D4">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B4))</f>
@@ -8122,7 +8146,7 @@
       </c>
       <c r="E4" s="6">
         <f t="shared" si="0"/>
-        <v>0.702380952380952</v>
+        <v>0.983333333333333</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>26</v>
@@ -8145,15 +8169,15 @@
         <v>65</v>
       </c>
       <c r="C5">
-        <v>61</v>
-      </c>
-      <c r="D5">
+        <v>45</v>
+      </c>
+      <c r="D5" cm="1">
         <f t="array" ref="D5">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B5))</f>
         <v>15</v>
       </c>
       <c r="E5" s="6">
         <f t="shared" si="0"/>
-        <v>0.245901639344262</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>21</v>
@@ -8176,15 +8200,15 @@
         <v>41</v>
       </c>
       <c r="C6">
-        <v>42</v>
-      </c>
-      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="D6" cm="1">
         <f t="array" ref="D6">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B6))</f>
         <v>11</v>
       </c>
       <c r="E6" s="6">
         <f t="shared" si="0"/>
-        <v>0.261904761904762</v>
+        <v>0.366666666666667</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>32</v>
@@ -8207,7 +8231,7 @@
         <v>43</v>
       </c>
       <c r="C7">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <f t="array" ref="D7">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B7))</f>
@@ -8215,7 +8239,7 @@
       </c>
       <c r="E7" s="6">
         <f t="shared" si="0"/>
-        <v>0.142857142857143</v>
+        <v>0.2</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>24</v>
@@ -8238,7 +8262,7 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <f t="array" ref="D8">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B8))</f>
@@ -8246,7 +8270,7 @@
       </c>
       <c r="E8" s="6">
         <f t="shared" si="0"/>
-        <v>0.142857142857143</v>
+        <v>0.2</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>23</v>
@@ -8269,7 +8293,7 @@
         <v>45</v>
       </c>
       <c r="C9">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <f t="array" ref="D9">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B9))</f>
@@ -8277,7 +8301,7 @@
       </c>
       <c r="E9" s="6">
         <f t="shared" si="0"/>
-        <v>0.30952380952381</v>
+        <v>0.433333333333333</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>25</v>
@@ -8300,7 +8324,7 @@
         <v>46</v>
       </c>
       <c r="C10">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <f t="array" ref="D10">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B10))</f>
@@ -8308,7 +8332,7 @@
       </c>
       <c r="E10" s="6">
         <f t="shared" si="0"/>
-        <v>1.02380952380952</v>
+        <v>1.43333333333333</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>30</v>
@@ -8331,15 +8355,15 @@
         <v>47</v>
       </c>
       <c r="C11">
-        <v>42</v>
-      </c>
-      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="D11" cm="1">
         <f t="array" ref="D11">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B11))</f>
         <v>16</v>
       </c>
       <c r="E11" s="6">
         <f t="shared" si="0"/>
-        <v>0.380952380952381</v>
+        <v>0.533333333333333</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>31</v>
@@ -8362,7 +8386,7 @@
         <v>48</v>
       </c>
       <c r="C12">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <f t="array" ref="D12">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B12))</f>
@@ -8370,7 +8394,7 @@
       </c>
       <c r="E12" s="6">
         <f t="shared" si="0"/>
-        <v>0.357142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>34</v>
@@ -8395,7 +8419,7 @@
       <c r="C13">
         <v>25</v>
       </c>
-      <c r="D13">
+      <c r="D13" cm="1">
         <f t="array" ref="D13">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B13))</f>
         <v>0</v>
       </c>

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -16,6 +16,7 @@
     <sheet name="商机统计" sheetId="7" r:id="rId7"/>
     <sheet name="交付高装" sheetId="8" r:id="rId8"/>
     <sheet name="激励" sheetId="9" r:id="rId9"/>
+    <sheet name="积分" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,30 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="94">
   <si>
     <t>团队</t>
   </si>
@@ -286,7 +265,22 @@
     <t>王洪明(挂整体指标)</t>
   </si>
   <si>
-    <t>累计商机统计表（所有数据）</t>
+    <t>净增积分</t>
+  </si>
+  <si>
+    <t>基本面</t>
+  </si>
+  <si>
+    <t>双线</t>
+  </si>
+  <si>
+    <t>增量积分落格率</t>
+  </si>
+  <si>
+    <t>高套数</t>
+  </si>
+  <si>
+    <t>新增积分（全业务）</t>
   </si>
   <si>
     <t>户数</t>
@@ -296,12 +290,6 @@
   </si>
   <si>
     <t>积分累计数</t>
-  </si>
-  <si>
-    <t>高套数</t>
-  </si>
-  <si>
-    <t>新增积分（全业务）</t>
   </si>
   <si>
     <t>负责客户经理</t>
@@ -347,13 +335,25 @@
     <numFmt numFmtId="177" formatCode="0.0%"/>
     <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="SimSun"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="WenQuanYi Micro Hei"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -488,46 +488,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FFDDEEFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1B3A6B"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1C2B3A"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -676,12 +636,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="60">
+  <fills count="52">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC2D8F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -788,60 +754,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B3A6B"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2E5FA3"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFD700"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8DC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8D8D8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F8F8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8A070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF5EE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBF2FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1032,12 +944,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="65">
+  <borders count="50">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1189,12 +1116,14 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right/>
-      <top/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1202,12 +1131,8 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1561,214 +1486,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF1B3A6B"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1B3A6B"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF1B3A6B"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF1B3A6B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF1B3A6B"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF1B3A6B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF1B3A6B"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF1B3A6B"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF1B3A6B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF1B3A6B"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF1B3A6B"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF2E5FA3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF2E5FA3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF2E5FA3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF2E5FA3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF2E5FA3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF2E5FA3"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF2E5FA3"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF2E5FA3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF1B3A6B"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF2E5FA3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF2E5FA3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF2E5FA3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF2E5FA3"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF2E5FA3"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF2E5FA3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1B3A6B"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF1B3A6B"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA0B8D8"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0B8D8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0B8D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0B8D8"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA0B8D8"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0B8D8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0B8D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0B8D8"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1B3A6B"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0B8D8"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFA0B8D8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF1B3A6B"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA0B8D8"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0B8D8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0B8D8"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFA0B8D8"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0B8D8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFA0B8D8"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF1B3A6B"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFA0B8D8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1886,490 +1603,420 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="42">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="43">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="29" borderId="57">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="43">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="44">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="45">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="58">
+    <xf numFmtId="0" fontId="33" fillId="23" borderId="46">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="58">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="45">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="59">
+    <xf numFmtId="0" fontId="35" fillId="24" borderId="47">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="48">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="30" borderId="60">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="49">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="31" borderId="61">
+    <xf numFmtId="0" fontId="38" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="31" borderId="60">
+    <xf numFmtId="0" fontId="39" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="62">
+    <xf numFmtId="0" fontId="40" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="63">
+    <xf numFmtId="0" fontId="41" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="64">
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="36" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="37" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="39" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="39" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="40" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="40" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="41" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="41" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="42" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="42" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="43" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="43" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="44" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="44" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="45" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="45" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="46" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="46" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="47" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="47" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="48" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="48" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="49" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="49" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="50" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="50" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="51" borderId="0">
+    <xf numFmtId="0" fontId="41" fillId="51" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="52" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="53" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="54" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="55" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="56" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="57" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="58" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="59" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="14" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="15" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="18" fillId="16" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="20" fillId="17" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="19" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="20" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="18" fillId="17" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="20" fillId="18" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="21" fillId="8" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="23" fillId="9" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2423,25 +2070,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="33">
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2672,25 +2301,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="22"/>
-      <tableStyleElement type="headerRow" dxfId="21"/>
-      <tableStyleElement type="totalRow" dxfId="20"/>
-      <tableStyleElement type="firstColumn" dxfId="19"/>
-      <tableStyleElement type="lastColumn" dxfId="18"/>
-      <tableStyleElement type="firstRowStripe" dxfId="17"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="16"/>
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="totalRow" dxfId="14"/>
+      <tableStyleElement type="firstColumn" dxfId="13"/>
+      <tableStyleElement type="lastColumn" dxfId="12"/>
+      <tableStyleElement type="firstRowStripe" dxfId="11"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="32"/>
-      <tableStyleElement type="totalRow" dxfId="31"/>
-      <tableStyleElement type="firstRowStripe" dxfId="30"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="29"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="28"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="27"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="26"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="25"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="24"/>
-      <tableStyleElement type="pageFieldValues" dxfId="23"/>
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="totalRow" dxfId="25"/>
+      <tableStyleElement type="firstRowStripe" dxfId="24"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="23"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="22"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="21"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="20"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="19"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="18"/>
+      <tableStyleElement type="pageFieldValues" dxfId="17"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2702,70 +2331,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表5_111617" displayName="表5_111617" ref="A51:D65" totalsRowShown="0">
-  <sortState ref="A51:D65">
-    <sortCondition ref="C51:C65" descending="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表5_1113" displayName="表5_1113" ref="F1:I2" totalsRowShown="0">
+  <sortState ref="F1:I2">
+    <sortCondition ref="H1:H2" descending="1"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" name="客户经理" dataDxfId="0">
-      <calculatedColumnFormula>商机统计!A2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" name="户数" dataDxfId="1">
-      <calculatedColumnFormula>商机统计!B2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" name="高套累计数" dataDxfId="2">
-      <calculatedColumnFormula>商机统计!C2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" name="积分累计数" dataDxfId="3">
-      <calculatedColumnFormula>商机统计!D2</calculatedColumnFormula>
-    </tableColumn>
+    <tableColumn id="1" name="客户经理" dataDxfId="2"/>
+    <tableColumn id="2" name="户数" dataDxfId="3"/>
+    <tableColumn id="3" name="高套累计数" dataDxfId="4"/>
+    <tableColumn id="4" name="积分累计数" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表5_11" displayName="表5_11" ref="G51:H65" totalsRowShown="0">
-  <sortState ref="G51:H65">
-    <sortCondition ref="H51:H65" descending="1"/>
-  </sortState>
-  <tableColumns count="2">
-    <tableColumn id="1" name="客户经理" dataDxfId="4">
-      <calculatedColumnFormula>商机统计!F2</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" name="户数" dataDxfId="5">
-      <calculatedColumnFormula>商机统计!G2</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表5_1113" displayName="表5_1113" ref="F1:I2" totalsRowShown="0">
-  <sortState ref="F1:I2">
-    <sortCondition ref="H1:H2" descending="1"/>
-  </sortState>
-  <tableColumns count="4">
-    <tableColumn id="1" name="客户经理" dataDxfId="8"/>
-    <tableColumn id="2" name="户数" dataDxfId="9"/>
-    <tableColumn id="3" name="高套累计数" dataDxfId="10"/>
-    <tableColumn id="4" name="积分累计数" dataDxfId="11"/>
-  </tableColumns>
-  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表3_12" displayName="表3_12" ref="A1:D15" totalsRowShown="0">
   <sortState ref="A1:D15">
     <sortCondition ref="C1:C15" descending="1"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" name="客户经理" dataDxfId="12"/>
-    <tableColumn id="2" name="户数" dataDxfId="13"/>
-    <tableColumn id="3" name="高套累计数" dataDxfId="14"/>
-    <tableColumn id="4" name="积分累计数" dataDxfId="15"/>
+    <tableColumn id="1" name="客户经理" dataDxfId="6"/>
+    <tableColumn id="2" name="户数" dataDxfId="7"/>
+    <tableColumn id="3" name="高套累计数" dataDxfId="8"/>
+    <tableColumn id="4" name="积分累计数" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3024,1926 +2613,1926 @@
   <dimension ref="A1:X104"/>
   <sheetFormatPr defaultColWidth="10.6363636363636" defaultRowHeight="14"/>
   <cols>
-    <col min="4" max="4" width="9.25454545454545" style="11" customWidth="1"/>
-    <col min="5" max="5" width="9.90909090909091" style="11" customWidth="1"/>
-    <col min="6" max="7" width="9.25454545454545" style="11" customWidth="1"/>
-    <col min="9" max="10" width="9.25454545454545" style="11" customWidth="1"/>
-    <col min="11" max="11" width="10.9" style="11" customWidth="1"/>
-    <col min="15" max="15" width="9.90909090909091" style="11" customWidth="1"/>
+    <col min="4" max="4" width="9.25454545454545" style="13" customWidth="1"/>
+    <col min="5" max="5" width="9.90909090909091" style="13" customWidth="1"/>
+    <col min="6" max="7" width="9.25454545454545" style="13" customWidth="1"/>
+    <col min="9" max="10" width="9.25454545454545" style="13" customWidth="1"/>
+    <col min="11" max="11" width="10.9" style="13" customWidth="1"/>
+    <col min="15" max="15" width="9.90909090909091" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="str">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至6月24日）</v>
-      </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
-      <c r="Q1" s="14"/>
-      <c r="R1" s="15"/>
+        <v>完美一单积分完成通报（截至6月28日）</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A2" s="16"/>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="13" t="s">
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-      <c r="M2" s="14"/>
-      <c r="N2" s="14"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="13" t="s">
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="14"/>
-      <c r="R2" s="15"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="17"/>
     </row>
     <row r="3" ht="70" customHeight="1" spans="1:24">
-      <c r="A3" s="18"/>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="N3" s="13" t="s">
+      <c r="N3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="19" t="s">
+      <c r="R3" s="23" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="24">
         <v>10</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="25">
         <f>_xlfn.XLOOKUP(B4,高套!A:A,高套!B:B,0)</f>
-        <v>5</v>
-      </c>
-      <c r="E4" s="22">
+        <v>0</v>
+      </c>
+      <c r="E4" s="26">
         <f t="shared" ref="E4:E20" si="0">D4/C4</f>
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="23">
+        <v>0</v>
+      </c>
+      <c r="F4" s="27">
         <f ca="1">D4/(C4/X5*U$5)</f>
-        <v>0.625</v>
-      </c>
-      <c r="G4" s="20">
+        <v>0</v>
+      </c>
+      <c r="G4" s="24">
         <f>_xlfn.XLOOKUP(B4,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>6.5</v>
-      </c>
-      <c r="H4" s="24" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="H4" s="28" t="str">
         <f t="shared" ref="H4:H10" si="1">IF(G4&gt;=3,"否","是")</f>
-        <v>否</v>
-      </c>
-      <c r="I4" s="20" t="str">
+        <v>是</v>
+      </c>
+      <c r="I4" s="24" t="str">
         <f t="shared" ref="I4:I10" si="2">IF(G4&gt;=15,"金牌",IF(G4&gt;=12,"银牌",""))</f>
         <v/>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="24">
         <v>2500</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>936</v>
-      </c>
-      <c r="L4" s="23">
+        <v>282</v>
+      </c>
+      <c r="L4" s="27">
         <f ca="1" t="shared" ref="L4:L20" si="3">K4/J4</f>
-        <v>0.3744</v>
-      </c>
-      <c r="M4" s="23">
+        <v>0.1128</v>
+      </c>
+      <c r="M4" s="27">
         <f ca="1">K4/(J4/X5*U$5)</f>
-        <v>0.468</v>
-      </c>
-      <c r="N4" s="25">
+        <v>0.120857142857143</v>
+      </c>
+      <c r="N4" s="29">
         <f ca="1" t="shared" ref="N4:N10" si="4">VLOOKUP(B:B,V:X,3,0)</f>
         <v>12</v>
       </c>
-      <c r="O4" s="25">
+      <c r="O4" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>3241.5</v>
-      </c>
-      <c r="P4" s="21">
+        <v>1036</v>
+      </c>
+      <c r="P4" s="25">
         <v>15</v>
       </c>
-      <c r="Q4" s="26">
+      <c r="Q4" s="30">
         <f>_xlfn.XLOOKUP(B4,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>4</v>
-      </c>
-      <c r="R4" s="27">
-        <f t="shared" ref="R4:R20" si="5">Q4/P4</f>
-        <v>0.266666666666667</v>
+        <v>0</v>
+      </c>
+      <c r="R4" s="31">
+        <f t="shared" ref="R4:R21" si="5">Q4/P4</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A5" s="16"/>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="24">
         <v>10</v>
       </c>
-      <c r="D5" s="21">
+      <c r="D5" s="25">
         <f>_xlfn.XLOOKUP(B5,高套!A:A,高套!B:B,0)</f>
-        <v>1.5</v>
-      </c>
-      <c r="E5" s="22">
+        <v>0</v>
+      </c>
+      <c r="E5" s="26">
         <f t="shared" si="0"/>
-        <v>0.15</v>
-      </c>
-      <c r="F5" s="23">
+        <v>0</v>
+      </c>
+      <c r="F5" s="27">
         <f ca="1">D5/(C5/X5*U$5)</f>
-        <v>0.1875</v>
-      </c>
-      <c r="G5" s="20">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24">
         <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>6</v>
-      </c>
-      <c r="H5" s="24" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I5" s="20" t="str">
+        <v>是</v>
+      </c>
+      <c r="I5" s="24" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="24">
         <v>2500</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1059.34</v>
-      </c>
-      <c r="L5" s="23">
+        <v>287</v>
+      </c>
+      <c r="L5" s="27">
         <f ca="1" t="shared" si="3"/>
-        <v>0.423736</v>
-      </c>
-      <c r="M5" s="23">
+        <v>0.1148</v>
+      </c>
+      <c r="M5" s="27">
         <f ca="1">K5/(J5/X5*U$5)</f>
-        <v>0.52967</v>
-      </c>
-      <c r="N5" s="25">
+        <v>0.123</v>
+      </c>
+      <c r="N5" s="29">
         <f ca="1" t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="O5" s="25">
+        <v>11</v>
+      </c>
+      <c r="O5" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1774.27</v>
-      </c>
-      <c r="P5" s="21">
+        <v>502.5</v>
+      </c>
+      <c r="P5" s="25">
         <v>15</v>
       </c>
-      <c r="Q5" s="26">
+      <c r="Q5" s="30">
         <f>_xlfn.XLOOKUP(B5,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="R5" s="27">
+      <c r="R5" s="31">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="T5" s="28" t="str">
+      <c r="T5" s="32" t="str">
         <f ca="1">MONTH(TODAY()-1)&amp;"月"</f>
         <v>6月</v>
       </c>
-      <c r="U5" s="28">
+      <c r="U5" s="32">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>24</v>
-      </c>
-      <c r="V5" s="28"/>
-      <c r="W5" s="29"/>
+        <v>28</v>
+      </c>
+      <c r="V5" s="32"/>
+      <c r="W5" s="33"/>
       <c r="X5">
         <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
         <v>30</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A6" s="16"/>
-      <c r="B6" s="20" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="24">
         <v>10</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="25">
         <f>_xlfn.XLOOKUP(B6,高套!A:A,高套!B:B,0)</f>
-        <v>8</v>
-      </c>
-      <c r="E6" s="22">
+        <v>3</v>
+      </c>
+      <c r="E6" s="26">
         <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="F6" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="27">
         <f ca="1">D6/(C6/X5*U$5)</f>
-        <v>1</v>
-      </c>
-      <c r="G6" s="20">
+        <v>0.321428571428571</v>
+      </c>
+      <c r="G6" s="24">
         <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>9.5</v>
-      </c>
-      <c r="H6" s="24" t="str">
+        <v>3</v>
+      </c>
+      <c r="H6" s="28" t="str">
         <f t="shared" si="1"/>
         <v>否</v>
       </c>
-      <c r="I6" s="20" t="str">
+      <c r="I6" s="24" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="24">
         <v>2500</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1445.54</v>
-      </c>
-      <c r="L6" s="23">
+        <v>2291.29</v>
+      </c>
+      <c r="L6" s="27">
         <f ca="1" t="shared" si="3"/>
-        <v>0.578216</v>
-      </c>
-      <c r="M6" s="23">
+        <v>0.916516</v>
+      </c>
+      <c r="M6" s="27">
         <f ca="1">K6/(J6/X5*U$5)</f>
-        <v>0.72277</v>
-      </c>
-      <c r="N6" s="25">
+        <v>0.981981428571429</v>
+      </c>
+      <c r="N6" s="29">
+        <f ca="1" t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="O6" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>4344</v>
+      </c>
+      <c r="P6" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="30">
+        <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>9</v>
+      </c>
+      <c r="R6" s="31">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A7" s="18"/>
+      <c r="B7" s="24" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="24">
+        <v>10</v>
+      </c>
+      <c r="D7" s="25">
+        <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
+        <v>26.5</v>
+      </c>
+      <c r="E7" s="26">
+        <f t="shared" si="0"/>
+        <v>2.65</v>
+      </c>
+      <c r="F7" s="27">
+        <f ca="1">D7/(C7/X5*U$5)</f>
+        <v>2.83928571428571</v>
+      </c>
+      <c r="G7" s="24">
+        <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>27.5</v>
+      </c>
+      <c r="H7" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I7" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>金牌</v>
+      </c>
+      <c r="J7" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K7" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)+2500</f>
+        <v>3258</v>
+      </c>
+      <c r="L7" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>1.3032</v>
+      </c>
+      <c r="M7" s="27">
+        <f ca="1">K7/(J7/X5*U$5)</f>
+        <v>1.39628571428571</v>
+      </c>
+      <c r="N7" s="29">
+        <f ca="1" t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="O7" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>1783.5</v>
+      </c>
+      <c r="P7" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q7" s="30">
+        <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A8" s="18"/>
+      <c r="B8" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="24">
+        <v>10</v>
+      </c>
+      <c r="D8" s="25">
+        <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
+        <v>18.33</v>
+      </c>
+      <c r="E8" s="26">
+        <f t="shared" si="0"/>
+        <v>1.833</v>
+      </c>
+      <c r="F8" s="27">
+        <f ca="1">D8/(C8/X5*U$5)</f>
+        <v>1.96392857142857</v>
+      </c>
+      <c r="G8" s="24">
+        <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>19.83</v>
+      </c>
+      <c r="H8" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I8" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v>金牌</v>
+      </c>
+      <c r="J8" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K8" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>1766.66</v>
+      </c>
+      <c r="L8" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.706664</v>
+      </c>
+      <c r="M8" s="27">
+        <f ca="1">K8/(J8/X5*U$5)</f>
+        <v>0.75714</v>
+      </c>
+      <c r="N8" s="29">
+        <f ca="1" t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="O8" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>4429</v>
+      </c>
+      <c r="P8" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="30">
+        <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A9" s="18"/>
+      <c r="B9" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="24">
+        <v>10</v>
+      </c>
+      <c r="D9" s="25">
+        <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
+        <v>9.52</v>
+      </c>
+      <c r="E9" s="26">
+        <f t="shared" si="0"/>
+        <v>0.952</v>
+      </c>
+      <c r="F9" s="27">
+        <f ca="1">D9/(C9/X5*U$5)</f>
+        <v>1.02</v>
+      </c>
+      <c r="G9" s="24">
+        <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>9.52</v>
+      </c>
+      <c r="H9" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I9" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J9" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K9" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>2182</v>
+      </c>
+      <c r="L9" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.8728</v>
+      </c>
+      <c r="M9" s="27">
+        <f ca="1">K9/(J9/X5*U$5)</f>
+        <v>0.935142857142857</v>
+      </c>
+      <c r="N9" s="29">
+        <f ca="1" t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="O9" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>5026</v>
+      </c>
+      <c r="P9" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q9" s="30">
+        <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>9</v>
+      </c>
+      <c r="R9" s="31">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+      <c r="V9" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="W9">
+        <f ca="1" t="shared" ref="W9:W22" si="6">VLOOKUP(V:V,B:K,10,0)</f>
+        <v>282</v>
+      </c>
+      <c r="X9">
+        <f ca="1" t="shared" ref="X9:X22" si="7">RANK(W9,W$9:W$22,0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A10" s="18"/>
+      <c r="B10" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="24">
+        <v>10</v>
+      </c>
+      <c r="D10" s="25">
+        <f>_xlfn.XLOOKUP(B10,高套!A:A,高套!B:B,0)</f>
+        <v>2.5</v>
+      </c>
+      <c r="E10" s="26">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="F10" s="27">
+        <f ca="1">D10/(C10/X5*U$5)</f>
+        <v>0.267857142857143</v>
+      </c>
+      <c r="G10" s="24">
+        <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>5.5</v>
+      </c>
+      <c r="H10" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>否</v>
+      </c>
+      <c r="I10" s="24" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J10" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K10" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>1254.03</v>
+      </c>
+      <c r="L10" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.501612</v>
+      </c>
+      <c r="M10" s="27">
+        <f ca="1">K10/(J10/X5*U$5)</f>
+        <v>0.537441428571429</v>
+      </c>
+      <c r="N10" s="29">
         <f ca="1" t="shared" si="4"/>
         <v>8</v>
       </c>
-      <c r="O6" s="25">
+      <c r="O10" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>4097.34</v>
-      </c>
-      <c r="P6" s="21">
+        <v>3491</v>
+      </c>
+      <c r="P10" s="25">
         <v>15</v>
       </c>
-      <c r="Q6" s="26">
-        <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="27">
+      <c r="Q10" s="30">
+        <f>_xlfn.XLOOKUP(B10,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>5</v>
+      </c>
+      <c r="R10" s="31">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A7" s="16"/>
-      <c r="B7" s="20" t="s">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="V10" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="W10">
+        <f ca="1" t="shared" si="6"/>
+        <v>287</v>
+      </c>
+      <c r="X10">
+        <f ca="1" t="shared" si="7"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A11" s="22"/>
+      <c r="B11" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="35">
+        <f>SUM(C4:C10)</f>
+        <v>70</v>
+      </c>
+      <c r="D11" s="35">
+        <f>SUM(D4:D10)</f>
+        <v>59.85</v>
+      </c>
+      <c r="E11" s="36">
+        <f t="shared" si="0"/>
+        <v>0.855</v>
+      </c>
+      <c r="F11" s="36">
+        <f ca="1">D11/(C11/X5*U$5)</f>
+        <v>0.916071428571428</v>
+      </c>
+      <c r="G11" s="35">
+        <f>SUM(G4:G10)</f>
+        <v>67.35</v>
+      </c>
+      <c r="H11" s="36"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37">
+        <f>SUM(J4:J10)</f>
+        <v>17500</v>
+      </c>
+      <c r="K11" s="35">
+        <f ca="1">SUM(K4:K10)</f>
+        <v>11320.98</v>
+      </c>
+      <c r="L11" s="36">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.646913142857143</v>
+      </c>
+      <c r="M11" s="36">
+        <f ca="1">K11/(J11/X5*U$5)</f>
+        <v>0.693121224489796</v>
+      </c>
+      <c r="N11" s="35"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="35">
+        <f>SUM(P4:P10)</f>
+        <v>105</v>
+      </c>
+      <c r="Q11" s="35">
+        <f>SUM(Q4:Q10)</f>
+        <v>23</v>
+      </c>
+      <c r="R11" s="38">
+        <f t="shared" si="5"/>
+        <v>0.219047619047619</v>
+      </c>
+      <c r="V11" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="W11">
+        <f ca="1" t="shared" si="6"/>
+        <v>2291.29</v>
+      </c>
+      <c r="X11">
+        <f ca="1" t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A12" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="24">
+        <v>10</v>
+      </c>
+      <c r="D12" s="25">
+        <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="27">
+        <f ca="1">D12/(C12/X5*U$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="24">
+        <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="28" t="str">
+        <f t="shared" ref="H12:H18" si="8">IF(G12&gt;=3,"否","是")</f>
+        <v>是</v>
+      </c>
+      <c r="I12" s="24" t="str">
+        <f t="shared" ref="I12:I18" si="9">IF(G12&gt;=15,"金牌",IF(G12&gt;=12,"银牌",""))</f>
+        <v/>
+      </c>
+      <c r="J12" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K12" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>63</v>
+      </c>
+      <c r="L12" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.0252</v>
+      </c>
+      <c r="M12" s="27">
+        <f ca="1">K12/(J12/X5*U$5)</f>
+        <v>0.027</v>
+      </c>
+      <c r="N12" s="29">
+        <f ca="1" t="shared" ref="N12:N18" si="10">VLOOKUP(B:B,V:X,3,0)</f>
+        <v>14</v>
+      </c>
+      <c r="O12" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>122.5</v>
+      </c>
+      <c r="P12" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="30">
+        <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V12" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20">
+      <c r="W12">
+        <f ca="1" t="shared" si="6"/>
+        <v>3258</v>
+      </c>
+      <c r="X12">
+        <f ca="1" t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A13" s="39"/>
+      <c r="B13" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="24">
         <v>10</v>
       </c>
-      <c r="D7" s="21">
-        <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
-        <v>4</v>
-      </c>
-      <c r="E7" s="22">
+      <c r="D13" s="25">
+        <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
+        <v>5</v>
+      </c>
+      <c r="E13" s="26">
         <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-      <c r="F7" s="23">
-        <f ca="1">D7/(C7/X5*U$5)</f>
         <v>0.5</v>
       </c>
-      <c r="G7" s="20">
-        <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>5.5</v>
-      </c>
-      <c r="H7" s="24" t="str">
-        <f t="shared" si="1"/>
+      <c r="F13" s="27">
+        <f ca="1">D13/(C13/X5*U$5)</f>
+        <v>0.535714285714286</v>
+      </c>
+      <c r="G13" s="24">
+        <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H13" s="28" t="str">
+        <f t="shared" si="8"/>
         <v>否</v>
       </c>
-      <c r="I7" s="20" t="str">
-        <f t="shared" si="2"/>
+      <c r="I13" s="24" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J7" s="20">
+      <c r="J13" s="24">
         <v>2500</v>
       </c>
-      <c r="K7" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)+2500</f>
-        <v>3536.17</v>
-      </c>
-      <c r="L7" s="23">
+      <c r="K13" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>689</v>
+      </c>
+      <c r="L13" s="27">
         <f ca="1" t="shared" si="3"/>
-        <v>1.414468</v>
-      </c>
-      <c r="M7" s="23">
-        <f ca="1">K7/(J7/X5*U$5)</f>
-        <v>1.768085</v>
-      </c>
-      <c r="N7" s="25">
-        <f ca="1" t="shared" si="4"/>
+        <v>0.2756</v>
+      </c>
+      <c r="M13" s="27">
+        <f ca="1">K13/(J13/X5*U$5)</f>
+        <v>0.295285714285714</v>
+      </c>
+      <c r="N13" s="29">
+        <f ca="1" t="shared" si="10"/>
+        <v>9</v>
+      </c>
+      <c r="O13" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>1339.5</v>
+      </c>
+      <c r="P13" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q13" s="30">
+        <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R13" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="V13" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="W13">
+        <f ca="1" t="shared" si="6"/>
+        <v>1766.66</v>
+      </c>
+      <c r="X13">
+        <f ca="1" t="shared" si="7"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A14" s="39"/>
+      <c r="B14" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="24">
+        <v>10</v>
+      </c>
+      <c r="D14" s="25">
+        <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
         <v>2</v>
       </c>
-      <c r="O7" s="25">
+      <c r="E14" s="26">
+        <f t="shared" si="0"/>
+        <v>0.2</v>
+      </c>
+      <c r="F14" s="27">
+        <f ca="1">D14/(C14/X5*U$5)</f>
+        <v>0.214285714285714</v>
+      </c>
+      <c r="G14" s="24">
+        <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>3</v>
+      </c>
+      <c r="H14" s="28" t="str">
+        <f t="shared" si="8"/>
+        <v>否</v>
+      </c>
+      <c r="I14" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="J14" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K14" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>387</v>
+      </c>
+      <c r="L14" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.1548</v>
+      </c>
+      <c r="M14" s="27">
+        <f ca="1">K14/(J14/X5*U$5)</f>
+        <v>0.165857142857143</v>
+      </c>
+      <c r="N14" s="29">
+        <f ca="1" t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="O14" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>2635.98</v>
-      </c>
-      <c r="P7" s="21">
+        <v>1661.5</v>
+      </c>
+      <c r="P14" s="25">
         <v>15</v>
       </c>
-      <c r="Q7" s="26">
-        <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
+      <c r="Q14" s="30">
+        <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
         <v>3</v>
       </c>
-      <c r="R7" s="27">
+      <c r="R14" s="31">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A8" s="16"/>
-      <c r="B8" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="20">
+      <c r="V14" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="W14">
+        <f ca="1" t="shared" si="6"/>
+        <v>2182</v>
+      </c>
+      <c r="X14">
+        <f ca="1" t="shared" si="7"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A15" s="39"/>
+      <c r="B15" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="24">
         <v>10</v>
       </c>
-      <c r="D8" s="21">
-        <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
-        <v>9</v>
-      </c>
-      <c r="E8" s="22">
+      <c r="D15" s="25">
+        <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
+        <v>6.5</v>
+      </c>
+      <c r="E15" s="26">
         <f t="shared" si="0"/>
-        <v>0.9</v>
-      </c>
-      <c r="F8" s="23">
-        <f ca="1">D8/(C8/X5*U$5)</f>
-        <v>1.125</v>
-      </c>
-      <c r="G8" s="20">
-        <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>9</v>
-      </c>
-      <c r="H8" s="24" t="str">
-        <f t="shared" si="1"/>
+        <v>0.65</v>
+      </c>
+      <c r="F15" s="27">
+        <f ca="1">D15/(C15/X5*U$5)</f>
+        <v>0.696428571428572</v>
+      </c>
+      <c r="G15" s="24">
+        <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>6.5</v>
+      </c>
+      <c r="H15" s="28" t="str">
+        <f t="shared" si="8"/>
         <v>否</v>
       </c>
-      <c r="I8" s="20" t="str">
-        <f t="shared" si="2"/>
+      <c r="I15" s="24" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J8" s="20">
+      <c r="J15" s="24">
         <v>2500</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K15" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1231.67</v>
-      </c>
-      <c r="L8" s="23">
+        <v>2117.76</v>
+      </c>
+      <c r="L15" s="27">
         <f ca="1" t="shared" si="3"/>
-        <v>0.492668</v>
-      </c>
-      <c r="M8" s="23">
-        <f ca="1">K8/(J8/X5*U$5)</f>
-        <v>0.615835</v>
-      </c>
-      <c r="N8" s="25">
-        <f ca="1" t="shared" si="4"/>
-        <v>9</v>
-      </c>
-      <c r="O8" s="25">
+        <v>0.847104</v>
+      </c>
+      <c r="M15" s="27">
+        <f ca="1">K15/(J15/X5*U$5)</f>
+        <v>0.907611428571429</v>
+      </c>
+      <c r="N15" s="29">
+        <f ca="1" t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="O15" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>2732</v>
-      </c>
-      <c r="P8" s="21">
+        <v>6846.5</v>
+      </c>
+      <c r="P15" s="25">
         <v>15</v>
       </c>
-      <c r="Q8" s="26">
-        <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
+      <c r="Q15" s="30">
+        <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>15</v>
+      </c>
+      <c r="R15" s="31">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="V15" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="W15">
+        <f ca="1" t="shared" si="6"/>
+        <v>1254.03</v>
+      </c>
+      <c r="X15">
+        <f ca="1" t="shared" si="7"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A16" s="39"/>
+      <c r="B16" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="24">
+        <v>10</v>
+      </c>
+      <c r="D16" s="25">
+        <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
+        <v>11.5</v>
+      </c>
+      <c r="E16" s="26">
+        <f t="shared" si="0"/>
+        <v>1.15</v>
+      </c>
+      <c r="F16" s="27">
+        <f ca="1">D16/(C16/X5*U$5)</f>
+        <v>1.23214285714286</v>
+      </c>
+      <c r="G16" s="24">
+        <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
         <v>13</v>
       </c>
-      <c r="R8" s="27">
+      <c r="H16" s="28" t="str">
+        <f t="shared" si="8"/>
+        <v>否</v>
+      </c>
+      <c r="I16" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v>银牌</v>
+      </c>
+      <c r="J16" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K16" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>2096</v>
+      </c>
+      <c r="L16" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.8384</v>
+      </c>
+      <c r="M16" s="27">
+        <f ca="1">K16/(J16/X5*U$5)</f>
+        <v>0.898285714285714</v>
+      </c>
+      <c r="N16" s="29">
+        <f ca="1" t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="O16" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>7387</v>
+      </c>
+      <c r="P16" s="25">
+        <v>15</v>
+      </c>
+      <c r="Q16" s="30">
+        <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>10</v>
+      </c>
+      <c r="R16" s="31">
         <f t="shared" si="5"/>
-        <v>0.866666666666667</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A9" s="16"/>
-      <c r="B9" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="20">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="V16" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="W16">
+        <f ca="1" t="shared" si="6"/>
+        <v>63</v>
+      </c>
+      <c r="X16">
+        <f ca="1" t="shared" si="7"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A17" s="39"/>
+      <c r="B17" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="24">
         <v>10</v>
       </c>
-      <c r="D9" s="21">
-        <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
-        <v>8</v>
-      </c>
-      <c r="E9" s="22">
+      <c r="D17" s="25">
+        <f>_xlfn.XLOOKUP(B17,高套!A:A,高套!B:B,0)</f>
+        <v>9.94</v>
+      </c>
+      <c r="E17" s="26">
         <f t="shared" si="0"/>
-        <v>0.8</v>
-      </c>
-      <c r="F9" s="23">
-        <f ca="1">D9/(C9/X5*U$5)</f>
-        <v>1</v>
-      </c>
-      <c r="G9" s="20">
-        <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>14.5</v>
-      </c>
-      <c r="H9" s="24" t="str">
-        <f t="shared" si="1"/>
+        <v>0.994</v>
+      </c>
+      <c r="F17" s="27">
+        <f ca="1">D17/(C17/X5*U$5)</f>
+        <v>1.065</v>
+      </c>
+      <c r="G17" s="24">
+        <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>9.94</v>
+      </c>
+      <c r="H17" s="28" t="str">
+        <f t="shared" si="8"/>
         <v>否</v>
       </c>
-      <c r="I9" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v>银牌</v>
-      </c>
-      <c r="J9" s="20">
+      <c r="I17" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="J17" s="24">
         <v>2500</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K17" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2619.81</v>
-      </c>
-      <c r="L9" s="23">
+        <v>1415</v>
+      </c>
+      <c r="L17" s="27">
         <f ca="1" t="shared" si="3"/>
-        <v>1.047924</v>
-      </c>
-      <c r="M9" s="23">
-        <f ca="1">K9/(J9/X5*U$5)</f>
-        <v>1.309905</v>
-      </c>
-      <c r="N9" s="25">
-        <f ca="1" t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="O9" s="25">
+        <v>0.566</v>
+      </c>
+      <c r="M17" s="27">
+        <f ca="1">K17/(J17/X5*U$5)</f>
+        <v>0.606428571428572</v>
+      </c>
+      <c r="N17" s="29">
+        <f ca="1" t="shared" si="10"/>
+        <v>7</v>
+      </c>
+      <c r="O17" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>5748</v>
-      </c>
-      <c r="P9" s="21">
+        <v>4117.5</v>
+      </c>
+      <c r="P17" s="25">
         <v>15</v>
       </c>
-      <c r="Q9" s="26">
-        <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>2</v>
-      </c>
-      <c r="R9" s="27">
-        <f t="shared" si="5"/>
-        <v>0.133333333333333</v>
-      </c>
-      <c r="V9" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="W9">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>936</v>
-      </c>
-      <c r="X9">
-        <f ca="1" t="shared" ref="X9:X22" si="6">RANK(W9,W$9:W$22,0)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A10" s="16"/>
-      <c r="B10" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="20">
-        <v>10</v>
-      </c>
-      <c r="D10" s="21">
-        <f>_xlfn.XLOOKUP(B10,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="23">
-        <f ca="1">D10/(C10/X5*U$5)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="20">
-        <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+      <c r="Q17" s="30">
+        <f>_xlfn.XLOOKUP(B17,全光组网!A:A,全光组网!B:B,0)</f>
         <v>3</v>
       </c>
-      <c r="H10" s="24" t="str">
-        <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I10" s="20" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J10" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K10" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2978</v>
-      </c>
-      <c r="L10" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>1.1912</v>
-      </c>
-      <c r="M10" s="23">
-        <f ca="1">K10/(J10/X5*U$5)</f>
-        <v>1.489</v>
-      </c>
-      <c r="N10" s="25">
-        <f ca="1" t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O10" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>3704</v>
-      </c>
-      <c r="P10" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="26">
-        <f>_xlfn.XLOOKUP(B10,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="27">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="V10" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="W10">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>1059.34</v>
-      </c>
-      <c r="X10">
-        <f ca="1" t="shared" si="6"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A11" s="18"/>
-      <c r="B11" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="31">
-        <f>SUM(C4:C10)</f>
-        <v>70</v>
-      </c>
-      <c r="D11" s="31">
-        <f>SUM(D4:D10)</f>
-        <v>35.5</v>
-      </c>
-      <c r="E11" s="32">
-        <f t="shared" si="0"/>
-        <v>0.507142857142857</v>
-      </c>
-      <c r="F11" s="32">
-        <f ca="1">D11/(C11/X5*U$5)</f>
-        <v>0.633928571428571</v>
-      </c>
-      <c r="G11" s="31">
-        <f>SUM(G4:G10)</f>
-        <v>54</v>
-      </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33">
-        <f>SUM(J4:J10)</f>
-        <v>17500</v>
-      </c>
-      <c r="K11" s="31">
-        <f ca="1">SUM(K4:K10)</f>
-        <v>13806.53</v>
-      </c>
-      <c r="L11" s="32">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.788944571428571</v>
-      </c>
-      <c r="M11" s="32">
-        <f ca="1">K11/(J11/X5*U$5)</f>
-        <v>0.986180714285714</v>
-      </c>
-      <c r="N11" s="31"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="31">
-        <f>SUM(P4:P10)</f>
-        <v>105</v>
-      </c>
-      <c r="Q11" s="31">
-        <f>SUM(Q4:Q10)</f>
-        <v>22</v>
-      </c>
-      <c r="R11" s="34">
-        <f t="shared" si="5"/>
-        <v>0.20952380952381</v>
-      </c>
-      <c r="V11" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="W11">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>1445.54</v>
-      </c>
-      <c r="X11">
-        <f ca="1" t="shared" si="6"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A12" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="20">
-        <v>10</v>
-      </c>
-      <c r="D12" s="21">
-        <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
-        <v>14</v>
-      </c>
-      <c r="E12" s="22">
-        <f t="shared" si="0"/>
-        <v>1.4</v>
-      </c>
-      <c r="F12" s="23">
-        <f ca="1">D12/(C12/X5*U$5)</f>
-        <v>1.75</v>
-      </c>
-      <c r="G12" s="20">
-        <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>18</v>
-      </c>
-      <c r="H12" s="24" t="str">
-        <f t="shared" ref="H12:H18" si="7">IF(G12&gt;=3,"否","是")</f>
-        <v>否</v>
-      </c>
-      <c r="I12" s="20" t="str">
-        <f t="shared" ref="I12:I18" si="8">IF(G12&gt;=15,"金牌",IF(G12&gt;=12,"银牌",""))</f>
-        <v>金牌</v>
-      </c>
-      <c r="J12" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K12" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>3446</v>
-      </c>
-      <c r="L12" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>1.3784</v>
-      </c>
-      <c r="M12" s="23">
-        <f ca="1">K12/(J12/X5*U$5)</f>
-        <v>1.723</v>
-      </c>
-      <c r="N12" s="25">
-        <f ca="1" t="shared" ref="N12:N18" si="9">VLOOKUP(B:B,V:X,3,0)</f>
-        <v>3</v>
-      </c>
-      <c r="O12" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>13055</v>
-      </c>
-      <c r="P12" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="26">
-        <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>17</v>
-      </c>
-      <c r="R12" s="27">
-        <f t="shared" si="5"/>
-        <v>1.13333333333333</v>
-      </c>
-      <c r="V12" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="W12">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>3536.17</v>
-      </c>
-      <c r="X12">
-        <f ca="1" t="shared" si="6"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A13" s="35"/>
-      <c r="B13" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="20">
-        <v>10</v>
-      </c>
-      <c r="D13" s="21">
-        <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
-        <v>18.98</v>
-      </c>
-      <c r="E13" s="22">
-        <f t="shared" si="0"/>
-        <v>1.898</v>
-      </c>
-      <c r="F13" s="23">
-        <f ca="1">D13/(C13/X5*U$5)</f>
-        <v>2.3725</v>
-      </c>
-      <c r="G13" s="20">
-        <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>22.98</v>
-      </c>
-      <c r="H13" s="24" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I13" s="20" t="str">
-        <f t="shared" si="8"/>
-        <v>金牌</v>
-      </c>
-      <c r="J13" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K13" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2703.2</v>
-      </c>
-      <c r="L13" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>1.08128</v>
-      </c>
-      <c r="M13" s="23">
-        <f ca="1">K13/(J13/X5*U$5)</f>
-        <v>1.3516</v>
-      </c>
-      <c r="N13" s="25">
-        <f ca="1" t="shared" si="9"/>
-        <v>5</v>
-      </c>
-      <c r="O13" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>6851.8</v>
-      </c>
-      <c r="P13" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="26">
-        <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>26</v>
-      </c>
-      <c r="R13" s="27">
-        <f t="shared" si="5"/>
-        <v>1.73333333333333</v>
-      </c>
-      <c r="V13" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="W13">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>1231.67</v>
-      </c>
-      <c r="X13">
-        <f ca="1" t="shared" si="6"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A14" s="35"/>
-      <c r="B14" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="20">
-        <v>10</v>
-      </c>
-      <c r="D14" s="21">
-        <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
-        <v>4.5</v>
-      </c>
-      <c r="E14" s="22">
-        <f t="shared" si="0"/>
-        <v>0.45</v>
-      </c>
-      <c r="F14" s="23">
-        <f ca="1">D14/(C14/X5*U$5)</f>
-        <v>0.5625</v>
-      </c>
-      <c r="G14" s="20">
-        <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>4.5</v>
-      </c>
-      <c r="H14" s="24" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I14" s="20" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J14" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K14" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>828</v>
-      </c>
-      <c r="L14" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.3312</v>
-      </c>
-      <c r="M14" s="23">
-        <f ca="1">K14/(J14/X5*U$5)</f>
-        <v>0.414</v>
-      </c>
-      <c r="N14" s="25">
-        <f ca="1" t="shared" si="9"/>
-        <v>13</v>
-      </c>
-      <c r="O14" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>2439</v>
-      </c>
-      <c r="P14" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q14" s="26">
-        <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R14" s="27">
+      <c r="R17" s="31">
         <f t="shared" si="5"/>
         <v>0.2</v>
       </c>
-      <c r="V14" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="W14">
-        <f ca="1" t="shared" ref="W14:W22" si="10">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>2619.81</v>
-      </c>
-      <c r="X14">
+      <c r="V17" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="W17">
         <f ca="1" t="shared" si="6"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A15" s="35"/>
-      <c r="B15" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="20">
+        <v>689</v>
+      </c>
+      <c r="X17">
+        <f ca="1" t="shared" si="7"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A18" s="39"/>
+      <c r="B18" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="24">
         <v>10</v>
       </c>
-      <c r="D15" s="21">
-        <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
-        <v>12.5</v>
-      </c>
-      <c r="E15" s="22">
+      <c r="D18" s="25">
+        <f>_xlfn.XLOOKUP(B18,高套!A:A,高套!B:B,0)</f>
+        <v>0.75</v>
+      </c>
+      <c r="E18" s="26">
         <f t="shared" si="0"/>
-        <v>1.25</v>
-      </c>
-      <c r="F15" s="23">
-        <f ca="1">D15/(C15/X5*U$5)</f>
-        <v>1.5625</v>
-      </c>
-      <c r="G15" s="20">
-        <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0.075</v>
+      </c>
+      <c r="F18" s="27">
+        <f ca="1">D18/(C18/X5*U$5)</f>
+        <v>0.0803571428571429</v>
+      </c>
+      <c r="G18" s="24">
+        <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0.75</v>
+      </c>
+      <c r="H18" s="28" t="str">
+        <f t="shared" si="8"/>
+        <v>是</v>
+      </c>
+      <c r="I18" s="24" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="J18" s="24">
+        <v>2500</v>
+      </c>
+      <c r="K18" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>154.92</v>
+      </c>
+      <c r="L18" s="27">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.061968</v>
+      </c>
+      <c r="M18" s="27">
+        <f ca="1">K18/(J18/X5*U$5)</f>
+        <v>0.0663942857142857</v>
+      </c>
+      <c r="N18" s="29">
+        <f ca="1" t="shared" si="10"/>
+        <v>13</v>
+      </c>
+      <c r="O18" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>232.38</v>
+      </c>
+      <c r="P18" s="25">
         <v>15</v>
       </c>
-      <c r="H15" s="24" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I15" s="20" t="str">
-        <f t="shared" si="8"/>
-        <v>金牌</v>
-      </c>
-      <c r="J15" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K15" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>3907</v>
-      </c>
-      <c r="L15" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>1.5628</v>
-      </c>
-      <c r="M15" s="23">
-        <f ca="1">K15/(J15/X5*U$5)</f>
-        <v>1.9535</v>
-      </c>
-      <c r="N15" s="25">
-        <f ca="1" t="shared" si="9"/>
-        <v>1</v>
-      </c>
-      <c r="O15" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>11230</v>
-      </c>
-      <c r="P15" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="26">
-        <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>11</v>
-      </c>
-      <c r="R15" s="27">
+      <c r="Q18" s="30">
+        <f>_xlfn.XLOOKUP(B18,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R18" s="31">
         <f t="shared" si="5"/>
-        <v>0.733333333333333</v>
-      </c>
-      <c r="V15" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="W15">
-        <f ca="1" t="shared" si="10"/>
-        <v>2978</v>
-      </c>
-      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="V18" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="W18">
         <f ca="1" t="shared" si="6"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A16" s="35"/>
-      <c r="B16" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="20">
+        <v>387</v>
+      </c>
+      <c r="X18">
+        <f ca="1" t="shared" si="7"/>
         <v>10</v>
       </c>
-      <c r="D16" s="21">
-        <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
-        <v>14</v>
-      </c>
-      <c r="E16" s="22">
-        <f t="shared" si="0"/>
-        <v>1.4</v>
-      </c>
-      <c r="F16" s="23">
-        <f ca="1">D16/(C16/X5*U$5)</f>
-        <v>1.75</v>
-      </c>
-      <c r="G16" s="20">
-        <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>14</v>
-      </c>
-      <c r="H16" s="24" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I16" s="20" t="str">
-        <f t="shared" si="8"/>
-        <v>银牌</v>
-      </c>
-      <c r="J16" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K16" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2137.65</v>
-      </c>
-      <c r="L16" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.85506</v>
-      </c>
-      <c r="M16" s="23">
-        <f ca="1">K16/(J16/X5*U$5)</f>
-        <v>1.068825</v>
-      </c>
-      <c r="N16" s="25">
-        <f ca="1" t="shared" si="9"/>
-        <v>7</v>
-      </c>
-      <c r="O16" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>6539.605</v>
-      </c>
-      <c r="P16" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q16" s="26">
-        <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>16</v>
-      </c>
-      <c r="R16" s="27">
-        <f t="shared" si="5"/>
-        <v>1.06666666666667</v>
-      </c>
-      <c r="V16" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="W16">
-        <f ca="1" t="shared" si="10"/>
-        <v>3446</v>
-      </c>
-      <c r="X16">
-        <f ca="1" t="shared" si="6"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A17" s="35"/>
-      <c r="B17" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="20">
-        <v>10</v>
-      </c>
-      <c r="D17" s="21">
-        <f>_xlfn.XLOOKUP(B17,高套!A:A,高套!B:B,0)</f>
-        <v>10</v>
-      </c>
-      <c r="E17" s="22">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F17" s="23">
-        <f ca="1">D17/(C17/X5*U$5)</f>
-        <v>1.25</v>
-      </c>
-      <c r="G17" s="20">
-        <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>10</v>
-      </c>
-      <c r="H17" s="24" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I17" s="20" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J17" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K17" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1019</v>
-      </c>
-      <c r="L17" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.4076</v>
-      </c>
-      <c r="M17" s="23">
-        <f ca="1">K17/(J17/X5*U$5)</f>
-        <v>0.5095</v>
-      </c>
-      <c r="N17" s="25">
-        <f ca="1" t="shared" si="9"/>
-        <v>11</v>
-      </c>
-      <c r="O17" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>4800.64</v>
-      </c>
-      <c r="P17" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q17" s="26">
-        <f>_xlfn.XLOOKUP(B17,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>9</v>
-      </c>
-      <c r="R17" s="27">
-        <f t="shared" si="5"/>
-        <v>0.6</v>
-      </c>
-      <c r="V17" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="W17">
-        <f ca="1" t="shared" si="10"/>
-        <v>2703.2</v>
-      </c>
-      <c r="X17">
-        <f ca="1" t="shared" si="6"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A18" s="35"/>
-      <c r="B18" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="20">
-        <v>10</v>
-      </c>
-      <c r="D18" s="21">
-        <f>_xlfn.XLOOKUP(B18,高套!A:A,高套!B:B,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="E18" s="22">
-        <f t="shared" si="0"/>
-        <v>0.35</v>
-      </c>
-      <c r="F18" s="23">
-        <f ca="1">D18/(C18/X5*U$5)</f>
-        <v>0.4375</v>
-      </c>
-      <c r="G18" s="20">
-        <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3.5</v>
-      </c>
-      <c r="H18" s="24" t="str">
-        <f t="shared" si="7"/>
-        <v>否</v>
-      </c>
-      <c r="I18" s="20" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="J18" s="20">
-        <v>2500</v>
-      </c>
-      <c r="K18" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>-127.05</v>
-      </c>
-      <c r="L18" s="23">
-        <f ca="1" t="shared" si="3"/>
-        <v>-0.05082</v>
-      </c>
-      <c r="M18" s="23">
-        <f ca="1">K18/(J18/X5*U$5)</f>
-        <v>-0.063525</v>
-      </c>
-      <c r="N18" s="25">
-        <f ca="1" t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="O18" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>-210.575</v>
-      </c>
-      <c r="P18" s="21">
-        <v>15</v>
-      </c>
-      <c r="Q18" s="26">
-        <f>_xlfn.XLOOKUP(B18,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>6</v>
-      </c>
-      <c r="R18" s="27">
-        <f t="shared" si="5"/>
-        <v>0.4</v>
-      </c>
-      <c r="V18" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="W18">
-        <f ca="1" t="shared" si="10"/>
-        <v>828</v>
-      </c>
-      <c r="X18">
-        <f ca="1" t="shared" si="6"/>
-        <v>13</v>
-      </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A19" s="36"/>
-      <c r="B19" s="37" t="s">
+      <c r="A19" s="40"/>
+      <c r="B19" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="41">
         <f>SUM(C12:C18)</f>
         <v>70</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="41">
         <f>SUM(D12:D18)</f>
-        <v>77.48</v>
-      </c>
-      <c r="E19" s="38">
+        <v>35.69</v>
+      </c>
+      <c r="E19" s="42">
         <f t="shared" si="0"/>
-        <v>1.10685714285714</v>
-      </c>
-      <c r="F19" s="32">
+        <v>0.509857142857143</v>
+      </c>
+      <c r="F19" s="36">
         <f ca="1">D19/(C19/X5*U$5)</f>
-        <v>1.38357142857143</v>
-      </c>
-      <c r="G19" s="37">
+        <v>0.546275510204081</v>
+      </c>
+      <c r="G19" s="41">
         <f>SUM(G12:G18)</f>
-        <v>87.98</v>
-      </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="39">
+        <v>39.69</v>
+      </c>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43">
         <f>SUM(J12:J18)</f>
         <v>17500</v>
       </c>
-      <c r="K19" s="37">
+      <c r="K19" s="41">
         <f ca="1">SUM(K12:K18)</f>
-        <v>13913.8</v>
-      </c>
-      <c r="L19" s="38">
+        <v>6922.68</v>
+      </c>
+      <c r="L19" s="42">
         <f ca="1" t="shared" si="3"/>
-        <v>0.795074285714286</v>
-      </c>
-      <c r="M19" s="38">
+        <v>0.395581714285714</v>
+      </c>
+      <c r="M19" s="42">
         <f ca="1">K19/(J19/X5*U$5)</f>
-        <v>0.993842857142857</v>
-      </c>
-      <c r="N19" s="37"/>
-      <c r="O19" s="39"/>
-      <c r="P19" s="37">
+        <v>0.423837551020408</v>
+      </c>
+      <c r="N19" s="41"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="41">
         <f>SUM(P12:P18)</f>
         <v>105</v>
       </c>
-      <c r="Q19" s="37">
+      <c r="Q19" s="41">
         <f>SUM(Q12:Q18)</f>
-        <v>88</v>
-      </c>
-      <c r="R19" s="34">
+        <v>31</v>
+      </c>
+      <c r="R19" s="38">
         <f t="shared" si="5"/>
-        <v>0.838095238095238</v>
-      </c>
-      <c r="V19" s="30" t="s">
+        <v>0.295238095238095</v>
+      </c>
+      <c r="V19" s="34" t="s">
         <v>33</v>
       </c>
       <c r="W19">
-        <f ca="1" t="shared" si="10"/>
-        <v>3907</v>
+        <f ca="1" t="shared" si="6"/>
+        <v>2117.76</v>
       </c>
       <c r="X19">
-        <f ca="1" t="shared" si="6"/>
-        <v>1</v>
+        <f ca="1" t="shared" si="7"/>
+        <v>4</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:24">
-      <c r="A20" s="40" t="s">
+      <c r="A20" s="44" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="42">
+      <c r="B20" s="45"/>
+      <c r="C20" s="46">
         <v>132</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="47">
         <f>_xlfn.XLOOKUP("端州",高套!A:A,高套!B:B,0)</f>
-        <v>114.48</v>
-      </c>
-      <c r="E20" s="44">
+        <v>95.54</v>
+      </c>
+      <c r="E20" s="48">
         <f t="shared" si="0"/>
-        <v>0.867272727272727</v>
-      </c>
-      <c r="F20" s="45">
+        <v>0.723787878787879</v>
+      </c>
+      <c r="F20" s="49">
         <f ca="1">D20/(C20/X5*U$5)</f>
-        <v>1.08409090909091</v>
-      </c>
-      <c r="G20" s="46">
+        <v>0.775487012987013</v>
+      </c>
+      <c r="G20" s="50">
         <f>G11+G19</f>
-        <v>141.98</v>
-      </c>
-      <c r="H20" s="45"/>
-      <c r="I20" s="47"/>
-      <c r="J20" s="48">
+        <v>107.04</v>
+      </c>
+      <c r="H20" s="49"/>
+      <c r="I20" s="51"/>
+      <c r="J20" s="52">
         <f>J11+J19</f>
         <v>35000</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="46">
         <f ca="1">K11+K19</f>
-        <v>27720.33</v>
-      </c>
-      <c r="L20" s="49">
+        <v>18243.66</v>
+      </c>
+      <c r="L20" s="53">
         <f ca="1" t="shared" si="3"/>
-        <v>0.792009428571429</v>
-      </c>
-      <c r="M20" s="50">
+        <v>0.521247428571429</v>
+      </c>
+      <c r="M20" s="54">
         <f ca="1">K20/(J20/X5*U$5)</f>
-        <v>0.990011785714286</v>
-      </c>
-      <c r="N20" s="51"/>
-      <c r="O20" s="52" t="s">
+        <v>0.558479387755102</v>
+      </c>
+      <c r="N20" s="55"/>
+      <c r="O20" s="56" t="s">
         <v>38</v>
       </c>
-      <c r="P20" s="53">
+      <c r="P20" s="57">
         <v>210</v>
       </c>
-      <c r="Q20" s="54">
+      <c r="Q20" s="58">
         <f>Q11+Q19</f>
-        <v>110</v>
-      </c>
-      <c r="R20" s="27">
+        <v>54</v>
+      </c>
+      <c r="R20" s="31">
         <f t="shared" si="5"/>
-        <v>0.523809523809524</v>
-      </c>
-      <c r="V20" s="30" t="s">
+        <v>0.257142857142857</v>
+      </c>
+      <c r="V20" s="34" t="s">
         <v>34</v>
       </c>
       <c r="W20">
-        <f ca="1" t="shared" si="10"/>
-        <v>2137.65</v>
+        <f ca="1" t="shared" si="6"/>
+        <v>2096</v>
       </c>
       <c r="X20">
+        <f ca="1" t="shared" si="7"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:24">
+      <c r="A21" s="22"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="40"/>
+      <c r="I21" s="60"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="61"/>
+      <c r="O21" s="56" t="s">
+        <v>39</v>
+      </c>
+      <c r="P21" s="62">
+        <v>310</v>
+      </c>
+      <c r="Q21" s="63">
+        <f>_xlfn.XLOOKUP(O21,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>233</v>
+      </c>
+      <c r="R21" s="31">
+        <f t="shared" si="5"/>
+        <v>0.751612903225806</v>
+      </c>
+      <c r="V21" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="W21">
         <f ca="1" t="shared" si="6"/>
+        <v>154.92</v>
+      </c>
+      <c r="X21">
+        <f ca="1" t="shared" si="7"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A22" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="24">
+        <f>高装高套!B2</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="27"/>
+      <c r="J22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="24">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N22" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O22" s="29">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P22" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R22" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="V22" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="W22">
+        <f ca="1" t="shared" si="6"/>
+        <v>1415</v>
+      </c>
+      <c r="X22">
+        <f ca="1" t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" spans="1:24">
-      <c r="A21" s="18"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="55"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="55"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="55"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="57"/>
-      <c r="O21" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="P21" s="58">
-        <v>310</v>
-      </c>
-      <c r="Q21" s="59">
-        <f>_xlfn.XLOOKUP(O21,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>274</v>
-      </c>
-      <c r="R21" s="27">
-        <f>Q21/P21</f>
-        <v>0.883870967741936</v>
-      </c>
-      <c r="V21" s="60" t="s">
-        <v>36</v>
-      </c>
-      <c r="W21">
-        <f ca="1" t="shared" si="10"/>
-        <v>-127.05</v>
-      </c>
-      <c r="X21">
-        <f ca="1" t="shared" si="6"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A22" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="20">
-        <f>高装高套!B2</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="20">
+    <row r="23" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A23" s="39"/>
+      <c r="B23" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="24">
+        <f>高装高套!B3</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K23" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M22" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N22" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O22" s="25">
+      <c r="L23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N23" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O23" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="P22" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q22" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R22" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="V22" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="W22">
-        <f ca="1" t="shared" si="10"/>
-        <v>1019</v>
-      </c>
-      <c r="X22">
-        <f ca="1" t="shared" si="6"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A23" s="35"/>
-      <c r="B23" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="20">
-        <f>高装高套!B3</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K23" s="20">
+      <c r="P23" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R23" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A24" s="39"/>
+      <c r="B24" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="24">
+        <f>高装高套!B4</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K24" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M23" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N23" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O23" s="25">
+      <c r="L24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N24" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O24" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>313.5</v>
-      </c>
-      <c r="P23" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q23" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R23" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A24" s="35"/>
-      <c r="B24" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="20">
-        <f>高装高套!B4</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K24" s="20">
+        <v>786.5</v>
+      </c>
+      <c r="P24" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q24" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R24" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A25" s="39"/>
+      <c r="B25" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="24">
+        <f>高装高套!B5</f>
+        <v>1</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M24" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N24" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O24" s="25">
+        <v>143</v>
+      </c>
+      <c r="L25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N25" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O25" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P24" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q24" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R24" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A25" s="35"/>
-      <c r="B25" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="20">
-        <f>高装高套!B5</f>
-        <v>2</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="20">
+        <v>281</v>
+      </c>
+      <c r="P25" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q25" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R25" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" ht="14.25" customHeight="1" spans="1:24">
+      <c r="A26" s="39"/>
+      <c r="B26" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="24">
+        <f>高装高套!B6</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I26" s="27"/>
+      <c r="J26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K26" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>138.6</v>
-      </c>
-      <c r="L25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M25" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N25" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O25" s="25">
+        <v>0</v>
+      </c>
+      <c r="L26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N26" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O26" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>762.3</v>
-      </c>
-      <c r="P25" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q25" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R25" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A26" s="35"/>
-      <c r="B26" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G26" s="20">
-        <f>高装高套!B6</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K26" s="20">
+        <v>0</v>
+      </c>
+      <c r="P26" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q26" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R26" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A27" s="39"/>
+      <c r="B27" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="24">
+        <f>高装高套!B7</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K27" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M26" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N26" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O26" s="25">
+      <c r="L27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N27" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O27" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="P26" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q26" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R26" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A27" s="35"/>
-      <c r="B27" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="20">
-        <f>高装高套!B7</f>
-        <v>1.5</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K27" s="20">
+      <c r="P27" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R27" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A28" s="39"/>
+      <c r="B28" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="24">
+        <f>高装高套!B8</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="27"/>
+      <c r="J28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K28" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>239</v>
-      </c>
-      <c r="L27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M27" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N27" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O27" s="25">
+        <v>0</v>
+      </c>
+      <c r="L28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N28" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O28" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1075.5</v>
-      </c>
-      <c r="P27" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q27" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R27" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A28" s="35"/>
-      <c r="B28" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="20">
-        <f>高装高套!B8</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28" s="23"/>
-      <c r="J28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K28" s="20">
+        <v>0</v>
+      </c>
+      <c r="P28" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q28" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R28" s="31" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" customHeight="1" spans="1:24">
+      <c r="A29" s="40"/>
+      <c r="B29" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="24">
+        <f>高装高套!B9</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="27"/>
+      <c r="J29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K29" s="24">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M28" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N28" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O28" s="25">
+      <c r="L29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N29" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="O29" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q28" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R28" s="27" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A29" s="36"/>
-      <c r="B29" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" s="20">
-        <f>高装高套!B9</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I29" s="23"/>
-      <c r="J29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K29" s="20">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M29" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N29" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="O29" s="25">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1345.5</v>
-      </c>
-      <c r="P29" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q29" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="R29" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="P29" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="R29" s="31" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A30" s="62" t="s">
+      <c r="A30" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" s="20">
+      <c r="B30" s="17"/>
+      <c r="C30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="24">
         <f>SUM(G22:G29)</f>
-        <v>3.5</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="K30" s="20">
+        <v>1</v>
+      </c>
+      <c r="H30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="I30" s="27"/>
+      <c r="J30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="24">
         <f ca="1">SUM(K22:K29)</f>
-        <v>377.6</v>
-      </c>
-      <c r="L30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="M30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="N30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="O30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="P30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q30" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="R30" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="L30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="M30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="O30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="P30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="R30" s="27" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4956,679 +4545,681 @@
       <c r="O32"/>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A33" s="63" t="str">
+      <c r="A33" s="67" t="str">
         <f>"高装高套目标完成情况"</f>
         <v>高装高套目标完成情况</v>
       </c>
       <c r="G33"/>
       <c r="I33"/>
-      <c r="J33" s="64" t="str">
+      <c r="J33" s="68" t="str">
         <f>"全光任务完成情况"</f>
         <v>全光任务完成情况</v>
       </c>
       <c r="O33"/>
-      <c r="P33" s="65" t="str">
+      <c r="P33" s="69" t="str">
         <f>"区县目标完成情况"</f>
         <v>区县目标完成情况</v>
       </c>
     </row>
     <row r="34" ht="33" customHeight="1" spans="1:20">
-      <c r="A34" s="66" t="s">
+      <c r="A34" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="66" t="s">
+      <c r="B34" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="66" t="s">
+      <c r="C34" s="70" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="66" t="s">
+      <c r="D34" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="E34" s="66" t="s">
+      <c r="E34" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="F34" s="66" t="s">
+      <c r="F34" s="70" t="s">
         <v>16</v>
       </c>
       <c r="G34"/>
       <c r="I34"/>
-      <c r="J34" s="67" t="s">
+      <c r="J34" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="K34" s="67" t="s">
+      <c r="K34" s="71" t="s">
         <v>52</v>
       </c>
-      <c r="L34" s="67" t="s">
+      <c r="L34" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="M34" s="68" t="s">
+      <c r="M34" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="N34" s="67" t="s">
+      <c r="N34" s="71" t="s">
         <v>19</v>
       </c>
       <c r="O34"/>
-      <c r="P34" s="69" t="s">
+      <c r="P34" s="73" t="s">
         <v>56</v>
       </c>
-      <c r="Q34" s="69" t="s">
+      <c r="Q34" s="73" t="s">
         <v>57</v>
       </c>
-      <c r="R34" s="69" t="s">
+      <c r="R34" s="73" t="s">
         <v>58</v>
       </c>
-      <c r="S34" s="69" t="s">
+      <c r="S34" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="T34" s="69" t="s">
+      <c r="T34" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A35" s="70" t="s">
+      <c r="A35" s="74" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="71" t="str">
+      <c r="B35" s="75" t="str">
         <f>高装高套!A2</f>
         <v>陈梓铭</v>
       </c>
-      <c r="C35" s="71">
+      <c r="C35" s="75">
         <v>1</v>
       </c>
-      <c r="D35" s="71">
+      <c r="D35" s="75">
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="E35" s="72">
+      <c r="E35" s="76">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="72">
+      <c r="F35" s="76">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G35"/>
       <c r="I35"/>
-      <c r="J35" s="73" t="s">
+      <c r="J35" s="77" t="s">
         <v>59</v>
       </c>
-      <c r="K35" s="74" t="s">
+      <c r="K35" s="78" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="74">
+      <c r="L35" s="78">
         <v>60</v>
       </c>
-      <c r="M35" s="74">
+      <c r="M35" s="78">
         <f>交付高装!D2</f>
-        <v>19</v>
-      </c>
-      <c r="N35" s="75">
+        <v>12</v>
+      </c>
+      <c r="N35" s="79">
         <f>交付高装!E2</f>
-        <v>0.316666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="O35"/>
-      <c r="P35" s="76" t="s">
+      <c r="P35" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="Q35" s="77">
+      <c r="Q35" s="81">
         <v>4.25</v>
       </c>
-      <c r="R35" s="77">
+      <c r="R35" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P35,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.77</v>
-      </c>
-      <c r="S35" s="78">
+        <v>3.41</v>
+      </c>
+      <c r="S35" s="82">
         <f ca="1" t="shared" ref="S35:S44" si="11">R35/Q35</f>
-        <v>1.12235294117647</v>
-      </c>
-      <c r="T35" s="79">
+        <v>0.802352941176471</v>
+      </c>
+      <c r="T35" s="83">
         <f ca="1">RANK(S35,S35:S43)</f>
         <v>9</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A36" s="80"/>
-      <c r="B36" s="81" t="str">
+      <c r="A36" s="84"/>
+      <c r="B36" s="85" t="str">
         <f>高装高套!A3</f>
         <v>程庆德</v>
       </c>
-      <c r="C36" s="81">
+      <c r="C36" s="85">
         <v>1</v>
       </c>
-      <c r="D36" s="81">
+      <c r="D36" s="85">
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="E36" s="82">
+      <c r="E36" s="86">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="82">
+      <c r="F36" s="86">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>313.5</v>
+        <v>0</v>
       </c>
       <c r="G36"/>
       <c r="I36"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="74" t="s">
+      <c r="J36" s="87"/>
+      <c r="K36" s="78" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="74">
+      <c r="L36" s="78">
         <v>60</v>
       </c>
-      <c r="M36" s="74">
+      <c r="M36" s="78">
         <f>交付高装!D3</f>
-        <v>17</v>
-      </c>
-      <c r="N36" s="75">
+        <v>29</v>
+      </c>
+      <c r="N36" s="79">
         <f>交付高装!E3</f>
-        <v>0.283333333333333</v>
+        <v>0.483333333333333</v>
       </c>
       <c r="O36"/>
-      <c r="P36" s="76" t="s">
+      <c r="P36" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="Q36" s="84">
+      <c r="Q36" s="88">
         <v>5.75</v>
       </c>
-      <c r="R36" s="84">
+      <c r="R36" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P36,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>10.27</v>
-      </c>
-      <c r="S36" s="78">
+        <v>4.8</v>
+      </c>
+      <c r="S36" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.78608695652174</v>
-      </c>
-      <c r="T36" s="85">
+        <v>0.834782608695652</v>
+      </c>
+      <c r="T36" s="89">
         <f ca="1">RANK(S36,S35:S43)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A37" s="80"/>
-      <c r="B37" s="71" t="str">
+      <c r="A37" s="84"/>
+      <c r="B37" s="75" t="str">
         <f>高装高套!A4</f>
         <v>刘奇峻</v>
       </c>
-      <c r="C37" s="71">
+      <c r="C37" s="75">
         <v>1</v>
       </c>
-      <c r="D37" s="71">
+      <c r="D37" s="75">
         <f>高装高套!B4</f>
         <v>0</v>
       </c>
-      <c r="E37" s="72">
+      <c r="E37" s="76">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="72">
+      <c r="F37" s="76">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>786.5</v>
       </c>
       <c r="G37"/>
       <c r="I37"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="86" t="s">
+      <c r="J37" s="87"/>
+      <c r="K37" s="90" t="s">
         <v>63</v>
       </c>
-      <c r="L37" s="74">
+      <c r="L37" s="78">
         <v>60</v>
       </c>
-      <c r="M37" s="74">
+      <c r="M37" s="78">
         <f>交付高装!D4</f>
-        <v>59</v>
-      </c>
-      <c r="N37" s="75">
+        <v>10</v>
+      </c>
+      <c r="N37" s="79">
         <f>交付高装!E4</f>
-        <v>0.983333333333333</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="O37"/>
-      <c r="P37" s="76" t="s">
+      <c r="P37" s="80" t="s">
         <v>64</v>
       </c>
-      <c r="Q37" s="77">
+      <c r="Q37" s="81">
         <v>3.52</v>
       </c>
-      <c r="R37" s="77">
+      <c r="R37" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P37,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>14.58</v>
-      </c>
-      <c r="S37" s="78">
+        <v>10.74</v>
+      </c>
+      <c r="S37" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>4.14204545454545</v>
-      </c>
-      <c r="T37" s="79">
+        <v>3.05113636363636</v>
+      </c>
+      <c r="T37" s="83">
         <f ca="1">RANK(S37,S35:S43)</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A38" s="80"/>
-      <c r="B38" s="81" t="str">
+      <c r="A38" s="84"/>
+      <c r="B38" s="85" t="str">
         <f>高装高套!A5</f>
         <v>龙家宝</v>
       </c>
-      <c r="C38" s="81">
+      <c r="C38" s="85">
         <v>1</v>
       </c>
-      <c r="D38" s="81">
+      <c r="D38" s="85">
         <f>高装高套!B5</f>
-        <v>2</v>
-      </c>
-      <c r="E38" s="82">
+        <v>1</v>
+      </c>
+      <c r="E38" s="86">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>138.6</v>
-      </c>
-      <c r="F38" s="82">
+        <v>143</v>
+      </c>
+      <c r="F38" s="86">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>762.3</v>
+        <v>281</v>
       </c>
       <c r="G38"/>
       <c r="I38"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="74" t="s">
+      <c r="J38" s="87"/>
+      <c r="K38" s="78" t="s">
         <v>65</v>
       </c>
-      <c r="L38" s="74">
+      <c r="L38" s="78">
         <v>45</v>
       </c>
-      <c r="M38" s="74">
+      <c r="M38" s="78">
         <f>交付高装!D5</f>
-        <v>15</v>
-      </c>
-      <c r="N38" s="75">
+        <v>3</v>
+      </c>
+      <c r="N38" s="79">
         <f>交付高装!E5</f>
-        <v>0.333333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
       <c r="O38"/>
-      <c r="P38" s="76" t="s">
+      <c r="P38" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="Q38" s="84">
+      <c r="Q38" s="88">
         <v>3.97</v>
       </c>
-      <c r="R38" s="84">
+      <c r="R38" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P38,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.68</v>
-      </c>
-      <c r="S38" s="78">
+        <v>4.42</v>
+      </c>
+      <c r="S38" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.17884130982368</v>
-      </c>
-      <c r="T38" s="85">
+        <v>1.11335012594458</v>
+      </c>
+      <c r="T38" s="89">
         <f ca="1">RANK(S38,S35:S43)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A39" s="80"/>
-      <c r="B39" s="71" t="str">
+      <c r="A39" s="84"/>
+      <c r="B39" s="75" t="str">
         <f>高装高套!A6</f>
         <v>罗紫杰</v>
       </c>
-      <c r="C39" s="71">
+      <c r="C39" s="75">
         <v>1</v>
       </c>
-      <c r="D39" s="71">
+      <c r="D39" s="75">
         <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="E39" s="72">
+      <c r="E39" s="76">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F39" s="72">
+      <c r="F39" s="76">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G39"/>
       <c r="I39"/>
-      <c r="J39" s="87" t="s">
+      <c r="J39" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="K39" s="88" t="s">
+      <c r="K39" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="L39" s="89">
+      <c r="L39" s="93">
         <v>30</v>
       </c>
-      <c r="M39" s="89">
+      <c r="M39" s="93">
         <f>交付高装!D6</f>
-        <v>11</v>
-      </c>
-      <c r="N39" s="90">
+        <v>20</v>
+      </c>
+      <c r="N39" s="94">
         <f>交付高装!E6</f>
-        <v>0.366666666666667</v>
+        <v>0.666666666666667</v>
       </c>
       <c r="O39"/>
-      <c r="P39" s="76" t="s">
+      <c r="P39" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="Q39" s="77">
+      <c r="Q39" s="81">
         <v>2.38</v>
       </c>
-      <c r="R39" s="77">
+      <c r="R39" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P39,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.43</v>
-      </c>
-      <c r="S39" s="78">
+        <v>3.05</v>
+      </c>
+      <c r="S39" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.86134453781513</v>
-      </c>
-      <c r="T39" s="79">
+        <v>1.28151260504202</v>
+      </c>
+      <c r="T39" s="83">
         <f ca="1">RANK(S39,S35:S43)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A40" s="80"/>
-      <c r="B40" s="81" t="str">
+      <c r="A40" s="84"/>
+      <c r="B40" s="85" t="str">
         <f>高装高套!A7</f>
         <v>莫健铭</v>
       </c>
-      <c r="C40" s="81">
+      <c r="C40" s="85">
         <v>1</v>
       </c>
-      <c r="D40" s="81">
+      <c r="D40" s="85">
         <f>高装高套!B7</f>
-        <v>1.5</v>
-      </c>
-      <c r="E40" s="82">
+        <v>0</v>
+      </c>
+      <c r="E40" s="86">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>239</v>
-      </c>
-      <c r="F40" s="82">
+        <v>0</v>
+      </c>
+      <c r="F40" s="86">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1075.5</v>
+        <v>0</v>
       </c>
       <c r="G40"/>
       <c r="I40"/>
-      <c r="J40" s="91"/>
-      <c r="K40" s="88" t="s">
+      <c r="J40" s="95"/>
+      <c r="K40" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="L40" s="89">
+      <c r="L40" s="93">
         <v>30</v>
       </c>
-      <c r="M40" s="89">
+      <c r="M40" s="93">
         <f>交付高装!D7</f>
+        <v>9</v>
+      </c>
+      <c r="N40" s="94">
+        <f>交付高装!E7</f>
+        <v>0.3</v>
+      </c>
+      <c r="O40"/>
+      <c r="P40" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q40" s="96">
+        <v>2.6</v>
+      </c>
+      <c r="R40" s="96">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(P40,高套!A:A,高套!B:B,0)/U5,2)</f>
+        <v>2.41</v>
+      </c>
+      <c r="S40" s="82">
+        <f ca="1" t="shared" si="11"/>
+        <v>0.926923076923077</v>
+      </c>
+      <c r="T40" s="89">
+        <f ca="1">RANK(S40,S35:S43)</f>
         <v>6</v>
       </c>
-      <c r="N40" s="90">
-        <f>交付高装!E7</f>
-        <v>0.2</v>
-      </c>
-      <c r="O40"/>
-      <c r="P40" s="76" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q40" s="92">
-        <v>2.6</v>
-      </c>
-      <c r="R40" s="92">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P40,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>3.94</v>
-      </c>
-      <c r="S40" s="78">
-        <f ca="1" t="shared" si="11"/>
-        <v>1.51538461538462</v>
-      </c>
-      <c r="T40" s="85">
-        <f ca="1">RANK(S40,S35:S43)</f>
-        <v>4</v>
-      </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A41" s="80"/>
-      <c r="B41" s="71" t="str">
+      <c r="A41" s="84"/>
+      <c r="B41" s="75" t="str">
         <f>高装高套!A8</f>
         <v>吴广仁</v>
       </c>
-      <c r="C41" s="71">
+      <c r="C41" s="75">
         <v>1</v>
       </c>
-      <c r="D41" s="71">
+      <c r="D41" s="75">
         <f>高装高套!B8</f>
         <v>0</v>
       </c>
-      <c r="E41" s="72">
+      <c r="E41" s="76">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="72">
+      <c r="F41" s="76">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G41"/>
-      <c r="J41" s="91"/>
-      <c r="K41" s="88" t="s">
+      <c r="J41" s="95"/>
+      <c r="K41" s="92" t="s">
         <v>44</v>
       </c>
-      <c r="L41" s="89">
+      <c r="L41" s="93">
         <v>30</v>
       </c>
-      <c r="M41" s="89">
+      <c r="M41" s="93">
         <f>交付高装!D8</f>
-        <v>6</v>
-      </c>
-      <c r="N41" s="90">
+        <v>3</v>
+      </c>
+      <c r="N41" s="94">
         <f>交付高装!E8</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="O41"/>
-      <c r="P41" s="76" t="s">
+      <c r="P41" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="Q41" s="77">
+      <c r="Q41" s="81">
         <v>2.41</v>
       </c>
-      <c r="R41" s="77">
+      <c r="R41" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P41,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>3.45</v>
-      </c>
-      <c r="S41" s="78">
+        <v>2.04</v>
+      </c>
+      <c r="S41" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.43153526970954</v>
-      </c>
-      <c r="T41" s="79">
+        <v>0.846473029045643</v>
+      </c>
+      <c r="T41" s="83">
         <f ca="1">RANK(S41,S35:S43)</f>
         <v>7</v>
       </c>
     </row>
     <row r="42" ht="13.5" customHeight="1" spans="1:20">
-      <c r="A42" s="93"/>
-      <c r="B42" s="81" t="str">
+      <c r="A42" s="97"/>
+      <c r="B42" s="85" t="str">
         <f>高装高套!A9</f>
         <v>王洪明</v>
       </c>
-      <c r="C42" s="81">
+      <c r="C42" s="85">
         <v>1</v>
       </c>
-      <c r="D42" s="81">
+      <c r="D42" s="85">
         <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="E42" s="82">
+      <c r="E42" s="86">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F42" s="82">
+      <c r="F42" s="86">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1345.5</v>
+        <v>25</v>
       </c>
       <c r="G42"/>
-      <c r="J42" s="91"/>
-      <c r="K42" s="88" t="s">
+      <c r="J42" s="95"/>
+      <c r="K42" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="L42" s="89">
+      <c r="L42" s="93">
         <v>30</v>
       </c>
-      <c r="M42" s="89">
+      <c r="M42" s="93">
         <f>交付高装!D9</f>
-        <v>13</v>
-      </c>
-      <c r="N42" s="90">
+        <v>9</v>
+      </c>
+      <c r="N42" s="94">
         <f>交付高装!E9</f>
-        <v>0.433333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="O42"/>
-      <c r="P42" s="76" t="s">
+      <c r="P42" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="Q42" s="84">
+      <c r="Q42" s="88">
         <v>3.22</v>
       </c>
-      <c r="R42" s="84">
+      <c r="R42" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P42,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.8</v>
-      </c>
-      <c r="S42" s="78">
+        <v>3</v>
+      </c>
+      <c r="S42" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.49068322981366</v>
-      </c>
-      <c r="T42" s="85">
+        <v>0.93167701863354</v>
+      </c>
+      <c r="T42" s="89">
         <f ca="1">RANK(S42,S35:S43)</f>
         <v>5</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A43" s="94" t="s">
+      <c r="A43" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="95"/>
-      <c r="C43" s="94">
+      <c r="B43" s="99"/>
+      <c r="C43" s="98">
         <f>SUM(C35:C42)</f>
         <v>8</v>
       </c>
-      <c r="D43" s="94">
+      <c r="D43" s="98">
         <f>SUM(D35:D42)</f>
-        <v>3.5</v>
-      </c>
-      <c r="E43" s="94">
+        <v>1</v>
+      </c>
+      <c r="E43" s="98">
         <f ca="1">SUM(E35:E42)</f>
-        <v>377.6</v>
-      </c>
-      <c r="F43" s="94" t="s">
+        <v>143</v>
+      </c>
+      <c r="F43" s="98" t="s">
         <v>42</v>
       </c>
       <c r="G43"/>
-      <c r="J43" s="91"/>
-      <c r="K43" s="88" t="s">
+      <c r="J43" s="95"/>
+      <c r="K43" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="L43" s="89">
+      <c r="L43" s="93">
         <v>30</v>
       </c>
-      <c r="M43" s="89">
+      <c r="M43" s="93">
         <f>交付高装!D10</f>
-        <v>43</v>
-      </c>
-      <c r="N43" s="90">
+        <v>0</v>
+      </c>
+      <c r="N43" s="94">
         <f>交付高装!E10</f>
-        <v>1.43333333333333</v>
+        <v>0</v>
       </c>
       <c r="O43"/>
-      <c r="P43" s="76" t="s">
+      <c r="P43" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="Q43" s="77">
+      <c r="Q43" s="81">
         <v>3.36</v>
       </c>
-      <c r="R43" s="77">
+      <c r="R43" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P43,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.92</v>
-      </c>
-      <c r="S43" s="78">
+        <v>4.49</v>
+      </c>
+      <c r="S43" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.46428571428571</v>
-      </c>
-      <c r="T43" s="79">
+        <v>1.33630952380952</v>
+      </c>
+      <c r="T43" s="83">
         <f ca="1">RANK(S43,S35:S43)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" ht="14.75" customHeight="1" spans="1:20">
       <c r="F44"/>
       <c r="G44"/>
-      <c r="J44" s="91"/>
-      <c r="K44" s="88" t="s">
+      <c r="J44" s="95"/>
+      <c r="K44" s="92" t="s">
         <v>47</v>
       </c>
-      <c r="L44" s="89">
+      <c r="L44" s="93">
         <v>30</v>
       </c>
-      <c r="M44" s="89">
+      <c r="M44" s="93">
         <f>交付高装!D11</f>
-        <v>16</v>
-      </c>
-      <c r="N44" s="90">
+        <v>10</v>
+      </c>
+      <c r="N44" s="94">
         <f>交付高装!E11</f>
-        <v>0.533333333333333</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="O44"/>
-      <c r="P44" s="96" t="s">
+      <c r="P44" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="Q44" s="97">
+      <c r="Q44" s="101">
         <f>SUM(Q35:Q43)</f>
         <v>31.46</v>
       </c>
-      <c r="R44" s="97">
+      <c r="R44" s="101">
         <f ca="1">SUM(R35:R43)</f>
-        <v>55.84</v>
-      </c>
-      <c r="S44" s="98">
+        <v>38.36</v>
+      </c>
+      <c r="S44" s="102">
         <f ca="1" t="shared" si="11"/>
-        <v>1.77495232040687</v>
-      </c>
-      <c r="T44" s="99" t="s">
+        <v>1.21932612841704</v>
+      </c>
+      <c r="T44" s="103" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="45" ht="13.5" customHeight="1" spans="1:20">
       <c r="F45"/>
       <c r="G45"/>
-      <c r="J45" s="91"/>
-      <c r="K45" s="88" t="s">
+      <c r="J45" s="95"/>
+      <c r="K45" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="L45" s="89">
+      <c r="L45" s="93">
         <v>30</v>
       </c>
-      <c r="M45" s="89">
+      <c r="M45" s="93">
         <f>交付高装!D12</f>
-        <v>15</v>
-      </c>
-      <c r="N45" s="90">
+        <v>3</v>
+      </c>
+      <c r="N45" s="94">
         <f>交付高装!E12</f>
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="O45"/>
     </row>
     <row r="46" ht="13.5" customHeight="1" spans="1:20">
       <c r="F46"/>
       <c r="G46"/>
-      <c r="J46" s="100"/>
-      <c r="K46" s="101" t="s">
+      <c r="J46" s="104"/>
+      <c r="K46" s="105" t="s">
         <v>74</v>
       </c>
-      <c r="L46" s="89">
+      <c r="L46" s="93">
         <v>210</v>
       </c>
-      <c r="M46" s="89">
+      <c r="M46" s="93">
         <f>SUM(M35:M38)</f>
-        <v>110</v>
-      </c>
-      <c r="N46" s="90">
+        <v>54</v>
+      </c>
+      <c r="N46" s="94">
         <f>M46/L46</f>
-        <v>0.523809523809524</v>
+        <v>0.257142857142857</v>
       </c>
       <c r="O46"/>
     </row>
     <row r="47" ht="13.5" customHeight="1"/>
     <row r="48" ht="13.5" customHeight="1" spans="1:20">
+      <c r="D48"/>
+      <c r="E48"/>
       <c r="F48"/>
       <c r="G48"/>
       <c r="I48"/>
@@ -5637,633 +5228,239 @@
       <c r="O48"/>
     </row>
     <row r="49" ht="13.5" customHeight="1" spans="1:15">
-      <c r="A49" s="102" t="str">
-        <f ca="1">""&amp;MONTH(TODAY())&amp;"月份商机统计表（预计转化时间为"&amp;MONTH(TODAY())&amp;"月）"</f>
-        <v>6月份商机统计表（预计转化时间为6月）</v>
-      </c>
-      <c r="B49" s="103"/>
-      <c r="C49" s="103"/>
-      <c r="D49" s="104"/>
+      <c r="D49"/>
+      <c r="E49"/>
       <c r="F49"/>
-      <c r="G49" s="105" t="s">
+      <c r="G49"/>
+      <c r="I49"/>
+      <c r="J49"/>
+      <c r="K49"/>
+    </row>
+    <row r="50" ht="13.5" customHeight="1" spans="1:15">
+      <c r="A50" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="50" ht="13.5" customHeight="1" spans="1:15">
-      <c r="A50" s="106" t="str">
-        <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止6月24日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
-      </c>
-      <c r="B50" s="107"/>
-      <c r="C50" s="107"/>
-      <c r="D50" s="108"/>
+      <c r="B50" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E50"/>
       <c r="F50"/>
-      <c r="G50" s="109" t="str">
-        <f ca="1">"（数据截止"&amp;TEXT(TODAY()-1,"m月d日")&amp;",剔除目前进度为""失败""、""已受理""的商机；剔除商机小类为""产数项目""的项）"</f>
-        <v>（数据截止6月24日,剔除目前进度为"失败"、"已受理"的商机；剔除商机小类为"产数项目"的项）</v>
-      </c>
+      <c r="G50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
     </row>
     <row r="51" ht="14.75" customHeight="1" spans="1:15">
-      <c r="A51" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>78</v>
-      </c>
+      <c r="A51" s="2">
+        <f>积分!A2</f>
+        <v>11117.68</v>
+      </c>
+      <c r="B51" s="2">
+        <f>积分!B2</f>
+        <v>8941.02</v>
+      </c>
+      <c r="C51" s="2">
+        <f>积分!C2</f>
+        <v>2010</v>
+      </c>
+      <c r="D51" s="2">
+        <f>积分!D2</f>
+        <v>0.89</v>
+      </c>
+      <c r="E51"/>
       <c r="F51"/>
-      <c r="G51" s="110" t="s">
-        <v>4</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I51" s="111"/>
-      <c r="J51" s="111" t="s">
-        <v>77</v>
-      </c>
-      <c r="K51" s="112" t="s">
-        <v>78</v>
-      </c>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="I51"/>
+      <c r="J51"/>
+      <c r="K51"/>
     </row>
     <row r="52" spans="1:15">
-      <c r="A52" s="113" t="str">
-        <f>商机统计!A2</f>
-        <v>谢卓和</v>
-      </c>
-      <c r="B52" s="114">
-        <f>商机统计!B2</f>
-        <v>14</v>
-      </c>
-      <c r="C52" s="114">
-        <f>商机统计!C2</f>
-        <v>47.5</v>
-      </c>
-      <c r="D52" s="115">
-        <f>商机统计!D2</f>
-        <v>5190</v>
-      </c>
+      <c r="D52"/>
+      <c r="E52"/>
       <c r="F52"/>
-      <c r="G52" s="113" t="str">
-        <f>商机统计!F2</f>
-        <v>谢卓和</v>
-      </c>
-      <c r="H52" s="114">
-        <f>商机统计!G2</f>
-        <v>17</v>
-      </c>
-      <c r="I52" s="114"/>
-      <c r="J52" s="114">
-        <f>商机统计!H2</f>
-        <v>60.5</v>
-      </c>
-      <c r="K52" s="115">
-        <f>商机统计!I2</f>
-        <v>6798</v>
-      </c>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
     </row>
     <row r="53" spans="1:15">
-      <c r="A53" s="116" t="str">
-        <f>商机统计!A3</f>
-        <v>黄淡妮</v>
-      </c>
-      <c r="B53" s="117">
-        <f>商机统计!B3</f>
-        <v>10</v>
-      </c>
-      <c r="C53" s="117">
-        <f>商机统计!C3</f>
-        <v>40.9</v>
-      </c>
-      <c r="D53" s="118">
-        <f>商机统计!D3</f>
-        <v>6793</v>
-      </c>
-      <c r="G53" s="116" t="str">
-        <f>商机统计!F3</f>
-        <v>邱海燕</v>
-      </c>
-      <c r="H53" s="117">
-        <f>商机统计!G3</f>
-        <v>5</v>
-      </c>
-      <c r="I53" s="117"/>
-      <c r="J53" s="117">
-        <f>商机统计!H3</f>
-        <v>49.2</v>
-      </c>
-      <c r="K53" s="118">
-        <f>商机统计!I3</f>
-        <v>6479</v>
-      </c>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
     </row>
     <row r="54" spans="1:15">
-      <c r="A54" s="119" t="str">
-        <f>商机统计!A4</f>
-        <v>具进康</v>
-      </c>
-      <c r="B54" s="120">
-        <f>商机统计!B4</f>
-        <v>8</v>
-      </c>
-      <c r="C54" s="120">
-        <f>商机统计!C4</f>
-        <v>20.5</v>
-      </c>
-      <c r="D54" s="121">
-        <f>商机统计!D4</f>
-        <v>4882</v>
-      </c>
-      <c r="G54" s="119" t="str">
-        <f>商机统计!F4</f>
-        <v>黄淡妮</v>
-      </c>
-      <c r="H54" s="120">
-        <f>商机统计!G4</f>
-        <v>11</v>
-      </c>
-      <c r="I54" s="120"/>
-      <c r="J54" s="120">
-        <f>商机统计!H4</f>
-        <v>43.9</v>
-      </c>
-      <c r="K54" s="121">
-        <f>商机统计!I4</f>
-        <v>7393</v>
-      </c>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54"/>
+      <c r="J54"/>
+      <c r="K54"/>
     </row>
     <row r="55" spans="1:15">
-      <c r="A55" s="122" t="str">
-        <f>商机统计!A5</f>
-        <v>张小敏</v>
-      </c>
-      <c r="B55" s="123">
-        <f>商机统计!B5</f>
-        <v>10</v>
-      </c>
-      <c r="C55" s="123">
-        <f>商机统计!C5</f>
-        <v>20</v>
-      </c>
-      <c r="D55" s="124">
-        <f>商机统计!D5</f>
-        <v>4375</v>
-      </c>
-      <c r="G55" s="122" t="str">
-        <f>商机统计!F5</f>
-        <v>潘观友</v>
-      </c>
-      <c r="H55" s="123">
-        <f>商机统计!G5</f>
-        <v>10</v>
-      </c>
-      <c r="I55" s="123"/>
-      <c r="J55" s="123">
-        <f>商机统计!H5</f>
-        <v>36.8</v>
-      </c>
-      <c r="K55" s="124">
-        <f>商机统计!I5</f>
-        <v>6317</v>
-      </c>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55"/>
+      <c r="J55"/>
+      <c r="K55"/>
     </row>
     <row r="56" ht="13.5" customHeight="1" spans="1:15">
-      <c r="A56" s="125" t="str">
-        <f>商机统计!A6</f>
-        <v>潘观友</v>
-      </c>
-      <c r="B56" s="126">
-        <f>商机统计!B6</f>
-        <v>6</v>
-      </c>
-      <c r="C56" s="126">
-        <f>商机统计!C6</f>
-        <v>19.8</v>
-      </c>
-      <c r="D56" s="127">
-        <f>商机统计!D6</f>
-        <v>1400</v>
-      </c>
-      <c r="G56" s="125" t="str">
-        <f>商机统计!F6</f>
-        <v>张小敏</v>
-      </c>
-      <c r="H56" s="126">
-        <f>商机统计!G6</f>
-        <v>11</v>
-      </c>
-      <c r="I56" s="126"/>
-      <c r="J56" s="126">
-        <f>商机统计!H6</f>
-        <v>23</v>
-      </c>
-      <c r="K56" s="127">
-        <f>商机统计!I6</f>
-        <v>5575</v>
-      </c>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
     </row>
     <row r="57" spans="1:15">
-      <c r="A57" s="122" t="str">
-        <f>商机统计!A7</f>
-        <v>李东</v>
-      </c>
-      <c r="B57" s="123">
-        <f>商机统计!B7</f>
-        <v>3</v>
-      </c>
-      <c r="C57" s="123">
-        <f>商机统计!C7</f>
-        <v>14</v>
-      </c>
-      <c r="D57" s="124">
-        <f>商机统计!D7</f>
-        <v>1329</v>
-      </c>
-      <c r="G57" s="122" t="str">
-        <f>商机统计!F7</f>
-        <v>具进康</v>
-      </c>
-      <c r="H57" s="123">
-        <f>商机统计!G7</f>
-        <v>10</v>
-      </c>
-      <c r="I57" s="123"/>
-      <c r="J57" s="123">
-        <f>商机统计!H7</f>
-        <v>22.5</v>
-      </c>
-      <c r="K57" s="124">
-        <f>商机统计!I7</f>
-        <v>5181</v>
-      </c>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
     </row>
     <row r="58" spans="1:15">
-      <c r="A58" s="125" t="str">
-        <f>商机统计!A8</f>
-        <v>王锦添</v>
-      </c>
-      <c r="B58" s="126">
-        <f>商机统计!B8</f>
-        <v>4</v>
-      </c>
-      <c r="C58" s="126">
-        <f>商机统计!C8</f>
-        <v>12</v>
-      </c>
-      <c r="D58" s="127">
-        <f>商机统计!D8</f>
-        <v>2280</v>
-      </c>
-      <c r="G58" s="125" t="str">
-        <f>商机统计!F8</f>
-        <v>黄观霞</v>
-      </c>
-      <c r="H58" s="126">
-        <f>商机统计!G8</f>
-        <v>4</v>
-      </c>
-      <c r="I58" s="126"/>
-      <c r="J58" s="126">
-        <f>商机统计!H8</f>
-        <v>22</v>
-      </c>
-      <c r="K58" s="127">
-        <f>商机统计!I8</f>
-        <v>4216</v>
-      </c>
+      <c r="D58"/>
+      <c r="E58"/>
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="I58"/>
+      <c r="J58"/>
+      <c r="K58"/>
     </row>
     <row r="59" spans="1:15">
-      <c r="A59" s="122" t="str">
-        <f>商机统计!A9</f>
-        <v>李玉强</v>
-      </c>
-      <c r="B59" s="123">
-        <f>商机统计!B9</f>
-        <v>6</v>
-      </c>
-      <c r="C59" s="123">
-        <f>商机统计!C9</f>
-        <v>9.5</v>
-      </c>
-      <c r="D59" s="124">
-        <f>商机统计!D9</f>
-        <v>1184</v>
-      </c>
+      <c r="D59"/>
       <c r="E59"/>
       <c r="F59"/>
-      <c r="G59" s="122" t="str">
-        <f>商机统计!F9</f>
-        <v>李玉强</v>
-      </c>
-      <c r="H59" s="123">
-        <f>商机统计!G9</f>
-        <v>8</v>
-      </c>
-      <c r="I59" s="123"/>
-      <c r="J59" s="123">
-        <f>商机统计!H9</f>
-        <v>19.5</v>
-      </c>
-      <c r="K59" s="124">
-        <f>商机统计!I9</f>
-        <v>3820</v>
-      </c>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="I59"/>
+      <c r="J59"/>
+      <c r="K59"/>
       <c r="O59"/>
     </row>
     <row r="60" spans="1:15">
-      <c r="A60" s="125" t="str">
-        <f>商机统计!A10</f>
-        <v>麦海芬</v>
-      </c>
-      <c r="B60" s="126">
-        <f>商机统计!B10</f>
-        <v>5</v>
-      </c>
-      <c r="C60" s="126">
-        <f>商机统计!C10</f>
-        <v>8.5</v>
-      </c>
-      <c r="D60" s="127">
-        <f>商机统计!D10</f>
-        <v>1498</v>
-      </c>
+      <c r="D60"/>
       <c r="E60"/>
       <c r="F60"/>
-      <c r="G60" s="125" t="str">
-        <f>商机统计!F10</f>
-        <v>伍颖敏</v>
-      </c>
-      <c r="H60" s="126">
-        <f>商机统计!G10</f>
-        <v>4</v>
-      </c>
-      <c r="I60" s="126"/>
-      <c r="J60" s="126">
-        <f>商机统计!H10</f>
-        <v>18.48</v>
-      </c>
-      <c r="K60" s="127">
-        <f>商机统计!I10</f>
-        <v>3675</v>
-      </c>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="I60"/>
+      <c r="J60"/>
+      <c r="K60"/>
       <c r="O60"/>
     </row>
     <row r="61" spans="1:15">
-      <c r="A61" s="122" t="str">
-        <f>商机统计!A11</f>
-        <v>钟俊杰</v>
-      </c>
-      <c r="B61" s="123">
-        <f>商机统计!B11</f>
-        <v>1</v>
-      </c>
-      <c r="C61" s="123">
-        <f>商机统计!C11</f>
-        <v>1.5</v>
-      </c>
-      <c r="D61" s="124">
-        <f>商机统计!D11</f>
-        <v>199</v>
-      </c>
+      <c r="D61"/>
       <c r="E61"/>
       <c r="F61"/>
-      <c r="G61" s="122" t="str">
-        <f>商机统计!F11</f>
-        <v>王锦添</v>
-      </c>
-      <c r="H61" s="123">
-        <f>商机统计!G11</f>
-        <v>5</v>
-      </c>
-      <c r="I61" s="123"/>
-      <c r="J61" s="123">
-        <f>商机统计!H11</f>
-        <v>16</v>
-      </c>
-      <c r="K61" s="124">
-        <f>商机统计!I11</f>
-        <v>3080</v>
-      </c>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="I61"/>
+      <c r="J61"/>
+      <c r="K61"/>
       <c r="O61"/>
     </row>
     <row r="62" spans="1:15">
-      <c r="A62" s="125" t="str">
-        <f>商机统计!A12</f>
-        <v>伍颖敏</v>
-      </c>
-      <c r="B62" s="126">
-        <f>商机统计!B12</f>
-        <v>1</v>
-      </c>
-      <c r="C62" s="126">
-        <f>商机统计!C12</f>
-        <v>1.5</v>
-      </c>
-      <c r="D62" s="127">
-        <f>商机统计!D12</f>
-        <v>280</v>
-      </c>
+      <c r="D62"/>
       <c r="E62"/>
       <c r="F62"/>
-      <c r="G62" s="125" t="str">
-        <f>商机统计!F12</f>
-        <v>李东</v>
-      </c>
-      <c r="H62" s="126">
-        <f>商机统计!G12</f>
-        <v>4</v>
-      </c>
-      <c r="I62" s="126"/>
-      <c r="J62" s="126">
-        <f>商机统计!H12</f>
-        <v>15</v>
-      </c>
-      <c r="K62" s="127">
-        <f>商机统计!I12</f>
-        <v>1529</v>
-      </c>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="I62"/>
+      <c r="J62"/>
+      <c r="K62"/>
       <c r="O62"/>
     </row>
     <row r="63" spans="1:15">
-      <c r="A63" s="122" t="str">
-        <f>商机统计!A13</f>
-        <v>邱海燕</v>
-      </c>
-      <c r="B63" s="123">
-        <f>商机统计!B13</f>
-        <v>1</v>
-      </c>
-      <c r="C63" s="123">
-        <f>商机统计!C13</f>
-        <v>1</v>
-      </c>
-      <c r="D63" s="124">
-        <f>商机统计!D13</f>
-        <v>169</v>
-      </c>
+      <c r="D63"/>
       <c r="E63"/>
       <c r="F63"/>
-      <c r="G63" s="122" t="str">
-        <f>商机统计!F13</f>
-        <v>麦海芬</v>
-      </c>
-      <c r="H63" s="123">
-        <f>商机统计!G13</f>
-        <v>5</v>
-      </c>
-      <c r="I63" s="123"/>
-      <c r="J63" s="123">
-        <f>商机统计!H13</f>
-        <v>8.5</v>
-      </c>
-      <c r="K63" s="124">
-        <f>商机统计!I13</f>
-        <v>1498</v>
-      </c>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="I63"/>
+      <c r="J63"/>
+      <c r="K63"/>
       <c r="O63"/>
     </row>
     <row r="64" spans="1:15">
-      <c r="A64" s="125" t="str">
-        <f>商机统计!A14</f>
-        <v>黄观霞</v>
-      </c>
-      <c r="B64" s="126">
-        <f>商机统计!B14</f>
-        <v>1</v>
-      </c>
-      <c r="C64" s="126">
-        <f>商机统计!C14</f>
-        <v>1</v>
-      </c>
-      <c r="D64" s="127">
-        <f>商机统计!D14</f>
-        <v>169</v>
-      </c>
+      <c r="D64"/>
       <c r="E64"/>
       <c r="F64"/>
-      <c r="G64" s="125" t="str">
-        <f>商机统计!F14</f>
-        <v>冯艺康</v>
-      </c>
-      <c r="H64" s="126">
-        <f>商机统计!G14</f>
-        <v>1</v>
-      </c>
-      <c r="I64" s="126"/>
-      <c r="J64" s="126">
-        <f>商机统计!H14</f>
-        <v>6</v>
-      </c>
-      <c r="K64" s="127">
-        <f>商机统计!I14</f>
-        <v>1200</v>
-      </c>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="I64"/>
+      <c r="J64"/>
+      <c r="K64"/>
       <c r="O64"/>
     </row>
-    <row r="65" ht="13.5" customHeight="1" spans="1:15">
-      <c r="A65" s="128" t="str">
-        <f>商机统计!A15</f>
-        <v>冯艺康</v>
-      </c>
-      <c r="B65" s="129">
-        <f>商机统计!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C65" s="129">
-        <f>商机统计!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D65" s="130">
-        <f>商机统计!D15</f>
-        <v>0</v>
-      </c>
+    <row r="65" ht="13.5" customHeight="1" spans="4:15">
+      <c r="D65"/>
       <c r="E65"/>
       <c r="F65"/>
-      <c r="G65" s="128" t="str">
-        <f>商机统计!F15</f>
-        <v>钟俊杰</v>
-      </c>
-      <c r="H65" s="129">
-        <f>商机统计!G15</f>
-        <v>1</v>
-      </c>
-      <c r="I65" s="129"/>
-      <c r="J65" s="129">
-        <f>商机统计!H15</f>
-        <v>1.5</v>
-      </c>
-      <c r="K65" s="130">
-        <f>商机统计!I15</f>
-        <v>199</v>
-      </c>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="I65"/>
+      <c r="J65"/>
+      <c r="K65"/>
       <c r="O65"/>
     </row>
-    <row r="66" ht="13.5" customHeight="1" spans="1:15">
-      <c r="A66" s="131" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="131">
-        <f>SUM(B52:B65)</f>
-        <v>70</v>
-      </c>
-      <c r="C66" s="131">
-        <f>SUM(C52:C65)</f>
-        <v>197.7</v>
-      </c>
-      <c r="D66" s="131">
-        <f>SUM(D52:D65)</f>
-        <v>29748</v>
-      </c>
+    <row r="66" ht="13.5" customHeight="1" spans="4:15">
+      <c r="D66"/>
       <c r="E66"/>
       <c r="F66"/>
-      <c r="G66" s="131" t="s">
-        <v>37</v>
-      </c>
-      <c r="H66" s="131">
-        <f>SUM(H52:H65)</f>
-        <v>96</v>
-      </c>
-      <c r="I66" s="131"/>
-      <c r="J66" s="131">
-        <f>SUM(J52:J65)</f>
-        <v>342.88</v>
-      </c>
-      <c r="K66" s="131">
-        <f>SUM(K52:K65)</f>
-        <v>56960</v>
-      </c>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="I66"/>
+      <c r="J66"/>
+      <c r="K66"/>
       <c r="O66"/>
     </row>
-    <row r="67" spans="1:15">
+    <row r="67" spans="4:15">
       <c r="D67"/>
       <c r="E67"/>
       <c r="F67"/>
       <c r="G67"/>
+      <c r="I67"/>
+      <c r="J67"/>
+      <c r="K67"/>
       <c r="O67"/>
     </row>
-    <row r="68" ht="13.5" customHeight="1" spans="1:15">
+    <row r="68" ht="13.5" customHeight="1" spans="4:15">
       <c r="D68"/>
       <c r="E68"/>
       <c r="F68"/>
       <c r="G68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
       <c r="O68"/>
     </row>
-    <row r="69" ht="52" customHeight="1" spans="1:15">
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="O69"/>
-    </row>
-    <row r="70" ht="13.5" customHeight="1" spans="1:15">
+    <row r="69" customFormat="1" ht="13.5" customHeight="1"/>
+    <row r="70" ht="13.5" customHeight="1" spans="4:15">
       <c r="D70"/>
       <c r="E70"/>
       <c r="F70"/>
@@ -6273,7 +5470,7 @@
       <c r="K70"/>
       <c r="O70"/>
     </row>
-    <row r="71" spans="1:15">
+    <row r="71" spans="4:15">
       <c r="D71"/>
       <c r="E71"/>
       <c r="F71"/>
@@ -6283,7 +5480,7 @@
       <c r="K71"/>
       <c r="O71"/>
     </row>
-    <row r="72" spans="1:15">
+    <row r="72" spans="4:15">
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72"/>
@@ -6293,7 +5490,7 @@
       <c r="K72"/>
       <c r="O72"/>
     </row>
-    <row r="73" spans="1:15">
+    <row r="73" spans="4:15">
       <c r="D73"/>
       <c r="E73"/>
       <c r="F73"/>
@@ -6303,7 +5500,7 @@
       <c r="K73"/>
       <c r="O73"/>
     </row>
-    <row r="74" spans="1:15">
+    <row r="74" spans="4:15">
       <c r="D74"/>
       <c r="E74"/>
       <c r="F74"/>
@@ -6313,7 +5510,7 @@
       <c r="K74"/>
       <c r="O74"/>
     </row>
-    <row r="75" ht="13.5" customHeight="1" spans="1:15">
+    <row r="75" ht="13.5" customHeight="1" spans="4:15">
       <c r="D75"/>
       <c r="E75"/>
       <c r="F75"/>
@@ -6323,7 +5520,7 @@
       <c r="K75"/>
       <c r="O75"/>
     </row>
-    <row r="76" spans="1:15">
+    <row r="76" spans="4:15">
       <c r="D76"/>
       <c r="E76"/>
       <c r="F76"/>
@@ -6333,7 +5530,7 @@
       <c r="K76"/>
       <c r="O76"/>
     </row>
-    <row r="77" spans="1:15">
+    <row r="77" spans="4:15">
       <c r="D77"/>
       <c r="E77"/>
       <c r="F77"/>
@@ -6343,7 +5540,7 @@
       <c r="K77"/>
       <c r="O77"/>
     </row>
-    <row r="78" spans="1:15">
+    <row r="78" spans="4:15">
       <c r="D78"/>
       <c r="E78"/>
       <c r="F78"/>
@@ -6353,7 +5550,7 @@
       <c r="K78"/>
       <c r="O78"/>
     </row>
-    <row r="79" spans="1:15">
+    <row r="79" spans="4:15">
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79"/>
@@ -6363,7 +5560,7 @@
       <c r="K79"/>
       <c r="O79"/>
     </row>
-    <row r="80" spans="1:15">
+    <row r="80" spans="4:15">
       <c r="D80"/>
       <c r="E80"/>
       <c r="F80"/>
@@ -6614,9 +5811,9 @@
       <c r="O104"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="29">
     <mergeCell ref="B1:R1"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B2:I2"/>
     <mergeCell ref="J2:O2"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="A30:B30"/>
@@ -6624,10 +5821,6 @@
     <mergeCell ref="J33:N33"/>
     <mergeCell ref="P33:T33"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="G49:K49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="G50:K50"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="A12:A19"/>
@@ -6650,12 +5843,12 @@
     <mergeCell ref="A20:B21"/>
   </mergeCells>
   <conditionalFormatting sqref="F20">
-    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H18">
-    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6668,26 +5861,22 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{7e9633ac-b9a7-477d-b85d-894e9dfcaebc}</x14:id>
+          <x14:id>{68b0e617-2644-403d-96f0-b09a47b9c717}</x14:id>
         </ext>
       </extLst>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(S35&lt;1,S35&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="44" orientation="portrait"/>
   <headerFooter/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-  </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{7e9633ac-b9a7-477d-b85d-894e9dfcaebc}">
+          <x14:cfRule type="dataBar" id="{68b0e617-2644-403d-96f0-b09a47b9c717}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -6706,6 +5895,46 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" ht="24" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2">
+        <v>11117.68</v>
+      </c>
+      <c r="B2" s="2">
+        <v>8941.02</v>
+      </c>
+      <c r="C2" s="2">
+        <v>2010</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.89</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -6713,10 +5942,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>79</v>
       </c>
     </row>
@@ -6725,7 +5954,7 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6733,7 +5962,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6741,7 +5970,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6749,7 +5978,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>4</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6757,7 +5986,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6765,7 +5994,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6773,7 +6002,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6781,7 +6010,7 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6789,7 +6018,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>18.98</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6797,7 +6026,7 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>4.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6805,7 +6034,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6813,7 +6042,7 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6821,7 +6050,7 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6829,7 +6058,7 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>3.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6837,7 +6066,7 @@
         <v>39</v>
       </c>
       <c r="B16">
-        <v>114.48</v>
+        <v>95.54</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -6845,7 +6074,7 @@
         <v>62</v>
       </c>
       <c r="B17">
-        <v>246.45</v>
+        <v>134.28</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -6853,7 +6082,7 @@
         <v>64</v>
       </c>
       <c r="B18">
-        <v>349.81</v>
+        <v>300.69</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -6861,7 +6090,7 @@
         <v>70</v>
       </c>
       <c r="B19">
-        <v>115.13</v>
+        <v>84.02</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -6869,7 +6098,7 @@
         <v>71</v>
       </c>
       <c r="B20">
-        <v>118.17</v>
+        <v>125.64</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -6877,7 +6106,7 @@
         <v>66</v>
       </c>
       <c r="B21">
-        <v>112.25</v>
+        <v>123.63</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -6885,7 +6114,7 @@
         <v>68</v>
       </c>
       <c r="B22">
-        <v>94.65</v>
+        <v>67.6</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -6893,7 +6122,7 @@
         <v>67</v>
       </c>
       <c r="B23">
-        <v>106.42</v>
+        <v>85.52</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -6901,7 +6130,7 @@
         <v>69</v>
       </c>
       <c r="B24">
-        <v>82.79</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -6917,10 +6146,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -6929,7 +6158,7 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6945,7 +6174,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6953,7 +6182,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6961,7 +6190,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6969,7 +6198,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6977,7 +6206,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6985,7 +6214,7 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6993,7 +6222,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7009,7 +6238,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7017,7 +6246,7 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7025,7 +6254,7 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7033,7 +6262,7 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -7041,7 +6270,7 @@
         <v>39</v>
       </c>
       <c r="B16">
-        <v>274</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -7057,16 +6286,16 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>80</v>
       </c>
     </row>
@@ -7075,13 +6304,13 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="C2">
-        <v>936</v>
+        <v>282</v>
       </c>
       <c r="D2">
-        <v>648</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7089,13 +6318,13 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C3">
-        <v>1059.34</v>
+        <v>287</v>
       </c>
       <c r="D3">
-        <v>756.66</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7103,13 +6332,13 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>9.5</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1445.54</v>
+        <v>2291.29</v>
       </c>
       <c r="D4">
-        <v>1316</v>
+        <v>738</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7117,13 +6346,13 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>27.5</v>
       </c>
       <c r="C5">
-        <v>1036.17</v>
+        <v>758</v>
       </c>
       <c r="D5">
-        <v>752.61</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7131,13 +6360,13 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>19.83</v>
       </c>
       <c r="C6">
-        <v>1231.67</v>
+        <v>1766.66</v>
       </c>
       <c r="D6">
-        <v>1150.67</v>
+        <v>666.66</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7145,13 +6374,13 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>14.5</v>
+        <v>9.52</v>
       </c>
       <c r="C7">
-        <v>2619.81</v>
+        <v>2182</v>
       </c>
       <c r="D7">
-        <v>2050</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7159,13 +6388,13 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="C8">
-        <v>2978</v>
+        <v>1254.03</v>
       </c>
       <c r="D8">
-        <v>2652</v>
+        <v>834</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7173,13 +6402,13 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>0.5</v>
       </c>
       <c r="C9">
-        <v>3446</v>
+        <v>63</v>
       </c>
       <c r="D9">
-        <v>3047</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7187,13 +6416,13 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>22.98</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>2703.2</v>
+        <v>689</v>
       </c>
       <c r="D10">
-        <v>2103.2</v>
+        <v>649</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7201,13 +6430,13 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>828</v>
+        <v>387</v>
       </c>
       <c r="D11">
-        <v>818</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7215,13 +6444,13 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>6.5</v>
       </c>
       <c r="C12">
-        <v>3907</v>
+        <v>2117.76</v>
       </c>
       <c r="D12">
-        <v>2868</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7229,13 +6458,13 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>2137.65</v>
+        <v>2096</v>
       </c>
       <c r="D13">
-        <v>1430</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7243,13 +6472,13 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="C14">
-        <v>1019</v>
+        <v>1415</v>
       </c>
       <c r="D14">
-        <v>69</v>
+        <v>938</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -7257,13 +6486,13 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>3.5</v>
+        <v>0.75</v>
       </c>
       <c r="C15">
-        <v>-127.05</v>
+        <v>154.92</v>
       </c>
       <c r="D15">
-        <v>470</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -7313,13 +6542,13 @@
         <v>45</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
-        <v>138.6</v>
+        <v>143</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -7341,13 +6570,13 @@
         <v>47</v>
       </c>
       <c r="B21">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -7391,10 +6620,10 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C1" t="s">
@@ -7439,7 +6668,7 @@
         <v>45</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7461,7 +6690,7 @@
         <v>47</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7502,10 +6731,10 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>79</v>
       </c>
     </row>
@@ -7514,7 +6743,7 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7522,7 +6751,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7530,7 +6759,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>9.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7538,7 +6767,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7546,7 +6775,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>19.83</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7554,7 +6783,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>14.5</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7562,7 +6791,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7570,7 +6799,7 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>18</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7578,7 +6807,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>22.98</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7586,7 +6815,7 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7594,7 +6823,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7602,7 +6831,7 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7610,7 +6839,7 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7618,7 +6847,7 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>3.5</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -7634,29 +6863,29 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" ht="14.75" customHeight="1" spans="1:9">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="8" t="s">
+      <c r="B1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>78</v>
+      <c r="G1" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -8055,24 +7284,24 @@
       <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>84</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="2" ht="14.75" customHeight="1" spans="1:13">
       <c r="A2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>60</v>
       </c>
       <c r="C2">
@@ -8080,22 +7309,22 @@
       </c>
       <c r="D2">
         <f t="array" ref="D2">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B2))</f>
-        <v>19</v>
-      </c>
-      <c r="E2" s="6">
+        <v>12</v>
+      </c>
+      <c r="E2" s="8">
         <f t="shared" ref="E2:E13" si="0">D2/C2</f>
-        <v>0.316666666666667</v>
-      </c>
-      <c r="J2" s="2" t="s">
+        <v>0.2</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M2" s="7" t="s">
+      <c r="L2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8103,7 +7332,7 @@
       <c r="A3" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>61</v>
       </c>
       <c r="C3">
@@ -8111,22 +7340,22 @@
       </c>
       <c r="D3">
         <f t="array" ref="D3">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B3))</f>
-        <v>17</v>
-      </c>
-      <c r="E3" s="6">
+        <v>29</v>
+      </c>
+      <c r="E3" s="8">
         <f t="shared" si="0"/>
-        <v>0.283333333333333</v>
-      </c>
-      <c r="J3" s="7" t="s">
+        <v>0.483333333333333</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="M3" s="7" t="s">
+      <c r="L3" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3" s="9" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8134,7 +7363,7 @@
       <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C4">
@@ -8142,22 +7371,22 @@
       </c>
       <c r="D4">
         <f t="array" ref="D4">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B4))</f>
-        <v>59</v>
-      </c>
-      <c r="E4" s="6">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8">
         <f t="shared" si="0"/>
-        <v>0.983333333333333</v>
-      </c>
-      <c r="J4" s="7" t="s">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="J4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M4" s="7" t="s">
+      <c r="L4" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="9" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8165,30 +7394,30 @@
       <c r="A5" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C5">
         <v>45</v>
       </c>
-      <c r="D5" cm="1">
+      <c r="D5">
         <f t="array" ref="D5">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B5))</f>
-        <v>15</v>
-      </c>
-      <c r="E5" s="6">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8">
         <f t="shared" si="0"/>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="J5" s="7" t="s">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M5" s="7" t="s">
+      <c r="L5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>61</v>
       </c>
     </row>
@@ -8196,30 +7425,30 @@
       <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C6">
         <v>30</v>
       </c>
-      <c r="D6" cm="1">
+      <c r="D6">
         <f t="array" ref="D6">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B6))</f>
-        <v>11</v>
-      </c>
-      <c r="E6" s="6">
+        <v>20</v>
+      </c>
+      <c r="E6" s="8">
         <f t="shared" si="0"/>
-        <v>0.366666666666667</v>
-      </c>
-      <c r="J6" s="7" t="s">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M6" s="7" t="s">
+      <c r="L6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -8227,7 +7456,7 @@
       <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>43</v>
       </c>
       <c r="C7">
@@ -8235,22 +7464,22 @@
       </c>
       <c r="D7">
         <f t="array" ref="D7">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B7))</f>
-        <v>6</v>
-      </c>
-      <c r="E7" s="6">
+        <v>9</v>
+      </c>
+      <c r="E7" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="J7" s="7" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="7" t="s">
+      <c r="K7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M7" s="7" t="s">
+      <c r="L7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M7" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -8258,7 +7487,7 @@
       <c r="A8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>44</v>
       </c>
       <c r="C8">
@@ -8266,22 +7495,22 @@
       </c>
       <c r="D8">
         <f t="array" ref="D8">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B8))</f>
-        <v>6</v>
-      </c>
-      <c r="E8" s="6">
+        <v>3</v>
+      </c>
+      <c r="E8" s="8">
         <f t="shared" si="0"/>
-        <v>0.2</v>
-      </c>
-      <c r="J8" s="7" t="s">
+        <v>0.1</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="7" t="s">
+      <c r="K8" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M8" s="7" t="s">
+      <c r="L8" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M8" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -8289,7 +7518,7 @@
       <c r="A9" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>45</v>
       </c>
       <c r="C9">
@@ -8297,22 +7526,22 @@
       </c>
       <c r="D9">
         <f t="array" ref="D9">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B9))</f>
-        <v>13</v>
-      </c>
-      <c r="E9" s="6">
+        <v>9</v>
+      </c>
+      <c r="E9" s="8">
         <f t="shared" si="0"/>
-        <v>0.433333333333333</v>
-      </c>
-      <c r="J9" s="7" t="s">
+        <v>0.3</v>
+      </c>
+      <c r="J9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K9" s="7" t="s">
+      <c r="K9" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M9" s="7" t="s">
+      <c r="L9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>60</v>
       </c>
     </row>
@@ -8320,7 +7549,7 @@
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>46</v>
       </c>
       <c r="C10">
@@ -8328,22 +7557,22 @@
       </c>
       <c r="D10">
         <f t="array" ref="D10">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B10))</f>
-        <v>43</v>
-      </c>
-      <c r="E10" s="6">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8">
         <f t="shared" si="0"/>
-        <v>1.43333333333333</v>
-      </c>
-      <c r="J10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M10" s="7" t="s">
+      <c r="L10" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M10" s="9" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8351,30 +7580,30 @@
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C11">
         <v>30</v>
       </c>
-      <c r="D11" cm="1">
+      <c r="D11">
         <f t="array" ref="D11">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B11))</f>
-        <v>16</v>
-      </c>
-      <c r="E11" s="6">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.533333333333333</v>
-      </c>
-      <c r="J11" s="7" t="s">
+        <v>0.333333333333333</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L11" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M11" s="7" t="s">
+      <c r="L11" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8382,7 +7611,7 @@
       <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>48</v>
       </c>
       <c r="C12">
@@ -8390,22 +7619,22 @@
       </c>
       <c r="D12">
         <f t="array" ref="D12">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B12))</f>
-        <v>15</v>
-      </c>
-      <c r="E12" s="6">
+        <v>3</v>
+      </c>
+      <c r="E12" s="8">
         <f t="shared" si="0"/>
-        <v>0.5</v>
-      </c>
-      <c r="J12" s="7" t="s">
+        <v>0.1</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="M12" s="7" t="s">
+      <c r="L12" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="9" t="s">
         <v>63</v>
       </c>
     </row>
@@ -8413,72 +7642,72 @@
       <c r="A13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>49</v>
       </c>
       <c r="C13">
         <v>25</v>
       </c>
-      <c r="D13" cm="1">
+      <c r="D13">
         <f t="array" ref="D13">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B13))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="L13" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="M13" s="7" t="s">
+      <c r="L13" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="14" ht="14.75" customHeight="1" spans="1:13">
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="L14" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M14" s="7" t="s">
+      <c r="L14" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" ht="14.75" customHeight="1" spans="1:13">
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="L15" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="M15" s="7" t="s">
+      <c r="L15" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="16" ht="14.75" customHeight="1" spans="1:13">
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K16" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="L16" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="M16" s="7" t="s">
+      <c r="M16" s="9" t="s">
         <v>65</v>
       </c>
     </row>
@@ -8495,11 +7724,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>90</v>
+      <c r="B1" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -8507,7 +7736,7 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>3241.5</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8515,7 +7744,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>1774.27</v>
+        <v>502.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8523,7 +7752,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>4097.34</v>
+        <v>4344</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8531,7 +7760,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>2635.98</v>
+        <v>1783.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -8539,7 +7768,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>2732</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -8547,7 +7776,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>5748</v>
+        <v>5026</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -8555,7 +7784,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>3704</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -8563,7 +7792,7 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>13055</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -8571,7 +7800,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>6851.8</v>
+        <v>1339.5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -8579,7 +7808,7 @@
         <v>32</v>
       </c>
       <c r="B11">
-        <v>2439</v>
+        <v>1661.5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -8587,7 +7816,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>11230</v>
+        <v>6846.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -8595,7 +7824,7 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>6539.605</v>
+        <v>7387</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -8603,7 +7832,7 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>4800.64</v>
+        <v>4117.5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -8611,7 +7840,7 @@
         <v>36</v>
       </c>
       <c r="B15">
-        <v>-210.575</v>
+        <v>232.38</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -8627,7 +7856,7 @@
         <v>43</v>
       </c>
       <c r="B17">
-        <v>313.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -8635,7 +7864,7 @@
         <v>44</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>786.5</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -8643,7 +7872,7 @@
         <v>45</v>
       </c>
       <c r="B19">
-        <v>762.3</v>
+        <v>281</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -8659,7 +7888,7 @@
         <v>47</v>
       </c>
       <c r="B21">
-        <v>1075.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -8675,7 +7904,7 @@
         <v>49</v>
       </c>
       <c r="B23">
-        <v>1345.5</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B1" s="15" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至6月28日）</v>
+        <v>完美一单积分完成通报（截至6月30日）</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="M4" s="27">
         <f ca="1">K4/(J4/X5*U$5)</f>
-        <v>0.120857142857143</v>
+        <v>0.11656</v>
       </c>
       <c r="N4" s="29">
         <f ca="1" t="shared" ref="N4:N10" si="4">VLOOKUP(B:B,V:X,3,0)</f>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="M5" s="27">
         <f ca="1">K5/(J5/X5*U$5)</f>
-        <v>0.123</v>
+        <v>0.118626666666667</v>
       </c>
       <c r="N5" s="29">
         <f ca="1" t="shared" si="4"/>
@@ -2867,13 +2867,13 @@
       </c>
       <c r="U5" s="32">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="V5" s="32"/>
       <c r="W5" s="33"/>
       <c r="X5">
         <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="1:24">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F6" s="27">
         <f ca="1">D6/(C6/X5*U$5)</f>
-        <v>0.321428571428571</v>
+        <v>0.31</v>
       </c>
       <c r="G6" s="24">
         <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -2921,11 +2921,11 @@
       </c>
       <c r="M6" s="27">
         <f ca="1">K6/(J6/X5*U$5)</f>
-        <v>0.981981428571429</v>
+        <v>0.947066533333333</v>
       </c>
       <c r="N6" s="29">
         <f ca="1" t="shared" si="4"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O6" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="F7" s="27">
         <f ca="1">D7/(C7/X5*U$5)</f>
-        <v>2.83928571428571</v>
+        <v>2.73833333333333</v>
       </c>
       <c r="G7" s="24">
         <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -2979,20 +2979,20 @@
         <v>2500</v>
       </c>
       <c r="K7" s="24">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)+2500</f>
-        <v>3258</v>
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>758</v>
       </c>
       <c r="L7" s="27">
         <f ca="1" t="shared" si="3"/>
-        <v>1.3032</v>
+        <v>0.3032</v>
       </c>
       <c r="M7" s="27">
         <f ca="1">K7/(J7/X5*U$5)</f>
-        <v>1.39628571428571</v>
+        <v>0.313306666666667</v>
       </c>
       <c r="N7" s="29">
         <f ca="1" t="shared" si="4"/>
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O7" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F8" s="27">
         <f ca="1">D8/(C8/X5*U$5)</f>
-        <v>1.96392857142857</v>
+        <v>1.8941</v>
       </c>
       <c r="G8" s="24">
         <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3055,11 +3055,11 @@
       </c>
       <c r="M8" s="27">
         <f ca="1">K8/(J8/X5*U$5)</f>
-        <v>0.75714</v>
+        <v>0.730219466666667</v>
       </c>
       <c r="N8" s="29">
         <f ca="1" t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O8" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="F9" s="27">
         <f ca="1">D9/(C9/X5*U$5)</f>
-        <v>1.02</v>
+        <v>0.983733333333333</v>
       </c>
       <c r="G9" s="24">
         <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3122,11 +3122,11 @@
       </c>
       <c r="M9" s="27">
         <f ca="1">K9/(J9/X5*U$5)</f>
-        <v>0.935142857142857</v>
+        <v>0.901893333333333</v>
       </c>
       <c r="N9" s="29">
         <f ca="1" t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O9" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="F10" s="27">
         <f ca="1">D10/(C10/X5*U$5)</f>
-        <v>0.267857142857143</v>
+        <v>0.258333333333333</v>
       </c>
       <c r="G10" s="24">
         <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3200,11 +3200,11 @@
       </c>
       <c r="M10" s="27">
         <f ca="1">K10/(J10/X5*U$5)</f>
-        <v>0.537441428571429</v>
+        <v>0.5183324</v>
       </c>
       <c r="N10" s="29">
         <f ca="1" t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O10" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F11" s="36">
         <f ca="1">D11/(C11/X5*U$5)</f>
-        <v>0.916071428571428</v>
+        <v>0.8835</v>
       </c>
       <c r="G11" s="35">
         <f>SUM(G4:G10)</f>
@@ -3266,15 +3266,15 @@
       </c>
       <c r="K11" s="35">
         <f ca="1">SUM(K4:K10)</f>
-        <v>11320.98</v>
+        <v>8820.98</v>
       </c>
       <c r="L11" s="36">
         <f ca="1" t="shared" si="3"/>
-        <v>0.646913142857143</v>
+        <v>0.504056</v>
       </c>
       <c r="M11" s="36">
         <f ca="1">K11/(J11/X5*U$5)</f>
-        <v>0.693121224489796</v>
+        <v>0.520857866666667</v>
       </c>
       <c r="N11" s="35"/>
       <c r="O11" s="37"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="X11">
         <f ca="1" t="shared" si="7"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1" spans="1:24">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="M12" s="27">
         <f ca="1">K12/(J12/X5*U$5)</f>
-        <v>0.027</v>
+        <v>0.02604</v>
       </c>
       <c r="N12" s="29">
         <f ca="1" t="shared" ref="N12:N18" si="10">VLOOKUP(B:B,V:X,3,0)</f>
@@ -3375,11 +3375,11 @@
       </c>
       <c r="W12">
         <f ca="1" t="shared" si="6"/>
-        <v>3258</v>
+        <v>758</v>
       </c>
       <c r="X12">
         <f ca="1" t="shared" si="7"/>
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" ht="16.5" customHeight="1" spans="1:24">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F13" s="27">
         <f ca="1">D13/(C13/X5*U$5)</f>
-        <v>0.535714285714286</v>
+        <v>0.516666666666667</v>
       </c>
       <c r="G13" s="24">
         <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="M13" s="27">
         <f ca="1">K13/(J13/X5*U$5)</f>
-        <v>0.295285714285714</v>
+        <v>0.284786666666667</v>
       </c>
       <c r="N13" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="X13">
         <f ca="1" t="shared" si="7"/>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:24">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F14" s="27">
         <f ca="1">D14/(C14/X5*U$5)</f>
-        <v>0.214285714285714</v>
+        <v>0.206666666666667</v>
       </c>
       <c r="G14" s="24">
         <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="M14" s="27">
         <f ca="1">K14/(J14/X5*U$5)</f>
-        <v>0.165857142857143</v>
+        <v>0.15996</v>
       </c>
       <c r="N14" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="X14">
         <f ca="1" t="shared" si="7"/>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:24">
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F15" s="27">
         <f ca="1">D15/(C15/X5*U$5)</f>
-        <v>0.696428571428572</v>
+        <v>0.671666666666667</v>
       </c>
       <c r="G15" s="24">
         <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3583,11 +3583,11 @@
       </c>
       <c r="M15" s="27">
         <f ca="1">K15/(J15/X5*U$5)</f>
-        <v>0.907611428571429</v>
+        <v>0.8753408</v>
       </c>
       <c r="N15" s="29">
         <f ca="1" t="shared" si="10"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O15" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="X15">
         <f ca="1" t="shared" si="7"/>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:24">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F16" s="27">
         <f ca="1">D16/(C16/X5*U$5)</f>
-        <v>1.23214285714286</v>
+        <v>1.18833333333333</v>
       </c>
       <c r="G16" s="24">
         <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3661,11 +3661,11 @@
       </c>
       <c r="M16" s="27">
         <f ca="1">K16/(J16/X5*U$5)</f>
-        <v>0.898285714285714</v>
+        <v>0.866346666666667</v>
       </c>
       <c r="N16" s="29">
         <f ca="1" t="shared" si="10"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="F17" s="27">
         <f ca="1">D17/(C17/X5*U$5)</f>
-        <v>1.065</v>
+        <v>1.02713333333333</v>
       </c>
       <c r="G17" s="24">
         <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3739,11 +3739,11 @@
       </c>
       <c r="M17" s="27">
         <f ca="1">K17/(J17/X5*U$5)</f>
-        <v>0.606428571428572</v>
+        <v>0.584866666666667</v>
       </c>
       <c r="N17" s="29">
         <f ca="1" t="shared" si="10"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O17" s="29">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F18" s="27">
         <f ca="1">D18/(C18/X5*U$5)</f>
-        <v>0.0803571428571429</v>
+        <v>0.0775</v>
       </c>
       <c r="G18" s="24">
         <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="M18" s="27">
         <f ca="1">K18/(J18/X5*U$5)</f>
-        <v>0.0663942857142857</v>
+        <v>0.0640336</v>
       </c>
       <c r="N18" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F19" s="36">
         <f ca="1">D19/(C19/X5*U$5)</f>
-        <v>0.546275510204081</v>
+        <v>0.526852380952381</v>
       </c>
       <c r="G19" s="41">
         <f>SUM(G12:G18)</f>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M19" s="42">
         <f ca="1">K19/(J19/X5*U$5)</f>
-        <v>0.423837551020408</v>
+        <v>0.408767771428571</v>
       </c>
       <c r="N19" s="41"/>
       <c r="O19" s="43"/>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="X19">
         <f ca="1" t="shared" si="7"/>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:24">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F20" s="49">
         <f ca="1">D20/(C20/X5*U$5)</f>
-        <v>0.775487012987013</v>
+        <v>0.747914141414141</v>
       </c>
       <c r="G20" s="50">
         <f>G11+G19</f>
@@ -3951,15 +3951,15 @@
       </c>
       <c r="K20" s="46">
         <f ca="1">K11+K19</f>
-        <v>18243.66</v>
+        <v>15743.66</v>
       </c>
       <c r="L20" s="53">
         <f ca="1" t="shared" si="3"/>
-        <v>0.521247428571429</v>
+        <v>0.449818857142857</v>
       </c>
       <c r="M20" s="54">
         <f ca="1">K20/(J20/X5*U$5)</f>
-        <v>0.558479387755102</v>
+        <v>0.464812819047619</v>
       </c>
       <c r="N20" s="55"/>
       <c r="O20" s="56" t="s">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="X20">
         <f ca="1" t="shared" si="7"/>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:24">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="X22">
         <f ca="1" t="shared" si="7"/>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" ht="14.25" customHeight="1" spans="1:24">
@@ -4665,11 +4665,11 @@
       </c>
       <c r="R35" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P35,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>3.41</v>
+        <v>3.18</v>
       </c>
       <c r="S35" s="82">
         <f ca="1" t="shared" ref="S35:S44" si="11">R35/Q35</f>
-        <v>0.802352941176471</v>
+        <v>0.748235294117647</v>
       </c>
       <c r="T35" s="83">
         <f ca="1">RANK(S35,S35:S43)</f>
@@ -4723,11 +4723,11 @@
       </c>
       <c r="R36" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P36,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.8</v>
+        <v>4.48</v>
       </c>
       <c r="S36" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.834782608695652</v>
+        <v>0.779130434782609</v>
       </c>
       <c r="T36" s="89">
         <f ca="1">RANK(S36,S35:S43)</f>
@@ -4781,11 +4781,11 @@
       </c>
       <c r="R37" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P37,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>10.74</v>
+        <v>10.02</v>
       </c>
       <c r="S37" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>3.05113636363636</v>
+        <v>2.84659090909091</v>
       </c>
       <c r="T37" s="83">
         <f ca="1">RANK(S37,S35:S43)</f>
@@ -4839,11 +4839,11 @@
       </c>
       <c r="R38" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P38,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.42</v>
+        <v>4.12</v>
       </c>
       <c r="S38" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.11335012594458</v>
+        <v>1.03778337531486</v>
       </c>
       <c r="T38" s="89">
         <f ca="1">RANK(S38,S35:S43)</f>
@@ -4899,11 +4899,11 @@
       </c>
       <c r="R39" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P39,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="S39" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.28151260504202</v>
+        <v>1.19747899159664</v>
       </c>
       <c r="T39" s="83">
         <f ca="1">RANK(S39,S35:S43)</f>
@@ -4957,11 +4957,11 @@
       </c>
       <c r="R40" s="96">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P40,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S40" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.926923076923077</v>
+        <v>0.865384615384615</v>
       </c>
       <c r="T40" s="89">
         <f ca="1">RANK(S40,S35:S43)</f>
@@ -5014,11 +5014,11 @@
       </c>
       <c r="R41" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P41,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="S41" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.846473029045643</v>
+        <v>0.788381742738589</v>
       </c>
       <c r="T41" s="83">
         <f ca="1">RANK(S41,S35:S43)</f>
@@ -5071,11 +5071,11 @@
       </c>
       <c r="R42" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P42,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="S42" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.93167701863354</v>
+        <v>0.869565217391304</v>
       </c>
       <c r="T42" s="89">
         <f ca="1">RANK(S42,S35:S43)</f>
@@ -5127,11 +5127,11 @@
       </c>
       <c r="R43" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P43,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.49</v>
+        <v>4.19</v>
       </c>
       <c r="S43" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.33630952380952</v>
+        <v>1.24702380952381</v>
       </c>
       <c r="T43" s="83">
         <f ca="1">RANK(S43,S35:S43)</f>
@@ -5166,11 +5166,11 @@
       </c>
       <c r="R44" s="101">
         <f ca="1">SUM(R35:R43)</f>
-        <v>38.36</v>
+        <v>35.79</v>
       </c>
       <c r="S44" s="102">
         <f ca="1" t="shared" si="11"/>
-        <v>1.21932612841704</v>
+        <v>1.13763509218055</v>
       </c>
       <c r="T44" s="103" t="s">
         <v>73</v>
@@ -5276,7 +5276,6 @@
       <c r="E51"/>
       <c r="F51"/>
       <c r="G51"/>
-      <c r="H51"/>
       <c r="I51"/>
       <c r="J51"/>
       <c r="K51"/>
@@ -5286,7 +5285,6 @@
       <c r="E52"/>
       <c r="F52"/>
       <c r="G52"/>
-      <c r="H52"/>
       <c r="I52"/>
       <c r="J52"/>
       <c r="K52"/>
@@ -5296,7 +5294,6 @@
       <c r="E53"/>
       <c r="F53"/>
       <c r="G53"/>
-      <c r="H53"/>
       <c r="I53"/>
       <c r="J53"/>
       <c r="K53"/>
@@ -5306,7 +5303,6 @@
       <c r="E54"/>
       <c r="F54"/>
       <c r="G54"/>
-      <c r="H54"/>
       <c r="I54"/>
       <c r="J54"/>
       <c r="K54"/>
@@ -5316,7 +5312,6 @@
       <c r="E55"/>
       <c r="F55"/>
       <c r="G55"/>
-      <c r="H55"/>
       <c r="I55"/>
       <c r="J55"/>
       <c r="K55"/>
@@ -5326,7 +5321,6 @@
       <c r="E56"/>
       <c r="F56"/>
       <c r="G56"/>
-      <c r="H56"/>
       <c r="I56"/>
       <c r="J56"/>
       <c r="K56"/>
@@ -5336,7 +5330,6 @@
       <c r="E57"/>
       <c r="F57"/>
       <c r="G57"/>
-      <c r="H57"/>
       <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
@@ -5346,7 +5339,6 @@
       <c r="E58"/>
       <c r="F58"/>
       <c r="G58"/>
-      <c r="H58"/>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
@@ -5356,7 +5348,6 @@
       <c r="E59"/>
       <c r="F59"/>
       <c r="G59"/>
-      <c r="H59"/>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
@@ -5367,7 +5358,6 @@
       <c r="E60"/>
       <c r="F60"/>
       <c r="G60"/>
-      <c r="H60"/>
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
@@ -5378,7 +5368,6 @@
       <c r="E61"/>
       <c r="F61"/>
       <c r="G61"/>
-      <c r="H61"/>
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
@@ -5389,7 +5378,6 @@
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62"/>
-      <c r="H62"/>
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
@@ -5400,7 +5388,6 @@
       <c r="E63"/>
       <c r="F63"/>
       <c r="G63"/>
-      <c r="H63"/>
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
@@ -5411,7 +5398,6 @@
       <c r="E64"/>
       <c r="F64"/>
       <c r="G64"/>
-      <c r="H64"/>
       <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
@@ -5422,7 +5408,6 @@
       <c r="E65"/>
       <c r="F65"/>
       <c r="G65"/>
-      <c r="H65"/>
       <c r="I65"/>
       <c r="J65"/>
       <c r="K65"/>
@@ -5433,7 +5418,6 @@
       <c r="E66"/>
       <c r="F66"/>
       <c r="G66"/>
-      <c r="H66"/>
       <c r="I66"/>
       <c r="J66"/>
       <c r="K66"/>
@@ -5861,7 +5845,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{68b0e617-2644-403d-96f0-b09a47b9c717}</x14:id>
+          <x14:id>{1fcb02ed-b02e-466f-b96e-b7e4bb01a4ef}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5876,7 +5860,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{68b0e617-2644-403d-96f0-b09a47b9c717}">
+          <x14:cfRule type="dataBar" id="{1fcb02ed-b02e-466f-b96e-b7e4bb01a4ef}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -2627,7 +2627,7 @@
       </c>
       <c r="B1" s="15" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至6月30日）</v>
+        <v>完美一单积分完成通报（截至7月1日）</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="M4" s="27">
         <f ca="1">K4/(J4/X5*U$5)</f>
-        <v>0.11656</v>
+        <v>3.4968</v>
       </c>
       <c r="N4" s="29">
         <f ca="1" t="shared" ref="N4:N10" si="4">VLOOKUP(B:B,V:X,3,0)</f>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="M5" s="27">
         <f ca="1">K5/(J5/X5*U$5)</f>
-        <v>0.118626666666667</v>
+        <v>3.5588</v>
       </c>
       <c r="N5" s="29">
         <f ca="1" t="shared" si="4"/>
@@ -2863,11 +2863,11 @@
       </c>
       <c r="T5" s="32" t="str">
         <f ca="1">MONTH(TODAY()-1)&amp;"月"</f>
-        <v>6月</v>
+        <v>7月</v>
       </c>
       <c r="U5" s="32">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="V5" s="32"/>
       <c r="W5" s="33"/>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F6" s="27">
         <f ca="1">D6/(C6/X5*U$5)</f>
-        <v>0.31</v>
+        <v>9.3</v>
       </c>
       <c r="G6" s="24">
         <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M6" s="27">
         <f ca="1">K6/(J6/X5*U$5)</f>
-        <v>0.947066533333333</v>
+        <v>28.411996</v>
       </c>
       <c r="N6" s="29">
         <f ca="1" t="shared" si="4"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="F7" s="27">
         <f ca="1">D7/(C7/X5*U$5)</f>
-        <v>2.73833333333333</v>
+        <v>82.15</v>
       </c>
       <c r="G7" s="24">
         <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="M7" s="27">
         <f ca="1">K7/(J7/X5*U$5)</f>
-        <v>0.313306666666667</v>
+        <v>9.3992</v>
       </c>
       <c r="N7" s="29">
         <f ca="1" t="shared" si="4"/>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="F8" s="27">
         <f ca="1">D8/(C8/X5*U$5)</f>
-        <v>1.8941</v>
+        <v>56.823</v>
       </c>
       <c r="G8" s="24">
         <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="M8" s="27">
         <f ca="1">K8/(J8/X5*U$5)</f>
-        <v>0.730219466666667</v>
+        <v>21.906584</v>
       </c>
       <c r="N8" s="29">
         <f ca="1" t="shared" si="4"/>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="F9" s="27">
         <f ca="1">D9/(C9/X5*U$5)</f>
-        <v>0.983733333333333</v>
+        <v>29.512</v>
       </c>
       <c r="G9" s="24">
         <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="M9" s="27">
         <f ca="1">K9/(J9/X5*U$5)</f>
-        <v>0.901893333333333</v>
+        <v>27.0568</v>
       </c>
       <c r="N9" s="29">
         <f ca="1" t="shared" si="4"/>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="F10" s="27">
         <f ca="1">D10/(C10/X5*U$5)</f>
-        <v>0.258333333333333</v>
+        <v>7.75</v>
       </c>
       <c r="G10" s="24">
         <f>_xlfn.XLOOKUP(B10,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3200,7 +3200,7 @@
       </c>
       <c r="M10" s="27">
         <f ca="1">K10/(J10/X5*U$5)</f>
-        <v>0.5183324</v>
+        <v>15.549972</v>
       </c>
       <c r="N10" s="29">
         <f ca="1" t="shared" si="4"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="F11" s="36">
         <f ca="1">D11/(C11/X5*U$5)</f>
-        <v>0.8835</v>
+        <v>26.505</v>
       </c>
       <c r="G11" s="35">
         <f>SUM(G4:G10)</f>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M11" s="36">
         <f ca="1">K11/(J11/X5*U$5)</f>
-        <v>0.520857866666667</v>
+        <v>15.625736</v>
       </c>
       <c r="N11" s="35"/>
       <c r="O11" s="37"/>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="M12" s="27">
         <f ca="1">K12/(J12/X5*U$5)</f>
-        <v>0.02604</v>
+        <v>0.7812</v>
       </c>
       <c r="N12" s="29">
         <f ca="1" t="shared" ref="N12:N18" si="10">VLOOKUP(B:B,V:X,3,0)</f>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="F13" s="27">
         <f ca="1">D13/(C13/X5*U$5)</f>
-        <v>0.516666666666667</v>
+        <v>15.5</v>
       </c>
       <c r="G13" s="24">
         <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="M13" s="27">
         <f ca="1">K13/(J13/X5*U$5)</f>
-        <v>0.284786666666667</v>
+        <v>8.5436</v>
       </c>
       <c r="N13" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F14" s="27">
         <f ca="1">D14/(C14/X5*U$5)</f>
-        <v>0.206666666666667</v>
+        <v>6.2</v>
       </c>
       <c r="G14" s="24">
         <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="M14" s="27">
         <f ca="1">K14/(J14/X5*U$5)</f>
-        <v>0.15996</v>
+        <v>4.7988</v>
       </c>
       <c r="N14" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="F15" s="27">
         <f ca="1">D15/(C15/X5*U$5)</f>
-        <v>0.671666666666667</v>
+        <v>20.15</v>
       </c>
       <c r="G15" s="24">
         <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="M15" s="27">
         <f ca="1">K15/(J15/X5*U$5)</f>
-        <v>0.8753408</v>
+        <v>26.260224</v>
       </c>
       <c r="N15" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="F16" s="27">
         <f ca="1">D16/(C16/X5*U$5)</f>
-        <v>1.18833333333333</v>
+        <v>35.65</v>
       </c>
       <c r="G16" s="24">
         <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="M16" s="27">
         <f ca="1">K16/(J16/X5*U$5)</f>
-        <v>0.866346666666667</v>
+        <v>25.9904</v>
       </c>
       <c r="N16" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="F17" s="27">
         <f ca="1">D17/(C17/X5*U$5)</f>
-        <v>1.02713333333333</v>
+        <v>30.814</v>
       </c>
       <c r="G17" s="24">
         <f>_xlfn.XLOOKUP(B17,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="M17" s="27">
         <f ca="1">K17/(J17/X5*U$5)</f>
-        <v>0.584866666666667</v>
+        <v>17.546</v>
       </c>
       <c r="N17" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F18" s="27">
         <f ca="1">D18/(C18/X5*U$5)</f>
-        <v>0.0775</v>
+        <v>2.325</v>
       </c>
       <c r="G18" s="24">
         <f>_xlfn.XLOOKUP(B18,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="M18" s="27">
         <f ca="1">K18/(J18/X5*U$5)</f>
-        <v>0.0640336</v>
+        <v>1.921008</v>
       </c>
       <c r="N18" s="29">
         <f ca="1" t="shared" si="10"/>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F19" s="36">
         <f ca="1">D19/(C19/X5*U$5)</f>
-        <v>0.526852380952381</v>
+        <v>15.8055714285714</v>
       </c>
       <c r="G19" s="41">
         <f>SUM(G12:G18)</f>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="M19" s="42">
         <f ca="1">K19/(J19/X5*U$5)</f>
-        <v>0.408767771428571</v>
+        <v>12.2630331428571</v>
       </c>
       <c r="N19" s="41"/>
       <c r="O19" s="43"/>
@@ -3937,7 +3937,7 @@
       </c>
       <c r="F20" s="49">
         <f ca="1">D20/(C20/X5*U$5)</f>
-        <v>0.747914141414141</v>
+        <v>22.4374242424242</v>
       </c>
       <c r="G20" s="50">
         <f>G11+G19</f>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="M20" s="54">
         <f ca="1">K20/(J20/X5*U$5)</f>
-        <v>0.464812819047619</v>
+        <v>13.9443845714286</v>
       </c>
       <c r="N20" s="55"/>
       <c r="O20" s="56" t="s">
@@ -4623,7 +4623,7 @@
         <v>陈梓铭</v>
       </c>
       <c r="C35" s="75">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D35" s="75">
         <f>高装高套!B2</f>
@@ -4665,11 +4665,11 @@
       </c>
       <c r="R35" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P35,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>3.18</v>
+        <v>95.54</v>
       </c>
       <c r="S35" s="82">
         <f ca="1" t="shared" ref="S35:S44" si="11">R35/Q35</f>
-        <v>0.748235294117647</v>
+        <v>22.48</v>
       </c>
       <c r="T35" s="83">
         <f ca="1">RANK(S35,S35:S43)</f>
@@ -4683,7 +4683,7 @@
         <v>程庆德</v>
       </c>
       <c r="C36" s="85">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D36" s="85">
         <f>高装高套!B3</f>
@@ -4723,11 +4723,11 @@
       </c>
       <c r="R36" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P36,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.48</v>
+        <v>134.28</v>
       </c>
       <c r="S36" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.779130434782609</v>
+        <v>23.3530434782609</v>
       </c>
       <c r="T36" s="89">
         <f ca="1">RANK(S36,S35:S43)</f>
@@ -4741,7 +4741,7 @@
         <v>刘奇峻</v>
       </c>
       <c r="C37" s="75">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D37" s="75">
         <f>高装高套!B4</f>
@@ -4781,11 +4781,11 @@
       </c>
       <c r="R37" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P37,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>10.02</v>
+        <v>300.69</v>
       </c>
       <c r="S37" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>2.84659090909091</v>
+        <v>85.4232954545455</v>
       </c>
       <c r="T37" s="83">
         <f ca="1">RANK(S37,S35:S43)</f>
@@ -4799,7 +4799,7 @@
         <v>龙家宝</v>
       </c>
       <c r="C38" s="85">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D38" s="85">
         <f>高装高套!B5</f>
@@ -4839,11 +4839,11 @@
       </c>
       <c r="R38" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P38,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.12</v>
+        <v>123.63</v>
       </c>
       <c r="S38" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.03778337531486</v>
+        <v>31.1410579345088</v>
       </c>
       <c r="T38" s="89">
         <f ca="1">RANK(S38,S35:S43)</f>
@@ -4857,7 +4857,7 @@
         <v>罗紫杰</v>
       </c>
       <c r="C39" s="75">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D39" s="75">
         <f>高装高套!B6</f>
@@ -4899,11 +4899,11 @@
       </c>
       <c r="R39" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P39,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>2.85</v>
+        <v>85.52</v>
       </c>
       <c r="S39" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.19747899159664</v>
+        <v>35.9327731092437</v>
       </c>
       <c r="T39" s="83">
         <f ca="1">RANK(S39,S35:S43)</f>
@@ -4917,7 +4917,7 @@
         <v>莫健铭</v>
       </c>
       <c r="C40" s="85">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D40" s="85">
         <f>高装高套!B7</f>
@@ -4957,11 +4957,11 @@
       </c>
       <c r="R40" s="96">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P40,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>2.25</v>
+        <v>67.6</v>
       </c>
       <c r="S40" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.865384615384615</v>
+        <v>26</v>
       </c>
       <c r="T40" s="89">
         <f ca="1">RANK(S40,S35:S43)</f>
@@ -4975,7 +4975,7 @@
         <v>吴广仁</v>
       </c>
       <c r="C41" s="75">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D41" s="75">
         <f>高装高套!B8</f>
@@ -5014,11 +5014,11 @@
       </c>
       <c r="R41" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P41,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>1.9</v>
+        <v>57</v>
       </c>
       <c r="S41" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.788381742738589</v>
+        <v>23.6514522821577</v>
       </c>
       <c r="T41" s="83">
         <f ca="1">RANK(S41,S35:S43)</f>
@@ -5032,7 +5032,7 @@
         <v>王洪明</v>
       </c>
       <c r="C42" s="85">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="D42" s="85">
         <f>高装高套!B9</f>
@@ -5071,11 +5071,11 @@
       </c>
       <c r="R42" s="88">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P42,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>2.8</v>
+        <v>84.02</v>
       </c>
       <c r="S42" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>0.869565217391304</v>
+        <v>26.0931677018634</v>
       </c>
       <c r="T42" s="89">
         <f ca="1">RANK(S42,S35:S43)</f>
@@ -5089,7 +5089,7 @@
       <c r="B43" s="99"/>
       <c r="C43" s="98">
         <f>SUM(C35:C42)</f>
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D43" s="98">
         <f>SUM(D35:D42)</f>
@@ -5127,11 +5127,11 @@
       </c>
       <c r="R43" s="81">
         <f ca="1">ROUND(_xlfn.XLOOKUP(P43,高套!A:A,高套!B:B,0)/U5,2)</f>
-        <v>4.19</v>
+        <v>125.64</v>
       </c>
       <c r="S43" s="82">
         <f ca="1" t="shared" si="11"/>
-        <v>1.24702380952381</v>
+        <v>37.3928571428571</v>
       </c>
       <c r="T43" s="83">
         <f ca="1">RANK(S43,S35:S43)</f>
@@ -5166,11 +5166,11 @@
       </c>
       <c r="R44" s="101">
         <f ca="1">SUM(R35:R43)</f>
-        <v>35.79</v>
+        <v>1073.92</v>
       </c>
       <c r="S44" s="102">
         <f ca="1" t="shared" si="11"/>
-        <v>1.13763509218055</v>
+        <v>34.1360457724094</v>
       </c>
       <c r="T44" s="103" t="s">
         <v>73</v>
@@ -5845,7 +5845,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{1fcb02ed-b02e-466f-b96e-b7e4bb01a4ef}</x14:id>
+          <x14:id>{8d5c784a-fc57-4f85-a768-0a2ffb51a4be}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5860,7 +5860,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{1fcb02ed-b02e-466f-b96e-b7e4bb01a4ef}">
+          <x14:cfRule type="dataBar" id="{8d5c784a-fc57-4f85-a768-0a2ffb51a4be}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -13,9 +13,10 @@
     <sheet name="完美一单" sheetId="4" r:id="rId4"/>
     <sheet name="高装高套" sheetId="5" r:id="rId5"/>
     <sheet name="红黄牌高套" sheetId="6" r:id="rId6"/>
-    <sheet name="交付高装" sheetId="8" r:id="rId7"/>
-    <sheet name="激励" sheetId="9" r:id="rId8"/>
-    <sheet name="积分" sheetId="10" r:id="rId9"/>
+    <sheet name="交付高装" sheetId="7" r:id="rId7"/>
+    <sheet name="激励" sheetId="8" r:id="rId8"/>
+    <sheet name="积分" sheetId="9" r:id="rId9"/>
+    <sheet name="净增积分" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="93">
   <si>
     <t>团队</t>
   </si>
@@ -76,7 +77,10 @@
     <t>积分任务值</t>
   </si>
   <si>
-    <t>积分完成</t>
+    <t>增量积分</t>
+  </si>
+  <si>
+    <t>净增积分</t>
   </si>
   <si>
     <t>积分完成率</t>
@@ -198,6 +202,9 @@
     <t>高套发展</t>
   </si>
   <si>
+    <t>积分完成</t>
+  </si>
+  <si>
     <t>协同CP发展的主从网关数</t>
   </si>
   <si>
@@ -258,7 +265,49 @@
     <t>王洪明(挂整体指标)</t>
   </si>
   <si>
-    <t>净增积分</t>
+    <t>高套数</t>
+  </si>
+  <si>
+    <t>钟俊杰</t>
+  </si>
+  <si>
+    <t>潘观友</t>
+  </si>
+  <si>
+    <t>张端</t>
+  </si>
+  <si>
+    <t>新增积分（全业务）</t>
+  </si>
+  <si>
+    <t>负责客户经理</t>
+  </si>
+  <si>
+    <t>装维协同结对</t>
+  </si>
+  <si>
+    <t>装维负责区域</t>
+  </si>
+  <si>
+    <t>协同交付经理</t>
+  </si>
+  <si>
+    <t>城东</t>
+  </si>
+  <si>
+    <t>城中</t>
+  </si>
+  <si>
+    <t>城西</t>
+  </si>
+  <si>
+    <t>陈泳诗（休产假）</t>
+  </si>
+  <si>
+    <t>王洪明（技能待提升，4月需协同其他装维上门)</t>
+  </si>
+  <si>
+    <t>激励金额</t>
   </si>
   <si>
     <t>基本面</t>
@@ -268,54 +317,6 @@
   </si>
   <si>
     <t>增量积分落格率</t>
-  </si>
-  <si>
-    <t>高套数</t>
-  </si>
-  <si>
-    <t>钟俊杰</t>
-  </si>
-  <si>
-    <t>冯艺康</t>
-  </si>
-  <si>
-    <t>潘观友</t>
-  </si>
-  <si>
-    <t>张端</t>
-  </si>
-  <si>
-    <t>新增积分（全业务）</t>
-  </si>
-  <si>
-    <t>负责客户经理</t>
-  </si>
-  <si>
-    <t>装维协同结对</t>
-  </si>
-  <si>
-    <t>装维负责区域</t>
-  </si>
-  <si>
-    <t>协同交付经理</t>
-  </si>
-  <si>
-    <t>城东</t>
-  </si>
-  <si>
-    <t>城中</t>
-  </si>
-  <si>
-    <t>城西</t>
-  </si>
-  <si>
-    <t>陈泳诗（休产假）</t>
-  </si>
-  <si>
-    <t>王洪明（技能待提升，4月需协同其他装维上门)</t>
-  </si>
-  <si>
-    <t>激励金额</t>
   </si>
 </sst>
 </file>
@@ -934,7 +935,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1061,19 +1062,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF000000"/>
       </left>
       <right/>
@@ -1081,17 +1069,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1565,7 +1542,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="40">
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="38">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
@@ -1577,34 +1554,34 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="41">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="41">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="39">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="42">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="40">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="21" borderId="43">
+    <xf numFmtId="0" fontId="32" fillId="21" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="22" borderId="44">
+    <xf numFmtId="0" fontId="33" fillId="22" borderId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="22" borderId="43">
+    <xf numFmtId="0" fontId="34" fillId="22" borderId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="45">
+    <xf numFmtId="0" fontId="35" fillId="23" borderId="43">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="46">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="44">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="47">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="45">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="24" borderId="0">
@@ -1689,7 +1666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1730,22 +1707,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1776,36 +1741,23 @@
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="5" fillId="5" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1815,66 +1767,68 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="4" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="4" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1887,100 +1841,103 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="14" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="14" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="20" fillId="16" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="20" fillId="16" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="19" fillId="19" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="19" fillId="19" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="20" fillId="17" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="178" fontId="20" fillId="17" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="23" fillId="8" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="23" fillId="8" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2521,7 +2478,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X102"/>
+  <dimension ref="A1:Z102"/>
   <sheetFormatPr defaultColWidth="10.6363636363636" defaultRowHeight="14"/>
   <cols>
     <col min="4" max="4" width="9.25454545454545" style="10" customWidth="1"/>
@@ -2529,16 +2486,16 @@
     <col min="6" max="7" width="9.25454545454545" style="10" customWidth="1"/>
     <col min="9" max="10" width="9.25454545454545" style="10" customWidth="1"/>
     <col min="11" max="11" width="10.9" style="10" customWidth="1"/>
-    <col min="15" max="15" width="9.90909090909091" style="10" customWidth="1"/>
+    <col min="16" max="16" width="9.90909090909091" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1" spans="1:24">
+    <row r="1" ht="14.25" customHeight="1" spans="1:26">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至7月8日）</v>
+        <v>完美一单积分完成通报（截至7月9日）</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2555,20 +2512,21 @@
       <c r="O1" s="13"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
-      <c r="R1" s="14"/>
-    </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:24">
+      <c r="R1" s="13"/>
+      <c r="S1" s="14"/>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" spans="1:26">
       <c r="A2" s="15"/>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="18"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="14"/>
       <c r="J2" s="12" t="s">
         <v>2</v>
       </c>
@@ -2576,15 +2534,16 @@
       <c r="L2" s="13"/>
       <c r="M2" s="13"/>
       <c r="N2" s="13"/>
-      <c r="O2" s="14"/>
-      <c r="P2" s="12" t="s">
+      <c r="O2" s="13"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="14"/>
-    </row>
-    <row r="3" ht="70" customHeight="1" spans="1:24">
-      <c r="A3" s="19"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="14"/>
+    </row>
+    <row r="3" ht="70" customHeight="1" spans="1:26">
+      <c r="A3" s="16"/>
       <c r="B3" s="12" t="s">
         <v>4</v>
       </c>
@@ -2619,10 +2578,10 @@
         <v>14</v>
       </c>
       <c r="M3" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="N3" s="12" t="s">
-        <v>15</v>
       </c>
       <c r="O3" s="12" t="s">
         <v>16</v>
@@ -2633,2346 +2592,2442 @@
       <c r="Q3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="20" t="s">
+      <c r="R3" s="12" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A4" s="21" t="s">
+      <c r="S3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="22" t="s">
+    </row>
+    <row r="4" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="22">
+      <c r="B4" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="18">
         <v>10</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="19">
         <f>_xlfn.XLOOKUP(B4,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="E4" s="24">
-        <f t="shared" ref="E4:E19" si="0">D4/C4</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="25">
-        <f ca="1">D4/(C4/X4*U$4)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="22">
+      <c r="E4" s="20">
+        <f t="shared" ref="E4:E18" si="0">D4/C4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="21">
+        <f ca="1">D4/(C4/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
         <f>_xlfn.XLOOKUP(B4,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="H4" s="22" t="str">
         <f t="shared" ref="H4:H9" si="1">IF(G4&gt;=3,"否","是")</f>
         <v>是</v>
       </c>
-      <c r="I4" s="22" t="str">
+      <c r="I4" s="18" t="str">
         <f t="shared" ref="I4:I9" si="2">IF(G4&gt;=15,"金牌",IF(G4&gt;=12,"银牌",""))</f>
         <v/>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="18">
         <v>2500</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>287</v>
-      </c>
-      <c r="L4" s="25">
-        <f ca="1" t="shared" ref="L4:L19" si="3">K4/J4</f>
-        <v>0.1148</v>
-      </c>
-      <c r="M4" s="25">
-        <f ca="1">K4/(J4/X4*U$4)</f>
-        <v>0.44485</v>
-      </c>
-      <c r="N4" s="27">
-        <f ca="1" t="shared" ref="N4:N9" si="4">VLOOKUP(B:B,V:X,3,0)</f>
-        <v>10</v>
-      </c>
-      <c r="O4" s="27">
+        <v>60</v>
+      </c>
+      <c r="L4" s="18">
+        <f>_xlfn.XLOOKUP(B4,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>99</v>
+      </c>
+      <c r="M4" s="21">
+        <f ca="1" t="shared" ref="M4:M18" si="3">K4/J4</f>
+        <v>0.024</v>
+      </c>
+      <c r="N4" s="21">
+        <f ca="1">K4/(J4/Z4*W$4)</f>
+        <v>0.0826666666666667</v>
+      </c>
+      <c r="O4" s="23">
+        <f ca="1" t="shared" ref="O4:O9" si="4">VLOOKUP(B:B,X:Z,3,0)</f>
+        <v>9</v>
+      </c>
+      <c r="P4" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>502.5</v>
-      </c>
-      <c r="P4" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="19">
         <v>15</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="R4" s="24">
         <f>_xlfn.XLOOKUP(B4,全光组网!A:A,全光组网!B:B,0)</f>
         <v>0</v>
       </c>
-      <c r="R4" s="29">
-        <f>Q4/P4</f>
-        <v>0</v>
-      </c>
-      <c r="T4" s="30" t="str">
+      <c r="S4" s="25">
+        <f t="shared" ref="S4:S19" si="5">R4/Q4</f>
+        <v>0</v>
+      </c>
+      <c r="V4" s="26" t="str">
         <f ca="1">MONTH(TODAY()-1)&amp;"月"</f>
         <v>7月</v>
       </c>
-      <c r="U4" s="30">
+      <c r="W4" s="26">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>8</v>
-      </c>
-      <c r="V4" s="30"/>
-      <c r="W4" s="31"/>
-      <c r="X4">
+        <v>9</v>
+      </c>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4">
         <f ca="1">DAY(EOMONTH(TODAY(),0))</f>
         <v>31</v>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A5" s="32"/>
-      <c r="B5" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="22">
+    <row r="5" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A5" s="15"/>
+      <c r="B5" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="18">
         <v>10</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="19">
         <f>_xlfn.XLOOKUP(B5,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="21">
+        <f ca="1">D5/(C5/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="18">
+        <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I5" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J5" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K5" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>1792.67</v>
+      </c>
+      <c r="L5" s="18">
+        <f>_xlfn.XLOOKUP(B5,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>1366.67</v>
+      </c>
+      <c r="M5" s="21">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.717068</v>
+      </c>
+      <c r="N5" s="21">
+        <f ca="1">K5/(J5/Z4*W$4)</f>
+        <v>2.46990088888889</v>
+      </c>
+      <c r="O5" s="23">
+        <f ca="1" t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="P5" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>3489</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>15</v>
+      </c>
+      <c r="R5" s="24">
+        <f>_xlfn.XLOOKUP(B5,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S5" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A6" s="15"/>
+      <c r="B6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="18">
+        <v>10</v>
+      </c>
+      <c r="D6" s="19">
+        <f>_xlfn.XLOOKUP(B6,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="21">
+        <f ca="1">D6/(C6/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="18">
+        <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I6" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J6" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K6" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>772.33</v>
+      </c>
+      <c r="L6" s="18">
+        <f>_xlfn.XLOOKUP(B6,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>316.83</v>
+      </c>
+      <c r="M6" s="21">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.308932</v>
+      </c>
+      <c r="N6" s="21">
+        <f ca="1">K6/(J6/Z4*W$4)</f>
+        <v>1.06409911111111</v>
+      </c>
+      <c r="O6" s="23">
+        <f ca="1" t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="E5" s="24">
+      <c r="P6" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>658.5</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>15</v>
+      </c>
+      <c r="R6" s="24">
+        <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S6" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A7" s="15"/>
+      <c r="B7" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="18">
+        <v>10</v>
+      </c>
+      <c r="D7" s="19">
+        <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E7" s="20">
         <f t="shared" si="0"/>
-        <v>0.3</v>
-      </c>
-      <c r="F5" s="25">
-        <f ca="1">D5/(C5/X4*U$4)</f>
-        <v>1.1625</v>
-      </c>
-      <c r="G5" s="22">
-        <f>_xlfn.XLOOKUP(B5,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="H5" s="26" t="str">
+        <v>0.15</v>
+      </c>
+      <c r="F7" s="21">
+        <f ca="1">D7/(C7/Z4*W$4)</f>
+        <v>0.516666666666667</v>
+      </c>
+      <c r="G7" s="18">
+        <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="22" t="str">
         <f t="shared" si="1"/>
         <v>否</v>
       </c>
-      <c r="I5" s="22" t="str">
+      <c r="I7" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J5" s="22">
+      <c r="J7" s="18">
         <v>2500</v>
       </c>
-      <c r="K5" s="22">
+      <c r="K7" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2291.29</v>
-      </c>
-      <c r="L5" s="25">
+        <v>-246</v>
+      </c>
+      <c r="L7" s="18">
+        <f>_xlfn.XLOOKUP(B7,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>-501</v>
+      </c>
+      <c r="M7" s="21">
         <f ca="1" t="shared" si="3"/>
-        <v>0.916516</v>
-      </c>
-      <c r="M5" s="25">
-        <f ca="1">K5/(J5/X4*U$4)</f>
-        <v>3.5514995</v>
-      </c>
-      <c r="N5" s="27">
+        <v>-0.0984</v>
+      </c>
+      <c r="N7" s="21">
+        <f ca="1">K7/(J7/Z4*W$4)</f>
+        <v>-0.338933333333333</v>
+      </c>
+      <c r="O7" s="23">
         <f ca="1" t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="O5" s="27">
+        <v>11</v>
+      </c>
+      <c r="P7" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>4344</v>
-      </c>
-      <c r="P5" s="23">
+        <v>-98</v>
+      </c>
+      <c r="Q7" s="19">
         <v>15</v>
       </c>
-      <c r="Q5" s="28">
-        <f>_xlfn.XLOOKUP(B5,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>9</v>
-      </c>
-      <c r="R5" s="29">
-        <f>Q5/P5</f>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A6" s="32"/>
-      <c r="B6" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="22">
+      <c r="R7" s="24">
+        <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>3</v>
+      </c>
+      <c r="S7" s="25">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A8" s="15"/>
+      <c r="B8" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="18">
         <v>10</v>
       </c>
-      <c r="D6" s="23">
-        <f>_xlfn.XLOOKUP(B6,高套!A:A,高套!B:B,0)</f>
-        <v>26.5</v>
-      </c>
-      <c r="E6" s="24">
+      <c r="D8" s="19">
+        <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="20">
         <f t="shared" si="0"/>
-        <v>2.65</v>
-      </c>
-      <c r="F6" s="25">
-        <f ca="1">D6/(C6/X4*U$4)</f>
-        <v>10.26875</v>
-      </c>
-      <c r="G6" s="22">
-        <f>_xlfn.XLOOKUP(B6,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>27.5</v>
-      </c>
-      <c r="H6" s="26" t="str">
+        <v>0</v>
+      </c>
+      <c r="F8" s="21">
+        <f ca="1">D8/(C8/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I6" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>金牌</v>
-      </c>
-      <c r="J6" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K6" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>758</v>
-      </c>
-      <c r="L6" s="25">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.3032</v>
-      </c>
-      <c r="M6" s="25">
-        <f ca="1">K6/(J6/X4*U$4)</f>
-        <v>1.1749</v>
-      </c>
-      <c r="N6" s="27">
-        <f ca="1" t="shared" si="4"/>
-        <v>7</v>
-      </c>
-      <c r="O6" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1783.5</v>
-      </c>
-      <c r="P6" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="28">
-        <f>_xlfn.XLOOKUP(B6,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="29">
-        <f>Q6/P6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A7" s="32"/>
-      <c r="B7" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="22">
-        <v>10</v>
-      </c>
-      <c r="D7" s="23">
-        <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
-        <v>18.33</v>
-      </c>
-      <c r="E7" s="24">
-        <f t="shared" si="0"/>
-        <v>1.833</v>
-      </c>
-      <c r="F7" s="25">
-        <f ca="1">D7/(C7/X4*U$4)</f>
-        <v>7.102875</v>
-      </c>
-      <c r="G7" s="22">
-        <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>19.83</v>
-      </c>
-      <c r="H7" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I7" s="22" t="str">
-        <f t="shared" si="2"/>
-        <v>金牌</v>
-      </c>
-      <c r="J7" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K7" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1766.66</v>
-      </c>
-      <c r="L7" s="25">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.706664</v>
-      </c>
-      <c r="M7" s="25">
-        <f ca="1">K7/(J7/X4*U$4)</f>
-        <v>2.738323</v>
-      </c>
-      <c r="N7" s="27">
-        <f ca="1" t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="O7" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>4429</v>
-      </c>
-      <c r="P7" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="28">
-        <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R7" s="29">
-        <f>Q7/P7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A8" s="32"/>
-      <c r="B8" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="22">
-        <v>10</v>
-      </c>
-      <c r="D8" s="23">
-        <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
-        <v>9.52</v>
-      </c>
-      <c r="E8" s="24">
-        <f t="shared" si="0"/>
-        <v>0.952</v>
-      </c>
-      <c r="F8" s="25">
-        <f ca="1">D8/(C8/X4*U$4)</f>
-        <v>3.689</v>
-      </c>
-      <c r="G8" s="22">
-        <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>9.52</v>
-      </c>
-      <c r="H8" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I8" s="22" t="str">
+        <v>是</v>
+      </c>
+      <c r="I8" s="18" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="18">
         <v>2500</v>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2182</v>
-      </c>
-      <c r="L8" s="25">
+        <v>203</v>
+      </c>
+      <c r="L8" s="18">
+        <f>_xlfn.XLOOKUP(B8,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>5.5</v>
+      </c>
+      <c r="M8" s="21">
         <f ca="1" t="shared" si="3"/>
-        <v>0.8728</v>
-      </c>
-      <c r="M8" s="25">
-        <f ca="1">K8/(J8/X4*U$4)</f>
-        <v>3.3821</v>
-      </c>
-      <c r="N8" s="27">
+        <v>0.0812</v>
+      </c>
+      <c r="N8" s="21">
+        <f ca="1">K8/(J8/Z4*W$4)</f>
+        <v>0.279688888888889</v>
+      </c>
+      <c r="O8" s="23">
         <f ca="1" t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="O8" s="27">
+        <v>8</v>
+      </c>
+      <c r="P8" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>5026</v>
-      </c>
-      <c r="P8" s="23">
+        <v>913.5</v>
+      </c>
+      <c r="Q8" s="19">
         <v>15</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="R8" s="24">
         <f>_xlfn.XLOOKUP(B8,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S8" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X8" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y8">
+        <f ca="1" t="shared" ref="Y8:Y19" si="6">VLOOKUP(X:X,B:K,10,0)</f>
+        <v>772.33</v>
+      </c>
+      <c r="Z8">
+        <f ca="1" t="shared" ref="Z8:Z19" si="7">RANK(Y8,Y$8:Y$19,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A9" s="15"/>
+      <c r="B9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="18">
+        <v>10</v>
+      </c>
+      <c r="D9" s="19">
+        <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="21">
+        <f ca="1">D9/(C9/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="18">
+        <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="22" t="str">
+        <f t="shared" si="1"/>
+        <v>是</v>
+      </c>
+      <c r="I9" s="18" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="J9" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K9" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>295.33</v>
+      </c>
+      <c r="L9" s="18">
+        <f>_xlfn.XLOOKUP(B9,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>-1648.67</v>
+      </c>
+      <c r="M9" s="21">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.118132</v>
+      </c>
+      <c r="N9" s="21">
+        <f ca="1">K9/(J9/Z4*W$4)</f>
+        <v>0.406899111111111</v>
+      </c>
+      <c r="O9" s="23">
+        <f ca="1" t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="P9" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>230.5</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>15</v>
+      </c>
+      <c r="R9" s="24">
+        <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S9" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X9" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y9">
+        <f ca="1" t="shared" si="6"/>
+        <v>60</v>
+      </c>
+      <c r="Z9">
+        <f ca="1" t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="R8" s="29">
-        <f>Q8/P8</f>
-        <v>0.6</v>
-      </c>
-      <c r="V8" s="33" t="s">
+    </row>
+    <row r="10" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A10" s="16"/>
+      <c r="B10" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="29">
+        <f>SUM(C4:C9)</f>
+        <v>60</v>
+      </c>
+      <c r="D10" s="29">
+        <f>SUM(D4:D9)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E10" s="30">
+        <f t="shared" si="0"/>
+        <v>0.025</v>
+      </c>
+      <c r="F10" s="30">
+        <f ca="1">D10/(C10/Z4*W$4)</f>
+        <v>0.0861111111111111</v>
+      </c>
+      <c r="G10" s="29">
+        <f>SUM(G4:G9)</f>
+        <v>5</v>
+      </c>
+      <c r="H10" s="30"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31">
+        <f>SUM(J4:J9)</f>
+        <v>15000</v>
+      </c>
+      <c r="K10" s="29">
+        <f ca="1">SUM(K4:K9)</f>
+        <v>2877.33</v>
+      </c>
+      <c r="L10" s="29">
+        <f>SUM(L4:L9)</f>
+        <v>-361.67</v>
+      </c>
+      <c r="M10" s="30">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.191822</v>
+      </c>
+      <c r="N10" s="30">
+        <f ca="1">K10/(J10/Z4*W$4)</f>
+        <v>0.660720222222222</v>
+      </c>
+      <c r="O10" s="29"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="29">
+        <f>SUM(Q4:Q9)</f>
+        <v>90</v>
+      </c>
+      <c r="R10" s="29">
+        <f>SUM(R4:R9)</f>
+        <v>3</v>
+      </c>
+      <c r="S10" s="32">
+        <f t="shared" si="5"/>
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="X10" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="W8">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>758</v>
-      </c>
-      <c r="X8">
-        <f ca="1">RANK(W8,W$8:W$19,0)</f>
+      <c r="Y10">
+        <f ca="1" t="shared" si="6"/>
+        <v>1792.67</v>
+      </c>
+      <c r="Z10">
+        <f ca="1" t="shared" si="7"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="18">
+        <v>10</v>
+      </c>
+      <c r="D11" s="19">
+        <f>_xlfn.XLOOKUP(B11,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="21">
+        <f ca="1">D11/(C11/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="18">
+        <f>_xlfn.XLOOKUP(B11,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="22" t="str">
+        <f t="shared" ref="H11:H16" si="8">IF(G11&gt;=3,"否","是")</f>
+        <v>是</v>
+      </c>
+      <c r="I11" s="18" t="str">
+        <f t="shared" ref="I11:I16" si="9">IF(G11&gt;=15,"金牌",IF(G11&gt;=12,"银牌",""))</f>
+        <v/>
+      </c>
+      <c r="J11" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K11" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>239</v>
+      </c>
+      <c r="L11" s="18">
+        <f>_xlfn.XLOOKUP(B11,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>961</v>
+      </c>
+      <c r="M11" s="21">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.0956</v>
+      </c>
+      <c r="N11" s="21">
+        <f ca="1">K11/(J11/Z4*W$4)</f>
+        <v>0.329288888888889</v>
+      </c>
+      <c r="O11" s="23">
+        <f ca="1" t="shared" ref="O11:O16" si="10">VLOOKUP(B:B,X:Z,3,0)</f>
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A9" s="32"/>
-      <c r="B9" s="22" t="s">
+      <c r="P11" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>15</v>
+      </c>
+      <c r="R11" s="24">
+        <f>_xlfn.XLOOKUP(B11,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S11" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X11" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y11">
+        <f ca="1" t="shared" si="6"/>
+        <v>-246</v>
+      </c>
+      <c r="Z11">
+        <f ca="1" t="shared" si="7"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A12" s="33"/>
+      <c r="B12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="18">
+        <v>10</v>
+      </c>
+      <c r="D12" s="19">
+        <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="20">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="F12" s="21">
+        <f ca="1">D12/(C12/Z4*W$4)</f>
+        <v>0.344444444444444</v>
+      </c>
+      <c r="G12" s="18">
+        <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="22" t="str">
+        <f t="shared" si="8"/>
+        <v>是</v>
+      </c>
+      <c r="I12" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="J12" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K12" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>744.5</v>
+      </c>
+      <c r="L12" s="18">
+        <f>_xlfn.XLOOKUP(B12,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>1112.49</v>
+      </c>
+      <c r="M12" s="21">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.2978</v>
+      </c>
+      <c r="N12" s="21">
+        <f ca="1">K12/(J12/Z4*W$4)</f>
+        <v>1.02575555555556</v>
+      </c>
+      <c r="O12" s="23">
+        <f ca="1" t="shared" si="10"/>
+        <v>4</v>
+      </c>
+      <c r="P12" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>892.5</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>15</v>
+      </c>
+      <c r="R12" s="24">
+        <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="22">
+      <c r="Y12">
+        <f ca="1" t="shared" si="6"/>
+        <v>203</v>
+      </c>
+      <c r="Z12">
+        <f ca="1" t="shared" si="7"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A13" s="33"/>
+      <c r="B13" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="18">
         <v>10</v>
       </c>
-      <c r="D9" s="23">
-        <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
+      <c r="D13" s="19">
+        <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="21">
+        <f ca="1">D13/(C13/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="18">
+        <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="22" t="str">
+        <f t="shared" si="8"/>
+        <v>是</v>
+      </c>
+      <c r="I13" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="J13" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K13" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="18">
+        <f>_xlfn.XLOOKUP(B13,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="21">
+        <f ca="1" t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="21">
+        <f ca="1">K13/(J13/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="O13" s="23">
+        <f ca="1" t="shared" si="10"/>
+        <v>10</v>
+      </c>
+      <c r="P13" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="19">
+        <v>15</v>
+      </c>
+      <c r="R13" s="24">
+        <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X13" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y13">
+        <f ca="1" t="shared" si="6"/>
+        <v>295.33</v>
+      </c>
+      <c r="Z13">
+        <f ca="1" t="shared" si="7"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A14" s="33"/>
+      <c r="B14" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="18">
+        <v>10</v>
+      </c>
+      <c r="D14" s="19">
+        <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
         <v>2.5</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E14" s="20">
         <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
-      <c r="F9" s="25">
-        <f ca="1">D9/(C9/X4*U$4)</f>
-        <v>0.96875</v>
-      </c>
-      <c r="G9" s="22">
-        <f>_xlfn.XLOOKUP(B9,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>5.5</v>
-      </c>
-      <c r="H9" s="26" t="str">
-        <f t="shared" si="1"/>
+      <c r="F14" s="21">
+        <f ca="1">D14/(C14/Z4*W$4)</f>
+        <v>0.861111111111111</v>
+      </c>
+      <c r="G14" s="18">
+        <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>6</v>
+      </c>
+      <c r="H14" s="22" t="str">
+        <f t="shared" si="8"/>
         <v>否</v>
       </c>
-      <c r="I9" s="22" t="str">
-        <f t="shared" si="2"/>
+      <c r="I14" s="18" t="str">
+        <f t="shared" si="9"/>
         <v/>
       </c>
-      <c r="J9" s="22">
+      <c r="J14" s="18">
         <v>2500</v>
       </c>
-      <c r="K9" s="22">
+      <c r="K14" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1254.03</v>
-      </c>
-      <c r="L9" s="25">
+        <v>872</v>
+      </c>
+      <c r="L14" s="18">
+        <f>_xlfn.XLOOKUP(B14,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>402.56</v>
+      </c>
+      <c r="M14" s="21">
         <f ca="1" t="shared" si="3"/>
-        <v>0.501612</v>
-      </c>
-      <c r="M9" s="25">
-        <f ca="1">K9/(J9/X4*U$4)</f>
-        <v>1.9437465</v>
-      </c>
-      <c r="N9" s="27">
-        <f ca="1" t="shared" si="4"/>
-        <v>6</v>
-      </c>
-      <c r="O9" s="27">
+        <v>0.3488</v>
+      </c>
+      <c r="N14" s="21">
+        <f ca="1">K14/(J14/Z4*W$4)</f>
+        <v>1.20142222222222</v>
+      </c>
+      <c r="O14" s="23">
+        <f ca="1" t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="P14" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>3491</v>
-      </c>
-      <c r="P9" s="23">
+        <v>3450</v>
+      </c>
+      <c r="Q14" s="19">
         <v>15</v>
       </c>
-      <c r="Q9" s="28">
-        <f>_xlfn.XLOOKUP(B9,全光组网!A:A,全光组网!B:B,0)</f>
+      <c r="R14" s="24">
+        <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
         <v>5</v>
       </c>
-      <c r="R9" s="29">
-        <f>Q9/P9</f>
+      <c r="S14" s="25">
+        <f t="shared" si="5"/>
         <v>0.333333333333333</v>
       </c>
-      <c r="V9" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="W9">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>287</v>
-      </c>
-      <c r="X9">
-        <f ca="1" t="shared" ref="X9:X19" si="5">RANK(W9,W$8:W$19,0)</f>
+      <c r="X14" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y14">
+        <f ca="1" t="shared" si="6"/>
+        <v>239</v>
+      </c>
+      <c r="Z14">
+        <f ca="1" t="shared" si="7"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A15" s="33"/>
+      <c r="B15" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="18">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A10" s="34"/>
-      <c r="B10" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="35">
-        <f>SUM(C4:C9)</f>
-        <v>60</v>
-      </c>
-      <c r="D10" s="35">
-        <f>SUM(D4:D9)</f>
-        <v>59.85</v>
-      </c>
-      <c r="E10" s="36">
+      <c r="D15" s="19">
+        <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="20">
         <f t="shared" si="0"/>
-        <v>0.9975</v>
-      </c>
-      <c r="F10" s="36">
-        <f ca="1">D10/(C10/X4*U$4)</f>
-        <v>3.8653125</v>
-      </c>
-      <c r="G10" s="35">
-        <f>SUM(G4:G9)</f>
-        <v>65.85</v>
-      </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37">
-        <f>SUM(J4:J9)</f>
-        <v>15000</v>
-      </c>
-      <c r="K10" s="35">
-        <f ca="1">SUM(K4:K9)</f>
-        <v>8538.98</v>
-      </c>
-      <c r="L10" s="36">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21">
+        <f ca="1">D15/(C15/Z4*W$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
+        <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="22" t="str">
+        <f t="shared" si="8"/>
+        <v>是</v>
+      </c>
+      <c r="I15" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="J15" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K15" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>698</v>
+      </c>
+      <c r="L15" s="18">
+        <f>_xlfn.XLOOKUP(B15,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="21">
         <f ca="1" t="shared" si="3"/>
-        <v>0.569265333333333</v>
-      </c>
-      <c r="M10" s="36">
-        <f ca="1">K10/(J10/X4*U$4)</f>
-        <v>2.20590316666667</v>
-      </c>
-      <c r="N10" s="35"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="35">
-        <f>SUM(P4:P9)</f>
-        <v>90</v>
-      </c>
-      <c r="Q10" s="35">
-        <f>SUM(Q4:Q9)</f>
-        <v>23</v>
-      </c>
-      <c r="R10" s="38">
-        <f>Q10/P10</f>
-        <v>0.255555555555556</v>
-      </c>
-      <c r="V10" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="W10">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>2291.29</v>
-      </c>
-      <c r="X10">
-        <f ca="1" t="shared" si="5"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A11" s="39" t="s">
+        <v>0.2792</v>
+      </c>
+      <c r="N15" s="21">
+        <f ca="1">K15/(J15/Z4*W$4)</f>
+        <v>0.961688888888889</v>
+      </c>
+      <c r="O15" s="23">
+        <f ca="1" t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="P15" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>1047</v>
+      </c>
+      <c r="Q15" s="19">
+        <v>15</v>
+      </c>
+      <c r="R15" s="24">
+        <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X15" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y15">
+        <f ca="1" t="shared" si="6"/>
+        <v>744.5</v>
+      </c>
+      <c r="Z15">
+        <f ca="1" t="shared" si="7"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A16" s="33"/>
+      <c r="B16" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="18">
+        <v>10</v>
+      </c>
+      <c r="D16" s="19">
+        <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
+        <v>1.5</v>
+      </c>
+      <c r="E16" s="20">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="F16" s="21">
+        <f ca="1">D16/(C16/Z4*W$4)</f>
+        <v>0.516666666666667</v>
+      </c>
+      <c r="G16" s="18">
+        <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
+        <v>1.5</v>
+      </c>
+      <c r="H16" s="22" t="str">
+        <f t="shared" si="8"/>
+        <v>是</v>
+      </c>
+      <c r="I16" s="18" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="J16" s="18">
+        <v>2500</v>
+      </c>
+      <c r="K16" s="18">
+        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
+        <v>-1647.54</v>
+      </c>
+      <c r="L16" s="18">
+        <f>_xlfn.XLOOKUP(B16,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>-1737.54</v>
+      </c>
+      <c r="M16" s="21">
+        <f ca="1" t="shared" si="3"/>
+        <v>-0.659016</v>
+      </c>
+      <c r="N16" s="21">
+        <f ca="1">K16/(J16/Z4*W$4)</f>
+        <v>-2.269944</v>
+      </c>
+      <c r="O16" s="23">
+        <f ca="1" t="shared" si="10"/>
+        <v>12</v>
+      </c>
+      <c r="P16" s="23">
+        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
+        <v>-2471.31</v>
+      </c>
+      <c r="Q16" s="19">
+        <v>15</v>
+      </c>
+      <c r="R16" s="24">
+        <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S16" s="25">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="X16" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y16">
+        <f ca="1" t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <f ca="1" t="shared" si="7"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A17" s="34"/>
+      <c r="B17" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="22">
-        <v>10</v>
-      </c>
-      <c r="D11" s="23">
-        <f>_xlfn.XLOOKUP(B11,高套!A:A,高套!B:B,0)</f>
-        <v>5</v>
-      </c>
-      <c r="E11" s="24">
-        <f>D11/C11</f>
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="25">
-        <f ca="1">D11/(C11/X4*U$4)</f>
-        <v>1.9375</v>
-      </c>
-      <c r="G11" s="22">
-        <f>_xlfn.XLOOKUP(B11,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>6</v>
-      </c>
-      <c r="H11" s="26" t="str">
-        <f t="shared" ref="H11:H16" si="6">IF(G11&gt;=3,"否","是")</f>
-        <v>否</v>
-      </c>
-      <c r="I11" s="22" t="str">
-        <f t="shared" ref="I11:I16" si="7">IF(G11&gt;=15,"金牌",IF(G11&gt;=12,"银牌",""))</f>
-        <v/>
-      </c>
-      <c r="J11" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K11" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>689</v>
-      </c>
-      <c r="L11" s="25">
-        <f ca="1">K11/J11</f>
-        <v>0.2756</v>
-      </c>
-      <c r="M11" s="25">
-        <f ca="1">K11/(J11/X4*U$4)</f>
-        <v>1.06795</v>
-      </c>
-      <c r="N11" s="27">
-        <f ca="1" t="shared" ref="N11:N16" si="8">VLOOKUP(B:B,V:X,3,0)</f>
-        <v>8</v>
-      </c>
-      <c r="O11" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1339.5</v>
-      </c>
-      <c r="P11" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="28">
-        <f>_xlfn.XLOOKUP(B11,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="29">
-        <f t="shared" ref="R11:R19" si="9">Q11/P11</f>
-        <v>0</v>
-      </c>
-      <c r="V11" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="W11">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>1766.66</v>
-      </c>
-      <c r="X11">
-        <f ca="1" t="shared" si="5"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A12" s="40"/>
-      <c r="B12" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="22">
-        <v>10</v>
-      </c>
-      <c r="D12" s="23">
-        <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
-        <v>2</v>
-      </c>
-      <c r="E12" s="24">
-        <f>D12/C12</f>
-        <v>0.2</v>
-      </c>
-      <c r="F12" s="25">
-        <f ca="1">D12/(C12/X4*U$4)</f>
-        <v>0.775</v>
-      </c>
-      <c r="G12" s="22">
-        <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="H12" s="26" t="str">
-        <f t="shared" si="6"/>
-        <v>否</v>
-      </c>
-      <c r="I12" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J12" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K12" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>387</v>
-      </c>
-      <c r="L12" s="25">
-        <f ca="1">K12/J12</f>
-        <v>0.1548</v>
-      </c>
-      <c r="M12" s="25">
-        <f ca="1">K12/(J12/X4*U$4)</f>
-        <v>0.59985</v>
-      </c>
-      <c r="N12" s="27">
-        <f ca="1" t="shared" si="8"/>
-        <v>9</v>
-      </c>
-      <c r="O12" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1661.5</v>
-      </c>
-      <c r="P12" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q12" s="28">
-        <f>_xlfn.XLOOKUP(B12,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R12" s="29">
-        <f t="shared" si="9"/>
-        <v>0.2</v>
-      </c>
-      <c r="V12" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="W12">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>2182</v>
-      </c>
-      <c r="X12">
-        <f ca="1" t="shared" si="5"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A13" s="40"/>
-      <c r="B13" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="22">
-        <v>10</v>
-      </c>
-      <c r="D13" s="23">
-        <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="24">
-        <f>D13/C13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="25">
-        <f ca="1">D13/(C13/X4*U$4)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="22">
-        <f>_xlfn.XLOOKUP(B13,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="26" t="str">
-        <f t="shared" si="6"/>
-        <v>是</v>
-      </c>
-      <c r="I13" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J13" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K13" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="25">
-        <f ca="1">K13/J13</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="25">
-        <f ca="1">K13/(J13/X4*U$4)</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="27">
-        <f ca="1" t="shared" si="8"/>
-        <v>12</v>
-      </c>
-      <c r="O13" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P13" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q13" s="28">
-        <f>_xlfn.XLOOKUP(B13,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R13" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V13" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="W13">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>1254.03</v>
-      </c>
-      <c r="X13">
-        <f ca="1" t="shared" si="5"/>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A14" s="40"/>
-      <c r="B14" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="22">
-        <v>10</v>
-      </c>
-      <c r="D14" s="23">
-        <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
-        <v>11.5</v>
-      </c>
-      <c r="E14" s="24">
-        <f>D14/C14</f>
-        <v>1.15</v>
-      </c>
-      <c r="F14" s="25">
-        <f ca="1">D14/(C14/X4*U$4)</f>
-        <v>4.45625</v>
-      </c>
-      <c r="G14" s="22">
-        <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>13</v>
-      </c>
-      <c r="H14" s="26" t="str">
-        <f t="shared" si="6"/>
-        <v>否</v>
-      </c>
-      <c r="I14" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v>银牌</v>
-      </c>
-      <c r="J14" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K14" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>2096</v>
-      </c>
-      <c r="L14" s="25">
-        <f ca="1">K14/J14</f>
-        <v>0.8384</v>
-      </c>
-      <c r="M14" s="25">
-        <f ca="1">K14/(J14/X4*U$4)</f>
-        <v>3.2488</v>
-      </c>
-      <c r="N14" s="27">
-        <f ca="1" t="shared" si="8"/>
-        <v>3</v>
-      </c>
-      <c r="O14" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>7387</v>
-      </c>
-      <c r="P14" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q14" s="28">
-        <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>10</v>
-      </c>
-      <c r="R14" s="29">
-        <f t="shared" si="9"/>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="V14" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="W14">
-        <f ca="1">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>689</v>
-      </c>
-      <c r="X14">
-        <f ca="1" t="shared" si="5"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A15" s="40"/>
-      <c r="B15" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" s="22">
-        <v>10</v>
-      </c>
-      <c r="D15" s="23">
-        <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
-        <v>9.94</v>
-      </c>
-      <c r="E15" s="24">
-        <f>D15/C15</f>
-        <v>0.994</v>
-      </c>
-      <c r="F15" s="25">
-        <f ca="1">D15/(C15/X4*U$4)</f>
-        <v>3.85175</v>
-      </c>
-      <c r="G15" s="22">
-        <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>9.94</v>
-      </c>
-      <c r="H15" s="26" t="str">
-        <f t="shared" si="6"/>
-        <v>否</v>
-      </c>
-      <c r="I15" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J15" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K15" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1415</v>
-      </c>
-      <c r="L15" s="25">
-        <f ca="1">K15/J15</f>
-        <v>0.566</v>
-      </c>
-      <c r="M15" s="25">
-        <f ca="1">K15/(J15/X4*U$4)</f>
-        <v>2.19325</v>
-      </c>
-      <c r="N15" s="27">
-        <f ca="1" t="shared" si="8"/>
-        <v>5</v>
-      </c>
-      <c r="O15" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>4117.5</v>
-      </c>
-      <c r="P15" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q15" s="28">
-        <f>_xlfn.XLOOKUP(B15,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R15" s="29">
-        <f t="shared" si="9"/>
-        <v>0.2</v>
-      </c>
-      <c r="V15" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="W15">
-        <f ca="1" t="shared" ref="W14:W19" si="10">VLOOKUP(V:V,B:K,10,0)</f>
-        <v>387</v>
-      </c>
-      <c r="X15">
-        <f ca="1" t="shared" si="5"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A16" s="40"/>
-      <c r="B16" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="22">
-        <v>10</v>
-      </c>
-      <c r="D16" s="23">
-        <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
-        <v>0.75</v>
-      </c>
-      <c r="E16" s="24">
-        <f>D16/C16</f>
-        <v>0.075</v>
-      </c>
-      <c r="F16" s="25">
-        <f ca="1">D16/(C16/X4*U$4)</f>
-        <v>0.290625</v>
-      </c>
-      <c r="G16" s="22">
-        <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0.75</v>
-      </c>
-      <c r="H16" s="26" t="str">
-        <f t="shared" si="6"/>
-        <v>是</v>
-      </c>
-      <c r="I16" s="22" t="str">
-        <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="J16" s="22">
-        <v>2500</v>
-      </c>
-      <c r="K16" s="22">
-        <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>154.92</v>
-      </c>
-      <c r="L16" s="25">
-        <f ca="1">K16/J16</f>
-        <v>0.061968</v>
-      </c>
-      <c r="M16" s="25">
-        <f ca="1">K16/(J16/X4*U$4)</f>
-        <v>0.240126</v>
-      </c>
-      <c r="N16" s="27">
-        <f ca="1" t="shared" si="8"/>
-        <v>11</v>
-      </c>
-      <c r="O16" s="27">
-        <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>232.38</v>
-      </c>
-      <c r="P16" s="23">
-        <v>15</v>
-      </c>
-      <c r="Q16" s="28">
-        <f>_xlfn.XLOOKUP(B16,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R16" s="29">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="V16" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="W16">
-        <f ca="1" t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <f ca="1" t="shared" si="5"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A17" s="41"/>
-      <c r="B17" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="42">
+      <c r="C17" s="35">
         <f>SUM(C11:C16)</f>
         <v>60</v>
       </c>
-      <c r="D17" s="42">
+      <c r="D17" s="35">
         <f>SUM(D11:D16)</f>
-        <v>29.19</v>
-      </c>
-      <c r="E17" s="43">
-        <f>D17/C17</f>
-        <v>0.4865</v>
-      </c>
-      <c r="F17" s="36">
-        <f ca="1">D17/(C17/X4*U$4)</f>
-        <v>1.8851875</v>
-      </c>
-      <c r="G17" s="42">
+        <v>5</v>
+      </c>
+      <c r="E17" s="36">
+        <f t="shared" si="0"/>
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="F17" s="30">
+        <f ca="1">D17/(C17/Z4*W$4)</f>
+        <v>0.287037037037037</v>
+      </c>
+      <c r="G17" s="35">
         <f>SUM(G11:G16)</f>
-        <v>32.69</v>
-      </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="44"/>
-      <c r="J17" s="44">
+        <v>8.5</v>
+      </c>
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37">
         <f>SUM(J11:J16)</f>
         <v>15000</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="35">
         <f ca="1">SUM(K11:K16)</f>
-        <v>4741.92</v>
-      </c>
-      <c r="L17" s="43">
-        <f ca="1">K17/J17</f>
-        <v>0.316128</v>
-      </c>
-      <c r="M17" s="43">
-        <f ca="1">K17/(J17/X4*U$4)</f>
-        <v>1.224996</v>
-      </c>
-      <c r="N17" s="42"/>
-      <c r="O17" s="44"/>
-      <c r="P17" s="42">
-        <f>SUM(P11:P16)</f>
+        <v>905.96</v>
+      </c>
+      <c r="L17" s="35">
+        <f>SUM(L11:L16)</f>
+        <v>738.51</v>
+      </c>
+      <c r="M17" s="36">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.0603973333333333</v>
+      </c>
+      <c r="N17" s="36">
+        <f ca="1">K17/(J17/Z4*W$4)</f>
+        <v>0.208035259259259</v>
+      </c>
+      <c r="O17" s="35"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="35">
+        <f>SUM(Q11:Q16)</f>
         <v>90</v>
       </c>
-      <c r="Q17" s="42">
-        <f>SUM(Q11:Q16)</f>
-        <v>16</v>
-      </c>
-      <c r="R17" s="38">
-        <f t="shared" si="9"/>
-        <v>0.177777777777778</v>
-      </c>
-      <c r="V17" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="W17">
-        <f ca="1" t="shared" si="10"/>
-        <v>2096</v>
-      </c>
-      <c r="X17">
-        <f ca="1" t="shared" si="5"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="1:24">
-      <c r="A18" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="47">
+      <c r="R17" s="35">
+        <f>SUM(R11:R16)</f>
+        <v>5</v>
+      </c>
+      <c r="S17" s="32">
+        <f t="shared" si="5"/>
+        <v>0.0555555555555556</v>
+      </c>
+      <c r="X17" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y17">
+        <f ca="1" t="shared" si="6"/>
+        <v>872</v>
+      </c>
+      <c r="Z17">
+        <f ca="1" t="shared" si="7"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="1:26">
+      <c r="A18" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="39"/>
+      <c r="C18" s="40">
         <v>132</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="41">
         <f>_xlfn.XLOOKUP("端州",高套!A:A,高套!B:B,0)</f>
-        <v>95.54</v>
-      </c>
-      <c r="E18" s="49">
-        <f>D18/C18</f>
-        <v>0.723787878787879</v>
-      </c>
-      <c r="F18" s="50">
-        <f ca="1">D18/(C18/X4*U$4)</f>
-        <v>2.80467803030303</v>
-      </c>
-      <c r="G18" s="51">
+        <v>6.5</v>
+      </c>
+      <c r="E18" s="42">
+        <f t="shared" si="0"/>
+        <v>0.0492424242424242</v>
+      </c>
+      <c r="F18" s="43">
+        <f ca="1">D18/(C18/Z4*W$4)</f>
+        <v>0.169612794612795</v>
+      </c>
+      <c r="G18" s="44">
         <f>G10+G17</f>
-        <v>98.54</v>
-      </c>
-      <c r="H18" s="50"/>
-      <c r="I18" s="52"/>
-      <c r="J18" s="53">
+        <v>13.5</v>
+      </c>
+      <c r="H18" s="43"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="46">
         <f>J10+J17</f>
         <v>30000</v>
       </c>
-      <c r="K18" s="47">
+      <c r="K18" s="40">
         <f ca="1">K10+K17</f>
-        <v>13280.9</v>
-      </c>
-      <c r="L18" s="54">
-        <f ca="1">K18/J18</f>
-        <v>0.442696666666667</v>
-      </c>
-      <c r="M18" s="55">
-        <f ca="1">K18/(J18/X4*U$4)</f>
-        <v>1.71544958333333</v>
-      </c>
-      <c r="N18" s="56"/>
-      <c r="O18" s="57" t="s">
-        <v>36</v>
-      </c>
-      <c r="P18" s="58">
+        <v>3783.29</v>
+      </c>
+      <c r="L18" s="47">
+        <f>L10+L17</f>
+        <v>376.84</v>
+      </c>
+      <c r="M18" s="48">
+        <f ca="1" t="shared" si="3"/>
+        <v>0.126109666666667</v>
+      </c>
+      <c r="N18" s="49">
+        <f ca="1">K18/(J18/Z4*W$4)</f>
+        <v>0.434377740740741</v>
+      </c>
+      <c r="O18" s="50"/>
+      <c r="P18" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q18" s="52">
         <v>210</v>
       </c>
-      <c r="Q18" s="59">
-        <f>Q10+Q17</f>
+      <c r="R18" s="53">
+        <f>R10+R17</f>
+        <v>8</v>
+      </c>
+      <c r="S18" s="25">
+        <f t="shared" si="5"/>
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="X18" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y18">
+        <f ca="1" t="shared" si="6"/>
+        <v>-1647.54</v>
+      </c>
+      <c r="Z18">
+        <f ca="1" t="shared" si="7"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="1:26">
+      <c r="A19" s="16"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="56"/>
+      <c r="J19" s="55"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="56"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="51" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q19" s="59">
+        <v>310</v>
+      </c>
+      <c r="R19" s="60">
+        <f>_xlfn.XLOOKUP(P19,全光组网!A:A,全光组网!B:B,0)</f>
+        <v>59</v>
+      </c>
+      <c r="S19" s="25">
+        <f t="shared" si="5"/>
+        <v>0.190322580645161</v>
+      </c>
+      <c r="X19" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y19">
+        <f ca="1" t="shared" si="6"/>
+        <v>698</v>
+      </c>
+      <c r="Z19">
+        <f ca="1" t="shared" si="7"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A20" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="R18" s="29">
-        <f t="shared" si="9"/>
-        <v>0.185714285714286</v>
-      </c>
-      <c r="V18" s="60" t="s">
-        <v>34</v>
-      </c>
-      <c r="W18">
-        <f ca="1" t="shared" si="10"/>
-        <v>154.92</v>
-      </c>
-      <c r="X18">
-        <f ca="1" t="shared" si="5"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="1:24">
-      <c r="A19" s="19"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="62"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="62"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="62"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="57" t="s">
-        <v>37</v>
-      </c>
-      <c r="P19" s="65">
-        <v>310</v>
-      </c>
-      <c r="Q19" s="66">
-        <f>_xlfn.XLOOKUP(O19,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>233</v>
-      </c>
-      <c r="R19" s="29">
-        <f t="shared" si="9"/>
-        <v>0.751612903225806</v>
-      </c>
-      <c r="V19" s="67" t="s">
-        <v>33</v>
-      </c>
-      <c r="W19">
-        <f ca="1" t="shared" si="10"/>
-        <v>1415</v>
-      </c>
-      <c r="X19">
-        <f ca="1" t="shared" si="5"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A20" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="25" t="s">
+      <c r="B20" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" s="22">
+      <c r="C20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="18">
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="H20" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K20" s="22">
+      <c r="H20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K20" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L20" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M20" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N20" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O20" s="27">
+      <c r="L20" s="21"/>
+      <c r="M20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O20" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P20" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="P20" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q20" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R20" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A21" s="68"/>
-      <c r="B21" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G21" s="22">
+      <c r="Q20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R20" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S20" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" ht="14.25" customHeight="1" spans="1:26">
+      <c r="A21" s="33"/>
+      <c r="B21" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="18">
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="H21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K21" s="22">
+      <c r="H21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K21" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M21" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N21" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O21" s="27">
+      <c r="L21" s="21"/>
+      <c r="M21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O21" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P21" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="P21" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q21" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R21" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A22" s="68"/>
-      <c r="B22" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G22" s="22">
+      <c r="Q21" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R21" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S21" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" ht="14.25" customHeight="1" spans="1:26">
+      <c r="A22" s="33"/>
+      <c r="B22" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="18">
         <f>高装高套!B4</f>
         <v>0</v>
       </c>
-      <c r="H22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K22" s="22">
+      <c r="H22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22" s="21"/>
+      <c r="J22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K22" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M22" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N22" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O22" s="27">
+      <c r="L22" s="21"/>
+      <c r="M22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N22" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O22" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P22" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>786.5</v>
-      </c>
-      <c r="P22" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q22" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R22" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="23" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A23" s="68"/>
-      <c r="B23" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R22" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S22" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" ht="14.25" customHeight="1" spans="1:26">
+      <c r="A23" s="33"/>
+      <c r="B23" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" s="18">
         <f>高装高套!B5</f>
-        <v>1</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K23" s="22">
+        <v>0</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>143</v>
-      </c>
-      <c r="L23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M23" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N23" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O23" s="27">
+        <v>0</v>
+      </c>
+      <c r="L23" s="21"/>
+      <c r="M23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O23" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P23" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>281</v>
-      </c>
-      <c r="P23" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q23" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R23" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:24">
-      <c r="A24" s="68"/>
-      <c r="B24" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G24" s="22">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R23" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S23" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" ht="14.25" customHeight="1" spans="1:26">
+      <c r="A24" s="33"/>
+      <c r="B24" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="18">
         <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="H24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K24" s="22">
+      <c r="H24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" s="21"/>
+      <c r="J24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M24" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N24" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O24" s="27">
+      <c r="L24" s="21"/>
+      <c r="M24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O24" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P24" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="P24" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q24" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R24" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A25" s="68"/>
-      <c r="B25" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G25" s="22">
+      <c r="Q24" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R24" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S24" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A25" s="33"/>
+      <c r="B25" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="18">
         <f>高装高套!B7</f>
         <v>0</v>
       </c>
-      <c r="H25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K25" s="22">
+      <c r="H25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="21"/>
+      <c r="J25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M25" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N25" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O25" s="27">
+      <c r="L25" s="21"/>
+      <c r="M25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N25" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O25" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P25" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
-      <c r="P25" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q25" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R25" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A26" s="68"/>
-      <c r="B26" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G26" s="22">
+      <c r="Q25" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R25" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S25" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A26" s="33"/>
+      <c r="B26" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="18">
         <f>高装高套!B8</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K26" s="22">
+        <v>1.5</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="21"/>
+      <c r="J26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="L26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M26" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N26" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O26" s="27">
+        <v>239</v>
+      </c>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N26" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O26" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P26" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q26" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R26" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A27" s="62"/>
-      <c r="B27" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G27" s="22">
+        <v>1055.5</v>
+      </c>
+      <c r="Q26" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R26" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S26" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A27" s="34"/>
+      <c r="B27" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="18">
         <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="H27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K27" s="22">
+      <c r="H27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I27" s="21"/>
+      <c r="J27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K27" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M27" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N27" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O27" s="27">
+      <c r="L27" s="21"/>
+      <c r="M27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N27" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O27" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="P27" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>25</v>
-      </c>
-      <c r="P27" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q27" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="R27" s="29" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="28" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A28" s="69" t="s">
-        <v>48</v>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="R27" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="S27" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A28" s="62" t="s">
+        <v>49</v>
       </c>
       <c r="B28" s="14"/>
-      <c r="C28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="G28" s="22">
+      <c r="C28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="G28" s="18">
         <f>SUM(G20:G27)</f>
-        <v>1</v>
-      </c>
-      <c r="H28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="K28" s="22">
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="K28" s="18">
         <f ca="1">SUM(K20:K27)</f>
-        <v>143</v>
-      </c>
-      <c r="L28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="M28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="N28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="O28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="P28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q28" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="R28" s="25" t="s">
-        <v>40</v>
+        <v>239</v>
+      </c>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="N28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="O28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="P28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="R28" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="S28" s="21" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1"/>
-    <row r="30" ht="16.5" customHeight="1" spans="1:24">
+    <row r="30" ht="16.5" customHeight="1" spans="1:26">
       <c r="G30"/>
       <c r="I30"/>
       <c r="J30"/>
       <c r="K30"/>
-      <c r="O30"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1" spans="1:24">
-      <c r="A31" s="70" t="str">
+      <c r="P30"/>
+    </row>
+    <row r="31" ht="16.5" customHeight="1" spans="1:26">
+      <c r="A31" s="63" t="str">
         <f>"高装高套目标完成情况"</f>
         <v>高装高套目标完成情况</v>
       </c>
       <c r="G31"/>
-      <c r="I31"/>
-      <c r="J31" s="71" t="str">
+      <c r="H31" s="64" t="str">
         <f>"全光任务完成情况"</f>
         <v>全光任务完成情况</v>
       </c>
-      <c r="O31"/>
-      <c r="P31" s="72" t="str">
+      <c r="N31" s="65" t="str">
         <f>"区县目标完成情况"</f>
         <v>区县目标完成情况</v>
       </c>
     </row>
-    <row r="32" ht="33" customHeight="1" spans="1:24">
-      <c r="A32" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="73" t="s">
+    <row r="32" ht="33" customHeight="1" spans="1:26">
+      <c r="A32" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="73" t="s">
+      <c r="B32" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="73" t="s">
+      <c r="C32" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="73" t="s">
-        <v>13</v>
-      </c>
-      <c r="F32" s="73" t="s">
+      <c r="D32" s="66" t="s">
+        <v>53</v>
+      </c>
+      <c r="E32" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="66" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32"/>
+      <c r="H32" s="67" t="s">
+        <v>50</v>
+      </c>
+      <c r="I32" s="67" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="K32" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="L32" s="67" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="O32" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="P32" s="69" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q32" s="70" t="s">
+        <v>14</v>
+      </c>
+      <c r="R32" s="69" t="s">
+        <v>20</v>
+      </c>
+      <c r="S32" s="70" t="s">
         <v>16</v>
       </c>
-      <c r="G32"/>
-      <c r="I32"/>
-      <c r="J32" s="74" t="s">
-        <v>49</v>
-      </c>
-      <c r="K32" s="74" t="s">
-        <v>50</v>
-      </c>
-      <c r="L32" s="74" t="s">
-        <v>17</v>
-      </c>
-      <c r="M32" s="75" t="s">
-        <v>53</v>
-      </c>
-      <c r="N32" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="O32"/>
-      <c r="P32" s="76" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q32" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="R32" s="76" t="s">
-        <v>56</v>
-      </c>
-      <c r="S32" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="T32" s="76" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A33" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="78" t="str">
+    </row>
+    <row r="33" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A33" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="72" t="str">
         <f>高装高套!A2</f>
         <v>陈梓铭</v>
       </c>
-      <c r="C33" s="78">
+      <c r="C33" s="72">
         <v>3.5</v>
       </c>
-      <c r="D33" s="78">
+      <c r="D33" s="72">
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="E33" s="79">
+      <c r="E33" s="73">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="79">
+      <c r="F33" s="73">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G33"/>
-      <c r="I33"/>
-      <c r="J33" s="80" t="s">
-        <v>57</v>
-      </c>
-      <c r="K33" s="81" t="s">
-        <v>58</v>
-      </c>
-      <c r="L33" s="81">
+      <c r="H33" s="74" t="s">
+        <v>59</v>
+      </c>
+      <c r="I33" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="M33" s="81">
+      <c r="J33" s="75">
+        <v>60</v>
+      </c>
+      <c r="K33" s="75">
         <f>交付高装!D2</f>
-        <v>12</v>
-      </c>
-      <c r="N33" s="82">
+        <v>3</v>
+      </c>
+      <c r="L33" s="76">
         <f>交付高装!E2</f>
-        <v>0.2</v>
-      </c>
-      <c r="O33"/>
-      <c r="P33" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q33" s="84">
+        <v>0.05</v>
+      </c>
+      <c r="N33" s="77" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33" s="78">
         <v>4.25</v>
       </c>
-      <c r="R33" s="84">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P33,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>11.94</v>
-      </c>
-      <c r="S33" s="85">
-        <f ca="1" t="shared" ref="S33:S42" si="11">R33/Q33</f>
-        <v>2.80941176470588</v>
-      </c>
-      <c r="T33" s="86">
-        <f ca="1">RANK(S33,S33:S41)</f>
+      <c r="P33" s="78">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N33,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>0.72</v>
+      </c>
+      <c r="Q33" s="78">
+        <f>_xlfn.XLOOKUP(N33,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>1294.22</v>
+      </c>
+      <c r="R33" s="79">
+        <f ca="1" t="shared" ref="R33:R42" si="11">P33/O33</f>
+        <v>0.169411764705882</v>
+      </c>
+      <c r="S33" s="80">
+        <f ca="1">RANK(R33,R33:R41)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A34" s="87"/>
-      <c r="B34" s="88" t="str">
+    <row r="34" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A34" s="81"/>
+      <c r="B34" s="82" t="str">
         <f>高装高套!A3</f>
         <v>程庆德</v>
       </c>
-      <c r="C34" s="88">
+      <c r="C34" s="82">
         <v>3.5</v>
       </c>
-      <c r="D34" s="88">
+      <c r="D34" s="82">
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="E34" s="89">
+      <c r="E34" s="83">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="89">
+      <c r="F34" s="83">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G34"/>
-      <c r="I34"/>
-      <c r="J34" s="90"/>
-      <c r="K34" s="81" t="s">
-        <v>59</v>
-      </c>
-      <c r="L34" s="81">
+      <c r="H34" s="84"/>
+      <c r="I34" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="J34" s="75">
         <v>60</v>
       </c>
-      <c r="M34" s="81">
+      <c r="K34" s="75">
         <f>交付高装!D3</f>
-        <v>14</v>
-      </c>
-      <c r="N34" s="82">
+        <v>0</v>
+      </c>
+      <c r="L34" s="76">
         <f>交付高装!E3</f>
-        <v>0.233333333333333</v>
-      </c>
-      <c r="O34"/>
-      <c r="P34" s="83" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q34" s="91">
+        <v>0</v>
+      </c>
+      <c r="N34" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="O34" s="85">
         <v>5.75</v>
       </c>
-      <c r="R34" s="91">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P34,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>16.79</v>
-      </c>
-      <c r="S34" s="85">
+      <c r="P34" s="85">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N34,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>2.56</v>
+      </c>
+      <c r="Q34" s="85">
+        <f>_xlfn.XLOOKUP(N34,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>377.74</v>
+      </c>
+      <c r="R34" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>2.92</v>
-      </c>
-      <c r="T34" s="92">
-        <f ca="1">RANK(S34,S33:S41)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A35" s="87"/>
-      <c r="B35" s="78" t="str">
+        <v>0.445217391304348</v>
+      </c>
+      <c r="S34" s="86">
+        <f ca="1">RANK(R34,R33:R41)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A35" s="81"/>
+      <c r="B35" s="72" t="str">
         <f>高装高套!A4</f>
         <v>刘奇峻</v>
       </c>
-      <c r="C35" s="78">
+      <c r="C35" s="72">
         <v>3.5</v>
       </c>
-      <c r="D35" s="78">
+      <c r="D35" s="72">
         <f>高装高套!B4</f>
         <v>0</v>
       </c>
-      <c r="E35" s="79">
+      <c r="E35" s="73">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="79">
+      <c r="F35" s="73">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>786.5</v>
+        <v>0</v>
       </c>
       <c r="G35"/>
-      <c r="I35"/>
-      <c r="J35" s="90"/>
-      <c r="K35" s="93" t="s">
-        <v>61</v>
-      </c>
-      <c r="L35" s="81">
+      <c r="H35" s="84"/>
+      <c r="I35" s="87" t="s">
+        <v>63</v>
+      </c>
+      <c r="J35" s="75">
         <v>60</v>
       </c>
-      <c r="M35" s="81">
+      <c r="K35" s="75">
         <f>交付高装!D4</f>
-        <v>10</v>
-      </c>
-      <c r="N35" s="82">
+        <v>5</v>
+      </c>
+      <c r="L35" s="76">
         <f>交付高装!E4</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="O35"/>
-      <c r="P35" s="83" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q35" s="84">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="N35" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="O35" s="78">
         <v>3.52</v>
       </c>
-      <c r="R35" s="84">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P35,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>37.59</v>
-      </c>
-      <c r="S35" s="85">
+      <c r="P35" s="78">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N35,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>2.97</v>
+      </c>
+      <c r="Q35" s="78">
+        <f>_xlfn.XLOOKUP(N35,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>320.35</v>
+      </c>
+      <c r="R35" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>10.6789772727273</v>
-      </c>
-      <c r="T35" s="86">
-        <f ca="1">RANK(S35,S33:S41)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A36" s="87"/>
-      <c r="B36" s="88" t="str">
+        <v>0.84375</v>
+      </c>
+      <c r="S35" s="80">
+        <f ca="1">RANK(R35,R33:R41)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A36" s="81"/>
+      <c r="B36" s="82" t="str">
         <f>高装高套!A5</f>
         <v>龙家宝</v>
       </c>
-      <c r="C36" s="88">
+      <c r="C36" s="82">
         <v>3.5</v>
       </c>
-      <c r="D36" s="88">
+      <c r="D36" s="82">
         <f>高装高套!B5</f>
-        <v>1</v>
-      </c>
-      <c r="E36" s="89">
+        <v>0</v>
+      </c>
+      <c r="E36" s="83">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>143</v>
-      </c>
-      <c r="F36" s="89">
+        <v>0</v>
+      </c>
+      <c r="F36" s="83">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="G36"/>
-      <c r="I36"/>
-      <c r="J36" s="90"/>
-      <c r="K36" s="81" t="s">
-        <v>63</v>
-      </c>
-      <c r="L36" s="81">
+      <c r="H36" s="84"/>
+      <c r="I36" s="75" t="s">
+        <v>65</v>
+      </c>
+      <c r="J36" s="75">
         <v>45</v>
       </c>
-      <c r="M36" s="81">
+      <c r="K36" s="75">
         <f>交付高装!D5</f>
-        <v>3</v>
-      </c>
-      <c r="N36" s="82">
+        <v>0</v>
+      </c>
+      <c r="L36" s="76">
         <f>交付高装!E5</f>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="O36"/>
-      <c r="P36" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q36" s="91">
+        <v>0</v>
+      </c>
+      <c r="N36" s="77" t="s">
+        <v>66</v>
+      </c>
+      <c r="O36" s="85">
         <v>3.97</v>
       </c>
-      <c r="R36" s="91">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P36,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>15.45</v>
-      </c>
-      <c r="S36" s="85">
+      <c r="P36" s="85">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N36,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>2.24</v>
+      </c>
+      <c r="Q36" s="85">
+        <f>_xlfn.XLOOKUP(N36,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>2729.87</v>
+      </c>
+      <c r="R36" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>3.89168765743073</v>
-      </c>
-      <c r="T36" s="92">
-        <f ca="1">RANK(S36,S33:S41)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A37" s="87"/>
-      <c r="B37" s="78" t="str">
+        <v>0.564231738035264</v>
+      </c>
+      <c r="S36" s="86">
+        <f ca="1">RANK(R36,R33:R41)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A37" s="81"/>
+      <c r="B37" s="72" t="str">
         <f>高装高套!A6</f>
         <v>罗紫杰</v>
       </c>
-      <c r="C37" s="78">
+      <c r="C37" s="72">
         <v>3.5</v>
       </c>
-      <c r="D37" s="78">
+      <c r="D37" s="72">
         <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="E37" s="79">
+      <c r="E37" s="73">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="79">
+      <c r="F37" s="73">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G37"/>
-      <c r="I37"/>
-      <c r="J37" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="K37" s="95" t="s">
+      <c r="H37" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="L37" s="96">
+      <c r="I37" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="90">
         <v>30</v>
       </c>
-      <c r="M37" s="96">
+      <c r="K37" s="90">
         <f>交付高装!D6</f>
-        <v>5</v>
-      </c>
-      <c r="N37" s="97">
+        <v>0</v>
+      </c>
+      <c r="L37" s="91">
         <f>交付高装!E6</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="O37"/>
-      <c r="P37" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q37" s="84">
+        <v>0</v>
+      </c>
+      <c r="N37" s="77" t="s">
+        <v>67</v>
+      </c>
+      <c r="O37" s="78">
         <v>2.38</v>
       </c>
-      <c r="R37" s="84">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P37,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>10.69</v>
-      </c>
-      <c r="S37" s="85">
+      <c r="P37" s="78">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N37,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>2.96</v>
+      </c>
+      <c r="Q37" s="78">
+        <f>_xlfn.XLOOKUP(N37,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>-5280.93</v>
+      </c>
+      <c r="R37" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>4.49159663865546</v>
-      </c>
-      <c r="T37" s="86">
-        <f ca="1">RANK(S37,S33:S41)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A38" s="87"/>
-      <c r="B38" s="88" t="str">
+        <v>1.2436974789916</v>
+      </c>
+      <c r="S37" s="80">
+        <f ca="1">RANK(R37,R33:R41)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A38" s="81"/>
+      <c r="B38" s="82" t="str">
         <f>高装高套!A7</f>
         <v>莫健铭</v>
       </c>
-      <c r="C38" s="88">
+      <c r="C38" s="82">
         <v>3.5</v>
       </c>
-      <c r="D38" s="88">
+      <c r="D38" s="82">
         <f>高装高套!B7</f>
         <v>0</v>
       </c>
-      <c r="E38" s="89">
+      <c r="E38" s="83">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="89">
+      <c r="F38" s="83">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G38"/>
-      <c r="I38"/>
-      <c r="J38" s="98"/>
-      <c r="K38" s="95" t="s">
-        <v>41</v>
-      </c>
-      <c r="L38" s="96">
+      <c r="H38" s="92"/>
+      <c r="I38" s="89" t="s">
+        <v>42</v>
+      </c>
+      <c r="J38" s="90">
         <v>30</v>
       </c>
-      <c r="M38" s="96">
+      <c r="K38" s="90">
         <f>交付高装!D7</f>
-        <v>9</v>
-      </c>
-      <c r="N38" s="97">
+        <v>0</v>
+      </c>
+      <c r="L38" s="91">
         <f>交付高装!E7</f>
-        <v>0.3</v>
-      </c>
-      <c r="O38"/>
-      <c r="P38" s="83" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q38" s="99">
+        <v>0</v>
+      </c>
+      <c r="N38" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="O38" s="93">
         <v>2.6</v>
       </c>
-      <c r="R38" s="99">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P38,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>8.45</v>
-      </c>
-      <c r="S38" s="85">
+      <c r="P38" s="93">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N38,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>0.47</v>
+      </c>
+      <c r="Q38" s="85">
+        <f>_xlfn.XLOOKUP(N38,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>11048.28</v>
+      </c>
+      <c r="R38" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>3.25</v>
-      </c>
-      <c r="T38" s="92">
-        <f ca="1">RANK(S38,S33:S41)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A39" s="87"/>
-      <c r="B39" s="78" t="str">
+        <v>0.180769230769231</v>
+      </c>
+      <c r="S38" s="86">
+        <f ca="1">RANK(R38,R33:R41)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A39" s="81"/>
+      <c r="B39" s="72" t="str">
         <f>高装高套!A8</f>
         <v>吴广仁</v>
       </c>
-      <c r="C39" s="78">
+      <c r="C39" s="72">
         <v>3.5</v>
       </c>
-      <c r="D39" s="78">
+      <c r="D39" s="72">
         <f>高装高套!B8</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="79">
+        <v>1.5</v>
+      </c>
+      <c r="E39" s="73">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>0</v>
-      </c>
-      <c r="F39" s="79">
+        <v>239</v>
+      </c>
+      <c r="F39" s="73">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>1055.5</v>
       </c>
       <c r="G39"/>
-      <c r="J39" s="98"/>
-      <c r="K39" s="95" t="s">
-        <v>42</v>
-      </c>
-      <c r="L39" s="96">
+      <c r="H39" s="92"/>
+      <c r="I39" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="J39" s="90">
         <v>30</v>
       </c>
-      <c r="M39" s="96">
+      <c r="K39" s="90">
         <f>交付高装!D8</f>
-        <v>3</v>
-      </c>
-      <c r="N39" s="97">
+        <v>0</v>
+      </c>
+      <c r="L39" s="91">
         <f>交付高装!E8</f>
-        <v>0.1</v>
-      </c>
-      <c r="O39"/>
-      <c r="P39" s="83" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q39" s="84">
+        <v>0</v>
+      </c>
+      <c r="N39" s="77" t="s">
+        <v>69</v>
+      </c>
+      <c r="O39" s="78">
         <v>2.41</v>
       </c>
-      <c r="R39" s="84">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P39,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>7.13</v>
-      </c>
-      <c r="S39" s="85">
+      <c r="P39" s="78">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N39,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>0.44</v>
+      </c>
+      <c r="Q39" s="78">
+        <f>_xlfn.XLOOKUP(N39,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>-67.55</v>
+      </c>
+      <c r="R39" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>2.95850622406639</v>
-      </c>
-      <c r="T39" s="86">
-        <f ca="1">RANK(S39,S33:S41)</f>
+        <v>0.182572614107884</v>
+      </c>
+      <c r="S39" s="80">
+        <f ca="1">RANK(R39,R33:R41)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="40" ht="13.5" customHeight="1" spans="1:20">
-      <c r="A40" s="100"/>
-      <c r="B40" s="88" t="str">
+    <row r="40" ht="13.5" customHeight="1" spans="1:19">
+      <c r="A40" s="94"/>
+      <c r="B40" s="82" t="str">
         <f>高装高套!A9</f>
         <v>王洪明</v>
       </c>
-      <c r="C40" s="88">
+      <c r="C40" s="82">
         <v>3.5</v>
       </c>
-      <c r="D40" s="88">
+      <c r="D40" s="82">
         <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="E40" s="89">
+      <c r="E40" s="83">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="89">
+      <c r="F40" s="83">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G40"/>
-      <c r="J40" s="98"/>
-      <c r="K40" s="95" t="s">
-        <v>43</v>
-      </c>
-      <c r="L40" s="96">
+      <c r="H40" s="92"/>
+      <c r="I40" s="89" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40" s="90">
         <v>30</v>
       </c>
-      <c r="M40" s="96">
+      <c r="K40" s="90">
         <f>交付高装!D9</f>
-        <v>9</v>
-      </c>
-      <c r="N40" s="97">
+        <v>3</v>
+      </c>
+      <c r="L40" s="91">
         <f>交付高装!E9</f>
-        <v>0.3</v>
-      </c>
-      <c r="O40"/>
-      <c r="P40" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q40" s="91">
+        <v>0.1</v>
+      </c>
+      <c r="N40" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="O40" s="85">
         <v>3.22</v>
       </c>
-      <c r="R40" s="91">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P40,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>10.5</v>
-      </c>
-      <c r="S40" s="85">
+      <c r="P40" s="85">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N40,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>2.72</v>
+      </c>
+      <c r="Q40" s="85">
+        <f>_xlfn.XLOOKUP(N40,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>-356088.16</v>
+      </c>
+      <c r="R40" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>3.26086956521739</v>
-      </c>
-      <c r="T40" s="92">
-        <f ca="1">RANK(S40,S33:S41)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1" spans="1:20">
-      <c r="A41" s="101" t="s">
-        <v>35</v>
-      </c>
-      <c r="B41" s="102"/>
-      <c r="C41" s="101">
+        <v>0.84472049689441</v>
+      </c>
+      <c r="S40" s="86">
+        <f ca="1">RANK(R40,R33:R41)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" customHeight="1" spans="1:19">
+      <c r="A41" s="95" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" s="96"/>
+      <c r="C41" s="95">
         <f>SUM(C33:C40)</f>
         <v>28</v>
       </c>
-      <c r="D41" s="101">
+      <c r="D41" s="95">
         <f>SUM(D33:D40)</f>
-        <v>1</v>
-      </c>
-      <c r="E41" s="101">
+        <v>1.5</v>
+      </c>
+      <c r="E41" s="95">
         <f ca="1">SUM(E33:E40)</f>
-        <v>143</v>
-      </c>
-      <c r="F41" s="101" t="s">
-        <v>40</v>
+        <v>239</v>
+      </c>
+      <c r="F41" s="95" t="s">
+        <v>41</v>
       </c>
       <c r="G41"/>
-      <c r="J41" s="98"/>
-      <c r="K41" s="95" t="s">
-        <v>44</v>
-      </c>
-      <c r="L41" s="96">
+      <c r="H41" s="92"/>
+      <c r="I41" s="89" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41" s="90">
         <v>30</v>
       </c>
-      <c r="M41" s="96">
+      <c r="K41" s="90">
         <f>交付高装!D10</f>
         <v>0</v>
       </c>
-      <c r="N41" s="97">
+      <c r="L41" s="91">
         <f>交付高装!E10</f>
         <v>0</v>
       </c>
-      <c r="O41"/>
-      <c r="P41" s="83" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q41" s="84">
+      <c r="N41" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="O41" s="78">
         <v>3.36</v>
       </c>
-      <c r="R41" s="84">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(P41,高套!A:A,高套!B:B,0)/U4,2)</f>
-        <v>15.71</v>
-      </c>
-      <c r="S41" s="85">
+      <c r="P41" s="78">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N41,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>4.14</v>
+      </c>
+      <c r="Q41" s="78">
+        <f>_xlfn.XLOOKUP(N41,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>2000.9</v>
+      </c>
+      <c r="R41" s="79">
         <f ca="1" t="shared" si="11"/>
-        <v>4.67559523809524</v>
-      </c>
-      <c r="T41" s="86">
-        <f ca="1">RANK(S41,S33:S41)</f>
+        <v>1.23214285714286</v>
+      </c>
+      <c r="S41" s="80">
+        <f ca="1">RANK(R41,R33:R41)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="42" ht="14.75" customHeight="1" spans="1:20">
+    <row r="42" ht="14.75" customHeight="1" spans="1:19">
       <c r="F42"/>
       <c r="G42"/>
-      <c r="J42" s="98"/>
-      <c r="K42" s="95" t="s">
-        <v>45</v>
-      </c>
-      <c r="L42" s="96">
+      <c r="H42" s="92"/>
+      <c r="I42" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="90">
         <v>30</v>
       </c>
-      <c r="M42" s="96">
+      <c r="K42" s="90">
         <f>交付高装!D11</f>
-        <v>10</v>
-      </c>
-      <c r="N42" s="97">
+        <v>5</v>
+      </c>
+      <c r="L42" s="91">
         <f>交付高装!E11</f>
-        <v>0.333333333333333</v>
-      </c>
-      <c r="O42"/>
-      <c r="P42" s="103" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q42" s="104">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="N42" s="97" t="s">
+        <v>72</v>
+      </c>
+      <c r="O42" s="98">
+        <f>SUM(O33:O41)</f>
+        <v>31.46</v>
+      </c>
+      <c r="P42" s="98">
+        <f ca="1">SUM(P33:P41)</f>
+        <v>19.22</v>
+      </c>
+      <c r="Q42" s="98">
         <f>SUM(Q33:Q41)</f>
-        <v>31.46</v>
-      </c>
-      <c r="R42" s="104">
-        <f ca="1">SUM(R33:R41)</f>
-        <v>134.25</v>
-      </c>
-      <c r="S42" s="105">
+        <v>-343665.28</v>
+      </c>
+      <c r="R42" s="99">
         <f ca="1" t="shared" si="11"/>
-        <v>4.2673235855054</v>
-      </c>
-      <c r="T42" s="106" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="43" ht="13.5" customHeight="1" spans="1:20">
+        <v>0.610934520025429</v>
+      </c>
+      <c r="S42" s="100" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="43" ht="13.5" customHeight="1" spans="1:19">
       <c r="F43"/>
       <c r="G43"/>
-      <c r="J43" s="98"/>
-      <c r="K43" s="95" t="s">
-        <v>46</v>
-      </c>
-      <c r="L43" s="96">
+      <c r="H43" s="92"/>
+      <c r="I43" s="89" t="s">
+        <v>47</v>
+      </c>
+      <c r="J43" s="90">
         <v>30</v>
       </c>
-      <c r="M43" s="96">
+      <c r="K43" s="90">
         <f>交付高装!D12</f>
-        <v>3</v>
-      </c>
-      <c r="N43" s="97">
+        <v>0</v>
+      </c>
+      <c r="L43" s="91">
         <f>交付高装!E12</f>
-        <v>0.1</v>
-      </c>
-      <c r="O43"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1" spans="1:20">
+        <v>0</v>
+      </c>
+      <c r="P43"/>
+    </row>
+    <row r="44" ht="13.5" customHeight="1" spans="1:19">
       <c r="F44"/>
       <c r="G44"/>
-      <c r="J44" s="107"/>
-      <c r="K44" s="108" t="s">
-        <v>72</v>
-      </c>
-      <c r="L44" s="96">
+      <c r="H44" s="101"/>
+      <c r="I44" s="102" t="s">
+        <v>74</v>
+      </c>
+      <c r="J44" s="90">
         <v>210</v>
       </c>
-      <c r="M44" s="96">
-        <f>SUM(M33:M36)</f>
-        <v>39</v>
-      </c>
-      <c r="N44" s="97">
-        <f>M44/L44</f>
-        <v>0.185714285714286</v>
-      </c>
-      <c r="O44"/>
+      <c r="K44" s="90">
+        <f>SUM(K33:K36)</f>
+        <v>8</v>
+      </c>
+      <c r="L44" s="91">
+        <f>K44/J44</f>
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="P44"/>
     </row>
     <row r="45" ht="13.5" customHeight="1"/>
-    <row r="46" ht="13.5" customHeight="1" spans="1:20">
+    <row r="46" ht="13.5" customHeight="1" spans="1:19">
       <c r="D46"/>
       <c r="E46"/>
       <c r="F46"/>
@@ -4980,9 +5035,9 @@
       <c r="I46"/>
       <c r="J46"/>
       <c r="K46"/>
-      <c r="O46"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1" spans="1:20">
+      <c r="P46"/>
+    </row>
+    <row r="47" ht="13.5" customHeight="1" spans="1:19">
       <c r="D47"/>
       <c r="E47"/>
       <c r="F47"/>
@@ -4991,19 +5046,8 @@
       <c r="J47"/>
       <c r="K47"/>
     </row>
-    <row r="48" ht="13.5" customHeight="1" spans="1:20">
-      <c r="A48" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>76</v>
-      </c>
+    <row r="48" ht="13.5" customHeight="1" spans="1:19">
+      <c r="D48"/>
       <c r="E48"/>
       <c r="F48"/>
       <c r="G48"/>
@@ -5011,23 +5055,8 @@
       <c r="J48"/>
       <c r="K48"/>
     </row>
-    <row r="49" ht="14.75" customHeight="1" spans="1:15">
-      <c r="A49" s="2">
-        <f>积分!A2</f>
-        <v>11117.68</v>
-      </c>
-      <c r="B49" s="2">
-        <f>积分!B2</f>
-        <v>8941.02</v>
-      </c>
-      <c r="C49" s="2">
-        <f>积分!C2</f>
-        <v>2010</v>
-      </c>
-      <c r="D49" s="2">
-        <f>积分!D2</f>
-        <v>0.89</v>
-      </c>
+    <row r="49" ht="14.75" customHeight="1" spans="4:11">
+      <c r="D49"/>
       <c r="E49"/>
       <c r="F49"/>
       <c r="G49"/>
@@ -5035,7 +5064,7 @@
       <c r="J49"/>
       <c r="K49"/>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="4:11">
       <c r="D50"/>
       <c r="E50"/>
       <c r="F50"/>
@@ -5044,7 +5073,7 @@
       <c r="J50"/>
       <c r="K50"/>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="4:11">
       <c r="D51"/>
       <c r="E51"/>
       <c r="F51"/>
@@ -5053,7 +5082,7 @@
       <c r="J51"/>
       <c r="K51"/>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="4:11">
       <c r="D52"/>
       <c r="E52"/>
       <c r="F52"/>
@@ -5062,7 +5091,7 @@
       <c r="J52"/>
       <c r="K52"/>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="4:11">
       <c r="D53"/>
       <c r="E53"/>
       <c r="F53"/>
@@ -5071,7 +5100,7 @@
       <c r="J53"/>
       <c r="K53"/>
     </row>
-    <row r="54" ht="13.5" customHeight="1" spans="1:15">
+    <row r="54" ht="13.5" customHeight="1" spans="4:11">
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
@@ -5080,7 +5109,7 @@
       <c r="J54"/>
       <c r="K54"/>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="4:11">
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
@@ -5089,7 +5118,7 @@
       <c r="J55"/>
       <c r="K55"/>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="4:11">
       <c r="D56"/>
       <c r="E56"/>
       <c r="F56"/>
@@ -5098,138 +5127,89 @@
       <c r="J56"/>
       <c r="K56"/>
     </row>
-    <row r="57" spans="1:15">
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
+    <row r="57" spans="4:11">
       <c r="G57"/>
       <c r="I57"/>
       <c r="J57"/>
       <c r="K57"/>
-      <c r="O57"/>
-    </row>
-    <row r="58" spans="1:15">
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
+    </row>
+    <row r="58" spans="4:11">
       <c r="G58"/>
       <c r="I58"/>
       <c r="J58"/>
       <c r="K58"/>
-      <c r="O58"/>
-    </row>
-    <row r="59" spans="1:15">
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
+    </row>
+    <row r="59" spans="4:11">
       <c r="G59"/>
       <c r="I59"/>
       <c r="J59"/>
       <c r="K59"/>
-      <c r="O59"/>
-    </row>
-    <row r="60" spans="1:15">
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
+    </row>
+    <row r="60" spans="4:11">
       <c r="G60"/>
       <c r="I60"/>
       <c r="J60"/>
       <c r="K60"/>
-      <c r="O60"/>
-    </row>
-    <row r="61" spans="1:15">
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
+    </row>
+    <row r="61" spans="4:11">
       <c r="G61"/>
       <c r="I61"/>
       <c r="J61"/>
       <c r="K61"/>
-      <c r="O61"/>
-    </row>
-    <row r="62" spans="1:15">
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
+    </row>
+    <row r="62" spans="4:11">
       <c r="G62"/>
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62"/>
-      <c r="O62"/>
-    </row>
-    <row r="63" ht="13.5" customHeight="1" spans="1:15">
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
+    </row>
+    <row r="63" ht="13.5" customHeight="1" spans="4:11">
       <c r="G63"/>
       <c r="I63"/>
       <c r="J63"/>
       <c r="K63"/>
-      <c r="O63"/>
-    </row>
-    <row r="64" ht="13.5" customHeight="1" spans="1:15">
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
+    </row>
+    <row r="64" ht="13.5" customHeight="1" spans="4:11">
       <c r="G64"/>
       <c r="I64"/>
       <c r="J64"/>
       <c r="K64"/>
-      <c r="O64"/>
-    </row>
-    <row r="65" spans="4:15">
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
+    </row>
+    <row r="65" spans="4:16">
       <c r="G65"/>
       <c r="I65"/>
       <c r="J65"/>
       <c r="K65"/>
-      <c r="O65"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1" spans="4:15">
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
+    </row>
+    <row r="66" ht="13.5" customHeight="1" spans="4:16">
       <c r="G66"/>
       <c r="I66"/>
       <c r="J66"/>
       <c r="K66"/>
-      <c r="O66"/>
-    </row>
-    <row r="67" customFormat="1" ht="13.5" customHeight="1"/>
-    <row r="68" ht="13.5" customHeight="1" spans="4:15">
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
+    </row>
+    <row r="67" ht="13.5" customHeight="1"/>
+    <row r="68" ht="13.5" customHeight="1" spans="4:16">
       <c r="G68"/>
       <c r="I68"/>
       <c r="J68"/>
       <c r="K68"/>
-      <c r="O68"/>
-    </row>
-    <row r="69" spans="4:15">
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
+      <c r="P68"/>
+    </row>
+    <row r="69" spans="4:16">
       <c r="G69"/>
       <c r="I69"/>
       <c r="J69"/>
       <c r="K69"/>
-      <c r="O69"/>
-    </row>
-    <row r="70" spans="4:15">
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
+      <c r="P69"/>
+    </row>
+    <row r="70" spans="4:16">
       <c r="G70"/>
       <c r="I70"/>
       <c r="J70"/>
       <c r="K70"/>
-      <c r="O70"/>
-    </row>
-    <row r="71" spans="4:15">
+      <c r="P70"/>
+    </row>
+    <row r="71" spans="4:16">
       <c r="D71"/>
       <c r="E71"/>
       <c r="F71"/>
@@ -5237,9 +5217,9 @@
       <c r="I71"/>
       <c r="J71"/>
       <c r="K71"/>
-      <c r="O71"/>
-    </row>
-    <row r="72" spans="4:15">
+      <c r="P71"/>
+    </row>
+    <row r="72" spans="4:16">
       <c r="D72"/>
       <c r="E72"/>
       <c r="F72"/>
@@ -5247,9 +5227,9 @@
       <c r="I72"/>
       <c r="J72"/>
       <c r="K72"/>
-      <c r="O72"/>
-    </row>
-    <row r="73" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P72"/>
+    </row>
+    <row r="73" ht="13.5" customHeight="1" spans="4:16">
       <c r="D73"/>
       <c r="E73"/>
       <c r="F73"/>
@@ -5257,9 +5237,9 @@
       <c r="I73"/>
       <c r="J73"/>
       <c r="K73"/>
-      <c r="O73"/>
-    </row>
-    <row r="74" spans="4:15">
+      <c r="P73"/>
+    </row>
+    <row r="74" spans="4:16">
       <c r="D74"/>
       <c r="E74"/>
       <c r="F74"/>
@@ -5267,9 +5247,9 @@
       <c r="I74"/>
       <c r="J74"/>
       <c r="K74"/>
-      <c r="O74"/>
-    </row>
-    <row r="75" spans="4:15">
+      <c r="P74"/>
+    </row>
+    <row r="75" spans="4:16">
       <c r="D75"/>
       <c r="E75"/>
       <c r="F75"/>
@@ -5277,9 +5257,9 @@
       <c r="I75"/>
       <c r="J75"/>
       <c r="K75"/>
-      <c r="O75"/>
-    </row>
-    <row r="76" spans="4:15">
+      <c r="P75"/>
+    </row>
+    <row r="76" spans="4:16">
       <c r="D76"/>
       <c r="E76"/>
       <c r="F76"/>
@@ -5287,9 +5267,9 @@
       <c r="I76"/>
       <c r="J76"/>
       <c r="K76"/>
-      <c r="O76"/>
-    </row>
-    <row r="77" spans="4:15">
+      <c r="P76"/>
+    </row>
+    <row r="77" spans="4:16">
       <c r="D77"/>
       <c r="E77"/>
       <c r="F77"/>
@@ -5297,9 +5277,9 @@
       <c r="I77"/>
       <c r="J77"/>
       <c r="K77"/>
-      <c r="O77"/>
-    </row>
-    <row r="78" spans="4:15">
+      <c r="P77"/>
+    </row>
+    <row r="78" spans="4:16">
       <c r="D78"/>
       <c r="E78"/>
       <c r="F78"/>
@@ -5307,9 +5287,9 @@
       <c r="I78"/>
       <c r="J78"/>
       <c r="K78"/>
-      <c r="O78"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P78"/>
+    </row>
+    <row r="79" ht="13.5" customHeight="1" spans="4:16">
       <c r="D79"/>
       <c r="E79"/>
       <c r="F79"/>
@@ -5317,9 +5297,9 @@
       <c r="I79"/>
       <c r="J79"/>
       <c r="K79"/>
-      <c r="O79"/>
-    </row>
-    <row r="80" spans="4:15">
+      <c r="P79"/>
+    </row>
+    <row r="80" spans="4:16">
       <c r="D80"/>
       <c r="E80"/>
       <c r="F80"/>
@@ -5327,9 +5307,9 @@
       <c r="I80"/>
       <c r="J80"/>
       <c r="K80"/>
-      <c r="O80"/>
-    </row>
-    <row r="81" spans="4:15">
+      <c r="P80"/>
+    </row>
+    <row r="81" spans="4:16">
       <c r="D81"/>
       <c r="E81"/>
       <c r="F81"/>
@@ -5337,9 +5317,9 @@
       <c r="I81"/>
       <c r="J81"/>
       <c r="K81"/>
-      <c r="O81"/>
-    </row>
-    <row r="82" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P81"/>
+    </row>
+    <row r="82" ht="13.5" customHeight="1" spans="4:16">
       <c r="D82"/>
       <c r="E82"/>
       <c r="F82"/>
@@ -5347,9 +5327,9 @@
       <c r="I82"/>
       <c r="J82"/>
       <c r="K82"/>
-      <c r="O82"/>
-    </row>
-    <row r="83" ht="52" customHeight="1" spans="4:15">
+      <c r="P82"/>
+    </row>
+    <row r="83" ht="52" customHeight="1" spans="4:16">
       <c r="D83"/>
       <c r="E83"/>
       <c r="F83"/>
@@ -5357,9 +5337,9 @@
       <c r="I83"/>
       <c r="J83"/>
       <c r="K83"/>
-      <c r="O83"/>
-    </row>
-    <row r="84" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P83"/>
+    </row>
+    <row r="84" ht="13.5" customHeight="1" spans="4:16">
       <c r="D84"/>
       <c r="E84"/>
       <c r="F84"/>
@@ -5367,9 +5347,9 @@
       <c r="I84"/>
       <c r="J84"/>
       <c r="K84"/>
-      <c r="O84"/>
-    </row>
-    <row r="85" spans="4:15">
+      <c r="P84"/>
+    </row>
+    <row r="85" spans="4:16">
       <c r="D85"/>
       <c r="E85"/>
       <c r="F85"/>
@@ -5377,9 +5357,9 @@
       <c r="I85"/>
       <c r="J85"/>
       <c r="K85"/>
-      <c r="O85"/>
-    </row>
-    <row r="86" spans="4:15">
+      <c r="P85"/>
+    </row>
+    <row r="86" spans="4:16">
       <c r="D86"/>
       <c r="E86"/>
       <c r="F86"/>
@@ -5387,9 +5367,9 @@
       <c r="I86"/>
       <c r="J86"/>
       <c r="K86"/>
-      <c r="O86"/>
-    </row>
-    <row r="87" spans="4:15">
+      <c r="P86"/>
+    </row>
+    <row r="87" spans="4:16">
       <c r="D87"/>
       <c r="E87"/>
       <c r="F87"/>
@@ -5397,9 +5377,9 @@
       <c r="I87"/>
       <c r="J87"/>
       <c r="K87"/>
-      <c r="O87"/>
-    </row>
-    <row r="88" spans="4:15">
+      <c r="P87"/>
+    </row>
+    <row r="88" spans="4:16">
       <c r="D88"/>
       <c r="E88"/>
       <c r="F88"/>
@@ -5407,9 +5387,9 @@
       <c r="I88"/>
       <c r="J88"/>
       <c r="K88"/>
-      <c r="O88"/>
-    </row>
-    <row r="89" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P88"/>
+    </row>
+    <row r="89" ht="13.5" customHeight="1" spans="4:16">
       <c r="D89"/>
       <c r="E89"/>
       <c r="F89"/>
@@ -5417,9 +5397,9 @@
       <c r="I89"/>
       <c r="J89"/>
       <c r="K89"/>
-      <c r="O89"/>
-    </row>
-    <row r="90" spans="4:15">
+      <c r="P89"/>
+    </row>
+    <row r="90" spans="4:16">
       <c r="D90"/>
       <c r="E90"/>
       <c r="F90"/>
@@ -5427,9 +5407,9 @@
       <c r="I90"/>
       <c r="J90"/>
       <c r="K90"/>
-      <c r="O90"/>
-    </row>
-    <row r="91" spans="4:15">
+      <c r="P90"/>
+    </row>
+    <row r="91" spans="4:16">
       <c r="D91"/>
       <c r="E91"/>
       <c r="F91"/>
@@ -5437,9 +5417,9 @@
       <c r="I91"/>
       <c r="J91"/>
       <c r="K91"/>
-      <c r="O91"/>
-    </row>
-    <row r="92" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P91"/>
+    </row>
+    <row r="92" ht="13.5" customHeight="1" spans="4:16">
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92"/>
@@ -5447,9 +5427,9 @@
       <c r="I92"/>
       <c r="J92"/>
       <c r="K92"/>
-      <c r="O92"/>
-    </row>
-    <row r="93" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P92"/>
+    </row>
+    <row r="93" ht="13.5" customHeight="1" spans="4:16">
       <c r="D93"/>
       <c r="E93"/>
       <c r="F93"/>
@@ -5457,9 +5437,9 @@
       <c r="I93"/>
       <c r="J93"/>
       <c r="K93"/>
-      <c r="O93"/>
-    </row>
-    <row r="94" spans="4:15">
+      <c r="P93"/>
+    </row>
+    <row r="94" spans="4:16">
       <c r="D94"/>
       <c r="E94"/>
       <c r="F94"/>
@@ -5467,9 +5447,9 @@
       <c r="I94"/>
       <c r="J94"/>
       <c r="K94"/>
-      <c r="O94"/>
-    </row>
-    <row r="95" spans="4:15">
+      <c r="P94"/>
+    </row>
+    <row r="95" spans="4:16">
       <c r="D95"/>
       <c r="E95"/>
       <c r="F95"/>
@@ -5477,9 +5457,9 @@
       <c r="I95"/>
       <c r="J95"/>
       <c r="K95"/>
-      <c r="O95"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P95"/>
+    </row>
+    <row r="96" ht="13.5" customHeight="1" spans="4:16">
       <c r="D96"/>
       <c r="E96"/>
       <c r="F96"/>
@@ -5487,9 +5467,9 @@
       <c r="I96"/>
       <c r="J96"/>
       <c r="K96"/>
-      <c r="O96"/>
-    </row>
-    <row r="97" ht="52" customHeight="1" spans="4:15">
+      <c r="P96"/>
+    </row>
+    <row r="97" ht="52" customHeight="1" spans="4:16">
       <c r="D97"/>
       <c r="E97"/>
       <c r="F97"/>
@@ -5497,9 +5477,9 @@
       <c r="I97"/>
       <c r="J97"/>
       <c r="K97"/>
-      <c r="O97"/>
-    </row>
-    <row r="98" ht="13.5" customHeight="1" spans="4:15">
+      <c r="P97"/>
+    </row>
+    <row r="98" ht="13.5" customHeight="1" spans="4:16">
       <c r="D98"/>
       <c r="E98"/>
       <c r="F98"/>
@@ -5507,9 +5487,9 @@
       <c r="I98"/>
       <c r="J98"/>
       <c r="K98"/>
-      <c r="O98"/>
-    </row>
-    <row r="99" spans="4:15">
+      <c r="P98"/>
+    </row>
+    <row r="99" spans="4:16">
       <c r="D99"/>
       <c r="E99"/>
       <c r="F99"/>
@@ -5517,9 +5497,9 @@
       <c r="I99"/>
       <c r="J99"/>
       <c r="K99"/>
-      <c r="O99"/>
-    </row>
-    <row r="100" spans="4:15">
+      <c r="P99"/>
+    </row>
+    <row r="100" spans="4:16">
       <c r="D100"/>
       <c r="E100"/>
       <c r="F100"/>
@@ -5527,9 +5507,9 @@
       <c r="I100"/>
       <c r="J100"/>
       <c r="K100"/>
-      <c r="O100"/>
-    </row>
-    <row r="101" spans="4:15">
+      <c r="P100"/>
+    </row>
+    <row r="101" spans="4:16">
       <c r="D101"/>
       <c r="E101"/>
       <c r="F101"/>
@@ -5537,9 +5517,9 @@
       <c r="I101"/>
       <c r="J101"/>
       <c r="K101"/>
-      <c r="O101"/>
-    </row>
-    <row r="102" spans="4:15">
+      <c r="P101"/>
+    </row>
+    <row r="102" spans="4:16">
       <c r="D102"/>
       <c r="E102"/>
       <c r="F102"/>
@@ -5547,18 +5527,18 @@
       <c r="I102"/>
       <c r="J102"/>
       <c r="K102"/>
-      <c r="O102"/>
+      <c r="P102"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="B1:R1"/>
+  <mergeCells count="30">
+    <mergeCell ref="B1:S1"/>
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="J2:O2"/>
-    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="J2:P2"/>
+    <mergeCell ref="Q2:S2"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="J31:N31"/>
-    <mergeCell ref="P31:T31"/>
+    <mergeCell ref="H31:L31"/>
+    <mergeCell ref="N31:S31"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="A4:A10"/>
@@ -5571,14 +5551,15 @@
     <mergeCell ref="F18:F19"/>
     <mergeCell ref="G18:G19"/>
     <mergeCell ref="H18:H19"/>
+    <mergeCell ref="H33:H36"/>
+    <mergeCell ref="H37:H44"/>
     <mergeCell ref="I18:I19"/>
     <mergeCell ref="J18:J19"/>
-    <mergeCell ref="J33:J36"/>
-    <mergeCell ref="J37:J44"/>
     <mergeCell ref="K18:K19"/>
     <mergeCell ref="L18:L19"/>
     <mergeCell ref="M18:M19"/>
     <mergeCell ref="N18:N19"/>
+    <mergeCell ref="O18:O19"/>
     <mergeCell ref="A18:B19"/>
   </mergeCells>
   <conditionalFormatting sqref="F18">
@@ -5591,7 +5572,7 @@
       <formula>"是"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S33:S41">
+  <conditionalFormatting sqref="R33:R41">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -5600,12 +5581,12 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{aa630747-b621-4803-929e-a22b87db575a}</x14:id>
+          <x14:id>{dd323c4c-cb0c-4deb-ba25-b306ac5144f0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(S33&lt;1,S33&lt;&gt;"")</formula>
+      <formula>AND(R33&lt;1,R33&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5615,7 +5596,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{aa630747-b621-4803-929e-a22b87db575a}">
+          <x14:cfRule type="dataBar" id="{dd323c4c-cb0c-4deb-ba25-b306ac5144f0}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5626,7 +5607,7 @@
               <x14:axisColor indexed="65"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>S33:S41</xm:sqref>
+          <xm:sqref>R33:R41</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -5634,23 +5615,211 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
+        <v>1366.67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4">
+        <v>316.83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5">
+        <v>-501</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7">
+        <v>-1648.67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9">
+        <v>1112.49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>402.56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13">
+        <v>-1737.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14">
+        <v>1294.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15">
+        <v>377.74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16">
+        <v>320.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17">
+        <v>2729.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18">
+        <v>-5280.93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19">
+        <v>11048.28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20">
+        <v>-67.55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21">
+        <v>-356088.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22">
+        <v>2000.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5658,7 +5827,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5666,47 +5835,47 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>26.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>18.33</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>9.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5714,66 +5883,66 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>11.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>9.94</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="B16">
-        <v>95.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="B17">
-        <v>134.28</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5781,31 +5950,31 @@
         <v>62</v>
       </c>
       <c r="B18">
-        <v>300.69</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B19">
-        <v>84.02</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20">
-        <v>125.64</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B21">
-        <v>123.63</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5813,15 +5982,15 @@
         <v>66</v>
       </c>
       <c r="B22">
-        <v>67.6</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B23">
-        <v>85.52</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5829,17 +5998,15 @@
         <v>67</v>
       </c>
       <c r="B24">
-        <v>57</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>81</v>
+        <v>69</v>
+      </c>
+      <c r="B25">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5851,20 +6018,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -5872,7 +6039,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -5880,15 +6047,15 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -5896,31 +6063,31 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -5928,7 +6095,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -5936,39 +6103,39 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -5976,20 +6143,18 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="B16">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="B17">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -6001,222 +6166,222 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>282</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>287</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <v>271</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>2291.29</v>
+        <v>1792.67</v>
       </c>
       <c r="D4">
-        <v>738</v>
+        <v>453.67</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>758</v>
+        <v>772.33</v>
       </c>
       <c r="D5">
-        <v>488</v>
+        <v>772.33</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>19.83</v>
+        <v>3.5</v>
       </c>
       <c r="C6">
-        <v>1766.66</v>
+        <v>-246</v>
       </c>
       <c r="D6">
-        <v>666.66</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>9.52</v>
+        <v>1.5</v>
       </c>
       <c r="C7">
-        <v>2182</v>
+        <v>203</v>
       </c>
       <c r="D7">
-        <v>1293</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1254.03</v>
+        <v>295.33</v>
       </c>
       <c r="D8">
-        <v>834</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>63</v>
+        <v>239</v>
       </c>
       <c r="D9">
-        <v>29</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10">
-        <v>689</v>
+        <v>744.5</v>
       </c>
       <c r="D10">
-        <v>649</v>
+        <v>744.5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="C11">
-        <v>387</v>
+        <v>878</v>
       </c>
       <c r="D11">
-        <v>299</v>
+        <v>878</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="C12">
-        <v>2117.76</v>
+        <v>872</v>
       </c>
       <c r="D12">
-        <v>1604</v>
+        <v>738</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>2096</v>
+        <v>698</v>
       </c>
       <c r="D13">
-        <v>1793</v>
+        <v>698</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>9.94</v>
+        <v>1.5</v>
       </c>
       <c r="C14">
-        <v>1415</v>
+        <v>-1647.54</v>
       </c>
       <c r="D14">
-        <v>938</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>154.92</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -6230,7 +6395,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -6261,13 +6426,13 @@
         <v>43</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -6320,7 +6485,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -6328,12 +6493,16 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>81</v>
+        <v>48</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6350,18 +6519,18 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6372,7 +6541,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6383,7 +6552,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -6394,10 +6563,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6405,7 +6574,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -6416,7 +6585,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -6427,10 +6596,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6438,7 +6607,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -6456,137 +6625,135 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>27.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>19.83</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>9.52</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>5.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>9.94</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15">
-        <v>0.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>78</v>
+      </c>
+      <c r="B16">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6603,287 +6770,287 @@
   <sheetData>
     <row r="1" ht="14.75" customHeight="1" spans="1:13">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="2" ht="14.75" customHeight="1" spans="1:13">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>60</v>
       </c>
       <c r="D2">
         <f t="array" ref="D2">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B2))</f>
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2" s="8">
         <f t="shared" ref="E2:E13" si="0">D2/C2</f>
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M2" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" ht="14.75" customHeight="1" spans="1:13">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C3">
         <v>60</v>
       </c>
       <c r="D3">
         <f t="array" ref="D3">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B3))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E3" s="8">
         <f t="shared" si="0"/>
-        <v>0.233333333333333</v>
+        <v>0</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M3" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="14.75" customHeight="1" spans="1:13">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>60</v>
       </c>
       <c r="D4">
         <f t="array" ref="D4">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B4))</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E4" s="8">
         <f t="shared" si="0"/>
-        <v>0.166666666666667</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" ht="14.75" customHeight="1" spans="1:13">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>45</v>
       </c>
       <c r="D5">
         <f t="array" ref="D5">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B5))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8">
         <f t="shared" si="0"/>
-        <v>0.0666666666666667</v>
+        <v>0</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M5" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="14.75" customHeight="1" spans="1:13">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6">
         <v>30</v>
       </c>
       <c r="D6">
         <f t="array" ref="D6">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B6))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6" s="8">
         <f t="shared" si="0"/>
-        <v>0.166666666666667</v>
+        <v>0</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" ht="14.75" customHeight="1" spans="1:13">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>30</v>
       </c>
       <c r="D7">
         <f t="array" ref="D7">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B7))</f>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" ht="14.75" customHeight="1" spans="1:13">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>30</v>
       </c>
       <c r="D8">
         <f t="array" ref="D8">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B8))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" ht="14.75" customHeight="1" spans="1:13">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>30</v>
       </c>
       <c r="D9">
         <f t="array" ref="D9">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B9))</f>
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" ht="14.75" customHeight="1" spans="1:13">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>30</v>
@@ -6897,86 +7064,86 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" ht="14.75" customHeight="1" spans="1:13">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11">
         <v>30</v>
       </c>
       <c r="D11">
         <f t="array" ref="D11">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B11))</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.333333333333333</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" ht="14.75" customHeight="1" spans="1:13">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12">
         <v>30</v>
       </c>
       <c r="D12">
         <f t="array" ref="D12">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B12))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M12" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" ht="14.75" customHeight="1" spans="1:13">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -6990,58 +7157,58 @@
         <v>0</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M13" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" ht="14.75" customHeight="1" spans="1:13">
       <c r="J14" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M14" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" ht="14.75" customHeight="1" spans="1:13">
       <c r="J15" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K15" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M15" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="14.75" customHeight="1" spans="1:13">
       <c r="J16" s="9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K16" s="9" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -7053,132 +7220,132 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2">
-        <v>1036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>502.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>4344</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>1783.5</v>
+        <v>658.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6">
-        <v>4429</v>
+        <v>-98</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7">
-        <v>5026</v>
+        <v>913.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
-        <v>3491</v>
+        <v>230.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>122.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>1339.5</v>
+        <v>892.5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="B11">
-        <v>1661.5</v>
+        <v>3411</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="B12">
-        <v>6846.5</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B13">
-        <v>7387</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14">
-        <v>4117.5</v>
+        <v>-2471.31</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B15">
-        <v>232.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -7186,7 +7353,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -7197,7 +7364,7 @@
         <v>42</v>
       </c>
       <c r="B18">
-        <v>786.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -7205,7 +7372,7 @@
         <v>43</v>
       </c>
       <c r="B19">
-        <v>281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -7237,17 +7404,15 @@
         <v>47</v>
       </c>
       <c r="B23">
-        <v>25</v>
+        <v>1055.5</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>81</v>
+        <v>48</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7262,32 +7427,32 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" ht="24" spans="1:4">
+    <row r="1" ht="24" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>11117.68</v>
+        <v>1294.22</v>
       </c>
       <c r="B2" s="2">
-        <v>8941.02</v>
+        <v>-415.28</v>
       </c>
       <c r="C2" s="2">
-        <v>2010</v>
+        <v>1100</v>
       </c>
       <c r="D2" s="2">
-        <v>0.89</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/assets/早会五张表.xlsx
+++ b/assets/早会五张表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\小辰\Desktop\代码实现\早会五张表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="22400" windowHeight="10080" tabRatio="659"/>
   </bookViews>
@@ -330,7 +335,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0_ "/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
-    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.0;[Red]0.0"/>
   </numFmts>
   <fonts count="43">
     <font>
@@ -1666,7 +1671,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1818,7 +1823,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2495,7 +2499,7 @@
       </c>
       <c r="B1" s="12" t="str">
         <f ca="1">"完美一单积分完成通报（截至"&amp;MONTH(TODAY()-1)&amp;"月"&amp;DAY(TODAY()-1)&amp;"日）"</f>
-        <v>完美一单积分完成通报（截至7月9日）</v>
+        <v>完美一单积分完成通报（截至8月5日）</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -2607,30 +2611,30 @@
         <v>22</v>
       </c>
       <c r="C4" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D4" s="19">
         <f>_xlfn.XLOOKUP(B4,高套!A:A,高套!B:B,0)</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="E4" s="20">
-        <f t="shared" ref="E4:E18" si="0">D4/C4</f>
-        <v>0</v>
+        <f>D4/C4</f>
+        <v>0.107142857142857</v>
       </c>
       <c r="F4" s="21">
         <f ca="1">D4/(C4/Z4*W$4)</f>
-        <v>0</v>
+        <v>0.664285714285714</v>
       </c>
       <c r="G4" s="18">
         <f>_xlfn.XLOOKUP(B4,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H4" s="22" t="str">
-        <f t="shared" ref="H4:H9" si="1">IF(G4&gt;=3,"否","是")</f>
+        <f t="shared" ref="H4:H9" si="0">IF(G4&gt;=3,"否","是")</f>
         <v>是</v>
       </c>
       <c r="I4" s="18" t="str">
-        <f t="shared" ref="I4:I9" si="2">IF(G4&gt;=15,"金牌",IF(G4&gt;=12,"银牌",""))</f>
+        <f t="shared" ref="I4:I9" si="1">IF(G4&gt;=15,"金牌",IF(G4&gt;=12,"银牌",""))</f>
         <v/>
       </c>
       <c r="J4" s="18">
@@ -2638,46 +2642,46 @@
       </c>
       <c r="K4" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="L4" s="18">
         <f>_xlfn.XLOOKUP(B4,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="M4" s="21">
-        <f ca="1" t="shared" ref="M4:M18" si="3">K4/J4</f>
-        <v>0.024</v>
+        <f ca="1" t="shared" ref="M4:M18" si="2">K4/J4</f>
+        <v>0.0516</v>
       </c>
       <c r="N4" s="21">
         <f ca="1">K4/(J4/Z4*W$4)</f>
-        <v>0.0826666666666667</v>
+        <v>0.31992</v>
       </c>
       <c r="O4" s="23">
-        <f ca="1" t="shared" ref="O4:O9" si="4">VLOOKUP(B:B,X:Z,3,0)</f>
-        <v>9</v>
+        <f ca="1" t="shared" ref="O4:O9" si="3">VLOOKUP(B:B,X:Z,3,0)</f>
+        <v>7</v>
       </c>
       <c r="P4" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="Q4" s="19">
         <v>15</v>
       </c>
       <c r="R4" s="24">
         <f>_xlfn.XLOOKUP(B4,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4" s="25">
-        <f t="shared" ref="S4:S19" si="5">R4/Q4</f>
-        <v>0</v>
+        <f t="shared" ref="S4:S19" si="4">R4/Q4</f>
+        <v>0.133333333333333</v>
       </c>
       <c r="V4" s="26" t="str">
         <f ca="1">MONTH(TODAY()-1)&amp;"月"</f>
-        <v>7月</v>
+        <v>8月</v>
       </c>
       <c r="W4" s="26">
         <f ca="1">DAY(TODAY()-1)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X4" s="26"/>
       <c r="Y4" s="27"/>
@@ -2692,14 +2696,14 @@
         <v>23</v>
       </c>
       <c r="C5" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="19">
         <f>_xlfn.XLOOKUP(B5,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
       <c r="E5" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E4:E18" si="5">D5/C5</f>
         <v>0</v>
       </c>
       <c r="F5" s="21">
@@ -2711,11 +2715,11 @@
         <v>0</v>
       </c>
       <c r="H5" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>是</v>
+      </c>
+      <c r="I5" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>是</v>
-      </c>
-      <c r="I5" s="18" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J5" s="18">
@@ -2723,27 +2727,27 @@
       </c>
       <c r="K5" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>1792.67</v>
+        <v>1145</v>
       </c>
       <c r="L5" s="18">
         <f>_xlfn.XLOOKUP(B5,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>1366.67</v>
+        <v>0</v>
       </c>
       <c r="M5" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.717068</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.458</v>
       </c>
       <c r="N5" s="21">
         <f ca="1">K5/(J5/Z4*W$4)</f>
-        <v>2.46990088888889</v>
+        <v>2.8396</v>
       </c>
       <c r="O5" s="23">
-        <f ca="1" t="shared" si="4"/>
+        <f ca="1" t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="P5" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>3489</v>
+        <v>1587</v>
       </c>
       <c r="Q5" s="19">
         <v>15</v>
@@ -2753,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="S5" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -2763,14 +2767,14 @@
         <v>24</v>
       </c>
       <c r="C6" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D6" s="19">
         <f>_xlfn.XLOOKUP(B6,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
       <c r="E6" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F6" s="21">
@@ -2782,11 +2786,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>是</v>
+      </c>
+      <c r="I6" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>是</v>
-      </c>
-      <c r="I6" s="18" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J6" s="18">
@@ -2794,27 +2798,27 @@
       </c>
       <c r="K6" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>772.33</v>
+        <v>29</v>
       </c>
       <c r="L6" s="18">
         <f>_xlfn.XLOOKUP(B6,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>316.83</v>
+        <v>0</v>
       </c>
       <c r="M6" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.308932</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.0116</v>
       </c>
       <c r="N6" s="21">
         <f ca="1">K6/(J6/Z4*W$4)</f>
-        <v>1.06409911111111</v>
+        <v>0.07192</v>
       </c>
       <c r="O6" s="23">
-        <f ca="1" t="shared" si="4"/>
-        <v>3</v>
+        <f ca="1" t="shared" si="3"/>
+        <v>9</v>
       </c>
       <c r="P6" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>658.5</v>
+        <v>43.5</v>
       </c>
       <c r="Q6" s="19">
         <v>15</v>
@@ -2824,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -2834,30 +2838,30 @@
         <v>25</v>
       </c>
       <c r="C7" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D7" s="19">
         <f>_xlfn.XLOOKUP(B7,高套!A:A,高套!B:B,0)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E7" s="20">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="F7" s="21">
         <f ca="1">D7/(C7/Z4*W$4)</f>
-        <v>0.516666666666667</v>
+        <v>0</v>
       </c>
       <c r="G7" s="18">
         <f>_xlfn.XLOOKUP(B7,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="H7" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>是</v>
+      </c>
+      <c r="I7" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>否</v>
-      </c>
-      <c r="I7" s="18" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J7" s="18">
@@ -2865,38 +2869,38 @@
       </c>
       <c r="K7" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>-246</v>
+        <v>0</v>
       </c>
       <c r="L7" s="18">
         <f>_xlfn.XLOOKUP(B7,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>-501</v>
+        <v>0</v>
       </c>
       <c r="M7" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>-0.0984</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="N7" s="21">
         <f ca="1">K7/(J7/Z4*W$4)</f>
-        <v>-0.338933333333333</v>
+        <v>0</v>
       </c>
       <c r="O7" s="23">
-        <f ca="1" t="shared" si="4"/>
-        <v>11</v>
+        <f ca="1" t="shared" si="3"/>
+        <v>10</v>
       </c>
       <c r="P7" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>-98</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="19">
         <v>15</v>
       </c>
       <c r="R7" s="24">
         <f>_xlfn.XLOOKUP(B7,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S7" s="25">
-        <f t="shared" si="5"/>
-        <v>0.2</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="16.5" customHeight="1" spans="1:26">
@@ -2905,14 +2909,14 @@
         <v>26</v>
       </c>
       <c r="C8" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" s="19">
         <f>_xlfn.XLOOKUP(B8,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
       <c r="E8" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F8" s="21">
@@ -2921,14 +2925,14 @@
       </c>
       <c r="G8" s="18">
         <f>_xlfn.XLOOKUP(B8,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H8" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>是</v>
+      </c>
+      <c r="I8" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>是</v>
-      </c>
-      <c r="I8" s="18" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J8" s="18">
@@ -2936,27 +2940,27 @@
       </c>
       <c r="K8" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="L8" s="18">
         <f>_xlfn.XLOOKUP(B8,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>5.5</v>
+        <v>-1941.01</v>
       </c>
       <c r="M8" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.0812</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.0164</v>
       </c>
       <c r="N8" s="21">
         <f ca="1">K8/(J8/Z4*W$4)</f>
-        <v>0.279688888888889</v>
+        <v>0.10168</v>
       </c>
       <c r="O8" s="23">
-        <f ca="1" t="shared" si="4"/>
+        <f ca="1" t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="P8" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>913.5</v>
+        <v>61.5</v>
       </c>
       <c r="Q8" s="19">
         <v>15</v>
@@ -2966,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X8" s="28" t="s">
@@ -2974,11 +2978,11 @@
       </c>
       <c r="Y8">
         <f ca="1" t="shared" ref="Y8:Y19" si="6">VLOOKUP(X:X,B:K,10,0)</f>
-        <v>772.33</v>
+        <v>29</v>
       </c>
       <c r="Z8">
         <f ca="1" t="shared" ref="Z8:Z19" si="7">RANK(Y8,Y$8:Y$19,0)</f>
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" ht="16.5" customHeight="1" spans="1:26">
@@ -2987,14 +2991,14 @@
         <v>27</v>
       </c>
       <c r="C9" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D9" s="19">
         <f>_xlfn.XLOOKUP(B9,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
       <c r="E9" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F9" s="21">
@@ -3006,11 +3010,11 @@
         <v>0</v>
       </c>
       <c r="H9" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v>是</v>
+      </c>
+      <c r="I9" s="18" t="str">
         <f t="shared" si="1"/>
-        <v>是</v>
-      </c>
-      <c r="I9" s="18" t="str">
-        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J9" s="18">
@@ -3018,27 +3022,27 @@
       </c>
       <c r="K9" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>295.33</v>
+        <v>228</v>
       </c>
       <c r="L9" s="18">
         <f>_xlfn.XLOOKUP(B9,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>-1648.67</v>
+        <v>0</v>
       </c>
       <c r="M9" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.118132</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.0912</v>
       </c>
       <c r="N9" s="21">
         <f ca="1">K9/(J9/Z4*W$4)</f>
-        <v>0.406899111111111</v>
+        <v>0.56544</v>
       </c>
       <c r="O9" s="23">
-        <f ca="1" t="shared" si="4"/>
-        <v>6</v>
+        <f ca="1" t="shared" si="3"/>
+        <v>4</v>
       </c>
       <c r="P9" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>230.5</v>
+        <v>88.5</v>
       </c>
       <c r="Q9" s="19">
         <v>15</v>
@@ -3048,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X9" s="28" t="s">
@@ -3056,11 +3060,11 @@
       </c>
       <c r="Y9">
         <f ca="1" t="shared" si="6"/>
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="Z9">
         <f ca="1" t="shared" si="7"/>
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="16.5" customHeight="1" spans="1:26">
@@ -3070,23 +3074,23 @@
       </c>
       <c r="C10" s="29">
         <f>SUM(C4:C9)</f>
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D10" s="29">
         <f>SUM(D4:D9)</f>
         <v>1.5</v>
       </c>
       <c r="E10" s="30">
-        <f t="shared" si="0"/>
-        <v>0.025</v>
+        <f t="shared" si="5"/>
+        <v>0.0178571428571429</v>
       </c>
       <c r="F10" s="30">
         <f ca="1">D10/(C10/Z4*W$4)</f>
-        <v>0.0861111111111111</v>
+        <v>0.110714285714286</v>
       </c>
       <c r="G10" s="29">
         <f>SUM(G4:G9)</f>
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="H10" s="30"/>
       <c r="I10" s="31"/>
@@ -3096,19 +3100,19 @@
       </c>
       <c r="K10" s="29">
         <f ca="1">SUM(K4:K9)</f>
-        <v>2877.33</v>
+        <v>1572</v>
       </c>
       <c r="L10" s="29">
         <f>SUM(L4:L9)</f>
-        <v>-361.67</v>
+        <v>-1877.01</v>
       </c>
       <c r="M10" s="30">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.191822</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.1048</v>
       </c>
       <c r="N10" s="30">
         <f ca="1">K10/(J10/Z4*W$4)</f>
-        <v>0.660720222222222</v>
+        <v>0.64976</v>
       </c>
       <c r="O10" s="29"/>
       <c r="P10" s="31"/>
@@ -3118,18 +3122,18 @@
       </c>
       <c r="R10" s="29">
         <f>SUM(R4:R9)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" s="32">
-        <f t="shared" si="5"/>
-        <v>0.0333333333333333</v>
+        <f t="shared" si="4"/>
+        <v>0.0222222222222222</v>
       </c>
       <c r="X10" s="28" t="s">
         <v>23</v>
       </c>
       <c r="Y10">
         <f ca="1" t="shared" si="6"/>
-        <v>1792.67</v>
+        <v>1145</v>
       </c>
       <c r="Z10">
         <f ca="1" t="shared" si="7"/>
@@ -3144,14 +3148,14 @@
         <v>30</v>
       </c>
       <c r="C11" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D11" s="19">
         <f>_xlfn.XLOOKUP(B11,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
       <c r="E11" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F11" s="21">
@@ -3175,27 +3179,27 @@
       </c>
       <c r="K11" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>239</v>
+        <v>468.17</v>
       </c>
       <c r="L11" s="18">
         <f>_xlfn.XLOOKUP(B11,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>961</v>
+        <v>155.17</v>
       </c>
       <c r="M11" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.0956</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.187268</v>
       </c>
       <c r="N11" s="21">
         <f ca="1">K11/(J11/Z4*W$4)</f>
-        <v>0.329288888888889</v>
+        <v>1.1610616</v>
       </c>
       <c r="O11" s="23">
         <f ca="1" t="shared" ref="O11:O16" si="10">VLOOKUP(B:B,X:Z,3,0)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P11" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>0</v>
+        <v>637.34</v>
       </c>
       <c r="Q11" s="19">
         <v>15</v>
@@ -3205,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X11" s="28" t="s">
@@ -3213,11 +3217,11 @@
       </c>
       <c r="Y11">
         <f ca="1" t="shared" si="6"/>
-        <v>-246</v>
+        <v>0</v>
       </c>
       <c r="Z11">
         <f ca="1" t="shared" si="7"/>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" ht="16.5" customHeight="1" spans="1:26">
@@ -3226,27 +3230,27 @@
         <v>31</v>
       </c>
       <c r="C12" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D12" s="19">
         <f>_xlfn.XLOOKUP(B12,高套!A:A,高套!B:B,0)</f>
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="E12" s="20">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
+        <f t="shared" si="5"/>
+        <v>0.321428571428571</v>
       </c>
       <c r="F12" s="21">
         <f ca="1">D12/(C12/Z4*W$4)</f>
-        <v>0.344444444444444</v>
+        <v>1.99285714285714</v>
       </c>
       <c r="G12" s="18">
         <f>_xlfn.XLOOKUP(B12,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="H12" s="22" t="str">
         <f t="shared" si="8"/>
-        <v>是</v>
+        <v>否</v>
       </c>
       <c r="I12" s="18" t="str">
         <f t="shared" si="9"/>
@@ -3257,27 +3261,27 @@
       </c>
       <c r="K12" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>744.5</v>
+        <v>580</v>
       </c>
       <c r="L12" s="18">
         <f>_xlfn.XLOOKUP(B12,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>1112.49</v>
+        <v>269</v>
       </c>
       <c r="M12" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.2978</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.232</v>
       </c>
       <c r="N12" s="21">
         <f ca="1">K12/(J12/Z4*W$4)</f>
-        <v>1.02575555555556</v>
+        <v>1.4384</v>
       </c>
       <c r="O12" s="23">
         <f ca="1" t="shared" si="10"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P12" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>892.5</v>
+        <v>732</v>
       </c>
       <c r="Q12" s="19">
         <v>15</v>
@@ -3287,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X12" s="28" t="s">
@@ -3295,7 +3299,7 @@
       </c>
       <c r="Y12">
         <f ca="1" t="shared" si="6"/>
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="Z12">
         <f ca="1" t="shared" si="7"/>
@@ -3308,14 +3312,14 @@
         <v>32</v>
       </c>
       <c r="C13" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D13" s="19">
         <f>_xlfn.XLOOKUP(B13,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
       <c r="E13" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F13" s="21">
@@ -3346,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="21">
-        <f ca="1" t="shared" si="3"/>
+        <f ca="1" t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N13" s="21">
@@ -3369,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="S13" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X13" s="28" t="s">
@@ -3377,11 +3381,11 @@
       </c>
       <c r="Y13">
         <f ca="1" t="shared" si="6"/>
-        <v>295.33</v>
+        <v>228</v>
       </c>
       <c r="Z13">
         <f ca="1" t="shared" si="7"/>
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" ht="16.5" customHeight="1" spans="1:26">
@@ -3390,23 +3394,23 @@
         <v>33</v>
       </c>
       <c r="C14" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D14" s="19">
         <f>_xlfn.XLOOKUP(B14,高套!A:A,高套!B:B,0)</f>
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="E14" s="20">
-        <f t="shared" si="0"/>
-        <v>0.25</v>
+        <f t="shared" si="5"/>
+        <v>0.285714285714286</v>
       </c>
       <c r="F14" s="21">
         <f ca="1">D14/(C14/Z4*W$4)</f>
-        <v>0.861111111111111</v>
+        <v>1.77142857142857</v>
       </c>
       <c r="G14" s="18">
         <f>_xlfn.XLOOKUP(B14,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>6</v>
+        <v>10.35</v>
       </c>
       <c r="H14" s="22" t="str">
         <f t="shared" si="8"/>
@@ -3421,49 +3425,49 @@
       </c>
       <c r="K14" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>872</v>
+        <v>163</v>
       </c>
       <c r="L14" s="18">
         <f>_xlfn.XLOOKUP(B14,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>402.56</v>
+        <v>636.48</v>
       </c>
       <c r="M14" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.3488</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.0652</v>
       </c>
       <c r="N14" s="21">
         <f ca="1">K14/(J14/Z4*W$4)</f>
-        <v>1.20142222222222</v>
+        <v>0.40424</v>
       </c>
       <c r="O14" s="23">
         <f ca="1" t="shared" si="10"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P14" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>3450</v>
+        <v>253.5</v>
       </c>
       <c r="Q14" s="19">
         <v>15</v>
       </c>
       <c r="R14" s="24">
         <f>_xlfn.XLOOKUP(B14,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S14" s="25">
-        <f t="shared" si="5"/>
-        <v>0.333333333333333</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="X14" s="28" t="s">
         <v>30</v>
       </c>
       <c r="Y14">
         <f ca="1" t="shared" si="6"/>
-        <v>239</v>
+        <v>468.17</v>
       </c>
       <c r="Z14">
         <f ca="1" t="shared" si="7"/>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:26">
@@ -3472,14 +3476,14 @@
         <v>34</v>
       </c>
       <c r="C15" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D15" s="19">
         <f>_xlfn.XLOOKUP(B15,高套!A:A,高套!B:B,0)</f>
         <v>0</v>
       </c>
       <c r="E15" s="20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F15" s="21">
@@ -3488,7 +3492,7 @@
       </c>
       <c r="G15" s="18">
         <f>_xlfn.XLOOKUP(B15,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="H15" s="22" t="str">
         <f t="shared" si="8"/>
@@ -3503,27 +3507,27 @@
       </c>
       <c r="K15" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>698</v>
+        <v>154</v>
       </c>
       <c r="L15" s="18">
         <f>_xlfn.XLOOKUP(B15,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="M15" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.2792</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.0616</v>
       </c>
       <c r="N15" s="21">
         <f ca="1">K15/(J15/Z4*W$4)</f>
-        <v>0.961688888888889</v>
+        <v>0.38192</v>
       </c>
       <c r="O15" s="23">
         <f ca="1" t="shared" si="10"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1047</v>
+        <v>539</v>
       </c>
       <c r="Q15" s="19">
         <v>15</v>
@@ -3533,7 +3537,7 @@
         <v>0</v>
       </c>
       <c r="S15" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X15" s="28" t="s">
@@ -3541,11 +3545,11 @@
       </c>
       <c r="Y15">
         <f ca="1" t="shared" si="6"/>
-        <v>744.5</v>
+        <v>580</v>
       </c>
       <c r="Z15">
         <f ca="1" t="shared" si="7"/>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:26">
@@ -3554,23 +3558,23 @@
         <v>35</v>
       </c>
       <c r="C16" s="18">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D16" s="19">
         <f>_xlfn.XLOOKUP(B16,高套!A:A,高套!B:B,0)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="E16" s="20">
-        <f t="shared" si="0"/>
-        <v>0.15</v>
+        <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="F16" s="21">
         <f ca="1">D16/(C16/Z4*W$4)</f>
-        <v>0.516666666666667</v>
+        <v>0</v>
       </c>
       <c r="G16" s="18">
         <f>_xlfn.XLOOKUP(B16,红黄牌高套!A:A,红黄牌高套!B:B,0)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H16" s="22" t="str">
         <f t="shared" si="8"/>
@@ -3585,19 +3589,19 @@
       </c>
       <c r="K16" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>-1647.54</v>
+        <v>-1</v>
       </c>
       <c r="L16" s="18">
         <f>_xlfn.XLOOKUP(B16,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>-1737.54</v>
+        <v>794</v>
       </c>
       <c r="M16" s="21">
-        <f ca="1" t="shared" si="3"/>
-        <v>-0.659016</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>-0.0004</v>
       </c>
       <c r="N16" s="21">
         <f ca="1">K16/(J16/Z4*W$4)</f>
-        <v>-2.269944</v>
+        <v>-0.00248</v>
       </c>
       <c r="O16" s="23">
         <f ca="1" t="shared" si="10"/>
@@ -3605,7 +3609,7 @@
       </c>
       <c r="P16" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>-2471.31</v>
+        <v>98.5</v>
       </c>
       <c r="Q16" s="19">
         <v>15</v>
@@ -3615,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="25">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="X16" s="28" t="s">
@@ -3637,23 +3641,23 @@
       </c>
       <c r="C17" s="35">
         <f>SUM(C11:C16)</f>
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D17" s="35">
         <f>SUM(D11:D16)</f>
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="E17" s="36">
-        <f t="shared" si="0"/>
-        <v>0.0833333333333333</v>
+        <f t="shared" si="5"/>
+        <v>0.101190476190476</v>
       </c>
       <c r="F17" s="30">
         <f ca="1">D17/(C17/Z4*W$4)</f>
-        <v>0.287037037037037</v>
+        <v>0.627380952380952</v>
       </c>
       <c r="G17" s="35">
         <f>SUM(G11:G16)</f>
-        <v>8.5</v>
+        <v>19.42</v>
       </c>
       <c r="H17" s="36"/>
       <c r="I17" s="37"/>
@@ -3663,19 +3667,19 @@
       </c>
       <c r="K17" s="35">
         <f ca="1">SUM(K11:K16)</f>
-        <v>905.96</v>
+        <v>1364.17</v>
       </c>
       <c r="L17" s="35">
         <f>SUM(L11:L16)</f>
-        <v>738.51</v>
+        <v>1912.65</v>
       </c>
       <c r="M17" s="36">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.0603973333333333</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.0909446666666667</v>
       </c>
       <c r="N17" s="36">
         <f ca="1">K17/(J17/Z4*W$4)</f>
-        <v>0.208035259259259</v>
+        <v>0.563856933333333</v>
       </c>
       <c r="O17" s="35"/>
       <c r="P17" s="37"/>
@@ -3685,22 +3689,22 @@
       </c>
       <c r="R17" s="35">
         <f>SUM(R11:R16)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S17" s="32">
-        <f t="shared" si="5"/>
-        <v>0.0555555555555556</v>
+        <f t="shared" si="4"/>
+        <v>0</v>
       </c>
       <c r="X17" s="28" t="s">
         <v>33</v>
       </c>
       <c r="Y17">
         <f ca="1" t="shared" si="6"/>
-        <v>872</v>
+        <v>163</v>
       </c>
       <c r="Z17">
         <f ca="1" t="shared" si="7"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:26">
@@ -3709,23 +3713,23 @@
       </c>
       <c r="B18" s="39"/>
       <c r="C18" s="40">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="D18" s="41">
         <f>_xlfn.XLOOKUP("端州",高套!A:A,高套!B:B,0)</f>
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="E18" s="42">
-        <f t="shared" si="0"/>
-        <v>0.0492424242424242</v>
+        <f t="shared" si="5"/>
+        <v>0.0606060606060606</v>
       </c>
       <c r="F18" s="43">
         <f ca="1">D18/(C18/Z4*W$4)</f>
-        <v>0.169612794612795</v>
+        <v>0.375757575757576</v>
       </c>
       <c r="G18" s="44">
         <f>G10+G17</f>
-        <v>13.5</v>
+        <v>20.92</v>
       </c>
       <c r="H18" s="43"/>
       <c r="I18" s="45"/>
@@ -3735,19 +3739,19 @@
       </c>
       <c r="K18" s="40">
         <f ca="1">K10+K17</f>
-        <v>3783.29</v>
+        <v>2936.17</v>
       </c>
       <c r="L18" s="47">
         <f>L10+L17</f>
-        <v>376.84</v>
+        <v>35.6400000000001</v>
       </c>
       <c r="M18" s="48">
-        <f ca="1" t="shared" si="3"/>
-        <v>0.126109666666667</v>
+        <f ca="1" t="shared" si="2"/>
+        <v>0.0978723333333333</v>
       </c>
       <c r="N18" s="49">
         <f ca="1">K18/(J18/Z4*W$4)</f>
-        <v>0.434377740740741</v>
+        <v>0.606808466666667</v>
       </c>
       <c r="O18" s="50"/>
       <c r="P18" s="51" t="s">
@@ -3758,18 +3762,18 @@
       </c>
       <c r="R18" s="53">
         <f>R10+R17</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S18" s="25">
-        <f t="shared" si="5"/>
-        <v>0.0380952380952381</v>
+        <f t="shared" si="4"/>
+        <v>0.00952380952380952</v>
       </c>
       <c r="X18" s="54" t="s">
         <v>35</v>
       </c>
       <c r="Y18">
         <f ca="1" t="shared" si="6"/>
-        <v>-1647.54</v>
+        <v>-1</v>
       </c>
       <c r="Z18">
         <f ca="1" t="shared" si="7"/>
@@ -3788,34 +3792,34 @@
       <c r="I19" s="56"/>
       <c r="J19" s="55"/>
       <c r="K19" s="55"/>
-      <c r="L19" s="57"/>
+      <c r="L19" s="56"/>
       <c r="M19" s="56"/>
       <c r="N19" s="34"/>
-      <c r="O19" s="58"/>
+      <c r="O19" s="57"/>
       <c r="P19" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="Q19" s="59">
+      <c r="Q19" s="58">
         <v>310</v>
       </c>
-      <c r="R19" s="60">
+      <c r="R19" s="59">
         <f>_xlfn.XLOOKUP(P19,全光组网!A:A,全光组网!B:B,0)</f>
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="S19" s="25">
-        <f t="shared" si="5"/>
-        <v>0.190322580645161</v>
-      </c>
-      <c r="X19" s="61" t="s">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="X19" s="60" t="s">
         <v>34</v>
       </c>
       <c r="Y19">
         <f ca="1" t="shared" si="6"/>
-        <v>698</v>
+        <v>154</v>
       </c>
       <c r="Z19">
         <f ca="1" t="shared" si="7"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:26">
@@ -4175,7 +4179,7 @@
       </c>
       <c r="G26" s="18">
         <f>高装高套!B8</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H26" s="21" t="s">
         <v>41</v>
@@ -4186,7 +4190,7 @@
       </c>
       <c r="K26" s="18">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="L26" s="21"/>
       <c r="M26" s="21" t="s">
@@ -4200,7 +4204,7 @@
       </c>
       <c r="P26" s="23">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1055.5</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="19" t="s">
         <v>41</v>
@@ -4269,7 +4273,7 @@
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:26">
-      <c r="A28" s="62" t="s">
+      <c r="A28" s="61" t="s">
         <v>49</v>
       </c>
       <c r="B28" s="14"/>
@@ -4287,7 +4291,7 @@
       </c>
       <c r="G28" s="18">
         <f>SUM(G20:G27)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="H28" s="21" t="s">
         <v>41</v>
@@ -4298,7 +4302,7 @@
       </c>
       <c r="K28" s="18">
         <f ca="1">SUM(K20:K27)</f>
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="L28" s="21"/>
       <c r="M28" s="21" t="s">
@@ -4332,675 +4336,675 @@
       <c r="P30"/>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:26">
-      <c r="A31" s="63" t="str">
+      <c r="A31" s="62" t="str">
         <f>"高装高套目标完成情况"</f>
         <v>高装高套目标完成情况</v>
       </c>
       <c r="G31"/>
-      <c r="H31" s="64" t="str">
+      <c r="H31" s="63" t="str">
         <f>"全光任务完成情况"</f>
         <v>全光任务完成情况</v>
       </c>
-      <c r="N31" s="65" t="str">
+      <c r="N31" s="64" t="str">
         <f>"区县目标完成情况"</f>
         <v>区县目标完成情况</v>
       </c>
     </row>
     <row r="32" ht="33" customHeight="1" spans="1:26">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="B32" s="66" t="s">
+      <c r="B32" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="66" t="s">
+      <c r="D32" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="66" t="s">
+      <c r="E32" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="66" t="s">
+      <c r="F32" s="65" t="s">
         <v>17</v>
       </c>
       <c r="G32"/>
-      <c r="H32" s="67" t="s">
+      <c r="H32" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="67" t="s">
+      <c r="I32" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="J32" s="67" t="s">
+      <c r="J32" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="K32" s="68" t="s">
+      <c r="K32" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="L32" s="67" t="s">
+      <c r="L32" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="N32" s="69" t="s">
+      <c r="N32" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="O32" s="69" t="s">
+      <c r="O32" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="P32" s="69" t="s">
+      <c r="P32" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="Q32" s="70" t="s">
+      <c r="Q32" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="R32" s="69" t="s">
+      <c r="R32" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="S32" s="70" t="s">
+      <c r="S32" s="69" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A33" s="71" t="s">
+      <c r="A33" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="72" t="str">
+      <c r="B33" s="71" t="str">
         <f>高装高套!A2</f>
         <v>陈梓铭</v>
       </c>
-      <c r="C33" s="72">
+      <c r="C33" s="71">
         <v>3.5</v>
       </c>
-      <c r="D33" s="72">
+      <c r="D33" s="71">
         <f>高装高套!B2</f>
         <v>0</v>
       </c>
-      <c r="E33" s="73">
+      <c r="E33" s="72">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F33" s="73">
+      <c r="F33" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G33"/>
-      <c r="H33" s="74" t="s">
+      <c r="H33" s="73" t="s">
         <v>59</v>
       </c>
-      <c r="I33" s="75" t="s">
+      <c r="I33" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="J33" s="75">
+      <c r="J33" s="74">
         <v>60</v>
       </c>
-      <c r="K33" s="75">
+      <c r="K33" s="74">
         <f>交付高装!D2</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="75">
+        <f>交付高装!E2</f>
+        <v>0</v>
+      </c>
+      <c r="N33" s="76" t="s">
+        <v>38</v>
+      </c>
+      <c r="O33" s="77">
+        <v>5.3</v>
+      </c>
+      <c r="P33" s="77">
+        <f ca="1">ROUND(_xlfn.XLOOKUP(N33,高套!A:A,高套!B:B,0)/W4,2)</f>
+        <v>2</v>
+      </c>
+      <c r="Q33" s="77">
+        <f>_xlfn.XLOOKUP(N33,净增积分!A:A,净增积分!B:B,0)</f>
+        <v>1122.06</v>
+      </c>
+      <c r="R33" s="78">
+        <f ca="1" t="shared" ref="R33:R42" si="11">P33/O33</f>
+        <v>0.377358490566038</v>
+      </c>
+      <c r="S33" s="79">
+        <f ca="1">RANK(R33,R33:R41)</f>
         <v>3</v>
       </c>
-      <c r="L33" s="76">
-        <f>交付高装!E2</f>
-        <v>0.05</v>
-      </c>
-      <c r="N33" s="77" t="s">
-        <v>38</v>
-      </c>
-      <c r="O33" s="78">
-        <v>4.25</v>
-      </c>
-      <c r="P33" s="78">
-        <f ca="1">ROUND(_xlfn.XLOOKUP(N33,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>0.72</v>
-      </c>
-      <c r="Q33" s="78">
-        <f>_xlfn.XLOOKUP(N33,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>1294.22</v>
-      </c>
-      <c r="R33" s="79">
-        <f ca="1" t="shared" ref="R33:R42" si="11">P33/O33</f>
-        <v>0.169411764705882</v>
-      </c>
-      <c r="S33" s="80">
-        <f ca="1">RANK(R33,R33:R41)</f>
-        <v>9</v>
-      </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A34" s="81"/>
-      <c r="B34" s="82" t="str">
+      <c r="A34" s="80"/>
+      <c r="B34" s="81" t="str">
         <f>高装高套!A3</f>
         <v>程庆德</v>
       </c>
-      <c r="C34" s="82">
+      <c r="C34" s="81">
         <v>3.5</v>
       </c>
-      <c r="D34" s="82">
+      <c r="D34" s="81">
         <f>高装高套!B3</f>
         <v>0</v>
       </c>
-      <c r="E34" s="83">
+      <c r="E34" s="82">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F34" s="83">
+      <c r="F34" s="82">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G34"/>
-      <c r="H34" s="84"/>
-      <c r="I34" s="75" t="s">
+      <c r="H34" s="83"/>
+      <c r="I34" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="J34" s="75">
+      <c r="J34" s="74">
         <v>60</v>
       </c>
-      <c r="K34" s="75">
+      <c r="K34" s="74">
         <f>交付高装!D3</f>
         <v>0</v>
       </c>
-      <c r="L34" s="76">
+      <c r="L34" s="75">
         <f>交付高装!E3</f>
         <v>0</v>
       </c>
-      <c r="N34" s="77" t="s">
+      <c r="N34" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="O34" s="85">
-        <v>5.75</v>
-      </c>
-      <c r="P34" s="85">
+      <c r="O34" s="84">
+        <v>5.7</v>
+      </c>
+      <c r="P34" s="84">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N34,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>2.56</v>
-      </c>
-      <c r="Q34" s="85">
+        <v>5.8</v>
+      </c>
+      <c r="Q34" s="84">
         <f>_xlfn.XLOOKUP(N34,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>377.74</v>
-      </c>
-      <c r="R34" s="79">
+        <v>-5728.86</v>
+      </c>
+      <c r="R34" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>0.445217391304348</v>
-      </c>
-      <c r="S34" s="86">
+        <v>1.01754385964912</v>
+      </c>
+      <c r="S34" s="85">
         <f ca="1">RANK(R34,R33:R41)</f>
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A35" s="81"/>
-      <c r="B35" s="72" t="str">
+      <c r="A35" s="80"/>
+      <c r="B35" s="71" t="str">
         <f>高装高套!A4</f>
         <v>刘奇峻</v>
       </c>
-      <c r="C35" s="72">
+      <c r="C35" s="71">
         <v>3.5</v>
       </c>
-      <c r="D35" s="72">
+      <c r="D35" s="71">
         <f>高装高套!B4</f>
         <v>0</v>
       </c>
-      <c r="E35" s="73">
+      <c r="E35" s="72">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F35" s="73">
+      <c r="F35" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G35"/>
-      <c r="H35" s="84"/>
-      <c r="I35" s="87" t="s">
+      <c r="H35" s="83"/>
+      <c r="I35" s="86" t="s">
         <v>63</v>
       </c>
-      <c r="J35" s="75">
+      <c r="J35" s="74">
         <v>60</v>
       </c>
-      <c r="K35" s="75">
+      <c r="K35" s="74">
         <f>交付高装!D4</f>
+        <v>2</v>
+      </c>
+      <c r="L35" s="75">
+        <f>交付高装!E4</f>
+        <v>0.0333333333333333</v>
+      </c>
+      <c r="N35" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="O35" s="77">
         <v>5</v>
       </c>
-      <c r="L35" s="76">
-        <f>交付高装!E4</f>
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="N35" s="77" t="s">
-        <v>64</v>
-      </c>
-      <c r="O35" s="78">
-        <v>3.52</v>
-      </c>
-      <c r="P35" s="78">
+      <c r="P35" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N35,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>2.97</v>
-      </c>
-      <c r="Q35" s="78">
+        <v>1.33</v>
+      </c>
+      <c r="Q35" s="77">
         <f>_xlfn.XLOOKUP(N35,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>320.35</v>
-      </c>
-      <c r="R35" s="79">
+        <v>-594.98</v>
+      </c>
+      <c r="R35" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>0.84375</v>
-      </c>
-      <c r="S35" s="80">
+        <v>0.266</v>
+      </c>
+      <c r="S35" s="79">
         <f ca="1">RANK(R35,R33:R41)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A36" s="81"/>
-      <c r="B36" s="82" t="str">
+      <c r="A36" s="80"/>
+      <c r="B36" s="81" t="str">
         <f>高装高套!A5</f>
         <v>龙家宝</v>
       </c>
-      <c r="C36" s="82">
+      <c r="C36" s="81">
         <v>3.5</v>
       </c>
-      <c r="D36" s="82">
+      <c r="D36" s="81">
         <f>高装高套!B5</f>
         <v>0</v>
       </c>
-      <c r="E36" s="83">
+      <c r="E36" s="82">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F36" s="83">
+      <c r="F36" s="82">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G36"/>
-      <c r="H36" s="84"/>
-      <c r="I36" s="75" t="s">
+      <c r="H36" s="83"/>
+      <c r="I36" s="74" t="s">
         <v>65</v>
       </c>
-      <c r="J36" s="75">
+      <c r="J36" s="74">
         <v>45</v>
       </c>
-      <c r="K36" s="75">
+      <c r="K36" s="74">
         <f>交付高装!D5</f>
         <v>0</v>
       </c>
-      <c r="L36" s="76">
+      <c r="L36" s="75">
         <f>交付高装!E5</f>
         <v>0</v>
       </c>
-      <c r="N36" s="77" t="s">
+      <c r="N36" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="O36" s="85">
-        <v>3.97</v>
-      </c>
-      <c r="P36" s="85">
+      <c r="O36" s="84">
+        <v>5</v>
+      </c>
+      <c r="P36" s="84">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N36,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>2.24</v>
-      </c>
-      <c r="Q36" s="85">
+        <v>1.4</v>
+      </c>
+      <c r="Q36" s="84">
         <f>_xlfn.XLOOKUP(N36,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>2729.87</v>
-      </c>
-      <c r="R36" s="79">
+        <v>2163.12</v>
+      </c>
+      <c r="R36" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>0.564231738035264</v>
-      </c>
-      <c r="S36" s="86">
+        <v>0.28</v>
+      </c>
+      <c r="S36" s="85">
         <f ca="1">RANK(R36,R33:R41)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A37" s="81"/>
-      <c r="B37" s="72" t="str">
+      <c r="A37" s="80"/>
+      <c r="B37" s="71" t="str">
         <f>高装高套!A6</f>
         <v>罗紫杰</v>
       </c>
-      <c r="C37" s="72">
+      <c r="C37" s="71">
         <v>3.5</v>
       </c>
-      <c r="D37" s="72">
+      <c r="D37" s="71">
         <f>高装高套!B6</f>
         <v>0</v>
       </c>
-      <c r="E37" s="73">
+      <c r="E37" s="72">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F37" s="73">
+      <c r="F37" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G37"/>
-      <c r="H37" s="88" t="s">
+      <c r="H37" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="I37" s="89" t="s">
+      <c r="I37" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="J37" s="90">
+      <c r="J37" s="89">
         <v>30</v>
       </c>
-      <c r="K37" s="90">
+      <c r="K37" s="89">
         <f>交付高装!D6</f>
         <v>0</v>
       </c>
-      <c r="L37" s="91">
+      <c r="L37" s="90">
         <f>交付高装!E6</f>
         <v>0</v>
       </c>
-      <c r="N37" s="77" t="s">
+      <c r="N37" s="76" t="s">
         <v>67</v>
       </c>
-      <c r="O37" s="78">
-        <v>2.38</v>
-      </c>
-      <c r="P37" s="78">
+      <c r="O37" s="77">
+        <v>3.4</v>
+      </c>
+      <c r="P37" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N37,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>2.96</v>
-      </c>
-      <c r="Q37" s="78">
+        <v>0.2</v>
+      </c>
+      <c r="Q37" s="77">
         <f>_xlfn.XLOOKUP(N37,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>-5280.93</v>
-      </c>
-      <c r="R37" s="79">
+        <v>-18358.2</v>
+      </c>
+      <c r="R37" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>1.2436974789916</v>
-      </c>
-      <c r="S37" s="80">
+        <v>0.0588235294117647</v>
+      </c>
+      <c r="S37" s="79">
         <f ca="1">RANK(R37,R33:R41)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A38" s="81"/>
-      <c r="B38" s="82" t="str">
+      <c r="A38" s="80"/>
+      <c r="B38" s="81" t="str">
         <f>高装高套!A7</f>
         <v>莫健铭</v>
       </c>
-      <c r="C38" s="82">
+      <c r="C38" s="81">
         <v>3.5</v>
       </c>
-      <c r="D38" s="82">
+      <c r="D38" s="81">
         <f>高装高套!B7</f>
         <v>0</v>
       </c>
-      <c r="E38" s="83">
+      <c r="E38" s="82">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F38" s="83">
+      <c r="F38" s="82">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G38"/>
-      <c r="H38" s="92"/>
-      <c r="I38" s="89" t="s">
+      <c r="H38" s="91"/>
+      <c r="I38" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="J38" s="90">
+      <c r="J38" s="89">
         <v>30</v>
       </c>
-      <c r="K38" s="90">
+      <c r="K38" s="89">
         <f>交付高装!D7</f>
         <v>0</v>
       </c>
-      <c r="L38" s="91">
+      <c r="L38" s="90">
         <f>交付高装!E7</f>
         <v>0</v>
       </c>
-      <c r="N38" s="77" t="s">
+      <c r="N38" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="O38" s="93">
-        <v>2.6</v>
-      </c>
-      <c r="P38" s="93">
+      <c r="O38" s="92">
+        <v>3.6</v>
+      </c>
+      <c r="P38" s="92">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N38,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>0.47</v>
-      </c>
-      <c r="Q38" s="85">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="84">
         <f>_xlfn.XLOOKUP(N38,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>11048.28</v>
-      </c>
-      <c r="R38" s="79">
+        <v>1098.45</v>
+      </c>
+      <c r="R38" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>0.180769230769231</v>
-      </c>
-      <c r="S38" s="86">
+        <v>0.0555555555555556</v>
+      </c>
+      <c r="S38" s="85">
         <f ca="1">RANK(R38,R33:R41)</f>
         <v>8</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A39" s="81"/>
-      <c r="B39" s="72" t="str">
+      <c r="A39" s="80"/>
+      <c r="B39" s="71" t="str">
         <f>高装高套!A8</f>
         <v>吴广仁</v>
       </c>
-      <c r="C39" s="72">
+      <c r="C39" s="71">
         <v>3.5</v>
       </c>
-      <c r="D39" s="72">
+      <c r="D39" s="71">
         <f>高装高套!B8</f>
-        <v>1.5</v>
-      </c>
-      <c r="E39" s="73">
+        <v>0</v>
+      </c>
+      <c r="E39" s="72">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
-        <v>239</v>
-      </c>
-      <c r="F39" s="73">
+        <v>0</v>
+      </c>
+      <c r="F39" s="72">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
-        <v>1055.5</v>
+        <v>0</v>
       </c>
       <c r="G39"/>
-      <c r="H39" s="92"/>
-      <c r="I39" s="89" t="s">
+      <c r="H39" s="91"/>
+      <c r="I39" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="J39" s="90">
+      <c r="J39" s="89">
         <v>30</v>
       </c>
-      <c r="K39" s="90">
+      <c r="K39" s="89">
         <f>交付高装!D8</f>
         <v>0</v>
       </c>
-      <c r="L39" s="91">
+      <c r="L39" s="90">
         <f>交付高装!E8</f>
         <v>0</v>
       </c>
-      <c r="N39" s="77" t="s">
+      <c r="N39" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="O39" s="78">
-        <v>2.41</v>
-      </c>
-      <c r="P39" s="78">
+      <c r="O39" s="77">
+        <v>3.4</v>
+      </c>
+      <c r="P39" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N39,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>0.44</v>
-      </c>
-      <c r="Q39" s="78">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="77">
         <f>_xlfn.XLOOKUP(N39,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>-67.55</v>
-      </c>
-      <c r="R39" s="79">
+        <v>1085.2</v>
+      </c>
+      <c r="R39" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>0.182572614107884</v>
-      </c>
-      <c r="S39" s="80">
+        <v>0</v>
+      </c>
+      <c r="S39" s="79">
         <f ca="1">RANK(R39,R33:R41)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" ht="13.5" customHeight="1" spans="1:19">
-      <c r="A40" s="94"/>
-      <c r="B40" s="82" t="str">
+      <c r="A40" s="93"/>
+      <c r="B40" s="81" t="str">
         <f>高装高套!A9</f>
         <v>王洪明</v>
       </c>
-      <c r="C40" s="82">
+      <c r="C40" s="81">
         <v>3.5</v>
       </c>
-      <c r="D40" s="82">
+      <c r="D40" s="81">
         <f>高装高套!B9</f>
         <v>0</v>
       </c>
-      <c r="E40" s="83">
+      <c r="E40" s="82">
         <f ca="1">VLOOKUP(B:B,完美一单!A:C,3,0)</f>
         <v>0</v>
       </c>
-      <c r="F40" s="83">
+      <c r="F40" s="82">
         <f ca="1">VLOOKUP(B:B,激励!A:B,2,0)</f>
         <v>0</v>
       </c>
       <c r="G40"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="89" t="s">
+      <c r="H40" s="91"/>
+      <c r="I40" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="J40" s="90">
+      <c r="J40" s="89">
         <v>30</v>
       </c>
-      <c r="K40" s="90">
+      <c r="K40" s="89">
         <f>交付高装!D9</f>
-        <v>3</v>
-      </c>
-      <c r="L40" s="91">
+        <v>0</v>
+      </c>
+      <c r="L40" s="90">
         <f>交付高装!E9</f>
-        <v>0.1</v>
-      </c>
-      <c r="N40" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="N40" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="O40" s="85">
-        <v>3.22</v>
-      </c>
-      <c r="P40" s="85">
+      <c r="O40" s="84">
+        <v>4.2</v>
+      </c>
+      <c r="P40" s="84">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N40,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>2.72</v>
-      </c>
-      <c r="Q40" s="85">
+        <v>2.75</v>
+      </c>
+      <c r="Q40" s="84">
         <f>_xlfn.XLOOKUP(N40,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>-356088.16</v>
-      </c>
-      <c r="R40" s="79">
+        <v>-110.22</v>
+      </c>
+      <c r="R40" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>0.84472049689441</v>
-      </c>
-      <c r="S40" s="86">
+        <v>0.654761904761905</v>
+      </c>
+      <c r="S40" s="85">
         <f ca="1">RANK(R40,R33:R41)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:19">
-      <c r="A41" s="95" t="s">
+      <c r="A41" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="B41" s="96"/>
-      <c r="C41" s="95">
+      <c r="B41" s="95"/>
+      <c r="C41" s="94">
         <f>SUM(C33:C40)</f>
         <v>28</v>
       </c>
-      <c r="D41" s="95">
+      <c r="D41" s="94">
         <f>SUM(D33:D40)</f>
-        <v>1.5</v>
-      </c>
-      <c r="E41" s="95">
+        <v>0</v>
+      </c>
+      <c r="E41" s="94">
         <f ca="1">SUM(E33:E40)</f>
-        <v>239</v>
-      </c>
-      <c r="F41" s="95" t="s">
+        <v>0</v>
+      </c>
+      <c r="F41" s="94" t="s">
         <v>41</v>
       </c>
       <c r="G41"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="89" t="s">
+      <c r="H41" s="91"/>
+      <c r="I41" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="J41" s="90">
+      <c r="J41" s="89">
         <v>30</v>
       </c>
-      <c r="K41" s="90">
+      <c r="K41" s="89">
         <f>交付高装!D10</f>
         <v>0</v>
       </c>
-      <c r="L41" s="91">
+      <c r="L41" s="90">
         <f>交付高装!E10</f>
         <v>0</v>
       </c>
-      <c r="N41" s="77" t="s">
+      <c r="N41" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="O41" s="78">
-        <v>3.36</v>
-      </c>
-      <c r="P41" s="78">
+      <c r="O41" s="77">
+        <v>4.4</v>
+      </c>
+      <c r="P41" s="77">
         <f ca="1">ROUND(_xlfn.XLOOKUP(N41,高套!A:A,高套!B:B,0)/W4,2)</f>
-        <v>4.14</v>
-      </c>
-      <c r="Q41" s="78">
+        <v>1.09</v>
+      </c>
+      <c r="Q41" s="77">
         <f>_xlfn.XLOOKUP(N41,净增积分!A:A,净增积分!B:B,0)</f>
-        <v>2000.9</v>
-      </c>
-      <c r="R41" s="79">
+        <v>1289.13</v>
+      </c>
+      <c r="R41" s="78">
         <f ca="1" t="shared" si="11"/>
-        <v>1.23214285714286</v>
-      </c>
-      <c r="S41" s="80">
+        <v>0.247727272727273</v>
+      </c>
+      <c r="S41" s="79">
         <f ca="1">RANK(R41,R33:R41)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" ht="14.75" customHeight="1" spans="1:19">
       <c r="F42"/>
       <c r="G42"/>
-      <c r="H42" s="92"/>
-      <c r="I42" s="89" t="s">
+      <c r="H42" s="91"/>
+      <c r="I42" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="J42" s="90">
+      <c r="J42" s="89">
         <v>30</v>
       </c>
-      <c r="K42" s="90">
+      <c r="K42" s="89">
         <f>交付高装!D11</f>
-        <v>5</v>
-      </c>
-      <c r="L42" s="91">
+        <v>2</v>
+      </c>
+      <c r="L42" s="90">
         <f>交付高装!E11</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="N42" s="97" t="s">
+        <v>0.0666666666666667</v>
+      </c>
+      <c r="N42" s="96" t="s">
         <v>72</v>
       </c>
-      <c r="O42" s="98">
+      <c r="O42" s="97">
         <f>SUM(O33:O41)</f>
-        <v>31.46</v>
-      </c>
-      <c r="P42" s="98">
+        <v>40</v>
+      </c>
+      <c r="P42" s="97">
         <f ca="1">SUM(P33:P41)</f>
-        <v>19.22</v>
-      </c>
-      <c r="Q42" s="98">
+        <v>14.77</v>
+      </c>
+      <c r="Q42" s="97">
         <f>SUM(Q33:Q41)</f>
-        <v>-343665.28</v>
-      </c>
-      <c r="R42" s="99">
+        <v>-18034.3</v>
+      </c>
+      <c r="R42" s="98">
         <f ca="1" t="shared" si="11"/>
-        <v>0.610934520025429</v>
-      </c>
-      <c r="S42" s="100" t="s">
+        <v>0.36925</v>
+      </c>
+      <c r="S42" s="99" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="43" ht="13.5" customHeight="1" spans="1:19">
       <c r="F43"/>
       <c r="G43"/>
-      <c r="H43" s="92"/>
-      <c r="I43" s="89" t="s">
+      <c r="H43" s="91"/>
+      <c r="I43" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="J43" s="90">
+      <c r="J43" s="89">
         <v>30</v>
       </c>
-      <c r="K43" s="90">
+      <c r="K43" s="89">
         <f>交付高装!D12</f>
         <v>0</v>
       </c>
-      <c r="L43" s="91">
+      <c r="L43" s="90">
         <f>交付高装!E12</f>
         <v>0</v>
       </c>
@@ -5009,20 +5013,20 @@
     <row r="44" ht="13.5" customHeight="1" spans="1:19">
       <c r="F44"/>
       <c r="G44"/>
-      <c r="H44" s="101"/>
-      <c r="I44" s="102" t="s">
+      <c r="H44" s="100"/>
+      <c r="I44" s="101" t="s">
         <v>74</v>
       </c>
-      <c r="J44" s="90">
+      <c r="J44" s="89">
         <v>210</v>
       </c>
-      <c r="K44" s="90">
+      <c r="K44" s="89">
         <f>SUM(K33:K36)</f>
-        <v>8</v>
-      </c>
-      <c r="L44" s="91">
+        <v>2</v>
+      </c>
+      <c r="L44" s="90">
         <f>K44/J44</f>
-        <v>0.0380952380952381</v>
+        <v>0.00952380952380952</v>
       </c>
       <c r="P44"/>
     </row>
@@ -5581,7 +5585,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{dd323c4c-cb0c-4deb-ba25-b306ac5144f0}</x14:id>
+          <x14:id>{ebf9d5fc-da7e-4fec-b017-83a025488dd6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -5596,7 +5600,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{dd323c4c-cb0c-4deb-ba25-b306ac5144f0}">
+          <x14:cfRule type="dataBar" id="{ebf9d5fc-da7e-4fec-b017-83a025488dd6}">
             <x14:dataBar minLength="10" maxLength="90" negativeBarColorSameAsPositive="1" axisPosition="none">
               <x14:cfvo type="num">
                 <xm:f>0</xm:f>
@@ -5634,7 +5638,7 @@
         <v>22</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5642,7 +5646,7 @@
         <v>23</v>
       </c>
       <c r="B3">
-        <v>1366.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5650,7 +5654,7 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>316.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5658,7 +5662,7 @@
         <v>25</v>
       </c>
       <c r="B5">
-        <v>-501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5666,7 +5670,7 @@
         <v>26</v>
       </c>
       <c r="B6">
-        <v>5.5</v>
+        <v>-1941.01</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5674,7 +5678,7 @@
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-1648.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5682,7 +5686,7 @@
         <v>30</v>
       </c>
       <c r="B8">
-        <v>961</v>
+        <v>155.17</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5690,7 +5694,7 @@
         <v>31</v>
       </c>
       <c r="B9">
-        <v>1112.49</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5706,7 +5710,7 @@
         <v>33</v>
       </c>
       <c r="B11">
-        <v>402.56</v>
+        <v>636.48</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5714,7 +5718,7 @@
         <v>34</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -5722,7 +5726,7 @@
         <v>35</v>
       </c>
       <c r="B13">
-        <v>-1737.54</v>
+        <v>794</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -5730,7 +5734,7 @@
         <v>38</v>
       </c>
       <c r="B14">
-        <v>1294.22</v>
+        <v>1122.06</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -5738,7 +5742,7 @@
         <v>62</v>
       </c>
       <c r="B15">
-        <v>377.74</v>
+        <v>-5728.86</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -5746,7 +5750,7 @@
         <v>64</v>
       </c>
       <c r="B16">
-        <v>320.35</v>
+        <v>-594.98</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -5754,7 +5758,7 @@
         <v>66</v>
       </c>
       <c r="B17">
-        <v>2729.87</v>
+        <v>2163.12</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5762,7 +5766,7 @@
         <v>67</v>
       </c>
       <c r="B18">
-        <v>-5280.93</v>
+        <v>-18358.2</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5770,7 +5774,7 @@
         <v>68</v>
       </c>
       <c r="B19">
-        <v>11048.28</v>
+        <v>1098.45</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5778,7 +5782,7 @@
         <v>69</v>
       </c>
       <c r="B20">
-        <v>-67.55</v>
+        <v>1085.2</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -5786,7 +5790,7 @@
         <v>70</v>
       </c>
       <c r="B21">
-        <v>-356088.16</v>
+        <v>-110.22</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5794,7 +5798,7 @@
         <v>71</v>
       </c>
       <c r="B22">
-        <v>2000.9</v>
+        <v>1289.13</v>
       </c>
     </row>
   </sheetData>
@@ -5830,7 +5834,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5854,7 +5858,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5886,7 +5890,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -5902,7 +5906,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>2.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -5918,7 +5922,7 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -5942,7 +5946,7 @@
         <v>38</v>
       </c>
       <c r="B17">
-        <v>6.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5950,7 +5954,7 @@
         <v>62</v>
       </c>
       <c r="B18">
-        <v>23</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5958,7 +5962,7 @@
         <v>64</v>
       </c>
       <c r="B19">
-        <v>26.75</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5966,7 +5970,7 @@
         <v>70</v>
       </c>
       <c r="B20">
-        <v>24.5</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -5974,7 +5978,7 @@
         <v>71</v>
       </c>
       <c r="B21">
-        <v>37.3</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5982,7 +5986,7 @@
         <v>66</v>
       </c>
       <c r="B22">
-        <v>20.13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5990,7 +5994,7 @@
         <v>68</v>
       </c>
       <c r="B23">
-        <v>4.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5998,7 +6002,7 @@
         <v>67</v>
       </c>
       <c r="B24">
-        <v>26.67</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -6006,7 +6010,7 @@
         <v>69</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6042,7 +6046,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6066,7 +6070,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6106,7 +6110,7 @@
         <v>77</v>
       </c>
       <c r="B11">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6114,7 +6118,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6154,7 +6158,7 @@
         <v>38</v>
       </c>
       <c r="B17">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -6202,13 +6206,13 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="D3">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -6219,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>1792.67</v>
+        <v>1145</v>
       </c>
       <c r="D4">
-        <v>453.67</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -6233,10 +6237,10 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>772.33</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>772.33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -6244,13 +6248,13 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>-246</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>173</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -6258,13 +6262,13 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>203</v>
+        <v>41</v>
       </c>
       <c r="D7">
-        <v>203</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -6275,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>295.33</v>
+        <v>228</v>
       </c>
       <c r="D8">
-        <v>295</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -6289,10 +6293,10 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>239</v>
+        <v>468.17</v>
       </c>
       <c r="D9">
-        <v>239</v>
+        <v>598</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -6300,13 +6304,13 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>6.5</v>
       </c>
       <c r="C10">
-        <v>744.5</v>
+        <v>580</v>
       </c>
       <c r="D10">
-        <v>744.5</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -6314,13 +6318,13 @@
         <v>77</v>
       </c>
       <c r="B11">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="C11">
-        <v>878</v>
+        <v>615</v>
       </c>
       <c r="D11">
-        <v>878</v>
+        <v>585</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -6328,13 +6332,13 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>10.35</v>
       </c>
       <c r="C12">
-        <v>872</v>
+        <v>163</v>
       </c>
       <c r="D12">
-        <v>738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -6342,13 +6346,13 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="C13">
-        <v>698</v>
+        <v>154</v>
       </c>
       <c r="D13">
-        <v>698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -6356,13 +6360,13 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>-1647.54</v>
+        <v>-1</v>
       </c>
       <c r="D14">
-        <v>90</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -6485,7 +6489,7 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -6599,7 +6603,7 @@
         <v>47</v>
       </c>
       <c r="B8">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6649,7 +6653,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6673,7 +6677,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6681,7 +6685,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6705,7 +6709,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6713,7 +6717,7 @@
         <v>77</v>
       </c>
       <c r="B11">
-        <v>4.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -6721,7 +6725,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -6729,7 +6733,7 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -6737,7 +6741,7 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -6809,11 +6813,11 @@
       </c>
       <c r="D2">
         <f t="array" ref="D2">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B2))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="8">
         <f t="shared" ref="E2:E13" si="0">D2/C2</f>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>32</v>
@@ -6871,11 +6875,11 @@
       </c>
       <c r="D4">
         <f t="array" ref="D4">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($M$2:$M$16=B4))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4" s="8">
         <f t="shared" si="0"/>
-        <v>0.0833333333333333</v>
+        <v>0.0333333333333333</v>
       </c>
       <c r="J4" s="9" t="s">
         <v>26</v>
@@ -7026,11 +7030,11 @@
       </c>
       <c r="D9">
         <f t="array" ref="D9">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B9))</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>25</v>
@@ -7088,11 +7092,11 @@
       </c>
       <c r="D11">
         <f t="array" ref="D11">SUMPRODUCT(SUMIF(全光组网!A:A,$J$2:$J$16,全光组网!B:B)*($K$2:$K$16=B11))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
-        <v>0.166666666666667</v>
+        <v>0.0666666666666667</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>30</v>
@@ -7244,7 +7248,7 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7252,7 +7256,7 @@
         <v>23</v>
       </c>
       <c r="B4">
-        <v>3489</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7260,7 +7264,7 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>658.5</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7268,7 +7272,7 @@
         <v>25</v>
       </c>
       <c r="B6">
-        <v>-98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7276,7 +7280,7 @@
         <v>26</v>
       </c>
       <c r="B7">
-        <v>913.5</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7284,7 +7288,7 @@
         <v>27</v>
       </c>
       <c r="B8">
-        <v>230.5</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7292,7 +7296,7 @@
         <v>30</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>637.34</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7300,7 +7304,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>892.5</v>
+        <v>732</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -7308,7 +7312,7 @@
         <v>77</v>
       </c>
       <c r="B11">
-        <v>3411</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -7316,7 +7320,7 @@
         <v>33</v>
       </c>
       <c r="B12">
-        <v>3450</v>
+        <v>253.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -7324,7 +7328,7 @@
         <v>34</v>
       </c>
       <c r="B13">
-        <v>1047</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -7332,7 +7336,7 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>-2471.31</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -7404,7 +7408,7 @@
         <v>47</v>
       </c>
       <c r="B23">
-        <v>1055.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:2">
